--- a/forward_test_2026-09-18.xlsx
+++ b/forward_test_2026-09-18.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +11,7 @@
     <sheet name="Read me" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -20,7 +19,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00;0.00"/>
+    <numFmt numFmtId="165" formatCode="\+0.00;\-0.00;0.00"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -32,57 +31,68 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <i val="1"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <i val="1"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <i val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -95,17 +105,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,9 +128,13 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -177,7 +191,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -541,58 +555,30 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AZ49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="7" customWidth="1" min="26" max="26"/>
-    <col width="7" customWidth="1" min="27" max="27"/>
-    <col width="7" customWidth="1" min="28" max="28"/>
-    <col width="7" customWidth="1" min="29" max="29"/>
-    <col width="7" customWidth="1" min="30" max="30"/>
-    <col width="7" customWidth="1" min="31" max="31"/>
-    <col width="7" customWidth="1" min="32" max="32"/>
-    <col width="7" customWidth="1" min="33" max="33"/>
-    <col width="7" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="8" max="13"/>
+    <col width="11" customWidth="1" min="14" max="19"/>
+    <col width="12" customWidth="1" min="20" max="25"/>
+    <col width="7" customWidth="1" min="26" max="34"/>
     <col width="14" customWidth="1" min="35" max="35"/>
     <col width="9" customWidth="1" min="36" max="36"/>
     <col width="10" customWidth="1" min="37" max="37"/>
     <col width="13" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="9" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
-    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="41" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
-    <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="44" max="46"/>
     <col width="8" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
-    <col width="8" customWidth="1" min="49" max="49"/>
-    <col width="8" customWidth="1" min="50" max="50"/>
+    <col width="8" customWidth="1" min="49" max="50"/>
     <col width="9" customWidth="1" min="51" max="51"/>
     <col width="20" customWidth="1" min="52" max="52"/>
   </cols>
@@ -4670,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="AL24" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM24" s="8" t="n"/>
       <c r="AN24" s="8" t="n"/>
@@ -4714,7 +4700,7 @@
       </c>
       <c r="AZ24" s="8" t="inlineStr">
         <is>
-          <t>played 17 Sep, ref R Eley (not known when predicted)</t>
+          <t>3 yellows (1+2) per afcwimbledon.co.uk match report; football-data still had 0 -- cards lag a few days</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8670,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -8718,7 +8704,7 @@
         <f>COUNTA(Predictions!$D$2:$D$47)</f>
         <v/>
       </c>
-      <c r="C2" s="17" t="inlineStr"/>
+      <c r="C2" s="17" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
@@ -8762,7 +8748,7 @@
         <f>IF(COUNT(Predictions!$AL$2:$AL$47)=0,"",AVERAGE(Predictions!$AL$2:$AL$47))</f>
         <v/>
       </c>
-      <c r="C5" s="17" t="inlineStr"/>
+      <c r="C5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -8797,9 +8783,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr"/>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr"/>
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
@@ -8807,8 +8793,8 @@
           <t>CALIBRATION -- THE NUMBER THAT MATTERS</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr"/>
-      <c r="C9" s="17" t="inlineStr"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -8820,7 +8806,7 @@
         <f>IF(COUNT(Predictions!$AL$2:$AL$47)=0,"",SUMPRODUCT(--ISNUMBER(Predictions!$AL$2:$AL$47),Predictions!$J$2:$J$47)/COUNT(Predictions!$AL$2:$AL$47))</f>
         <v/>
       </c>
-      <c r="C10" s="17" t="inlineStr"/>
+      <c r="C10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -8832,7 +8818,7 @@
         <f>IF(COUNT(Predictions!$AL$2:$AL$47)=0,"",COUNTIF(Predictions!$AL$2:$AL$47,"&gt;3.5")/COUNT(Predictions!$AL$2:$AL$47))</f>
         <v/>
       </c>
-      <c r="C11" s="17" t="inlineStr"/>
+      <c r="C11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -8860,7 +8846,7 @@
         <f>IF(COUNT(Predictions!$AL$2:$AL$47)=0,"",SUMPRODUCT(--ISNUMBER(Predictions!$AL$2:$AL$47),Predictions!$I$2:$I$47)/COUNT(Predictions!$AL$2:$AL$47))</f>
         <v/>
       </c>
-      <c r="C13" s="17" t="inlineStr"/>
+      <c r="C13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -8872,7 +8858,7 @@
         <f>IF(COUNT(Predictions!$AL$2:$AL$47)=0,"",COUNTIF(Predictions!$AL$2:$AL$47,"&gt;2.5")/COUNT(Predictions!$AL$2:$AL$47))</f>
         <v/>
       </c>
-      <c r="C14" s="17" t="inlineStr"/>
+      <c r="C14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -8884,7 +8870,7 @@
         <f>IF(COUNT(Predictions!$AL$2:$AL$47)=0,"",SUMPRODUCT(--ISNUMBER(Predictions!$AL$2:$AL$47),Predictions!$K$2:$K$47)/COUNT(Predictions!$AL$2:$AL$47))</f>
         <v/>
       </c>
-      <c r="C15" s="17" t="inlineStr"/>
+      <c r="C15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -8896,12 +8882,12 @@
         <f>IF(COUNT(Predictions!$AL$2:$AL$47)=0,"",COUNTIF(Predictions!$AL$2:$AL$47,"&gt;4.5")/COUNT(Predictions!$AL$2:$AL$47))</f>
         <v/>
       </c>
-      <c r="C16" s="17" t="inlineStr"/>
+      <c r="C16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr"/>
-      <c r="B17" s="16" t="inlineStr"/>
-      <c r="C17" s="17" t="inlineStr"/>
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
@@ -8909,8 +8895,8 @@
           <t>BETTING -- ONLY IF YOU ENTERED PRICES</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr"/>
-      <c r="C18" s="17" t="inlineStr"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -8938,7 +8924,7 @@
         <f>COUNTIF(Predictions!$AV$2:$AV$47,"OVER")</f>
         <v/>
       </c>
-      <c r="C20" s="17" t="inlineStr"/>
+      <c r="C20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -8966,7 +8952,7 @@
         <f>COUNTIF(Predictions!$AX$2:$AX$47,"WON")+COUNTIF(Predictions!$AX$2:$AX$47,"LOST")</f>
         <v/>
       </c>
-      <c r="C22" s="17" t="inlineStr"/>
+      <c r="C22" s="17" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -8978,7 +8964,7 @@
         <f>COUNTIF(Predictions!$AX$2:$AX$47,"WON")</f>
         <v/>
       </c>
-      <c r="C23" s="17" t="inlineStr"/>
+      <c r="C23" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -9040,7 +9026,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
@@ -9053,7 +9039,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr"/>
+      <c r="A2" s="23" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="23" t="inlineStr">
@@ -9084,7 +9070,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr"/>
+      <c r="A7" s="23" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="22" t="inlineStr">
@@ -9093,7 +9079,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Every probability is also shown as FAIR DECIMAL ODDS, which is 1 / probability -- the same form a bookmaker quotes.</t>
@@ -9122,7 +9108,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr"/>
+      <c r="A13" s="23" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
@@ -9138,21 +9124,21 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
         <is>
           <t>Premier League fixtures carry their real referee appointment. The EFL had not published its appointments when this was generated, so those 36 fixtures ran with the referee unknown.</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
           <t>That matters: referee features carry 47% of this model's value. The PL rows test the model at full strength; the EFL rows test it without its most important input.</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
           <t>No match odds were used as model inputs -- only partial prices were available and the margin cannot be removed from one side alone.</t>
@@ -9160,7 +9146,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr"/>
+      <c r="A19" s="23" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
@@ -9176,7 +9162,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
         <is>
           <t>Mean absolute error near 1.5 cards is EXPECTED, not a failure: the match-level standard deviation of yellows is about 1.9.</t>
@@ -9191,7 +9177,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr"/>
+      <c r="A24" s="23" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="22" t="inlineStr">
@@ -9207,7 +9193,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
           <t>Fixtures: ESPN, cross-checked against Sky Sports and the EFL news feed -- ESPN alone was missing two Friday/Thursday evening games.</t>
@@ -9221,7 +9207,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
           <t>These fixtures are the 2026/27 holdout. Generating predictions is not a holdout look. Scoring them is, and it will be logged.</t>

--- a/forward_test_2026-09-18.xlsx
+++ b/forward_test_2026-09-18.xlsx
@@ -969,7 +969,9 @@
       <c r="AK2" s="5" t="n">
         <v>394</v>
       </c>
-      <c r="AL2" s="6" t="n"/>
+      <c r="AL2" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="AM2" s="6" t="inlineStr">
         <is>
           <t>screenshot</t>
@@ -1022,7 +1024,7 @@
       </c>
       <c r="AZ2" s="6" t="inlineStr">
         <is>
-          <t>also offered o4.5 2.14 / u4.5 1.60</t>
+          <t>also offered o4.5 2.14 / u4.5 1.60; actual from BBC 2026-09-18 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1152,9 @@
       <c r="AK3" s="5" t="n">
         <v>167</v>
       </c>
-      <c r="AL3" s="8" t="n"/>
+      <c r="AL3" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM3" s="8" t="n"/>
       <c r="AN3" s="8" t="n"/>
       <c r="AO3" s="8" t="n"/>
@@ -1191,7 +1195,11 @@
         <f>IF($AX3="","",IF($AX3="WON",IF($AV3="OVER",$AO3-1,$AP3-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ3" s="8" t="n"/>
+      <c r="AZ3" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1317,7 +1325,9 @@
       <c r="AK4" s="5" t="n">
         <v>280</v>
       </c>
-      <c r="AL4" s="8" t="n"/>
+      <c r="AL4" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="AM4" s="8" t="n"/>
       <c r="AN4" s="8" t="n"/>
       <c r="AO4" s="8" t="n"/>
@@ -1358,7 +1368,11 @@
         <f>IF($AX4="","",IF($AX4="WON",IF($AV4="OVER",$AO4-1,$AP4-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ4" s="8" t="n"/>
+      <c r="AZ4" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1484,7 +1498,9 @@
       <c r="AK5" s="5" t="n">
         <v>448</v>
       </c>
-      <c r="AL5" s="8" t="n"/>
+      <c r="AL5" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM5" s="8" t="n"/>
       <c r="AN5" s="8" t="n"/>
       <c r="AO5" s="8" t="n"/>
@@ -1525,7 +1541,11 @@
         <f>IF($AX5="","",IF($AX5="WON",IF($AV5="OVER",$AO5-1,$AP5-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ5" s="8" t="n"/>
+      <c r="AZ5" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1651,7 +1671,9 @@
       <c r="AK6" s="5" t="n">
         <v>317</v>
       </c>
-      <c r="AL6" s="8" t="n"/>
+      <c r="AL6" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="AM6" s="8" t="n"/>
       <c r="AN6" s="8" t="n"/>
       <c r="AO6" s="8" t="n"/>
@@ -1692,7 +1714,11 @@
         <f>IF($AX6="","",IF($AX6="WON",IF($AV6="OVER",$AO6-1,$AP6-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ6" s="8" t="n"/>
+      <c r="AZ6" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1818,7 +1844,9 @@
       <c r="AK7" s="5" t="n">
         <v>164</v>
       </c>
-      <c r="AL7" s="8" t="n"/>
+      <c r="AL7" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="AM7" s="8" t="n"/>
       <c r="AN7" s="8" t="n"/>
       <c r="AO7" s="8" t="n"/>
@@ -1859,7 +1887,11 @@
         <f>IF($AX7="","",IF($AX7="WON",IF($AV7="OVER",$AO7-1,$AP7-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ7" s="8" t="n"/>
+      <c r="AZ7" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1985,7 +2017,9 @@
       <c r="AK8" s="5" t="n">
         <v>537</v>
       </c>
-      <c r="AL8" s="8" t="n"/>
+      <c r="AL8" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM8" s="8" t="n"/>
       <c r="AN8" s="8" t="n"/>
       <c r="AO8" s="8" t="n"/>
@@ -2026,7 +2060,11 @@
         <f>IF($AX8="","",IF($AX8="WON",IF($AV8="OVER",$AO8-1,$AP8-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ8" s="8" t="n"/>
+      <c r="AZ8" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-20 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2152,7 +2190,9 @@
       <c r="AK9" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="AL9" s="8" t="n"/>
+      <c r="AL9" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="AM9" s="8" t="n"/>
       <c r="AN9" s="8" t="n"/>
       <c r="AO9" s="8" t="n"/>
@@ -2193,7 +2233,11 @@
         <f>IF($AX9="","",IF($AX9="WON",IF($AV9="OVER",$AO9-1,$AP9-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ9" s="8" t="n"/>
+      <c r="AZ9" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-20 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2319,7 +2363,9 @@
       <c r="AK10" s="5" t="n">
         <v>270</v>
       </c>
-      <c r="AL10" s="8" t="n"/>
+      <c r="AL10" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="AM10" s="8" t="n"/>
       <c r="AN10" s="8" t="n"/>
       <c r="AO10" s="8" t="n"/>
@@ -2360,7 +2406,11 @@
         <f>IF($AX10="","",IF($AX10="WON",IF($AV10="OVER",$AO10-1,$AP10-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ10" s="8" t="n"/>
+      <c r="AZ10" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-20 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2486,7 +2536,9 @@
       <c r="AK11" s="5" t="n">
         <v>311</v>
       </c>
-      <c r="AL11" s="8" t="n"/>
+      <c r="AL11" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM11" s="8" t="n"/>
       <c r="AN11" s="8" t="n"/>
       <c r="AO11" s="8" t="n"/>
@@ -2527,7 +2579,11 @@
         <f>IF($AX11="","",IF($AX11="WON",IF($AV11="OVER",$AO11-1,$AP11-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ11" s="8" t="n"/>
+      <c r="AZ11" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-20 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2653,7 +2709,9 @@
       <c r="AK12" s="5" t="n">
         <v>524</v>
       </c>
-      <c r="AL12" s="8" t="n"/>
+      <c r="AL12" s="8" t="n">
+        <v>7</v>
+      </c>
       <c r="AM12" s="8" t="n"/>
       <c r="AN12" s="8" t="n"/>
       <c r="AO12" s="8" t="n"/>
@@ -2694,7 +2752,11 @@
         <f>IF($AX12="","",IF($AX12="WON",IF($AV12="OVER",$AO12-1,$AP12-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ12" s="8" t="n"/>
+      <c r="AZ12" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-18 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2820,7 +2882,9 @@
       <c r="AK13" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="AL13" s="8" t="n"/>
+      <c r="AL13" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="AM13" s="8" t="n"/>
       <c r="AN13" s="8" t="n"/>
       <c r="AO13" s="8" t="n"/>
@@ -2861,7 +2925,11 @@
         <f>IF($AX13="","",IF($AX13="WON",IF($AV13="OVER",$AO13-1,$AP13-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ13" s="8" t="n"/>
+      <c r="AZ13" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2987,7 +3055,9 @@
       <c r="AK14" s="5" t="n">
         <v>412</v>
       </c>
-      <c r="AL14" s="8" t="n"/>
+      <c r="AL14" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="AM14" s="8" t="n"/>
       <c r="AN14" s="8" t="n"/>
       <c r="AO14" s="8" t="n"/>
@@ -3028,7 +3098,11 @@
         <f>IF($AX14="","",IF($AX14="WON",IF($AV14="OVER",$AO14-1,$AP14-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ14" s="8" t="n"/>
+      <c r="AZ14" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3154,7 +3228,9 @@
       <c r="AK15" s="5" t="n">
         <v>402</v>
       </c>
-      <c r="AL15" s="8" t="n"/>
+      <c r="AL15" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="AM15" s="8" t="n"/>
       <c r="AN15" s="8" t="n"/>
       <c r="AO15" s="8" t="n"/>
@@ -3195,7 +3271,11 @@
         <f>IF($AX15="","",IF($AX15="WON",IF($AV15="OVER",$AO15-1,$AP15-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ15" s="8" t="n"/>
+      <c r="AZ15" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3321,7 +3401,9 @@
       <c r="AK16" s="5" t="n">
         <v>507</v>
       </c>
-      <c r="AL16" s="8" t="n"/>
+      <c r="AL16" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="AM16" s="8" t="n"/>
       <c r="AN16" s="8" t="n"/>
       <c r="AO16" s="8" t="n"/>
@@ -3362,7 +3444,11 @@
         <f>IF($AX16="","",IF($AX16="WON",IF($AV16="OVER",$AO16-1,$AP16-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ16" s="8" t="n"/>
+      <c r="AZ16" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3488,7 +3574,9 @@
       <c r="AK17" s="5" t="n">
         <v>409</v>
       </c>
-      <c r="AL17" s="8" t="n"/>
+      <c r="AL17" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="AM17" s="8" t="n"/>
       <c r="AN17" s="8" t="n"/>
       <c r="AO17" s="8" t="n"/>
@@ -3529,7 +3617,11 @@
         <f>IF($AX17="","",IF($AX17="WON",IF($AV17="OVER",$AO17-1,$AP17-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ17" s="8" t="n"/>
+      <c r="AZ17" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3655,7 +3747,9 @@
       <c r="AK18" s="5" t="n">
         <v>238</v>
       </c>
-      <c r="AL18" s="8" t="n"/>
+      <c r="AL18" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM18" s="8" t="n"/>
       <c r="AN18" s="8" t="n"/>
       <c r="AO18" s="8" t="n"/>
@@ -3696,7 +3790,11 @@
         <f>IF($AX18="","",IF($AX18="WON",IF($AV18="OVER",$AO18-1,$AP18-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ18" s="8" t="n"/>
+      <c r="AZ18" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3822,7 +3920,9 @@
       <c r="AK19" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="AL19" s="8" t="n"/>
+      <c r="AL19" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM19" s="8" t="n"/>
       <c r="AN19" s="8" t="n"/>
       <c r="AO19" s="8" t="n"/>
@@ -3863,7 +3963,11 @@
         <f>IF($AX19="","",IF($AX19="WON",IF($AV19="OVER",$AO19-1,$AP19-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ19" s="8" t="n"/>
+      <c r="AZ19" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3989,7 +4093,9 @@
       <c r="AK20" s="5" t="n">
         <v>105</v>
       </c>
-      <c r="AL20" s="8" t="n"/>
+      <c r="AL20" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="AM20" s="8" t="n"/>
       <c r="AN20" s="8" t="n"/>
       <c r="AO20" s="8" t="n"/>
@@ -4030,7 +4136,11 @@
         <f>IF($AX20="","",IF($AX20="WON",IF($AV20="OVER",$AO20-1,$AP20-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ20" s="8" t="n"/>
+      <c r="AZ20" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4156,7 +4266,9 @@
       <c r="AK21" s="5" t="n">
         <v>534</v>
       </c>
-      <c r="AL21" s="8" t="n"/>
+      <c r="AL21" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="AM21" s="8" t="n"/>
       <c r="AN21" s="8" t="n"/>
       <c r="AO21" s="8" t="n"/>
@@ -4197,7 +4309,11 @@
         <f>IF($AX21="","",IF($AX21="WON",IF($AV21="OVER",$AO21-1,$AP21-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ21" s="8" t="n"/>
+      <c r="AZ21" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4323,7 +4439,9 @@
       <c r="AK22" s="5" t="n">
         <v>196</v>
       </c>
-      <c r="AL22" s="8" t="n"/>
+      <c r="AL22" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM22" s="8" t="n"/>
       <c r="AN22" s="8" t="n"/>
       <c r="AO22" s="8" t="n"/>
@@ -4364,7 +4482,11 @@
         <f>IF($AX22="","",IF($AX22="WON",IF($AV22="OVER",$AO22-1,$AP22-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ22" s="8" t="n"/>
+      <c r="AZ22" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-20 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4490,7 +4612,9 @@
       <c r="AK23" s="5" t="n">
         <v>219</v>
       </c>
-      <c r="AL23" s="8" t="n"/>
+      <c r="AL23" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="AM23" s="8" t="n"/>
       <c r="AN23" s="8" t="n"/>
       <c r="AO23" s="8" t="n"/>
@@ -4531,7 +4655,11 @@
         <f>IF($AX23="","",IF($AX23="WON",IF($AV23="OVER",$AO23-1,$AP23-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ23" s="8" t="n"/>
+      <c r="AZ23" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-20 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4828,7 +4956,9 @@
       <c r="AK25" s="5" t="n">
         <v>359</v>
       </c>
-      <c r="AL25" s="8" t="n"/>
+      <c r="AL25" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="AM25" s="8" t="n"/>
       <c r="AN25" s="8" t="n"/>
       <c r="AO25" s="8" t="n"/>
@@ -4869,7 +4999,11 @@
         <f>IF($AX25="","",IF($AX25="WON",IF($AV25="OVER",$AO25-1,$AP25-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ25" s="8" t="n"/>
+      <c r="AZ25" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4995,7 +5129,9 @@
       <c r="AK26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AL26" s="8" t="n"/>
+      <c r="AL26" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="AM26" s="8" t="n"/>
       <c r="AN26" s="8" t="n"/>
       <c r="AO26" s="8" t="n"/>
@@ -5036,7 +5172,11 @@
         <f>IF($AX26="","",IF($AX26="WON",IF($AV26="OVER",$AO26-1,$AP26-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ26" s="8" t="n"/>
+      <c r="AZ26" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5162,7 +5302,9 @@
       <c r="AK27" s="5" t="n">
         <v>497</v>
       </c>
-      <c r="AL27" s="8" t="n"/>
+      <c r="AL27" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM27" s="8" t="n"/>
       <c r="AN27" s="8" t="n"/>
       <c r="AO27" s="8" t="n"/>
@@ -5203,7 +5345,11 @@
         <f>IF($AX27="","",IF($AX27="WON",IF($AV27="OVER",$AO27-1,$AP27-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ27" s="8" t="n"/>
+      <c r="AZ27" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5329,7 +5475,9 @@
       <c r="AK28" s="5" t="n">
         <v>165</v>
       </c>
-      <c r="AL28" s="8" t="n"/>
+      <c r="AL28" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="AM28" s="8" t="n"/>
       <c r="AN28" s="8" t="n"/>
       <c r="AO28" s="8" t="n"/>
@@ -5370,7 +5518,11 @@
         <f>IF($AX28="","",IF($AX28="WON",IF($AV28="OVER",$AO28-1,$AP28-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ28" s="8" t="n"/>
+      <c r="AZ28" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5496,7 +5648,9 @@
       <c r="AK29" s="5" t="n">
         <v>223</v>
       </c>
-      <c r="AL29" s="8" t="n"/>
+      <c r="AL29" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="AM29" s="8" t="n"/>
       <c r="AN29" s="8" t="n"/>
       <c r="AO29" s="8" t="n"/>
@@ -5537,7 +5691,11 @@
         <f>IF($AX29="","",IF($AX29="WON",IF($AV29="OVER",$AO29-1,$AP29-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ29" s="8" t="n"/>
+      <c r="AZ29" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5663,7 +5821,9 @@
       <c r="AK30" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AL30" s="8" t="n"/>
+      <c r="AL30" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="AM30" s="8" t="n"/>
       <c r="AN30" s="8" t="n"/>
       <c r="AO30" s="8" t="n"/>
@@ -5704,7 +5864,11 @@
         <f>IF($AX30="","",IF($AX30="WON",IF($AV30="OVER",$AO30-1,$AP30-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ30" s="8" t="n"/>
+      <c r="AZ30" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5830,7 +5994,9 @@
       <c r="AK31" s="5" t="n">
         <v>113</v>
       </c>
-      <c r="AL31" s="8" t="n"/>
+      <c r="AL31" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="AM31" s="8" t="n"/>
       <c r="AN31" s="8" t="n"/>
       <c r="AO31" s="8" t="n"/>
@@ -5871,7 +6037,11 @@
         <f>IF($AX31="","",IF($AX31="WON",IF($AV31="OVER",$AO31-1,$AP31-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ31" s="8" t="n"/>
+      <c r="AZ31" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5997,7 +6167,9 @@
       <c r="AK32" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="AL32" s="8" t="n"/>
+      <c r="AL32" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM32" s="8" t="n"/>
       <c r="AN32" s="8" t="n"/>
       <c r="AO32" s="8" t="n"/>
@@ -6038,7 +6210,11 @@
         <f>IF($AX32="","",IF($AX32="WON",IF($AV32="OVER",$AO32-1,$AP32-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ32" s="8" t="n"/>
+      <c r="AZ32" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6164,7 +6340,9 @@
       <c r="AK33" s="5" t="n">
         <v>149</v>
       </c>
-      <c r="AL33" s="8" t="n"/>
+      <c r="AL33" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM33" s="8" t="n"/>
       <c r="AN33" s="8" t="n"/>
       <c r="AO33" s="8" t="n"/>
@@ -6205,7 +6383,11 @@
         <f>IF($AX33="","",IF($AX33="WON",IF($AV33="OVER",$AO33-1,$AP33-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ33" s="8" t="n"/>
+      <c r="AZ33" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6331,7 +6513,9 @@
       <c r="AK34" s="5" t="n">
         <v>310</v>
       </c>
-      <c r="AL34" s="8" t="n"/>
+      <c r="AL34" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="AM34" s="8" t="n"/>
       <c r="AN34" s="8" t="n"/>
       <c r="AO34" s="8" t="n"/>
@@ -6372,7 +6556,11 @@
         <f>IF($AX34="","",IF($AX34="WON",IF($AV34="OVER",$AO34-1,$AP34-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ34" s="8" t="n"/>
+      <c r="AZ34" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6498,7 +6686,9 @@
       <c r="AK35" s="5" t="n">
         <v>580</v>
       </c>
-      <c r="AL35" s="8" t="n"/>
+      <c r="AL35" s="8" t="n">
+        <v>7</v>
+      </c>
       <c r="AM35" s="8" t="n"/>
       <c r="AN35" s="8" t="n"/>
       <c r="AO35" s="8" t="n"/>
@@ -6539,7 +6729,11 @@
         <f>IF($AX35="","",IF($AX35="WON",IF($AV35="OVER",$AO35-1,$AP35-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ35" s="8" t="n"/>
+      <c r="AZ35" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6665,7 +6859,9 @@
       <c r="AK36" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="AL36" s="8" t="n"/>
+      <c r="AL36" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="AM36" s="8" t="n"/>
       <c r="AN36" s="8" t="n"/>
       <c r="AO36" s="8" t="n"/>
@@ -6706,7 +6902,11 @@
         <f>IF($AX36="","",IF($AX36="WON",IF($AV36="OVER",$AO36-1,$AP36-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ36" s="8" t="n"/>
+      <c r="AZ36" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -6832,7 +7032,9 @@
       <c r="AK37" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="AL37" s="8" t="n"/>
+      <c r="AL37" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="AM37" s="8" t="n"/>
       <c r="AN37" s="8" t="n"/>
       <c r="AO37" s="8" t="n"/>
@@ -6873,7 +7075,11 @@
         <f>IF($AX37="","",IF($AX37="WON",IF($AV37="OVER",$AO37-1,$AP37-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ37" s="8" t="n"/>
+      <c r="AZ37" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -6999,7 +7205,9 @@
       <c r="AK38" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="AL38" s="8" t="n"/>
+      <c r="AL38" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="AM38" s="8" t="n"/>
       <c r="AN38" s="8" t="n"/>
       <c r="AO38" s="8" t="n"/>
@@ -7040,7 +7248,11 @@
         <f>IF($AX38="","",IF($AX38="WON",IF($AV38="OVER",$AO38-1,$AP38-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ38" s="8" t="n"/>
+      <c r="AZ38" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7166,7 +7378,9 @@
       <c r="AK39" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="AL39" s="8" t="n"/>
+      <c r="AL39" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="AM39" s="8" t="n"/>
       <c r="AN39" s="8" t="n"/>
       <c r="AO39" s="8" t="n"/>
@@ -7207,7 +7421,11 @@
         <f>IF($AX39="","",IF($AX39="WON",IF($AV39="OVER",$AO39-1,$AP39-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ39" s="8" t="n"/>
+      <c r="AZ39" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7333,7 +7551,9 @@
       <c r="AK40" s="5" t="n">
         <v>184</v>
       </c>
-      <c r="AL40" s="8" t="n"/>
+      <c r="AL40" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM40" s="8" t="n"/>
       <c r="AN40" s="8" t="n"/>
       <c r="AO40" s="8" t="n"/>
@@ -7374,7 +7594,11 @@
         <f>IF($AX40="","",IF($AX40="WON",IF($AV40="OVER",$AO40-1,$AP40-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ40" s="8" t="n"/>
+      <c r="AZ40" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7500,7 +7724,9 @@
       <c r="AK41" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="AL41" s="8" t="n"/>
+      <c r="AL41" s="8" t="n">
+        <v>7</v>
+      </c>
       <c r="AM41" s="8" t="n"/>
       <c r="AN41" s="8" t="n"/>
       <c r="AO41" s="8" t="n"/>
@@ -7541,7 +7767,11 @@
         <f>IF($AX41="","",IF($AX41="WON",IF($AV41="OVER",$AO41-1,$AP41-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ41" s="8" t="n"/>
+      <c r="AZ41" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7667,7 +7897,9 @@
       <c r="AK42" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="AL42" s="8" t="n"/>
+      <c r="AL42" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="AM42" s="8" t="n"/>
       <c r="AN42" s="8" t="n"/>
       <c r="AO42" s="8" t="n"/>
@@ -7708,7 +7940,11 @@
         <f>IF($AX42="","",IF($AX42="WON",IF($AV42="OVER",$AO42-1,$AP42-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ42" s="8" t="n"/>
+      <c r="AZ42" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -7834,7 +8070,9 @@
       <c r="AK43" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="AL43" s="8" t="n"/>
+      <c r="AL43" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="AM43" s="8" t="n"/>
       <c r="AN43" s="8" t="n"/>
       <c r="AO43" s="8" t="n"/>
@@ -7875,7 +8113,11 @@
         <f>IF($AX43="","",IF($AX43="WON",IF($AV43="OVER",$AO43-1,$AP43-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ43" s="8" t="n"/>
+      <c r="AZ43" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8001,7 +8243,9 @@
       <c r="AK44" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="AL44" s="8" t="n"/>
+      <c r="AL44" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM44" s="8" t="n"/>
       <c r="AN44" s="8" t="n"/>
       <c r="AO44" s="8" t="n"/>
@@ -8042,7 +8286,11 @@
         <f>IF($AX44="","",IF($AX44="WON",IF($AV44="OVER",$AO44-1,$AP44-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ44" s="8" t="n"/>
+      <c r="AZ44" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8168,7 +8416,9 @@
       <c r="AK45" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="AL45" s="8" t="n"/>
+      <c r="AL45" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="AM45" s="8" t="n"/>
       <c r="AN45" s="8" t="n"/>
       <c r="AO45" s="8" t="n"/>
@@ -8209,7 +8459,11 @@
         <f>IF($AX45="","",IF($AX45="WON",IF($AV45="OVER",$AO45-1,$AP45-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ45" s="8" t="n"/>
+      <c r="AZ45" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8335,7 +8589,9 @@
       <c r="AK46" s="5" t="n">
         <v>195</v>
       </c>
-      <c r="AL46" s="8" t="n"/>
+      <c r="AL46" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="AM46" s="8" t="n"/>
       <c r="AN46" s="8" t="n"/>
       <c r="AO46" s="8" t="n"/>
@@ -8376,7 +8632,11 @@
         <f>IF($AX46="","",IF($AX46="WON",IF($AV46="OVER",$AO46-1,$AP46-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ46" s="8" t="n"/>
+      <c r="AZ46" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8502,7 +8762,9 @@
       <c r="AK47" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="AL47" s="8" t="n"/>
+      <c r="AL47" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="AM47" s="8" t="n"/>
       <c r="AN47" s="8" t="n"/>
       <c r="AO47" s="8" t="n"/>
@@ -8543,7 +8805,11 @@
         <f>IF($AX47="","",IF($AX47="WON",IF($AV47="OVER",$AO47-1,$AP47-1),-1))</f>
         <v/>
       </c>
-      <c r="AZ47" s="8" t="n"/>
+      <c r="AZ47" s="8" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="D48" s="9" t="inlineStr">

--- a/forward_test_2026-09-18.xlsx
+++ b/forward_test_2026-09-18.xlsx
@@ -9,6 +9,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Scoring" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Read me" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Week 26 Sep" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -17,11 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="\+0.00;\-0.00;0.00"/>
+    <numFmt numFmtId="166" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,8 +97,23 @@
       <family val="2"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -118,8 +135,28 @@
         <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5C9A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -136,11 +173,16 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -188,6 +230,32 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="13" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9483,4 +9551,3018 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BD50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="7" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
+    <col width="9" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="11" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="8" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="9" customWidth="1" min="51" max="51"/>
+    <col width="14" customWidth="1" min="52" max="52"/>
+    <col width="8" customWidth="1" min="53" max="53"/>
+    <col width="9" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="34" customWidth="1" min="56" max="56"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>Div</t>
+        </is>
+      </c>
+      <c r="C1" s="24" t="inlineStr">
+        <is>
+          <t>League</t>
+        </is>
+      </c>
+      <c r="D1" s="24" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="E1" s="24" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F1" s="25" t="inlineStr">
+        <is>
+          <t>Referee</t>
+        </is>
+      </c>
+      <c r="G1" s="24" t="inlineStr">
+        <is>
+          <t>Ref matches</t>
+        </is>
+      </c>
+      <c r="H1" s="24" t="inlineStr">
+        <is>
+          <t>Ref vs avg</t>
+        </is>
+      </c>
+      <c r="I1" s="24" t="inlineStr">
+        <is>
+          <t>League avg</t>
+        </is>
+      </c>
+      <c r="J1" s="24" t="inlineStr">
+        <is>
+          <t>Model expects</t>
+        </is>
+      </c>
+      <c r="K1" s="24" t="inlineStr">
+        <is>
+          <t>vs league avg</t>
+        </is>
+      </c>
+      <c r="L1" s="24" t="inlineStr">
+        <is>
+          <t>Most likely</t>
+        </is>
+      </c>
+      <c r="M1" s="24" t="inlineStr">
+        <is>
+          <t>80% range</t>
+        </is>
+      </c>
+      <c r="N1" s="24" t="inlineStr">
+        <is>
+          <t>P(0)</t>
+        </is>
+      </c>
+      <c r="O1" s="24" t="inlineStr">
+        <is>
+          <t>P(1)</t>
+        </is>
+      </c>
+      <c r="P1" s="24" t="inlineStr">
+        <is>
+          <t>P(2)</t>
+        </is>
+      </c>
+      <c r="Q1" s="24" t="inlineStr">
+        <is>
+          <t>P(3)</t>
+        </is>
+      </c>
+      <c r="R1" s="24" t="inlineStr">
+        <is>
+          <t>P(4)</t>
+        </is>
+      </c>
+      <c r="S1" s="24" t="inlineStr">
+        <is>
+          <t>P(5)</t>
+        </is>
+      </c>
+      <c r="T1" s="24" t="inlineStr">
+        <is>
+          <t>P(6)</t>
+        </is>
+      </c>
+      <c r="U1" s="24" t="inlineStr">
+        <is>
+          <t>P(7)</t>
+        </is>
+      </c>
+      <c r="V1" s="24" t="inlineStr">
+        <is>
+          <t>P(8)</t>
+        </is>
+      </c>
+      <c r="W1" s="24" t="inlineStr">
+        <is>
+          <t>P(o1.5)</t>
+        </is>
+      </c>
+      <c r="X1" s="24" t="inlineStr">
+        <is>
+          <t>P(o2.5)</t>
+        </is>
+      </c>
+      <c r="Y1" s="24" t="inlineStr">
+        <is>
+          <t>P(o3.5)</t>
+        </is>
+      </c>
+      <c r="Z1" s="24" t="inlineStr">
+        <is>
+          <t>P(o4.5)</t>
+        </is>
+      </c>
+      <c r="AA1" s="24" t="inlineStr">
+        <is>
+          <t>P(o5.5)</t>
+        </is>
+      </c>
+      <c r="AB1" s="24" t="inlineStr">
+        <is>
+          <t>P(o6.5)</t>
+        </is>
+      </c>
+      <c r="AC1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 1.5</t>
+        </is>
+      </c>
+      <c r="AD1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 2.5</t>
+        </is>
+      </c>
+      <c r="AE1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 3.5</t>
+        </is>
+      </c>
+      <c r="AF1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 4.5</t>
+        </is>
+      </c>
+      <c r="AG1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 5.5</t>
+        </is>
+      </c>
+      <c r="AH1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 6.5</t>
+        </is>
+      </c>
+      <c r="AI1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 1.5</t>
+        </is>
+      </c>
+      <c r="AJ1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 2.5</t>
+        </is>
+      </c>
+      <c r="AK1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 3.5</t>
+        </is>
+      </c>
+      <c r="AL1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 4.5</t>
+        </is>
+      </c>
+      <c r="AM1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 5.5</t>
+        </is>
+      </c>
+      <c r="AN1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 6.5</t>
+        </is>
+      </c>
+      <c r="AO1" s="25" t="inlineStr">
+        <is>
+          <t>Bookmaker</t>
+        </is>
+      </c>
+      <c r="AP1" s="25" t="inlineStr">
+        <is>
+          <t>Settles on</t>
+        </is>
+      </c>
+      <c r="AQ1" s="25" t="inlineStr">
+        <is>
+          <t>Card line</t>
+        </is>
+      </c>
+      <c r="AR1" s="25" t="inlineStr">
+        <is>
+          <t>Over price</t>
+        </is>
+      </c>
+      <c r="AS1" s="25" t="inlineStr">
+        <is>
+          <t>Under price</t>
+        </is>
+      </c>
+      <c r="AT1" s="25" t="inlineStr">
+        <is>
+          <t>Stake EUR</t>
+        </is>
+      </c>
+      <c r="AU1" s="24" t="inlineStr">
+        <is>
+          <t>Model P(over)</t>
+        </is>
+      </c>
+      <c r="AV1" s="24" t="inlineStr">
+        <is>
+          <t>Implied P(over)</t>
+        </is>
+      </c>
+      <c r="AW1" s="24" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="AX1" s="24" t="inlineStr">
+        <is>
+          <t>BET?</t>
+        </is>
+      </c>
+      <c r="AY1" s="24" t="inlineStr">
+        <is>
+          <t>EV EUR</t>
+        </is>
+      </c>
+      <c r="AZ1" s="25" t="inlineStr">
+        <is>
+          <t>ACTUAL yellows</t>
+        </is>
+      </c>
+      <c r="BA1" s="24" t="inlineStr">
+        <is>
+          <t>Won?</t>
+        </is>
+      </c>
+      <c r="BB1" s="24" t="inlineStr">
+        <is>
+          <t>P/L EUR</t>
+        </is>
+      </c>
+      <c r="BC1" s="24" t="inlineStr">
+        <is>
+          <t>Running P/L</t>
+        </is>
+      </c>
+      <c r="BD1" s="25" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D2" s="26" t="inlineStr">
+        <is>
+          <t>Cambridge</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="inlineStr">
+        <is>
+          <t>AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G2" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="28" t="n"/>
+      <c r="I2" s="29" t="n">
+        <v>3.472222222222222</v>
+      </c>
+      <c r="J2" s="29" t="n">
+        <v>3.289325166183198</v>
+      </c>
+      <c r="K2" s="30" t="n">
+        <v>-0.0526743521392391</v>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N2" s="31" t="n">
+        <v>0.04153661022668442</v>
+      </c>
+      <c r="O2" s="31" t="n">
+        <v>0.1278382304613683</v>
+      </c>
+      <c r="P2" s="31" t="n">
+        <v>0.2008372987654529</v>
+      </c>
+      <c r="Q2" s="31" t="n">
+        <v>0.2146537933632891</v>
+      </c>
+      <c r="R2" s="31" t="n">
+        <v>0.1755177378159682</v>
+      </c>
+      <c r="S2" s="31" t="n">
+        <v>0.1170718262806028</v>
+      </c>
+      <c r="T2" s="31" t="n">
+        <v>0.06632845176952512</v>
+      </c>
+      <c r="U2" s="31" t="n">
+        <v>0.03282028244020434</v>
+      </c>
+      <c r="V2" s="31" t="n">
+        <v>0.01447387332526355</v>
+      </c>
+      <c r="W2" s="28" t="n">
+        <v>0.8306251593119474</v>
+      </c>
+      <c r="X2" s="28" t="n">
+        <v>0.6297878605464944</v>
+      </c>
+      <c r="Y2" s="28" t="n">
+        <v>0.4151340671832053</v>
+      </c>
+      <c r="Z2" s="28" t="n">
+        <v>0.2396163293672371</v>
+      </c>
+      <c r="AA2" s="28" t="n">
+        <v>0.1225445030866343</v>
+      </c>
+      <c r="AB2" s="28" t="n">
+        <v>0.05621605131710927</v>
+      </c>
+      <c r="AC2" s="29" t="n">
+        <v>1.203912485420445</v>
+      </c>
+      <c r="AD2" s="29" t="n">
+        <v>1.587836258279504</v>
+      </c>
+      <c r="AE2" s="29" t="n">
+        <v>2.408860363557404</v>
+      </c>
+      <c r="AF2" s="29" t="n">
+        <v>4.173338280578514</v>
+      </c>
+      <c r="AG2" s="29" t="n">
+        <v>8.160300746358551</v>
+      </c>
+      <c r="AH2" s="29" t="n">
+        <v>17.78851371753412</v>
+      </c>
+      <c r="AI2" s="29" t="n">
+        <v>5.904064593877655</v>
+      </c>
+      <c r="AJ2" s="29" t="n">
+        <v>2.701153996398296</v>
+      </c>
+      <c r="AK2" s="29" t="n">
+        <v>1.709793550778146</v>
+      </c>
+      <c r="AL2" s="29" t="n">
+        <v>1.315125559137583</v>
+      </c>
+      <c r="AM2" s="29" t="n">
+        <v>1.139658938279731</v>
+      </c>
+      <c r="AN2" s="29" t="n">
+        <v>1.059564534230066</v>
+      </c>
+      <c r="AO2" s="27" t="n"/>
+      <c r="AP2" s="27" t="n"/>
+      <c r="AQ2" s="27" t="n"/>
+      <c r="AR2" s="27" t="n"/>
+      <c r="AS2" s="27" t="n"/>
+      <c r="AT2" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU2" s="32">
+        <f>IFERROR(IF($AQ2="","",INDEX($W2:$AB2,$AQ2-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV2" s="32">
+        <f>IF($AR2="","",IF($AS2="",1/$AR2,(1/$AR2)/((1/$AR2)+(1/$AS2))))</f>
+        <v/>
+      </c>
+      <c r="AW2" s="32">
+        <f>IF(OR($AU2="",$AV2=""),"",$AU2-$AV2)</f>
+        <v/>
+      </c>
+      <c r="AX2" s="33">
+        <f>IF($AW2="","",IF($AP2="","units?",IF(ISNUMBER(SEARCH("yellow",$AP2)),IF($AW2&gt;=0.05,"OVER",IF($AW2&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY2" s="34">
+        <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?"),"",IF($AX2="OVER",$AT2*($AU2*$AR2-1),$AT2*((1-$AU2)*$AS2-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ2" s="27" t="n"/>
+      <c r="BA2" s="33">
+        <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?",$AZ2="",$AQ2=""),"",IF($AX2="OVER",IF($AZ2&gt;$AQ2,"WON","LOST"),IF($AZ2&lt;$AQ2,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB2" s="34">
+        <f>IF($BA2="","",IF($BA2="WON",IF($AX2="OVER",$AT2*($AR2-1),$AT2*($AS2-1)),-$AT2))</f>
+        <v/>
+      </c>
+      <c r="BC2" s="34">
+        <f>IF(COUNT($BB$2:$BB2)=0,"",SUM($BB$2:$BB2))</f>
+        <v/>
+      </c>
+      <c r="BD2" s="27" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Plymouth</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>Burton</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="28" t="n"/>
+      <c r="I3" s="29" t="n">
+        <v>3.472222222222222</v>
+      </c>
+      <c r="J3" s="29" t="n">
+        <v>3.890149039155168</v>
+      </c>
+      <c r="K3" s="30" t="n">
+        <v>0.1203629232766883</v>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N3" s="31" t="n">
+        <v>0.02375229884063753</v>
+      </c>
+      <c r="O3" s="31" t="n">
+        <v>0.0854518387933499</v>
+      </c>
+      <c r="P3" s="31" t="n">
+        <v>0.15692462446769</v>
+      </c>
+      <c r="Q3" s="31" t="n">
+        <v>0.1960520368534862</v>
+      </c>
+      <c r="R3" s="31" t="n">
+        <v>0.1873871768537115</v>
+      </c>
+      <c r="S3" s="31" t="n">
+        <v>0.146102387580781</v>
+      </c>
+      <c r="T3" s="31" t="n">
+        <v>0.09675888264256971</v>
+      </c>
+      <c r="U3" s="31" t="n">
+        <v>0.05596536789322262</v>
+      </c>
+      <c r="V3" s="31" t="n">
+        <v>0.02885013705890107</v>
+      </c>
+      <c r="W3" s="28" t="n">
+        <v>0.8907958623660126</v>
+      </c>
+      <c r="X3" s="28" t="n">
+        <v>0.7338712378983225</v>
+      </c>
+      <c r="Y3" s="28" t="n">
+        <v>0.5378192010448364</v>
+      </c>
+      <c r="Z3" s="28" t="n">
+        <v>0.3504320241911248</v>
+      </c>
+      <c r="AA3" s="28" t="n">
+        <v>0.2043296366103438</v>
+      </c>
+      <c r="AB3" s="28" t="n">
+        <v>0.107570753967774</v>
+      </c>
+      <c r="AC3" s="29" t="n">
+        <v>1.122591653427682</v>
+      </c>
+      <c r="AD3" s="29" t="n">
+        <v>1.362636861016414</v>
+      </c>
+      <c r="AE3" s="29" t="n">
+        <v>1.859360911728834</v>
+      </c>
+      <c r="AF3" s="29" t="n">
+        <v>2.853620476919091</v>
+      </c>
+      <c r="AG3" s="29" t="n">
+        <v>4.894052652317873</v>
+      </c>
+      <c r="AH3" s="29" t="n">
+        <v>9.296207036901304</v>
+      </c>
+      <c r="AI3" s="29" t="n">
+        <v>9.15716218877747</v>
+      </c>
+      <c r="AJ3" s="29" t="n">
+        <v>3.757579572019122</v>
+      </c>
+      <c r="AK3" s="29" t="n">
+        <v>2.163655440166848</v>
+      </c>
+      <c r="AL3" s="29" t="n">
+        <v>1.53948476101327</v>
+      </c>
+      <c r="AM3" s="29" t="n">
+        <v>1.256801869231215</v>
+      </c>
+      <c r="AN3" s="29" t="n">
+        <v>1.120537011136779</v>
+      </c>
+      <c r="AO3" s="27" t="n"/>
+      <c r="AP3" s="27" t="n"/>
+      <c r="AQ3" s="27" t="n"/>
+      <c r="AR3" s="27" t="n"/>
+      <c r="AS3" s="27" t="n"/>
+      <c r="AT3" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU3" s="32">
+        <f>IFERROR(IF($AQ3="","",INDEX($W3:$AB3,$AQ3-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV3" s="32">
+        <f>IF($AR3="","",IF($AS3="",1/$AR3,(1/$AR3)/((1/$AR3)+(1/$AS3))))</f>
+        <v/>
+      </c>
+      <c r="AW3" s="32">
+        <f>IF(OR($AU3="",$AV3=""),"",$AU3-$AV3)</f>
+        <v/>
+      </c>
+      <c r="AX3" s="33">
+        <f>IF($AW3="","",IF($AP3="","units?",IF(ISNUMBER(SEARCH("yellow",$AP3)),IF($AW3&gt;=0.05,"OVER",IF($AW3&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY3" s="34">
+        <f>IF(OR($AX3="",$AX3="skip",$AX3="units?",$AX3="UNITS?"),"",IF($AX3="OVER",$AT3*($AU3*$AR3-1),$AT3*((1-$AU3)*$AS3-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ3" s="27" t="n"/>
+      <c r="BA3" s="33">
+        <f>IF(OR($AX3="",$AX3="skip",$AX3="units?",$AX3="UNITS?",$AZ3="",$AQ3=""),"",IF($AX3="OVER",IF($AZ3&gt;$AQ3,"WON","LOST"),IF($AZ3&lt;$AQ3,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB3" s="34">
+        <f>IF($BA3="","",IF($BA3="WON",IF($AX3="OVER",$AT3*($AR3-1),$AT3*($AS3-1)),-$AT3))</f>
+        <v/>
+      </c>
+      <c r="BC3" s="34">
+        <f>IF(COUNT($BB$2:$BB3)=0,"",SUM($BB$2:$BB3))</f>
+        <v/>
+      </c>
+      <c r="BD3" s="27" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>Stockport</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>Peterboro</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="28" t="n"/>
+      <c r="I4" s="29" t="n">
+        <v>3.472222222222222</v>
+      </c>
+      <c r="J4" s="29" t="n">
+        <v>3.098576747918274</v>
+      </c>
+      <c r="K4" s="30" t="n">
+        <v>-0.1076098965995372</v>
+      </c>
+      <c r="L4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N4" s="31" t="n">
+        <v>0.04966927813172286</v>
+      </c>
+      <c r="O4" s="31" t="n">
+        <v>0.1445426972495613</v>
+      </c>
+      <c r="P4" s="31" t="n">
+        <v>0.2147130211491994</v>
+      </c>
+      <c r="Q4" s="31" t="n">
+        <v>0.216985736259735</v>
+      </c>
+      <c r="R4" s="31" t="n">
+        <v>0.1677614759031135</v>
+      </c>
+      <c r="S4" s="31" t="n">
+        <v>0.1058040338494758</v>
+      </c>
+      <c r="T4" s="31" t="n">
+        <v>0.0566797987817786</v>
+      </c>
+      <c r="U4" s="31" t="n">
+        <v>0.02651852478939308</v>
+      </c>
+      <c r="V4" s="31" t="n">
+        <v>0.01105784304317155</v>
+      </c>
+      <c r="W4" s="28" t="n">
+        <v>0.8057880246187158</v>
+      </c>
+      <c r="X4" s="28" t="n">
+        <v>0.5910750034695164</v>
+      </c>
+      <c r="Y4" s="28" t="n">
+        <v>0.3740892672097813</v>
+      </c>
+      <c r="Z4" s="28" t="n">
+        <v>0.2063277913066679</v>
+      </c>
+      <c r="AA4" s="28" t="n">
+        <v>0.1005237574571921</v>
+      </c>
+      <c r="AB4" s="28" t="n">
+        <v>0.04384395867541346</v>
+      </c>
+      <c r="AC4" s="29" t="n">
+        <v>1.241021173618436</v>
+      </c>
+      <c r="AD4" s="29" t="n">
+        <v>1.691832667817382</v>
+      </c>
+      <c r="AE4" s="29" t="n">
+        <v>2.673158755552378</v>
+      </c>
+      <c r="AF4" s="29" t="n">
+        <v>4.846656835063416</v>
+      </c>
+      <c r="AG4" s="29" t="n">
+        <v>9.947897146859523</v>
+      </c>
+      <c r="AH4" s="29" t="n">
+        <v>22.8081594411495</v>
+      </c>
+      <c r="AI4" s="29" t="n">
+        <v>5.149013072117528</v>
+      </c>
+      <c r="AJ4" s="29" t="n">
+        <v>2.445436225431267</v>
+      </c>
+      <c r="AK4" s="29" t="n">
+        <v>1.597671916476246</v>
+      </c>
+      <c r="AL4" s="29" t="n">
+        <v>1.259966002395822</v>
+      </c>
+      <c r="AM4" s="29" t="n">
+        <v>1.111758101773775</v>
+      </c>
+      <c r="AN4" s="29" t="n">
+        <v>1.045854396960851</v>
+      </c>
+      <c r="AO4" s="27" t="n"/>
+      <c r="AP4" s="27" t="n"/>
+      <c r="AQ4" s="27" t="n"/>
+      <c r="AR4" s="27" t="n"/>
+      <c r="AS4" s="27" t="n"/>
+      <c r="AT4" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU4" s="32">
+        <f>IFERROR(IF($AQ4="","",INDEX($W4:$AB4,$AQ4-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV4" s="32">
+        <f>IF($AR4="","",IF($AS4="",1/$AR4,(1/$AR4)/((1/$AR4)+(1/$AS4))))</f>
+        <v/>
+      </c>
+      <c r="AW4" s="32">
+        <f>IF(OR($AU4="",$AV4=""),"",$AU4-$AV4)</f>
+        <v/>
+      </c>
+      <c r="AX4" s="33">
+        <f>IF($AW4="","",IF($AP4="","units?",IF(ISNUMBER(SEARCH("yellow",$AP4)),IF($AW4&gt;=0.05,"OVER",IF($AW4&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY4" s="34">
+        <f>IF(OR($AX4="",$AX4="skip",$AX4="units?",$AX4="UNITS?"),"",IF($AX4="OVER",$AT4*($AU4*$AR4-1),$AT4*((1-$AU4)*$AS4-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ4" s="27" t="n"/>
+      <c r="BA4" s="33">
+        <f>IF(OR($AX4="",$AX4="skip",$AX4="units?",$AX4="UNITS?",$AZ4="",$AQ4=""),"",IF($AX4="OVER",IF($AZ4&gt;$AQ4,"WON","LOST"),IF($AZ4&lt;$AQ4,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB4" s="34">
+        <f>IF($BA4="","",IF($BA4="WON",IF($AX4="OVER",$AT4*($AR4-1),$AT4*($AS4-1)),-$AT4))</f>
+        <v/>
+      </c>
+      <c r="BC4" s="34">
+        <f>IF(COUNT($BB$2:$BB4)=0,"",SUM($BB$2:$BB4))</f>
+        <v/>
+      </c>
+      <c r="BD4" s="27" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Wycombe</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="29" t="n">
+        <v>3.472222222222222</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>3.442715886149748</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>-0.008497824788872732</v>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N5" s="31" t="n">
+        <v>0.03599092783437825</v>
+      </c>
+      <c r="O5" s="31" t="n">
+        <v>0.1155889288251183</v>
+      </c>
+      <c r="P5" s="31" t="n">
+        <v>0.1894930810163485</v>
+      </c>
+      <c r="Q5" s="31" t="n">
+        <v>0.2113396823627093</v>
+      </c>
+      <c r="R5" s="31" t="n">
+        <v>0.1803254366266395</v>
+      </c>
+      <c r="S5" s="31" t="n">
+        <v>0.1255110231462327</v>
+      </c>
+      <c r="T5" s="31" t="n">
+        <v>0.07420323404562959</v>
+      </c>
+      <c r="U5" s="31" t="n">
+        <v>0.03831411379503388</v>
+      </c>
+      <c r="V5" s="31" t="n">
+        <v>0.01763172221760719</v>
+      </c>
+      <c r="W5" s="28" t="n">
+        <v>0.8484201433405034</v>
+      </c>
+      <c r="X5" s="28" t="n">
+        <v>0.658927062324155</v>
+      </c>
+      <c r="Y5" s="28" t="n">
+        <v>0.4475873799614456</v>
+      </c>
+      <c r="Z5" s="28" t="n">
+        <v>0.2672619433348061</v>
+      </c>
+      <c r="AA5" s="28" t="n">
+        <v>0.1417509201885734</v>
+      </c>
+      <c r="AB5" s="28" t="n">
+        <v>0.06754768614294382</v>
+      </c>
+      <c r="AC5" s="29" t="n">
+        <v>1.178661312852236</v>
+      </c>
+      <c r="AD5" s="29" t="n">
+        <v>1.517618651862346</v>
+      </c>
+      <c r="AE5" s="29" t="n">
+        <v>2.234200615947077</v>
+      </c>
+      <c r="AF5" s="29" t="n">
+        <v>3.741647566886369</v>
+      </c>
+      <c r="AG5" s="29" t="n">
+        <v>7.05462792530507</v>
+      </c>
+      <c r="AH5" s="29" t="n">
+        <v>14.80435610901325</v>
+      </c>
+      <c r="AI5" s="29" t="n">
+        <v>6.597182647074032</v>
+      </c>
+      <c r="AJ5" s="29" t="n">
+        <v>2.931924200184999</v>
+      </c>
+      <c r="AK5" s="29" t="n">
+        <v>1.810241047589042</v>
+      </c>
+      <c r="AL5" s="29" t="n">
+        <v>1.364744182322339</v>
+      </c>
+      <c r="AM5" s="29" t="n">
+        <v>1.165162915432101</v>
+      </c>
+      <c r="AN5" s="29" t="n">
+        <v>1.072440901415682</v>
+      </c>
+      <c r="AO5" s="27" t="n"/>
+      <c r="AP5" s="27" t="n"/>
+      <c r="AQ5" s="27" t="n"/>
+      <c r="AR5" s="27" t="n"/>
+      <c r="AS5" s="27" t="n"/>
+      <c r="AT5" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU5" s="32">
+        <f>IFERROR(IF($AQ5="","",INDEX($W5:$AB5,$AQ5-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV5" s="32">
+        <f>IF($AR5="","",IF($AS5="",1/$AR5,(1/$AR5)/((1/$AR5)+(1/$AS5))))</f>
+        <v/>
+      </c>
+      <c r="AW5" s="32">
+        <f>IF(OR($AU5="",$AV5=""),"",$AU5-$AV5)</f>
+        <v/>
+      </c>
+      <c r="AX5" s="33">
+        <f>IF($AW5="","",IF($AP5="","units?",IF(ISNUMBER(SEARCH("yellow",$AP5)),IF($AW5&gt;=0.05,"OVER",IF($AW5&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY5" s="34">
+        <f>IF(OR($AX5="",$AX5="skip",$AX5="units?",$AX5="UNITS?"),"",IF($AX5="OVER",$AT5*($AU5*$AR5-1),$AT5*((1-$AU5)*$AS5-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ5" s="27" t="n"/>
+      <c r="BA5" s="33">
+        <f>IF(OR($AX5="",$AX5="skip",$AX5="units?",$AX5="UNITS?",$AZ5="",$AQ5=""),"",IF($AX5="OVER",IF($AZ5&gt;$AQ5,"WON","LOST"),IF($AZ5&lt;$AQ5,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB5" s="34">
+        <f>IF($BA5="","",IF($BA5="WON",IF($AX5="OVER",$AT5*($AR5-1),$AT5*($AS5-1)),-$AT5))</f>
+        <v/>
+      </c>
+      <c r="BC5" s="34">
+        <f>IF(COUNT($BB$2:$BB5)=0,"",SUM($BB$2:$BB5))</f>
+        <v/>
+      </c>
+      <c r="BD5" s="27" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Bristol Rvs</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>Exeter</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n"/>
+      <c r="I6" s="29" t="n">
+        <v>3.944444444444445</v>
+      </c>
+      <c r="J6" s="29" t="n">
+        <v>4.132477614255593</v>
+      </c>
+      <c r="K6" s="30" t="n">
+        <v>0.04767038107888255</v>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N6" s="31" t="n">
+        <v>0.01899348869749633</v>
+      </c>
+      <c r="O6" s="31" t="n">
+        <v>0.07224955957154593</v>
+      </c>
+      <c r="P6" s="31" t="n">
+        <v>0.1402876974119978</v>
+      </c>
+      <c r="Q6" s="31" t="n">
+        <v>0.1853166945871978</v>
+      </c>
+      <c r="R6" s="31" t="n">
+        <v>0.1872827390406429</v>
+      </c>
+      <c r="S6" s="31" t="n">
+        <v>0.1543938136750537</v>
+      </c>
+      <c r="T6" s="31" t="n">
+        <v>0.1081130510629067</v>
+      </c>
+      <c r="U6" s="31" t="n">
+        <v>0.0661182483974864</v>
+      </c>
+      <c r="V6" s="31" t="n">
+        <v>0.03603832147343904</v>
+      </c>
+      <c r="W6" s="28" t="n">
+        <v>0.9087569517309577</v>
+      </c>
+      <c r="X6" s="28" t="n">
+        <v>0.76846925431896</v>
+      </c>
+      <c r="Y6" s="28" t="n">
+        <v>0.5831525597317621</v>
+      </c>
+      <c r="Z6" s="28" t="n">
+        <v>0.3958698206911191</v>
+      </c>
+      <c r="AA6" s="28" t="n">
+        <v>0.2414760070160654</v>
+      </c>
+      <c r="AB6" s="28" t="n">
+        <v>0.1333629559531587</v>
+      </c>
+      <c r="AC6" s="29" t="n">
+        <v>1.100404236903219</v>
+      </c>
+      <c r="AD6" s="29" t="n">
+        <v>1.301288235514678</v>
+      </c>
+      <c r="AE6" s="29" t="n">
+        <v>1.71481713200398</v>
+      </c>
+      <c r="AF6" s="29" t="n">
+        <v>2.526082938714994</v>
+      </c>
+      <c r="AG6" s="29" t="n">
+        <v>4.141198176817086</v>
+      </c>
+      <c r="AH6" s="29" t="n">
+        <v>7.49833409774774</v>
+      </c>
+      <c r="AI6" s="29" t="n">
+        <v>10.95973905925816</v>
+      </c>
+      <c r="AJ6" s="29" t="n">
+        <v>4.319080807425956</v>
+      </c>
+      <c r="AK6" s="29" t="n">
+        <v>2.398959195614847</v>
+      </c>
+      <c r="AL6" s="29" t="n">
+        <v>1.655272380439577</v>
+      </c>
+      <c r="AM6" s="29" t="n">
+        <v>1.318349860056674</v>
+      </c>
+      <c r="AN6" s="29" t="n">
+        <v>1.153885593593378</v>
+      </c>
+      <c r="AO6" s="27" t="n"/>
+      <c r="AP6" s="27" t="n"/>
+      <c r="AQ6" s="27" t="n"/>
+      <c r="AR6" s="27" t="n"/>
+      <c r="AS6" s="27" t="n"/>
+      <c r="AT6" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU6" s="32">
+        <f>IFERROR(IF($AQ6="","",INDEX($W6:$AB6,$AQ6-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV6" s="32">
+        <f>IF($AR6="","",IF($AS6="",1/$AR6,(1/$AR6)/((1/$AR6)+(1/$AS6))))</f>
+        <v/>
+      </c>
+      <c r="AW6" s="32">
+        <f>IF(OR($AU6="",$AV6=""),"",$AU6-$AV6)</f>
+        <v/>
+      </c>
+      <c r="AX6" s="33">
+        <f>IF($AW6="","",IF($AP6="","units?",IF(ISNUMBER(SEARCH("yellow",$AP6)),IF($AW6&gt;=0.05,"OVER",IF($AW6&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY6" s="34">
+        <f>IF(OR($AX6="",$AX6="skip",$AX6="units?",$AX6="UNITS?"),"",IF($AX6="OVER",$AT6*($AU6*$AR6-1),$AT6*((1-$AU6)*$AS6-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ6" s="27" t="n"/>
+      <c r="BA6" s="33">
+        <f>IF(OR($AX6="",$AX6="skip",$AX6="units?",$AX6="UNITS?",$AZ6="",$AQ6=""),"",IF($AX6="OVER",IF($AZ6&gt;$AQ6,"WON","LOST"),IF($AZ6&lt;$AQ6,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB6" s="34">
+        <f>IF($BA6="","",IF($BA6="WON",IF($AX6="OVER",$AT6*($AR6-1),$AT6*($AS6-1)),-$AT6))</f>
+        <v/>
+      </c>
+      <c r="BC6" s="34">
+        <f>IF(COUNT($BB$2:$BB6)=0,"",SUM($BB$2:$BB6))</f>
+        <v/>
+      </c>
+      <c r="BD6" s="27" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="29" t="n">
+        <v>3.944444444444445</v>
+      </c>
+      <c r="J7" s="29" t="n">
+        <v>3.743316424126105</v>
+      </c>
+      <c r="K7" s="30" t="n">
+        <v>-0.05099020233422702</v>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N7" s="31" t="n">
+        <v>0.02721215436587866</v>
+      </c>
+      <c r="O7" s="31" t="n">
+        <v>0.09447205997704582</v>
+      </c>
+      <c r="P7" s="31" t="n">
+        <v>0.167416310371261</v>
+      </c>
+      <c r="Q7" s="31" t="n">
+        <v>0.201837901744763</v>
+      </c>
+      <c r="R7" s="31" t="n">
+        <v>0.1861640968983338</v>
+      </c>
+      <c r="S7" s="31" t="n">
+        <v>0.1400677229249185</v>
+      </c>
+      <c r="T7" s="31" t="n">
+        <v>0.08951509881167047</v>
+      </c>
+      <c r="U7" s="31" t="n">
+        <v>0.04996311527289864</v>
+      </c>
+      <c r="V7" s="31" t="n">
+        <v>0.02485436791171724</v>
+      </c>
+      <c r="W7" s="28" t="n">
+        <v>0.8783157856570756</v>
+      </c>
+      <c r="X7" s="28" t="n">
+        <v>0.7108994752858145</v>
+      </c>
+      <c r="Y7" s="28" t="n">
+        <v>0.5090615735410515</v>
+      </c>
+      <c r="Z7" s="28" t="n">
+        <v>0.3228974766427177</v>
+      </c>
+      <c r="AA7" s="28" t="n">
+        <v>0.1828297537177993</v>
+      </c>
+      <c r="AB7" s="28" t="n">
+        <v>0.09331465490612878</v>
+      </c>
+      <c r="AC7" s="29" t="n">
+        <v>1.138542670335694</v>
+      </c>
+      <c r="AD7" s="29" t="n">
+        <v>1.406668642705009</v>
+      </c>
+      <c r="AE7" s="29" t="n">
+        <v>1.964398909632802</v>
+      </c>
+      <c r="AF7" s="29" t="n">
+        <v>3.096958237014928</v>
+      </c>
+      <c r="AG7" s="29" t="n">
+        <v>5.469569255907418</v>
+      </c>
+      <c r="AH7" s="29" t="n">
+        <v>10.71643035068784</v>
+      </c>
+      <c r="AI7" s="29" t="n">
+        <v>8.217992821828553</v>
+      </c>
+      <c r="AJ7" s="29" t="n">
+        <v>3.459004444867867</v>
+      </c>
+      <c r="AK7" s="29" t="n">
+        <v>2.036915315863177</v>
+      </c>
+      <c r="AL7" s="29" t="n">
+        <v>1.476881218876121</v>
+      </c>
+      <c r="AM7" s="29" t="n">
+        <v>1.22373520640234</v>
+      </c>
+      <c r="AN7" s="29" t="n">
+        <v>1.102918455019771</v>
+      </c>
+      <c r="AO7" s="27" t="n"/>
+      <c r="AP7" s="27" t="n"/>
+      <c r="AQ7" s="27" t="n"/>
+      <c r="AR7" s="27" t="n"/>
+      <c r="AS7" s="27" t="n"/>
+      <c r="AT7" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU7" s="32">
+        <f>IFERROR(IF($AQ7="","",INDEX($W7:$AB7,$AQ7-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV7" s="32">
+        <f>IF($AR7="","",IF($AS7="",1/$AR7,(1/$AR7)/((1/$AR7)+(1/$AS7))))</f>
+        <v/>
+      </c>
+      <c r="AW7" s="32">
+        <f>IF(OR($AU7="",$AV7=""),"",$AU7-$AV7)</f>
+        <v/>
+      </c>
+      <c r="AX7" s="33">
+        <f>IF($AW7="","",IF($AP7="","units?",IF(ISNUMBER(SEARCH("yellow",$AP7)),IF($AW7&gt;=0.05,"OVER",IF($AW7&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY7" s="34">
+        <f>IF(OR($AX7="",$AX7="skip",$AX7="units?",$AX7="UNITS?"),"",IF($AX7="OVER",$AT7*($AU7*$AR7-1),$AT7*((1-$AU7)*$AS7-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ7" s="27" t="n"/>
+      <c r="BA7" s="33">
+        <f>IF(OR($AX7="",$AX7="skip",$AX7="units?",$AX7="UNITS?",$AZ7="",$AQ7=""),"",IF($AX7="OVER",IF($AZ7&gt;$AQ7,"WON","LOST"),IF($AZ7&lt;$AQ7,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB7" s="34">
+        <f>IF($BA7="","",IF($BA7="WON",IF($AX7="OVER",$AT7*($AR7-1),$AT7*($AS7-1)),-$AT7))</f>
+        <v/>
+      </c>
+      <c r="BC7" s="34">
+        <f>IF(COUNT($BB$2:$BB7)=0,"",SUM($BB$2:$BB7))</f>
+        <v/>
+      </c>
+      <c r="BD7" s="27" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Rochdale</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="29" t="n">
+        <v>3.944444444444445</v>
+      </c>
+      <c r="J8" s="29" t="n">
+        <v>3.803863558246142</v>
+      </c>
+      <c r="K8" s="30" t="n">
+        <v>-0.03564022466999206</v>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N8" s="31" t="n">
+        <v>0.02572705251403077</v>
+      </c>
+      <c r="O8" s="31" t="n">
+        <v>0.09065451713766508</v>
+      </c>
+      <c r="P8" s="31" t="n">
+        <v>0.1630582536601907</v>
+      </c>
+      <c r="Q8" s="31" t="n">
+        <v>0.1995293095177963</v>
+      </c>
+      <c r="R8" s="31" t="n">
+        <v>0.1867922534445548</v>
+      </c>
+      <c r="S8" s="31" t="n">
+        <v>0.1426461184585814</v>
+      </c>
+      <c r="T8" s="31" t="n">
+        <v>0.09252884523654314</v>
+      </c>
+      <c r="U8" s="31" t="n">
+        <v>0.0524190701522175</v>
+      </c>
+      <c r="V8" s="31" t="n">
+        <v>0.02646680287762022</v>
+      </c>
+      <c r="W8" s="28" t="n">
+        <v>0.8836184303483041</v>
+      </c>
+      <c r="X8" s="28" t="n">
+        <v>0.7205601766881135</v>
+      </c>
+      <c r="Y8" s="28" t="n">
+        <v>0.5210308671703172</v>
+      </c>
+      <c r="Z8" s="28" t="n">
+        <v>0.3342386137257624</v>
+      </c>
+      <c r="AA8" s="28" t="n">
+        <v>0.1915924952671809</v>
+      </c>
+      <c r="AB8" s="28" t="n">
+        <v>0.09906365003063777</v>
+      </c>
+      <c r="AC8" s="29" t="n">
+        <v>1.131710210713713</v>
+      </c>
+      <c r="AD8" s="29" t="n">
+        <v>1.387809141210476</v>
+      </c>
+      <c r="AE8" s="29" t="n">
+        <v>1.919272087335115</v>
+      </c>
+      <c r="AF8" s="29" t="n">
+        <v>2.991874543916355</v>
+      </c>
+      <c r="AG8" s="29" t="n">
+        <v>5.219411118402487</v>
+      </c>
+      <c r="AH8" s="29" t="n">
+        <v>10.0945200352574</v>
+      </c>
+      <c r="AI8" s="29" t="n">
+        <v>8.592425785223359</v>
+      </c>
+      <c r="AJ8" s="29" t="n">
+        <v>3.578588005632564</v>
+      </c>
+      <c r="AK8" s="29" t="n">
+        <v>2.087817212963473</v>
+      </c>
+      <c r="AL8" s="29" t="n">
+        <v>1.502039650566463</v>
+      </c>
+      <c r="AM8" s="29" t="n">
+        <v>1.236999896890496</v>
+      </c>
+      <c r="AN8" s="29" t="n">
+        <v>1.109956324921296</v>
+      </c>
+      <c r="AO8" s="27" t="n"/>
+      <c r="AP8" s="27" t="n"/>
+      <c r="AQ8" s="27" t="n"/>
+      <c r="AR8" s="27" t="n"/>
+      <c r="AS8" s="27" t="n"/>
+      <c r="AT8" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU8" s="32">
+        <f>IFERROR(IF($AQ8="","",INDEX($W8:$AB8,$AQ8-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV8" s="32">
+        <f>IF($AR8="","",IF($AS8="",1/$AR8,(1/$AR8)/((1/$AR8)+(1/$AS8))))</f>
+        <v/>
+      </c>
+      <c r="AW8" s="32">
+        <f>IF(OR($AU8="",$AV8=""),"",$AU8-$AV8)</f>
+        <v/>
+      </c>
+      <c r="AX8" s="33">
+        <f>IF($AW8="","",IF($AP8="","units?",IF(ISNUMBER(SEARCH("yellow",$AP8)),IF($AW8&gt;=0.05,"OVER",IF($AW8&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY8" s="34">
+        <f>IF(OR($AX8="",$AX8="skip",$AX8="units?",$AX8="UNITS?"),"",IF($AX8="OVER",$AT8*($AU8*$AR8-1),$AT8*((1-$AU8)*$AS8-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ8" s="27" t="n"/>
+      <c r="BA8" s="33">
+        <f>IF(OR($AX8="",$AX8="skip",$AX8="units?",$AX8="UNITS?",$AZ8="",$AQ8=""),"",IF($AX8="OVER",IF($AZ8&gt;$AQ8,"WON","LOST"),IF($AZ8&lt;$AQ8,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB8" s="34">
+        <f>IF($BA8="","",IF($BA8="WON",IF($AX8="OVER",$AT8*($AR8-1),$AT8*($AS8-1)),-$AT8))</f>
+        <v/>
+      </c>
+      <c r="BC8" s="34">
+        <f>IF(COUNT($BB$2:$BB8)=0,"",SUM($BB$2:$BB8))</f>
+        <v/>
+      </c>
+      <c r="BD8" s="27" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>Grimsby</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="29" t="n">
+        <v>3.944444444444445</v>
+      </c>
+      <c r="J9" s="29" t="n">
+        <v>3.951010701673985</v>
+      </c>
+      <c r="K9" s="30" t="n">
+        <v>0.001664684931432792</v>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N9" s="31" t="n">
+        <v>0.02245306915157847</v>
+      </c>
+      <c r="O9" s="31" t="n">
+        <v>0.08194506740272584</v>
+      </c>
+      <c r="P9" s="31" t="n">
+        <v>0.1526595020285814</v>
+      </c>
+      <c r="Q9" s="31" t="n">
+        <v>0.1934797159608328</v>
+      </c>
+      <c r="R9" s="31" t="n">
+        <v>0.1876010607919963</v>
+      </c>
+      <c r="S9" s="31" t="n">
+        <v>0.148382974854516</v>
+      </c>
+      <c r="T9" s="31" t="n">
+        <v>0.09968939130824399</v>
+      </c>
+      <c r="U9" s="31" t="n">
+        <v>0.0584936607227403</v>
+      </c>
+      <c r="V9" s="31" t="n">
+        <v>0.03058923800374037</v>
+      </c>
+      <c r="W9" s="28" t="n">
+        <v>0.8956018634456957</v>
+      </c>
+      <c r="X9" s="28" t="n">
+        <v>0.7429423614171142</v>
+      </c>
+      <c r="Y9" s="28" t="n">
+        <v>0.5494626454562814</v>
+      </c>
+      <c r="Z9" s="28" t="n">
+        <v>0.3618615846642851</v>
+      </c>
+      <c r="AA9" s="28" t="n">
+        <v>0.2134786098097691</v>
+      </c>
+      <c r="AB9" s="28" t="n">
+        <v>0.1137892185015251</v>
+      </c>
+      <c r="AC9" s="29" t="n">
+        <v>1.116567574069853</v>
+      </c>
+      <c r="AD9" s="29" t="n">
+        <v>1.345999436743067</v>
+      </c>
+      <c r="AE9" s="29" t="n">
+        <v>1.819959934072654</v>
+      </c>
+      <c r="AF9" s="29" t="n">
+        <v>2.763487594096909</v>
+      </c>
+      <c r="AG9" s="29" t="n">
+        <v>4.684310062217009</v>
+      </c>
+      <c r="AH9" s="29" t="n">
+        <v>8.788178820180551</v>
+      </c>
+      <c r="AI9" s="29" t="n">
+        <v>9.578715032713584</v>
+      </c>
+      <c r="AJ9" s="29" t="n">
+        <v>3.890178115355088</v>
+      </c>
+      <c r="AK9" s="29" t="n">
+        <v>2.21957178448111</v>
+      </c>
+      <c r="AL9" s="29" t="n">
+        <v>1.567058142823004</v>
+      </c>
+      <c r="AM9" s="29" t="n">
+        <v>1.271421238471514</v>
+      </c>
+      <c r="AN9" s="29" t="n">
+        <v>1.128399722590963</v>
+      </c>
+      <c r="AO9" s="27" t="n"/>
+      <c r="AP9" s="27" t="n"/>
+      <c r="AQ9" s="27" t="n"/>
+      <c r="AR9" s="27" t="n"/>
+      <c r="AS9" s="27" t="n"/>
+      <c r="AT9" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU9" s="32">
+        <f>IFERROR(IF($AQ9="","",INDEX($W9:$AB9,$AQ9-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV9" s="32">
+        <f>IF($AR9="","",IF($AS9="",1/$AR9,(1/$AR9)/((1/$AR9)+(1/$AS9))))</f>
+        <v/>
+      </c>
+      <c r="AW9" s="32">
+        <f>IF(OR($AU9="",$AV9=""),"",$AU9-$AV9)</f>
+        <v/>
+      </c>
+      <c r="AX9" s="33">
+        <f>IF($AW9="","",IF($AP9="","units?",IF(ISNUMBER(SEARCH("yellow",$AP9)),IF($AW9&gt;=0.05,"OVER",IF($AW9&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY9" s="34">
+        <f>IF(OR($AX9="",$AX9="skip",$AX9="units?",$AX9="UNITS?"),"",IF($AX9="OVER",$AT9*($AU9*$AR9-1),$AT9*((1-$AU9)*$AS9-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ9" s="27" t="n"/>
+      <c r="BA9" s="33">
+        <f>IF(OR($AX9="",$AX9="skip",$AX9="units?",$AX9="UNITS?",$AZ9="",$AQ9=""),"",IF($AX9="OVER",IF($AZ9&gt;$AQ9,"WON","LOST"),IF($AZ9&lt;$AQ9,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB9" s="34">
+        <f>IF($BA9="","",IF($BA9="WON",IF($AX9="OVER",$AT9*($AR9-1),$AT9*($AS9-1)),-$AT9))</f>
+        <v/>
+      </c>
+      <c r="BC9" s="34">
+        <f>IF(COUNT($BB$2:$BB9)=0,"",SUM($BB$2:$BB9))</f>
+        <v/>
+      </c>
+      <c r="BD9" s="27" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>Oldham</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>Salford</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="29" t="n">
+        <v>3.944444444444445</v>
+      </c>
+      <c r="J10" s="29" t="n">
+        <v>3.988892656406128</v>
+      </c>
+      <c r="K10" s="30" t="n">
+        <v>0.01126856077901817</v>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N10" s="31" t="n">
+        <v>0.0216812515521691</v>
+      </c>
+      <c r="O10" s="31" t="n">
+        <v>0.07982851849571937</v>
+      </c>
+      <c r="P10" s="31" t="n">
+        <v>0.1500326265601378</v>
+      </c>
+      <c r="Q10" s="31" t="n">
+        <v>0.1918332702393027</v>
+      </c>
+      <c r="R10" s="31" t="n">
+        <v>0.1876507900946615</v>
+      </c>
+      <c r="S10" s="31" t="n">
+        <v>0.1497358525355113</v>
+      </c>
+      <c r="T10" s="31" t="n">
+        <v>0.1014886062630259</v>
+      </c>
+      <c r="U10" s="31" t="n">
+        <v>0.06007638118362885</v>
+      </c>
+      <c r="V10" s="31" t="n">
+        <v>0.03169496228556746</v>
+      </c>
+      <c r="W10" s="28" t="n">
+        <v>0.8984902299521116</v>
+      </c>
+      <c r="X10" s="28" t="n">
+        <v>0.7484576033919736</v>
+      </c>
+      <c r="Y10" s="28" t="n">
+        <v>0.556624333152671</v>
+      </c>
+      <c r="Z10" s="28" t="n">
+        <v>0.3689735430580096</v>
+      </c>
+      <c r="AA10" s="28" t="n">
+        <v>0.2192376905224982</v>
+      </c>
+      <c r="AB10" s="28" t="n">
+        <v>0.1177490842594723</v>
+      </c>
+      <c r="AC10" s="29" t="n">
+        <v>1.112978156761147</v>
+      </c>
+      <c r="AD10" s="29" t="n">
+        <v>1.336081022449433</v>
+      </c>
+      <c r="AE10" s="29" t="n">
+        <v>1.796543809603307</v>
+      </c>
+      <c r="AF10" s="29" t="n">
+        <v>2.710221420517354</v>
+      </c>
+      <c r="AG10" s="29" t="n">
+        <v>4.561259506140345</v>
+      </c>
+      <c r="AH10" s="29" t="n">
+        <v>8.492635049257764</v>
+      </c>
+      <c r="AI10" s="29" t="n">
+        <v>9.851268498867039</v>
+      </c>
+      <c r="AJ10" s="29" t="n">
+        <v>3.97547297586689</v>
+      </c>
+      <c r="AK10" s="29" t="n">
+        <v>2.255423729296218</v>
+      </c>
+      <c r="AL10" s="29" t="n">
+        <v>1.584719608819712</v>
+      </c>
+      <c r="AM10" s="29" t="n">
+        <v>1.280799531254545</v>
+      </c>
+      <c r="AN10" s="29" t="n">
+        <v>1.13346439449217</v>
+      </c>
+      <c r="AO10" s="27" t="n"/>
+      <c r="AP10" s="27" t="n"/>
+      <c r="AQ10" s="27" t="n"/>
+      <c r="AR10" s="27" t="n"/>
+      <c r="AS10" s="27" t="n"/>
+      <c r="AT10" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU10" s="32">
+        <f>IFERROR(IF($AQ10="","",INDEX($W10:$AB10,$AQ10-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV10" s="32">
+        <f>IF($AR10="","",IF($AS10="",1/$AR10,(1/$AR10)/((1/$AR10)+(1/$AS10))))</f>
+        <v/>
+      </c>
+      <c r="AW10" s="32">
+        <f>IF(OR($AU10="",$AV10=""),"",$AU10-$AV10)</f>
+        <v/>
+      </c>
+      <c r="AX10" s="33">
+        <f>IF($AW10="","",IF($AP10="","units?",IF(ISNUMBER(SEARCH("yellow",$AP10)),IF($AW10&gt;=0.05,"OVER",IF($AW10&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY10" s="34">
+        <f>IF(OR($AX10="",$AX10="skip",$AX10="units?",$AX10="UNITS?"),"",IF($AX10="OVER",$AT10*($AU10*$AR10-1),$AT10*((1-$AU10)*$AS10-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ10" s="27" t="n"/>
+      <c r="BA10" s="33">
+        <f>IF(OR($AX10="",$AX10="skip",$AX10="units?",$AX10="UNITS?",$AZ10="",$AQ10=""),"",IF($AX10="OVER",IF($AZ10&gt;$AQ10,"WON","LOST"),IF($AZ10&lt;$AQ10,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB10" s="34">
+        <f>IF($BA10="","",IF($BA10="WON",IF($AX10="OVER",$AT10*($AR10-1),$AT10*($AS10-1)),-$AT10))</f>
+        <v/>
+      </c>
+      <c r="BC10" s="34">
+        <f>IF(COUNT($BB$2:$BB10)=0,"",SUM($BB$2:$BB10))</f>
+        <v/>
+      </c>
+      <c r="BD10" s="27" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>Rotherham</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Crewe</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="29" t="n">
+        <v>3.944444444444445</v>
+      </c>
+      <c r="J11" s="29" t="n">
+        <v>3.779473526757345</v>
+      </c>
+      <c r="K11" s="30" t="n">
+        <v>-0.04182361293475756</v>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N11" s="31" t="n">
+        <v>0.02631507779845588</v>
+      </c>
+      <c r="O11" s="31" t="n">
+        <v>0.09217551938536964</v>
+      </c>
+      <c r="P11" s="31" t="n">
+        <v>0.1648088201229892</v>
+      </c>
+      <c r="Q11" s="31" t="n">
+        <v>0.2004729966614404</v>
+      </c>
+      <c r="R11" s="31" t="n">
+        <v>0.1865604424645629</v>
+      </c>
+      <c r="S11" s="31" t="n">
+        <v>0.1416224748267896</v>
+      </c>
+      <c r="T11" s="31" t="n">
+        <v>0.09131894427642613</v>
+      </c>
+      <c r="U11" s="31" t="n">
+        <v>0.05142621625734514</v>
+      </c>
+      <c r="V11" s="31" t="n">
+        <v>0.0258112038534315</v>
+      </c>
+      <c r="W11" s="28" t="n">
+        <v>0.8815094028161745</v>
+      </c>
+      <c r="X11" s="28" t="n">
+        <v>0.7167005826931853</v>
+      </c>
+      <c r="Y11" s="28" t="n">
+        <v>0.5162275860317449</v>
+      </c>
+      <c r="Z11" s="28" t="n">
+        <v>0.3296671435671821</v>
+      </c>
+      <c r="AA11" s="28" t="n">
+        <v>0.1880446687403925</v>
+      </c>
+      <c r="AB11" s="28" t="n">
+        <v>0.09672572446396632</v>
+      </c>
+      <c r="AC11" s="29" t="n">
+        <v>1.1344178483012</v>
+      </c>
+      <c r="AD11" s="29" t="n">
+        <v>1.395282805885611</v>
+      </c>
+      <c r="AE11" s="29" t="n">
+        <v>1.937130109002943</v>
+      </c>
+      <c r="AF11" s="29" t="n">
+        <v>3.03336264930573</v>
+      </c>
+      <c r="AG11" s="29" t="n">
+        <v>5.3178854082833</v>
+      </c>
+      <c r="AH11" s="29" t="n">
+        <v>10.33851134785281</v>
+      </c>
+      <c r="AI11" s="29" t="n">
+        <v>8.439488227480252</v>
+      </c>
+      <c r="AJ11" s="29" t="n">
+        <v>3.529834298660046</v>
+      </c>
+      <c r="AK11" s="29" t="n">
+        <v>2.067087686536875</v>
+      </c>
+      <c r="AL11" s="29" t="n">
+        <v>1.491796188122881</v>
+      </c>
+      <c r="AM11" s="29" t="n">
+        <v>1.231594844569434</v>
+      </c>
+      <c r="AN11" s="29" t="n">
+        <v>1.107083448608747</v>
+      </c>
+      <c r="AO11" s="27" t="n"/>
+      <c r="AP11" s="27" t="n"/>
+      <c r="AQ11" s="27" t="n"/>
+      <c r="AR11" s="27" t="n"/>
+      <c r="AS11" s="27" t="n"/>
+      <c r="AT11" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU11" s="32">
+        <f>IFERROR(IF($AQ11="","",INDEX($W11:$AB11,$AQ11-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV11" s="32">
+        <f>IF($AR11="","",IF($AS11="",1/$AR11,(1/$AR11)/((1/$AR11)+(1/$AS11))))</f>
+        <v/>
+      </c>
+      <c r="AW11" s="32">
+        <f>IF(OR($AU11="",$AV11=""),"",$AU11-$AV11)</f>
+        <v/>
+      </c>
+      <c r="AX11" s="33">
+        <f>IF($AW11="","",IF($AP11="","units?",IF(ISNUMBER(SEARCH("yellow",$AP11)),IF($AW11&gt;=0.05,"OVER",IF($AW11&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY11" s="34">
+        <f>IF(OR($AX11="",$AX11="skip",$AX11="units?",$AX11="UNITS?"),"",IF($AX11="OVER",$AT11*($AU11*$AR11-1),$AT11*((1-$AU11)*$AS11-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ11" s="27" t="n"/>
+      <c r="BA11" s="33">
+        <f>IF(OR($AX11="",$AX11="skip",$AX11="units?",$AX11="UNITS?",$AZ11="",$AQ11=""),"",IF($AX11="OVER",IF($AZ11&gt;$AQ11,"WON","LOST"),IF($AZ11&lt;$AQ11,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB11" s="34">
+        <f>IF($BA11="","",IF($BA11="WON",IF($AX11="OVER",$AT11*($AR11-1),$AT11*($AS11-1)),-$AT11))</f>
+        <v/>
+      </c>
+      <c r="BC11" s="34">
+        <f>IF(COUNT($BB$2:$BB11)=0,"",SUM($BB$2:$BB11))</f>
+        <v/>
+      </c>
+      <c r="BD11" s="27" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Shrewsbury</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>Colchester</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="29" t="n">
+        <v>3.944444444444445</v>
+      </c>
+      <c r="J12" s="29" t="n">
+        <v>3.661687497053693</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>-0.07168485990188078</v>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N12" s="31" t="n">
+        <v>0.02935401358792699</v>
+      </c>
+      <c r="O12" s="31" t="n">
+        <v>0.09984364979446908</v>
+      </c>
+      <c r="P12" s="31" t="n">
+        <v>0.1733513896203132</v>
+      </c>
+      <c r="Q12" s="31" t="n">
+        <v>0.2047598400637181</v>
+      </c>
+      <c r="R12" s="31" t="n">
+        <v>0.1850335515430969</v>
+      </c>
+      <c r="S12" s="31" t="n">
+        <v>0.1363970957888725</v>
+      </c>
+      <c r="T12" s="31" t="n">
+        <v>0.08540353519482435</v>
+      </c>
+      <c r="U12" s="31" t="n">
+        <v>0.04670265390096463</v>
+      </c>
+      <c r="V12" s="31" t="n">
+        <v>0.02276183503908508</v>
+      </c>
+      <c r="W12" s="28" t="n">
+        <v>0.8708023366176039</v>
+      </c>
+      <c r="X12" s="28" t="n">
+        <v>0.6974509469972907</v>
+      </c>
+      <c r="Y12" s="28" t="n">
+        <v>0.4926911069335727</v>
+      </c>
+      <c r="Z12" s="28" t="n">
+        <v>0.3076575553904758</v>
+      </c>
+      <c r="AA12" s="28" t="n">
+        <v>0.1712604596016032</v>
+      </c>
+      <c r="AB12" s="28" t="n">
+        <v>0.08585692440677883</v>
+      </c>
+      <c r="AC12" s="29" t="n">
+        <v>1.148366234160819</v>
+      </c>
+      <c r="AD12" s="29" t="n">
+        <v>1.43379259043989</v>
+      </c>
+      <c r="AE12" s="29" t="n">
+        <v>2.02966927132871</v>
+      </c>
+      <c r="AF12" s="29" t="n">
+        <v>3.250367112651631</v>
+      </c>
+      <c r="AG12" s="29" t="n">
+        <v>5.839059420523935</v>
+      </c>
+      <c r="AH12" s="29" t="n">
+        <v>11.64728421043982</v>
+      </c>
+      <c r="AI12" s="29" t="n">
+        <v>7.740078061940053</v>
+      </c>
+      <c r="AJ12" s="29" t="n">
+        <v>3.305249149105898</v>
+      </c>
+      <c r="AK12" s="29" t="n">
+        <v>1.971185630032035</v>
+      </c>
+      <c r="AL12" s="29" t="n">
+        <v>1.444371940194989</v>
+      </c>
+      <c r="AM12" s="29" t="n">
+        <v>1.206651729829705</v>
+      </c>
+      <c r="AN12" s="29" t="n">
+        <v>1.09392066373315</v>
+      </c>
+      <c r="AO12" s="27" t="n"/>
+      <c r="AP12" s="27" t="n"/>
+      <c r="AQ12" s="27" t="n"/>
+      <c r="AR12" s="27" t="n"/>
+      <c r="AS12" s="27" t="n"/>
+      <c r="AT12" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU12" s="32">
+        <f>IFERROR(IF($AQ12="","",INDEX($W12:$AB12,$AQ12-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV12" s="32">
+        <f>IF($AR12="","",IF($AS12="",1/$AR12,(1/$AR12)/((1/$AR12)+(1/$AS12))))</f>
+        <v/>
+      </c>
+      <c r="AW12" s="32">
+        <f>IF(OR($AU12="",$AV12=""),"",$AU12-$AV12)</f>
+        <v/>
+      </c>
+      <c r="AX12" s="33">
+        <f>IF($AW12="","",IF($AP12="","units?",IF(ISNUMBER(SEARCH("yellow",$AP12)),IF($AW12&gt;=0.05,"OVER",IF($AW12&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY12" s="34">
+        <f>IF(OR($AX12="",$AX12="skip",$AX12="units?",$AX12="UNITS?"),"",IF($AX12="OVER",$AT12*($AU12*$AR12-1),$AT12*((1-$AU12)*$AS12-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ12" s="27" t="n"/>
+      <c r="BA12" s="33">
+        <f>IF(OR($AX12="",$AX12="skip",$AX12="units?",$AX12="UNITS?",$AZ12="",$AQ12=""),"",IF($AX12="OVER",IF($AZ12&gt;$AQ12,"WON","LOST"),IF($AZ12&lt;$AQ12,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB12" s="34">
+        <f>IF($BA12="","",IF($BA12="WON",IF($AX12="OVER",$AT12*($AR12-1),$AT12*($AS12-1)),-$AT12))</f>
+        <v/>
+      </c>
+      <c r="BC12" s="34">
+        <f>IF(COUNT($BB$2:$BB12)=0,"",SUM($BB$2:$BB12))</f>
+        <v/>
+      </c>
+      <c r="BD12" s="27" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Swindon</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>Accrington</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="28" t="n"/>
+      <c r="I13" s="29" t="n">
+        <v>3.944444444444445</v>
+      </c>
+      <c r="J13" s="29" t="n">
+        <v>3.655552285793862</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>-0.07324026557338714</v>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N13" s="31" t="n">
+        <v>0.02952179071426797</v>
+      </c>
+      <c r="O13" s="31" t="n">
+        <v>0.1002580176697927</v>
+      </c>
+      <c r="P13" s="31" t="n">
+        <v>0.1737998716302122</v>
+      </c>
+      <c r="Q13" s="31" t="n">
+        <v>0.2049700299025294</v>
+      </c>
+      <c r="R13" s="31" t="n">
+        <v>0.1849351766488166</v>
+      </c>
+      <c r="S13" s="31" t="n">
+        <v>0.1361123787230974</v>
+      </c>
+      <c r="T13" s="31" t="n">
+        <v>0.08509260274331201</v>
+      </c>
+      <c r="U13" s="31" t="n">
+        <v>0.04646018968662033</v>
+      </c>
+      <c r="V13" s="31" t="n">
+        <v>0.0226084166814375</v>
+      </c>
+      <c r="W13" s="28" t="n">
+        <v>0.8702201916159393</v>
+      </c>
+      <c r="X13" s="28" t="n">
+        <v>0.6964203199857272</v>
+      </c>
+      <c r="Y13" s="28" t="n">
+        <v>0.4914502900831978</v>
+      </c>
+      <c r="Z13" s="28" t="n">
+        <v>0.3065151134343813</v>
+      </c>
+      <c r="AA13" s="28" t="n">
+        <v>0.170402734711284</v>
+      </c>
+      <c r="AB13" s="28" t="n">
+        <v>0.08531013196797199</v>
+      </c>
+      <c r="AC13" s="29" t="n">
+        <v>1.149134448538902</v>
+      </c>
+      <c r="AD13" s="29" t="n">
+        <v>1.435914448935802</v>
+      </c>
+      <c r="AE13" s="29" t="n">
+        <v>2.034793793347257</v>
+      </c>
+      <c r="AF13" s="29" t="n">
+        <v>3.262481868497097</v>
+      </c>
+      <c r="AG13" s="29" t="n">
+        <v>5.86845041949776</v>
+      </c>
+      <c r="AH13" s="29" t="n">
+        <v>11.72193708920097</v>
+      </c>
+      <c r="AI13" s="29" t="n">
+        <v>7.705358887883967</v>
+      </c>
+      <c r="AJ13" s="29" t="n">
+        <v>3.294028111344557</v>
+      </c>
+      <c r="AK13" s="29" t="n">
+        <v>1.966376109355363</v>
+      </c>
+      <c r="AL13" s="29" t="n">
+        <v>1.441992492370457</v>
+      </c>
+      <c r="AM13" s="29" t="n">
+        <v>1.205404166384252</v>
+      </c>
+      <c r="AN13" s="29" t="n">
+        <v>1.093266728920392</v>
+      </c>
+      <c r="AO13" s="27" t="n"/>
+      <c r="AP13" s="27" t="n"/>
+      <c r="AQ13" s="27" t="n"/>
+      <c r="AR13" s="27" t="n"/>
+      <c r="AS13" s="27" t="n"/>
+      <c r="AT13" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU13" s="32">
+        <f>IFERROR(IF($AQ13="","",INDEX($W13:$AB13,$AQ13-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV13" s="32">
+        <f>IF($AR13="","",IF($AS13="",1/$AR13,(1/$AR13)/((1/$AR13)+(1/$AS13))))</f>
+        <v/>
+      </c>
+      <c r="AW13" s="32">
+        <f>IF(OR($AU13="",$AV13=""),"",$AU13-$AV13)</f>
+        <v/>
+      </c>
+      <c r="AX13" s="33">
+        <f>IF($AW13="","",IF($AP13="","units?",IF(ISNUMBER(SEARCH("yellow",$AP13)),IF($AW13&gt;=0.05,"OVER",IF($AW13&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY13" s="34">
+        <f>IF(OR($AX13="",$AX13="skip",$AX13="units?",$AX13="UNITS?"),"",IF($AX13="OVER",$AT13*($AU13*$AR13-1),$AT13*((1-$AU13)*$AS13-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ13" s="27" t="n"/>
+      <c r="BA13" s="33">
+        <f>IF(OR($AX13="",$AX13="skip",$AX13="units?",$AX13="UNITS?",$AZ13="",$AQ13=""),"",IF($AX13="OVER",IF($AZ13&gt;$AQ13,"WON","LOST"),IF($AZ13&lt;$AQ13,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB13" s="34">
+        <f>IF($BA13="","",IF($BA13="WON",IF($AX13="OVER",$AT13*($AR13-1),$AT13*($AS13-1)),-$AT13))</f>
+        <v/>
+      </c>
+      <c r="BC13" s="34">
+        <f>IF(COUNT($BB$2:$BB13)=0,"",SUM($BB$2:$BB13))</f>
+        <v/>
+      </c>
+      <c r="BD13" s="27" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Tranmere</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="29" t="n">
+        <v>3.944444444444445</v>
+      </c>
+      <c r="J14" s="29" t="n">
+        <v>3.739201960720967</v>
+      </c>
+      <c r="K14" s="30" t="n">
+        <v>-0.0520333057327127</v>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N14" s="31" t="n">
+        <v>0.02731619578767016</v>
+      </c>
+      <c r="O14" s="31" t="n">
+        <v>0.09473657930728337</v>
+      </c>
+      <c r="P14" s="31" t="n">
+        <v>0.1677139176214074</v>
+      </c>
+      <c r="Q14" s="31" t="n">
+        <v>0.201990564628612</v>
+      </c>
+      <c r="R14" s="31" t="n">
+        <v>0.1861149720839194</v>
+      </c>
+      <c r="S14" s="31" t="n">
+        <v>0.1398880045649534</v>
+      </c>
+      <c r="T14" s="31" t="n">
+        <v>0.08930910257994443</v>
+      </c>
+      <c r="U14" s="31" t="n">
+        <v>0.04979731909957766</v>
+      </c>
+      <c r="V14" s="31" t="n">
+        <v>0.02474663764218845</v>
+      </c>
+      <c r="W14" s="28" t="n">
+        <v>0.8779472249050465</v>
+      </c>
+      <c r="X14" s="28" t="n">
+        <v>0.7102333072836391</v>
+      </c>
+      <c r="Y14" s="28" t="n">
+        <v>0.5082427426550271</v>
+      </c>
+      <c r="Z14" s="28" t="n">
+        <v>0.3221277705711076</v>
+      </c>
+      <c r="AA14" s="28" t="n">
+        <v>0.1822397660061542</v>
+      </c>
+      <c r="AB14" s="28" t="n">
+        <v>0.09293066342620981</v>
+      </c>
+      <c r="AC14" s="29" t="n">
+        <v>1.139020628612561</v>
+      </c>
+      <c r="AD14" s="29" t="n">
+        <v>1.407988036810895</v>
+      </c>
+      <c r="AE14" s="29" t="n">
+        <v>1.967563756594073</v>
+      </c>
+      <c r="AF14" s="29" t="n">
+        <v>3.104358243398504</v>
+      </c>
+      <c r="AG14" s="29" t="n">
+        <v>5.487276580272991</v>
+      </c>
+      <c r="AH14" s="29" t="n">
+        <v>10.76071086906675</v>
+      </c>
+      <c r="AI14" s="29" t="n">
+        <v>8.193177084437689</v>
+      </c>
+      <c r="AJ14" s="29" t="n">
+        <v>3.451052260788487</v>
+      </c>
+      <c r="AK14" s="29" t="n">
+        <v>2.033523623828269</v>
+      </c>
+      <c r="AL14" s="29" t="n">
+        <v>1.475204259130811</v>
+      </c>
+      <c r="AM14" s="29" t="n">
+        <v>1.222852320803271</v>
+      </c>
+      <c r="AN14" s="29" t="n">
+        <v>1.10245155434008</v>
+      </c>
+      <c r="AO14" s="27" t="n"/>
+      <c r="AP14" s="27" t="n"/>
+      <c r="AQ14" s="27" t="n"/>
+      <c r="AR14" s="27" t="n"/>
+      <c r="AS14" s="27" t="n"/>
+      <c r="AT14" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU14" s="32">
+        <f>IFERROR(IF($AQ14="","",INDEX($W14:$AB14,$AQ14-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV14" s="32">
+        <f>IF($AR14="","",IF($AS14="",1/$AR14,(1/$AR14)/((1/$AR14)+(1/$AS14))))</f>
+        <v/>
+      </c>
+      <c r="AW14" s="32">
+        <f>IF(OR($AU14="",$AV14=""),"",$AU14-$AV14)</f>
+        <v/>
+      </c>
+      <c r="AX14" s="33">
+        <f>IF($AW14="","",IF($AP14="","units?",IF(ISNUMBER(SEARCH("yellow",$AP14)),IF($AW14&gt;=0.05,"OVER",IF($AW14&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY14" s="34">
+        <f>IF(OR($AX14="",$AX14="skip",$AX14="units?",$AX14="UNITS?"),"",IF($AX14="OVER",$AT14*($AU14*$AR14-1),$AT14*((1-$AU14)*$AS14-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ14" s="27" t="n"/>
+      <c r="BA14" s="33">
+        <f>IF(OR($AX14="",$AX14="skip",$AX14="units?",$AX14="UNITS?",$AZ14="",$AQ14=""),"",IF($AX14="OVER",IF($AZ14&gt;$AQ14,"WON","LOST"),IF($AZ14&lt;$AQ14,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB14" s="34">
+        <f>IF($BA14="","",IF($BA14="WON",IF($AX14="OVER",$AT14*($AR14-1),$AT14*($AS14-1)),-$AT14))</f>
+        <v/>
+      </c>
+      <c r="BC14" s="34">
+        <f>IF(COUNT($BB$2:$BB14)=0,"",SUM($BB$2:$BB14))</f>
+        <v/>
+      </c>
+      <c r="BD14" s="27" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="29" t="n">
+        <v>3.944444444444445</v>
+      </c>
+      <c r="J15" s="29" t="n">
+        <v>3.550515082634137</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>-0.0998694156702189</v>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N15" s="31" t="n">
+        <v>0.03255104917359056</v>
+      </c>
+      <c r="O15" s="31" t="n">
+        <v>0.1075886520380344</v>
+      </c>
+      <c r="P15" s="31" t="n">
+        <v>0.1815189050871059</v>
+      </c>
+      <c r="Q15" s="31" t="n">
+        <v>0.2083472801179382</v>
+      </c>
+      <c r="R15" s="31" t="n">
+        <v>0.1829540619892132</v>
+      </c>
+      <c r="S15" s="31" t="n">
+        <v>0.1310524705631448</v>
+      </c>
+      <c r="T15" s="31" t="n">
+        <v>0.07973783786146683</v>
+      </c>
+      <c r="U15" s="31" t="n">
+        <v>0.04237197283250714</v>
+      </c>
+      <c r="V15" s="31" t="n">
+        <v>0.0200674834868803</v>
+      </c>
+      <c r="W15" s="28" t="n">
+        <v>0.859860298788375</v>
+      </c>
+      <c r="X15" s="28" t="n">
+        <v>0.6783413937012691</v>
+      </c>
+      <c r="Y15" s="28" t="n">
+        <v>0.469994113583331</v>
+      </c>
+      <c r="Z15" s="28" t="n">
+        <v>0.2870400515941177</v>
+      </c>
+      <c r="AA15" s="28" t="n">
+        <v>0.155987581030973</v>
+      </c>
+      <c r="AB15" s="28" t="n">
+        <v>0.07624974316950617</v>
+      </c>
+      <c r="AC15" s="29" t="n">
+        <v>1.162979615885389</v>
+      </c>
+      <c r="AD15" s="29" t="n">
+        <v>1.474183957053908</v>
+      </c>
+      <c r="AE15" s="29" t="n">
+        <v>2.127686222229032</v>
+      </c>
+      <c r="AF15" s="29" t="n">
+        <v>3.483834379370955</v>
+      </c>
+      <c r="AG15" s="29" t="n">
+        <v>6.410766763550487</v>
+      </c>
+      <c r="AH15" s="29" t="n">
+        <v>13.11479827252612</v>
+      </c>
+      <c r="AI15" s="29" t="n">
+        <v>7.135736635330053</v>
+      </c>
+      <c r="AJ15" s="29" t="n">
+        <v>3.108886193056746</v>
+      </c>
+      <c r="AK15" s="29" t="n">
+        <v>1.886771497503408</v>
+      </c>
+      <c r="AL15" s="29" t="n">
+        <v>1.402603333098745</v>
+      </c>
+      <c r="AM15" s="29" t="n">
+        <v>1.184816689334399</v>
+      </c>
+      <c r="AN15" s="29" t="n">
+        <v>1.082543677369172</v>
+      </c>
+      <c r="AO15" s="27" t="n"/>
+      <c r="AP15" s="27" t="n"/>
+      <c r="AQ15" s="27" t="n"/>
+      <c r="AR15" s="27" t="n"/>
+      <c r="AS15" s="27" t="n"/>
+      <c r="AT15" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU15" s="32">
+        <f>IFERROR(IF($AQ15="","",INDEX($W15:$AB15,$AQ15-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV15" s="32">
+        <f>IF($AR15="","",IF($AS15="",1/$AR15,(1/$AR15)/((1/$AR15)+(1/$AS15))))</f>
+        <v/>
+      </c>
+      <c r="AW15" s="32">
+        <f>IF(OR($AU15="",$AV15=""),"",$AU15-$AV15)</f>
+        <v/>
+      </c>
+      <c r="AX15" s="33">
+        <f>IF($AW15="","",IF($AP15="","units?",IF(ISNUMBER(SEARCH("yellow",$AP15)),IF($AW15&gt;=0.05,"OVER",IF($AW15&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY15" s="34">
+        <f>IF(OR($AX15="",$AX15="skip",$AX15="units?",$AX15="UNITS?"),"",IF($AX15="OVER",$AT15*($AU15*$AR15-1),$AT15*((1-$AU15)*$AS15-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ15" s="27" t="n"/>
+      <c r="BA15" s="33">
+        <f>IF(OR($AX15="",$AX15="skip",$AX15="units?",$AX15="UNITS?",$AZ15="",$AQ15=""),"",IF($AX15="OVER",IF($AZ15&gt;$AQ15,"WON","LOST"),IF($AZ15&lt;$AQ15,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB15" s="34">
+        <f>IF($BA15="","",IF($BA15="WON",IF($AX15="OVER",$AT15*($AR15-1),$AT15*($AS15-1)),-$AT15))</f>
+        <v/>
+      </c>
+      <c r="BC15" s="34">
+        <f>IF(COUNT($BB$2:$BB15)=0,"",SUM($BB$2:$BB15))</f>
+        <v/>
+      </c>
+      <c r="BD15" s="27" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>bets placed</t>
+        </is>
+      </c>
+      <c r="E18" s="37">
+        <f>COUNTIF($AX$2:$AX15,"OVER")+COUNTIF($AX$2:$AX15,"UNDER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>bets won</t>
+        </is>
+      </c>
+      <c r="E19" s="37">
+        <f>COUNTIF($BA$2:$BA15,"WON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="inlineStr">
+        <is>
+          <t>total staked</t>
+        </is>
+      </c>
+      <c r="E20" s="38">
+        <f>SUMPRODUCT(($BA$2:$BA15&lt;&gt;"")*$AT$2:$AT15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="inlineStr">
+        <is>
+          <t>profit / loss EUR</t>
+        </is>
+      </c>
+      <c r="E21" s="38">
+        <f>IF(COUNT($BB$2:$BB15)=0,"",SUM($BB$2:$BB15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t>return on stake</t>
+        </is>
+      </c>
+      <c r="E22" s="39">
+        <f>IF($E20=0,"",$E21/$E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <t>HOW TO USE THIS SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>1. Fill the yellow columns only. Everything green is computed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>2. 'Settles on' must say what the market actually pays out on. Write 'yellow cards' only if the bookmaker settles on yellows alone. If it says total cards or booking points, BET? shows UNITS? and gives no verdict -- on purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The model predicts yellows. Counting a red as two cards adds about 5-6 percentage points at every line, always upward, which is larger than the 5% edge threshold. Priced against the wrong market the model shows an OVER edge on nearly every game, and that looks identical to finding an edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="41" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The market to look for is 'Yellow Cards', as in the Chelsea screenshot -- not 'Cards' and not 'Booking Points'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="41" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>3. Record BOTH sides of the price. With one side only, the de-vig cannot run and the implied probability is overstated by the whole margin, which invents edge that is not there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="41" t="inlineStr">
+        <is>
+          <t>4. Record the price when you see it, before kick-off. A price looked up afterwards is not one you could have taken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="41" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="41" t="inlineStr">
+        <is>
+          <t>5. Stake is EUR 100 a bet. Change the column if you want; the P/L follows it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="41" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="40" t="inlineStr">
+        <is>
+          <t>WHAT THIS WEEK IS AND IS NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="41" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>Fourteen fixtures, League One and League Two only -- 26 September starts a two-weekend international break, and seven more EFL matches are postponed. No Premier League or Championship football until 10 October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="41" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>Fourteen matches is far too few to tell you anything about whether the model beats a bookmaker. Treat this as practice for the workflow. A verdict on profitability needs thousands of bets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="41" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="41" t="inlineStr">
+        <is>
+          <t>Referees are not in yet. The EFL publishes appointments one to three days ahead, and the referee is 48% of the model's value -- so these numbers are the weaker version of the model. Re-run cards/run_week_sheet.py once the appointments are out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="41" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="41" t="inlineStr">
+        <is>
+          <t>Model fingerprint d30beac40c73a847, frozen for the season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>Scoring these results against the model is a holdout look.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/forward_test_2026-09-18.xlsx
+++ b/forward_test_2026-09-18.xlsx
@@ -182,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -251,6 +251,12 @@
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -12429,134 +12435,134 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="40" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>HOW TO USE THIS SHEET</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="41" t="inlineStr"/>
+      <c r="A26" s="43" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="41" t="inlineStr">
+      <c r="A27" s="43" t="inlineStr">
         <is>
           <t>1. Fill the yellow columns only. Everything green is computed.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="41" t="inlineStr"/>
+      <c r="A28" s="43" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="41" t="inlineStr">
+      <c r="A29" s="43" t="inlineStr">
         <is>
           <t>2. 'Settles on' must say what the market actually pays out on. Write 'yellow cards' only if the bookmaker settles on yellows alone. If it says total cards or booking points, BET? shows UNITS? and gives no verdict -- on purpose.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="41" t="inlineStr"/>
+      <c r="A30" s="43" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="41" t="inlineStr">
+      <c r="A31" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">   The model predicts yellows. Counting a red as two cards adds about 5-6 percentage points at every line, always upward, which is larger than the 5% edge threshold. Priced against the wrong market the model shows an OVER edge on nearly every game, and that looks identical to finding an edge.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="41" t="inlineStr"/>
+      <c r="A32" s="43" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="41" t="inlineStr">
+      <c r="A33" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">   The market to look for is 'Yellow Cards', as in the Chelsea screenshot -- not 'Cards' and not 'Booking Points'.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="41" t="inlineStr"/>
+      <c r="A34" s="43" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="41" t="inlineStr">
+      <c r="A35" s="43" t="inlineStr">
         <is>
           <t>3. Record BOTH sides of the price. With one side only, the de-vig cannot run and the implied probability is overstated by the whole margin, which invents edge that is not there.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="41" t="inlineStr"/>
+      <c r="A36" s="43" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="41" t="inlineStr">
+      <c r="A37" s="43" t="inlineStr">
         <is>
           <t>4. Record the price when you see it, before kick-off. A price looked up afterwards is not one you could have taken.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="41" t="inlineStr"/>
+      <c r="A38" s="43" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="41" t="inlineStr">
+      <c r="A39" s="43" t="inlineStr">
         <is>
           <t>5. Stake is EUR 100 a bet. Change the column if you want; the P/L follows it.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="41" t="inlineStr"/>
+      <c r="A40" s="43" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="40" t="inlineStr">
+      <c r="A41" s="42" t="inlineStr">
         <is>
           <t>WHAT THIS WEEK IS AND IS NOT</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="41" t="inlineStr"/>
+      <c r="A42" s="43" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="41" t="inlineStr">
+      <c r="A43" s="43" t="inlineStr">
         <is>
           <t>Fourteen fixtures, League One and League Two only -- 26 September starts a two-weekend international break, and seven more EFL matches are postponed. No Premier League or Championship football until 10 October.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="41" t="inlineStr"/>
+      <c r="A44" s="43" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="41" t="inlineStr">
+      <c r="A45" s="43" t="inlineStr">
         <is>
           <t>Fourteen matches is far too few to tell you anything about whether the model beats a bookmaker. Treat this as practice for the workflow. A verdict on profitability needs thousands of bets.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="41" t="inlineStr"/>
+      <c r="A46" s="43" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="41" t="inlineStr">
+      <c r="A47" s="43" t="inlineStr">
         <is>
           <t>Referees are not in yet. The EFL publishes appointments one to three days ahead, and the referee is 48% of the model's value -- so these numbers are the weaker version of the model. Re-run cards/run_week_sheet.py once the appointments are out.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="41" t="inlineStr"/>
+      <c r="A48" s="43" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="41" t="inlineStr">
+      <c r="A49" s="43" t="inlineStr">
         <is>
           <t>Model fingerprint d30beac40c73a847, frozen for the season.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="41" t="inlineStr">
+      <c r="A50" s="43" t="inlineStr">
         <is>
           <t>Scoring these results against the model is a holdout look.</t>
         </is>

--- a/forward_test_2026-09-18.xlsx
+++ b/forward_test_2026-09-18.xlsx
@@ -1746,7 +1746,7 @@
         <v>317</v>
       </c>
       <c r="AL6" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM6" s="8" t="n"/>
       <c r="AN6" s="8" t="n"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AZ6" s="8" t="inlineStr">
         <is>
-          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data)</t>
+          <t>actual from BBC 2026-09-19 (provisional, ~97% exact vs football-data); corrected 2026-09-28 from 6 to 5: football-data (the source the model was trained on) says 1+4, cards confirmed, fouls agree 14/14</t>
         </is>
       </c>
     </row>

--- a/forward_test_2026-09-18.xlsx
+++ b/forward_test_2026-09-18.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Scoring" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Read me" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Week 26 Sep" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Week 3 Oct" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -182,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -251,6 +252,12 @@
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -12571,4 +12578,2480 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BD45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="7" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
+    <col width="9" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="11" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="8" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="9" customWidth="1" min="51" max="51"/>
+    <col width="14" customWidth="1" min="52" max="52"/>
+    <col width="8" customWidth="1" min="53" max="53"/>
+    <col width="9" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="34" customWidth="1" min="56" max="56"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>Div</t>
+        </is>
+      </c>
+      <c r="C1" s="24" t="inlineStr">
+        <is>
+          <t>League</t>
+        </is>
+      </c>
+      <c r="D1" s="24" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="E1" s="24" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F1" s="25" t="inlineStr">
+        <is>
+          <t>Referee</t>
+        </is>
+      </c>
+      <c r="G1" s="24" t="inlineStr">
+        <is>
+          <t>Ref matches</t>
+        </is>
+      </c>
+      <c r="H1" s="24" t="inlineStr">
+        <is>
+          <t>Ref vs avg</t>
+        </is>
+      </c>
+      <c r="I1" s="24" t="inlineStr">
+        <is>
+          <t>League avg</t>
+        </is>
+      </c>
+      <c r="J1" s="24" t="inlineStr">
+        <is>
+          <t>Model expects</t>
+        </is>
+      </c>
+      <c r="K1" s="24" t="inlineStr">
+        <is>
+          <t>vs league avg</t>
+        </is>
+      </c>
+      <c r="L1" s="24" t="inlineStr">
+        <is>
+          <t>Most likely</t>
+        </is>
+      </c>
+      <c r="M1" s="24" t="inlineStr">
+        <is>
+          <t>80% range</t>
+        </is>
+      </c>
+      <c r="N1" s="24" t="inlineStr">
+        <is>
+          <t>P(0)</t>
+        </is>
+      </c>
+      <c r="O1" s="24" t="inlineStr">
+        <is>
+          <t>P(1)</t>
+        </is>
+      </c>
+      <c r="P1" s="24" t="inlineStr">
+        <is>
+          <t>P(2)</t>
+        </is>
+      </c>
+      <c r="Q1" s="24" t="inlineStr">
+        <is>
+          <t>P(3)</t>
+        </is>
+      </c>
+      <c r="R1" s="24" t="inlineStr">
+        <is>
+          <t>P(4)</t>
+        </is>
+      </c>
+      <c r="S1" s="24" t="inlineStr">
+        <is>
+          <t>P(5)</t>
+        </is>
+      </c>
+      <c r="T1" s="24" t="inlineStr">
+        <is>
+          <t>P(6)</t>
+        </is>
+      </c>
+      <c r="U1" s="24" t="inlineStr">
+        <is>
+          <t>P(7)</t>
+        </is>
+      </c>
+      <c r="V1" s="24" t="inlineStr">
+        <is>
+          <t>P(8)</t>
+        </is>
+      </c>
+      <c r="W1" s="24" t="inlineStr">
+        <is>
+          <t>P(o1.5)</t>
+        </is>
+      </c>
+      <c r="X1" s="24" t="inlineStr">
+        <is>
+          <t>P(o2.5)</t>
+        </is>
+      </c>
+      <c r="Y1" s="24" t="inlineStr">
+        <is>
+          <t>P(o3.5)</t>
+        </is>
+      </c>
+      <c r="Z1" s="24" t="inlineStr">
+        <is>
+          <t>P(o4.5)</t>
+        </is>
+      </c>
+      <c r="AA1" s="24" t="inlineStr">
+        <is>
+          <t>P(o5.5)</t>
+        </is>
+      </c>
+      <c r="AB1" s="24" t="inlineStr">
+        <is>
+          <t>P(o6.5)</t>
+        </is>
+      </c>
+      <c r="AC1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 1.5</t>
+        </is>
+      </c>
+      <c r="AD1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 2.5</t>
+        </is>
+      </c>
+      <c r="AE1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 3.5</t>
+        </is>
+      </c>
+      <c r="AF1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 4.5</t>
+        </is>
+      </c>
+      <c r="AG1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 5.5</t>
+        </is>
+      </c>
+      <c r="AH1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 6.5</t>
+        </is>
+      </c>
+      <c r="AI1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 1.5</t>
+        </is>
+      </c>
+      <c r="AJ1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 2.5</t>
+        </is>
+      </c>
+      <c r="AK1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 3.5</t>
+        </is>
+      </c>
+      <c r="AL1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 4.5</t>
+        </is>
+      </c>
+      <c r="AM1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 5.5</t>
+        </is>
+      </c>
+      <c r="AN1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 6.5</t>
+        </is>
+      </c>
+      <c r="AO1" s="25" t="inlineStr">
+        <is>
+          <t>Bookmaker</t>
+        </is>
+      </c>
+      <c r="AP1" s="25" t="inlineStr">
+        <is>
+          <t>Settles on</t>
+        </is>
+      </c>
+      <c r="AQ1" s="25" t="inlineStr">
+        <is>
+          <t>Card line</t>
+        </is>
+      </c>
+      <c r="AR1" s="25" t="inlineStr">
+        <is>
+          <t>Over price</t>
+        </is>
+      </c>
+      <c r="AS1" s="25" t="inlineStr">
+        <is>
+          <t>Under price</t>
+        </is>
+      </c>
+      <c r="AT1" s="25" t="inlineStr">
+        <is>
+          <t>Stake EUR</t>
+        </is>
+      </c>
+      <c r="AU1" s="24" t="inlineStr">
+        <is>
+          <t>Model P(over)</t>
+        </is>
+      </c>
+      <c r="AV1" s="24" t="inlineStr">
+        <is>
+          <t>Implied P(over)</t>
+        </is>
+      </c>
+      <c r="AW1" s="24" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="AX1" s="24" t="inlineStr">
+        <is>
+          <t>BET?</t>
+        </is>
+      </c>
+      <c r="AY1" s="24" t="inlineStr">
+        <is>
+          <t>EV EUR</t>
+        </is>
+      </c>
+      <c r="AZ1" s="25" t="inlineStr">
+        <is>
+          <t>ACTUAL yellows</t>
+        </is>
+      </c>
+      <c r="BA1" s="24" t="inlineStr">
+        <is>
+          <t>Won?</t>
+        </is>
+      </c>
+      <c r="BB1" s="24" t="inlineStr">
+        <is>
+          <t>P/L EUR</t>
+        </is>
+      </c>
+      <c r="BC1" s="24" t="inlineStr">
+        <is>
+          <t>Running P/L</t>
+        </is>
+      </c>
+      <c r="BD1" s="25" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D2" s="26" t="inlineStr">
+        <is>
+          <t>Burton</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="inlineStr">
+        <is>
+          <t>Huddersfield</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G2" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="28" t="n"/>
+      <c r="I2" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J2" s="29" t="n">
+        <v>3.757476221117926</v>
+      </c>
+      <c r="K2" s="30" t="n">
+        <v>0.01521873055049539</v>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N2" s="31" t="n">
+        <v>0.02684027481775449</v>
+      </c>
+      <c r="O2" s="31" t="n">
+        <v>0.0935399723429607</v>
+      </c>
+      <c r="P2" s="31" t="n">
+        <v>0.1663870273390385</v>
+      </c>
+      <c r="Q2" s="31" t="n">
+        <v>0.2013316111052611</v>
+      </c>
+      <c r="R2" s="31" t="n">
+        <v>0.1863605617397721</v>
+      </c>
+      <c r="S2" s="31" t="n">
+        <v>0.1407044281278266</v>
+      </c>
+      <c r="T2" s="31" t="n">
+        <v>0.09022809525399321</v>
+      </c>
+      <c r="U2" s="31" t="n">
+        <v>0.05052848895882353</v>
+      </c>
+      <c r="V2" s="31" t="n">
+        <v>0.0252172426634796</v>
+      </c>
+      <c r="W2" s="28" t="n">
+        <v>0.8796197528392848</v>
+      </c>
+      <c r="X2" s="28" t="n">
+        <v>0.7132327255002463</v>
+      </c>
+      <c r="Y2" s="28" t="n">
+        <v>0.5119011143949852</v>
+      </c>
+      <c r="Z2" s="28" t="n">
+        <v>0.3255405526552131</v>
+      </c>
+      <c r="AA2" s="28" t="n">
+        <v>0.1848361245273864</v>
+      </c>
+      <c r="AB2" s="28" t="n">
+        <v>0.09460802927339318</v>
+      </c>
+      <c r="AC2" s="29" t="n">
+        <v>1.136854870268824</v>
+      </c>
+      <c r="AD2" s="29" t="n">
+        <v>1.402066905018444</v>
+      </c>
+      <c r="AE2" s="29" t="n">
+        <v>1.953502291515614</v>
+      </c>
+      <c r="AF2" s="29" t="n">
+        <v>3.071813916403592</v>
+      </c>
+      <c r="AG2" s="29" t="n">
+        <v>5.410197830953949</v>
+      </c>
+      <c r="AH2" s="29" t="n">
+        <v>10.56992739073186</v>
+      </c>
+      <c r="AI2" s="29" t="n">
+        <v>8.307010689759903</v>
+      </c>
+      <c r="AJ2" s="29" t="n">
+        <v>3.487148251990863</v>
+      </c>
+      <c r="AK2" s="29" t="n">
+        <v>2.048765177491579</v>
+      </c>
+      <c r="AL2" s="29" t="n">
+        <v>1.482668830478692</v>
+      </c>
+      <c r="AM2" s="29" t="n">
+        <v>1.226747197819853</v>
+      </c>
+      <c r="AN2" s="29" t="n">
+        <v>1.104494000755791</v>
+      </c>
+      <c r="AO2" s="27" t="n"/>
+      <c r="AP2" s="27" t="n"/>
+      <c r="AQ2" s="27" t="n"/>
+      <c r="AR2" s="27" t="n"/>
+      <c r="AS2" s="27" t="n"/>
+      <c r="AT2" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU2" s="32">
+        <f>IFERROR(IF($AQ2="","",INDEX($W2:$AB2,$AQ2-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV2" s="32">
+        <f>IF($AR2="","",IF($AS2="",1/$AR2,(1/$AR2)/((1/$AR2)+(1/$AS2))))</f>
+        <v/>
+      </c>
+      <c r="AW2" s="32">
+        <f>IF(OR($AU2="",$AV2=""),"",$AU2-$AV2)</f>
+        <v/>
+      </c>
+      <c r="AX2" s="33">
+        <f>IF($AW2="","",IF($AP2="","units?",IF(ISNUMBER(SEARCH("yellow",$AP2)),IF($AW2&gt;=0.05,"OVER",IF($AW2&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY2" s="34">
+        <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?"),"",IF($AX2="OVER",$AT2*($AU2*$AR2-1),$AT2*((1-$AU2)*$AS2-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ2" s="27" t="n"/>
+      <c r="BA2" s="33">
+        <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?",$AZ2="",$AQ2=""),"",IF($AX2="OVER",IF($AZ2&gt;$AQ2,"WON","LOST"),IF($AZ2&lt;$AQ2,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB2" s="34">
+        <f>IF($BA2="","",IF($BA2="WON",IF($AX2="OVER",$AT2*($AR2-1),$AT2*($AS2-1)),-$AT2))</f>
+        <v/>
+      </c>
+      <c r="BC2" s="34">
+        <f>IF(COUNT($BB$2:$BB2)=0,"",SUM($BB$2:$BB2))</f>
+        <v/>
+      </c>
+      <c r="BD2" s="27" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Leyton Orient</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>Plymouth</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="28" t="n"/>
+      <c r="I3" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J3" s="29" t="n">
+        <v>4.192678159403322</v>
+      </c>
+      <c r="K3" s="30" t="n">
+        <v>0.1328043474164253</v>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N3" s="31" t="n">
+        <v>0.01795626295405502</v>
+      </c>
+      <c r="O3" s="31" t="n">
+        <v>0.06924523896805033</v>
+      </c>
+      <c r="P3" s="31" t="n">
+        <v>0.1362937141747345</v>
+      </c>
+      <c r="Q3" s="31" t="n">
+        <v>0.1824870353361113</v>
+      </c>
+      <c r="R3" s="31" t="n">
+        <v>0.1869122392836804</v>
+      </c>
+      <c r="S3" s="31" t="n">
+        <v>0.1561547422791686</v>
+      </c>
+      <c r="T3" s="31" t="n">
+        <v>0.1108033484070047</v>
+      </c>
+      <c r="U3" s="31" t="n">
+        <v>0.0686611525324158</v>
+      </c>
+      <c r="V3" s="31" t="n">
+        <v>0.03791718247774829</v>
+      </c>
+      <c r="W3" s="28" t="n">
+        <v>0.9127984980778947</v>
+      </c>
+      <c r="X3" s="28" t="n">
+        <v>0.7765047839031601</v>
+      </c>
+      <c r="Y3" s="28" t="n">
+        <v>0.5940177485670489</v>
+      </c>
+      <c r="Z3" s="28" t="n">
+        <v>0.4071055092833685</v>
+      </c>
+      <c r="AA3" s="28" t="n">
+        <v>0.2509507670041999</v>
+      </c>
+      <c r="AB3" s="28" t="n">
+        <v>0.1401474185971953</v>
+      </c>
+      <c r="AC3" s="29" t="n">
+        <v>1.095532039224131</v>
+      </c>
+      <c r="AD3" s="29" t="n">
+        <v>1.287822072355336</v>
+      </c>
+      <c r="AE3" s="29" t="n">
+        <v>1.683451382407855</v>
+      </c>
+      <c r="AF3" s="29" t="n">
+        <v>2.456365677193387</v>
+      </c>
+      <c r="AG3" s="29" t="n">
+        <v>3.984845362051689</v>
+      </c>
+      <c r="AH3" s="29" t="n">
+        <v>7.135343697440124</v>
+      </c>
+      <c r="AI3" s="29" t="n">
+        <v>11.46769239012962</v>
+      </c>
+      <c r="AJ3" s="29" t="n">
+        <v>4.474368702221808</v>
+      </c>
+      <c r="AK3" s="29" t="n">
+        <v>2.463161865993919</v>
+      </c>
+      <c r="AL3" s="29" t="n">
+        <v>1.686640735675078</v>
+      </c>
+      <c r="AM3" s="29" t="n">
+        <v>1.335025731220002</v>
+      </c>
+      <c r="AN3" s="29" t="n">
+        <v>1.16299005390965</v>
+      </c>
+      <c r="AO3" s="27" t="n"/>
+      <c r="AP3" s="27" t="n"/>
+      <c r="AQ3" s="27" t="n"/>
+      <c r="AR3" s="27" t="n"/>
+      <c r="AS3" s="27" t="n"/>
+      <c r="AT3" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU3" s="32">
+        <f>IFERROR(IF($AQ3="","",INDEX($W3:$AB3,$AQ3-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV3" s="32">
+        <f>IF($AR3="","",IF($AS3="",1/$AR3,(1/$AR3)/((1/$AR3)+(1/$AS3))))</f>
+        <v/>
+      </c>
+      <c r="AW3" s="32">
+        <f>IF(OR($AU3="",$AV3=""),"",$AU3-$AV3)</f>
+        <v/>
+      </c>
+      <c r="AX3" s="33">
+        <f>IF($AW3="","",IF($AP3="","units?",IF(ISNUMBER(SEARCH("yellow",$AP3)),IF($AW3&gt;=0.05,"OVER",IF($AW3&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY3" s="34">
+        <f>IF(OR($AX3="",$AX3="skip",$AX3="units?",$AX3="UNITS?"),"",IF($AX3="OVER",$AT3*($AU3*$AR3-1),$AT3*((1-$AU3)*$AS3-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ3" s="27" t="n"/>
+      <c r="BA3" s="33">
+        <f>IF(OR($AX3="",$AX3="skip",$AX3="units?",$AX3="UNITS?",$AZ3="",$AQ3=""),"",IF($AX3="OVER",IF($AZ3&gt;$AQ3,"WON","LOST"),IF($AZ3&lt;$AQ3,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB3" s="34">
+        <f>IF($BA3="","",IF($BA3="WON",IF($AX3="OVER",$AT3*($AR3-1),$AT3*($AS3-1)),-$AT3))</f>
+        <v/>
+      </c>
+      <c r="BC3" s="34">
+        <f>IF(COUNT($BB$2:$BB3)=0,"",SUM($BB$2:$BB3))</f>
+        <v/>
+      </c>
+      <c r="BD3" s="27" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>Bradford</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="28" t="n"/>
+      <c r="I4" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J4" s="29" t="n">
+        <v>3.966951843542349</v>
+      </c>
+      <c r="K4" s="30" t="n">
+        <v>0.07181618132976508</v>
+      </c>
+      <c r="L4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N4" s="31" t="n">
+        <v>0.02210947920908284</v>
+      </c>
+      <c r="O4" s="31" t="n">
+        <v>0.08102101696785004</v>
+      </c>
+      <c r="P4" s="31" t="n">
+        <v>0.15154053425682</v>
+      </c>
+      <c r="Q4" s="31" t="n">
+        <v>0.1928102947440807</v>
+      </c>
+      <c r="R4" s="31" t="n">
+        <v>0.1876640820630388</v>
+      </c>
+      <c r="S4" s="31" t="n">
+        <v>0.1489854344561662</v>
+      </c>
+      <c r="T4" s="31" t="n">
+        <v>0.1004585103796798</v>
+      </c>
+      <c r="U4" s="31" t="n">
+        <v>0.05915482229153495</v>
+      </c>
+      <c r="V4" s="31" t="n">
+        <v>0.03104276084246595</v>
+      </c>
+      <c r="W4" s="28" t="n">
+        <v>0.8968695038230672</v>
+      </c>
+      <c r="X4" s="28" t="n">
+        <v>0.7453289695662471</v>
+      </c>
+      <c r="Y4" s="28" t="n">
+        <v>0.5525186748221663</v>
+      </c>
+      <c r="Z4" s="28" t="n">
+        <v>0.3648545927591276</v>
+      </c>
+      <c r="AA4" s="28" t="n">
+        <v>0.2158691583029614</v>
+      </c>
+      <c r="AB4" s="28" t="n">
+        <v>0.1154106479232816</v>
+      </c>
+      <c r="AC4" s="29" t="n">
+        <v>1.114989411210127</v>
+      </c>
+      <c r="AD4" s="29" t="n">
+        <v>1.34168942954406</v>
+      </c>
+      <c r="AE4" s="29" t="n">
+        <v>1.809893575673003</v>
+      </c>
+      <c r="AF4" s="29" t="n">
+        <v>2.740817903476927</v>
+      </c>
+      <c r="AG4" s="29" t="n">
+        <v>4.632435721070218</v>
+      </c>
+      <c r="AH4" s="29" t="n">
+        <v>8.664711774815984</v>
+      </c>
+      <c r="AI4" s="29" t="n">
+        <v>9.696452912282894</v>
+      </c>
+      <c r="AJ4" s="29" t="n">
+        <v>3.926634286973319</v>
+      </c>
+      <c r="AK4" s="29" t="n">
+        <v>2.234730130028532</v>
+      </c>
+      <c r="AL4" s="29" t="n">
+        <v>1.574442621484249</v>
+      </c>
+      <c r="AM4" s="29" t="n">
+        <v>1.275297369806002</v>
+      </c>
+      <c r="AN4" s="29" t="n">
+        <v>1.130468050121038</v>
+      </c>
+      <c r="AO4" s="27" t="n"/>
+      <c r="AP4" s="27" t="n"/>
+      <c r="AQ4" s="27" t="n"/>
+      <c r="AR4" s="27" t="n"/>
+      <c r="AS4" s="27" t="n"/>
+      <c r="AT4" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU4" s="32">
+        <f>IFERROR(IF($AQ4="","",INDEX($W4:$AB4,$AQ4-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV4" s="32">
+        <f>IF($AR4="","",IF($AS4="",1/$AR4,(1/$AR4)/((1/$AR4)+(1/$AS4))))</f>
+        <v/>
+      </c>
+      <c r="AW4" s="32">
+        <f>IF(OR($AU4="",$AV4=""),"",$AU4-$AV4)</f>
+        <v/>
+      </c>
+      <c r="AX4" s="33">
+        <f>IF($AW4="","",IF($AP4="","units?",IF(ISNUMBER(SEARCH("yellow",$AP4)),IF($AW4&gt;=0.05,"OVER",IF($AW4&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY4" s="34">
+        <f>IF(OR($AX4="",$AX4="skip",$AX4="units?",$AX4="UNITS?"),"",IF($AX4="OVER",$AT4*($AU4*$AR4-1),$AT4*((1-$AU4)*$AS4-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ4" s="27" t="n"/>
+      <c r="BA4" s="33">
+        <f>IF(OR($AX4="",$AX4="skip",$AX4="units?",$AX4="UNITS?",$AZ4="",$AQ4=""),"",IF($AX4="OVER",IF($AZ4&gt;$AQ4,"WON","LOST"),IF($AZ4&lt;$AQ4,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB4" s="34">
+        <f>IF($BA4="","",IF($BA4="WON",IF($AX4="OVER",$AT4*($AR4-1),$AT4*($AS4-1)),-$AT4))</f>
+        <v/>
+      </c>
+      <c r="BC4" s="34">
+        <f>IF(COUNT($BB$2:$BB4)=0,"",SUM($BB$2:$BB4))</f>
+        <v/>
+      </c>
+      <c r="BD4" s="27" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Accrington</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>3.853696280018084</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>-0.002073139609642283</v>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N5" s="31" t="n">
+        <v>0.02455074407846696</v>
+      </c>
+      <c r="O5" s="31" t="n">
+        <v>0.08758921630413619</v>
+      </c>
+      <c r="P5" s="31" t="n">
+        <v>0.1594955492911613</v>
+      </c>
+      <c r="Q5" s="31" t="n">
+        <v>0.197568079060859</v>
+      </c>
+      <c r="R5" s="31" t="n">
+        <v>0.1872123615945189</v>
+      </c>
+      <c r="S5" s="31" t="n">
+        <v>0.1446984832322112</v>
+      </c>
+      <c r="T5" s="31" t="n">
+        <v>0.09498908520665909</v>
+      </c>
+      <c r="U5" s="31" t="n">
+        <v>0.05445577326164713</v>
+      </c>
+      <c r="V5" s="31" t="n">
+        <v>0.02782152416092906</v>
+      </c>
+      <c r="W5" s="28" t="n">
+        <v>0.8878600396173968</v>
+      </c>
+      <c r="X5" s="28" t="n">
+        <v>0.7283644903262356</v>
+      </c>
+      <c r="Y5" s="28" t="n">
+        <v>0.5307964112653766</v>
+      </c>
+      <c r="Z5" s="28" t="n">
+        <v>0.3435840496708576</v>
+      </c>
+      <c r="AA5" s="28" t="n">
+        <v>0.1988855664386464</v>
+      </c>
+      <c r="AB5" s="28" t="n">
+        <v>0.1038964812319874</v>
+      </c>
+      <c r="AC5" s="29" t="n">
+        <v>1.126303646271689</v>
+      </c>
+      <c r="AD5" s="29" t="n">
+        <v>1.372938979427866</v>
+      </c>
+      <c r="AE5" s="29" t="n">
+        <v>1.883961494042658</v>
+      </c>
+      <c r="AF5" s="29" t="n">
+        <v>2.910495993507171</v>
+      </c>
+      <c r="AG5" s="29" t="n">
+        <v>5.0280169542041</v>
+      </c>
+      <c r="AH5" s="29" t="n">
+        <v>9.624965043494878</v>
+      </c>
+      <c r="AI5" s="29" t="n">
+        <v>8.917427798156549</v>
+      </c>
+      <c r="AJ5" s="29" t="n">
+        <v>3.681403809100677</v>
+      </c>
+      <c r="AK5" s="29" t="n">
+        <v>2.131270996236112</v>
+      </c>
+      <c r="AL5" s="29" t="n">
+        <v>1.523424285315701</v>
+      </c>
+      <c r="AM5" s="29" t="n">
+        <v>1.248261119893323</v>
+      </c>
+      <c r="AN5" s="29" t="n">
+        <v>1.115942498892122</v>
+      </c>
+      <c r="AO5" s="27" t="n"/>
+      <c r="AP5" s="27" t="n"/>
+      <c r="AQ5" s="27" t="n"/>
+      <c r="AR5" s="27" t="n"/>
+      <c r="AS5" s="27" t="n"/>
+      <c r="AT5" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU5" s="32">
+        <f>IFERROR(IF($AQ5="","",INDEX($W5:$AB5,$AQ5-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV5" s="32">
+        <f>IF($AR5="","",IF($AS5="",1/$AR5,(1/$AR5)/((1/$AR5)+(1/$AS5))))</f>
+        <v/>
+      </c>
+      <c r="AW5" s="32">
+        <f>IF(OR($AU5="",$AV5=""),"",$AU5-$AV5)</f>
+        <v/>
+      </c>
+      <c r="AX5" s="33">
+        <f>IF($AW5="","",IF($AP5="","units?",IF(ISNUMBER(SEARCH("yellow",$AP5)),IF($AW5&gt;=0.05,"OVER",IF($AW5&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY5" s="34">
+        <f>IF(OR($AX5="",$AX5="skip",$AX5="units?",$AX5="UNITS?"),"",IF($AX5="OVER",$AT5*($AU5*$AR5-1),$AT5*((1-$AU5)*$AS5-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ5" s="27" t="n"/>
+      <c r="BA5" s="33">
+        <f>IF(OR($AX5="",$AX5="skip",$AX5="units?",$AX5="UNITS?",$AZ5="",$AQ5=""),"",IF($AX5="OVER",IF($AZ5&gt;$AQ5,"WON","LOST"),IF($AZ5&lt;$AQ5,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB5" s="34">
+        <f>IF($BA5="","",IF($BA5="WON",IF($AX5="OVER",$AT5*($AR5-1),$AT5*($AS5-1)),-$AT5))</f>
+        <v/>
+      </c>
+      <c r="BC5" s="34">
+        <f>IF(COUNT($BB$2:$BB5)=0,"",SUM($BB$2:$BB5))</f>
+        <v/>
+      </c>
+      <c r="BD5" s="27" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>Tranmere</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n"/>
+      <c r="I6" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J6" s="29" t="n">
+        <v>3.955031986521905</v>
+      </c>
+      <c r="K6" s="30" t="n">
+        <v>0.02416806262550697</v>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N6" s="31" t="n">
+        <v>0.02235430381607915</v>
+      </c>
+      <c r="O6" s="31" t="n">
+        <v>0.08169075151842646</v>
+      </c>
+      <c r="P6" s="31" t="n">
+        <v>0.1523689870433689</v>
+      </c>
+      <c r="Q6" s="31" t="n">
+        <v>0.1933261266851954</v>
+      </c>
+      <c r="R6" s="31" t="n">
+        <v>0.187643729107364</v>
+      </c>
+      <c r="S6" s="31" t="n">
+        <v>0.148555683944624</v>
+      </c>
+      <c r="T6" s="31" t="n">
+        <v>0.09989063191555866</v>
+      </c>
+      <c r="U6" s="31" t="n">
+        <v>0.05865712131366928</v>
+      </c>
+      <c r="V6" s="31" t="n">
+        <v>0.03069612081949522</v>
+      </c>
+      <c r="W6" s="28" t="n">
+        <v>0.8959549446654944</v>
+      </c>
+      <c r="X6" s="28" t="n">
+        <v>0.7435859576221255</v>
+      </c>
+      <c r="Y6" s="28" t="n">
+        <v>0.5502598309369301</v>
+      </c>
+      <c r="Z6" s="28" t="n">
+        <v>0.3626161018295661</v>
+      </c>
+      <c r="AA6" s="28" t="n">
+        <v>0.2140604178849421</v>
+      </c>
+      <c r="AB6" s="28" t="n">
+        <v>0.1141697859693834</v>
+      </c>
+      <c r="AC6" s="29" t="n">
+        <v>1.116127553013674</v>
+      </c>
+      <c r="AD6" s="29" t="n">
+        <v>1.344834433396036</v>
+      </c>
+      <c r="AE6" s="29" t="n">
+        <v>1.817323278526974</v>
+      </c>
+      <c r="AF6" s="29" t="n">
+        <v>2.757737439001018</v>
+      </c>
+      <c r="AG6" s="29" t="n">
+        <v>4.671578285610476</v>
+      </c>
+      <c r="AH6" s="29" t="n">
+        <v>8.758884774192071</v>
+      </c>
+      <c r="AI6" s="29" t="n">
+        <v>9.611220800306107</v>
+      </c>
+      <c r="AJ6" s="29" t="n">
+        <v>3.899942416282769</v>
+      </c>
+      <c r="AK6" s="29" t="n">
+        <v>2.223506079261877</v>
+      </c>
+      <c r="AL6" s="29" t="n">
+        <v>1.568913182260221</v>
+      </c>
+      <c r="AM6" s="29" t="n">
+        <v>1.272362434411154</v>
+      </c>
+      <c r="AN6" s="29" t="n">
+        <v>1.128884501974593</v>
+      </c>
+      <c r="AO6" s="27" t="n"/>
+      <c r="AP6" s="27" t="n"/>
+      <c r="AQ6" s="27" t="n"/>
+      <c r="AR6" s="27" t="n"/>
+      <c r="AS6" s="27" t="n"/>
+      <c r="AT6" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU6" s="32">
+        <f>IFERROR(IF($AQ6="","",INDEX($W6:$AB6,$AQ6-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV6" s="32">
+        <f>IF($AR6="","",IF($AS6="",1/$AR6,(1/$AR6)/((1/$AR6)+(1/$AS6))))</f>
+        <v/>
+      </c>
+      <c r="AW6" s="32">
+        <f>IF(OR($AU6="",$AV6=""),"",$AU6-$AV6)</f>
+        <v/>
+      </c>
+      <c r="AX6" s="33">
+        <f>IF($AW6="","",IF($AP6="","units?",IF(ISNUMBER(SEARCH("yellow",$AP6)),IF($AW6&gt;=0.05,"OVER",IF($AW6&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY6" s="34">
+        <f>IF(OR($AX6="",$AX6="skip",$AX6="units?",$AX6="UNITS?"),"",IF($AX6="OVER",$AT6*($AU6*$AR6-1),$AT6*((1-$AU6)*$AS6-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ6" s="27" t="n"/>
+      <c r="BA6" s="33">
+        <f>IF(OR($AX6="",$AX6="skip",$AX6="units?",$AX6="UNITS?",$AZ6="",$AQ6=""),"",IF($AX6="OVER",IF($AZ6&gt;$AQ6,"WON","LOST"),IF($AZ6&lt;$AQ6,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB6" s="34">
+        <f>IF($BA6="","",IF($BA6="WON",IF($AX6="OVER",$AT6*($AR6-1),$AT6*($AS6-1)),-$AT6))</f>
+        <v/>
+      </c>
+      <c r="BC6" s="34">
+        <f>IF(COUNT($BB$2:$BB6)=0,"",SUM($BB$2:$BB6))</f>
+        <v/>
+      </c>
+      <c r="BD6" s="27" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Crewe</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>Bristol Rvs</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J7" s="29" t="n">
+        <v>3.877587531423699</v>
+      </c>
+      <c r="K7" s="30" t="n">
+        <v>0.004113575630379396</v>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N7" s="31" t="n">
+        <v>0.02401381214585648</v>
+      </c>
+      <c r="O7" s="31" t="n">
+        <v>0.08616510746785132</v>
+      </c>
+      <c r="P7" s="31" t="n">
+        <v>0.1578024369540142</v>
+      </c>
+      <c r="Q7" s="31" t="n">
+        <v>0.1965921888392699</v>
+      </c>
+      <c r="R7" s="31" t="n">
+        <v>0.1873563194529881</v>
+      </c>
+      <c r="S7" s="31" t="n">
+        <v>0.1456404952127562</v>
+      </c>
+      <c r="T7" s="31" t="n">
+        <v>0.09615596199184685</v>
+      </c>
+      <c r="U7" s="31" t="n">
+        <v>0.05544096550543399</v>
+      </c>
+      <c r="V7" s="31" t="n">
+        <v>0.02848735435224952</v>
+      </c>
+      <c r="W7" s="28" t="n">
+        <v>0.8898210803862923</v>
+      </c>
+      <c r="X7" s="28" t="n">
+        <v>0.7320186434322781</v>
+      </c>
+      <c r="Y7" s="28" t="n">
+        <v>0.5354264545930081</v>
+      </c>
+      <c r="Z7" s="28" t="n">
+        <v>0.3480701351400201</v>
+      </c>
+      <c r="AA7" s="28" t="n">
+        <v>0.2024296399272638</v>
+      </c>
+      <c r="AB7" s="28" t="n">
+        <v>0.106273677935417</v>
+      </c>
+      <c r="AC7" s="29" t="n">
+        <v>1.123821431119475</v>
+      </c>
+      <c r="AD7" s="29" t="n">
+        <v>1.3660854255176</v>
+      </c>
+      <c r="AE7" s="29" t="n">
+        <v>1.867670137367655</v>
+      </c>
+      <c r="AF7" s="29" t="n">
+        <v>2.872984203593694</v>
+      </c>
+      <c r="AG7" s="29" t="n">
+        <v>4.939988039099985</v>
+      </c>
+      <c r="AH7" s="29" t="n">
+        <v>9.409667750538423</v>
+      </c>
+      <c r="AI7" s="29" t="n">
+        <v>9.076146358178544</v>
+      </c>
+      <c r="AJ7" s="29" t="n">
+        <v>3.731602872706888</v>
+      </c>
+      <c r="AK7" s="29" t="n">
+        <v>2.152511717222179</v>
+      </c>
+      <c r="AL7" s="29" t="n">
+        <v>1.533907332523841</v>
+      </c>
+      <c r="AM7" s="29" t="n">
+        <v>1.253807877099147</v>
+      </c>
+      <c r="AN7" s="29" t="n">
+        <v>1.118910761954416</v>
+      </c>
+      <c r="AO7" s="27" t="n"/>
+      <c r="AP7" s="27" t="n"/>
+      <c r="AQ7" s="27" t="n"/>
+      <c r="AR7" s="27" t="n"/>
+      <c r="AS7" s="27" t="n"/>
+      <c r="AT7" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU7" s="32">
+        <f>IFERROR(IF($AQ7="","",INDEX($W7:$AB7,$AQ7-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV7" s="32">
+        <f>IF($AR7="","",IF($AS7="",1/$AR7,(1/$AR7)/((1/$AR7)+(1/$AS7))))</f>
+        <v/>
+      </c>
+      <c r="AW7" s="32">
+        <f>IF(OR($AU7="",$AV7=""),"",$AU7-$AV7)</f>
+        <v/>
+      </c>
+      <c r="AX7" s="33">
+        <f>IF($AW7="","",IF($AP7="","units?",IF(ISNUMBER(SEARCH("yellow",$AP7)),IF($AW7&gt;=0.05,"OVER",IF($AW7&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY7" s="34">
+        <f>IF(OR($AX7="",$AX7="skip",$AX7="units?",$AX7="UNITS?"),"",IF($AX7="OVER",$AT7*($AU7*$AR7-1),$AT7*((1-$AU7)*$AS7-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ7" s="27" t="n"/>
+      <c r="BA7" s="33">
+        <f>IF(OR($AX7="",$AX7="skip",$AX7="units?",$AX7="UNITS?",$AZ7="",$AQ7=""),"",IF($AX7="OVER",IF($AZ7&gt;$AQ7,"WON","LOST"),IF($AZ7&lt;$AQ7,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB7" s="34">
+        <f>IF($BA7="","",IF($BA7="WON",IF($AX7="OVER",$AT7*($AR7-1),$AT7*($AS7-1)),-$AT7))</f>
+        <v/>
+      </c>
+      <c r="BC7" s="34">
+        <f>IF(COUNT($BB$2:$BB7)=0,"",SUM($BB$2:$BB7))</f>
+        <v/>
+      </c>
+      <c r="BD7" s="27" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Exeter</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Rotherham</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J8" s="29" t="n">
+        <v>3.825034073797117</v>
+      </c>
+      <c r="K8" s="30" t="n">
+        <v>-0.009495308713694195</v>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N8" s="31" t="n">
+        <v>0.0252111013973157</v>
+      </c>
+      <c r="O8" s="31" t="n">
+        <v>0.0893254935760782</v>
+      </c>
+      <c r="P8" s="31" t="n">
+        <v>0.1615366145477368</v>
+      </c>
+      <c r="Q8" s="31" t="n">
+        <v>0.1987178178793453</v>
+      </c>
+      <c r="R8" s="31" t="n">
+        <v>0.1870045519996365</v>
+      </c>
+      <c r="S8" s="31" t="n">
+        <v>0.143542087981395</v>
+      </c>
+      <c r="T8" s="31" t="n">
+        <v>0.0935807690280003</v>
+      </c>
+      <c r="U8" s="31" t="n">
+        <v>0.05327880286863997</v>
+      </c>
+      <c r="V8" s="31" t="n">
+        <v>0.02703267799772081</v>
+      </c>
+      <c r="W8" s="28" t="n">
+        <v>0.8854634050266061</v>
+      </c>
+      <c r="X8" s="28" t="n">
+        <v>0.7239267904788693</v>
+      </c>
+      <c r="Y8" s="28" t="n">
+        <v>0.5252089725995239</v>
+      </c>
+      <c r="Z8" s="28" t="n">
+        <v>0.3382044205998874</v>
+      </c>
+      <c r="AA8" s="28" t="n">
+        <v>0.1946623326184924</v>
+      </c>
+      <c r="AB8" s="28" t="n">
+        <v>0.1010815635904921</v>
+      </c>
+      <c r="AC8" s="29" t="n">
+        <v>1.129352149759314</v>
+      </c>
+      <c r="AD8" s="29" t="n">
+        <v>1.381355149653339</v>
+      </c>
+      <c r="AE8" s="29" t="n">
+        <v>1.904004029197171</v>
+      </c>
+      <c r="AF8" s="29" t="n">
+        <v>2.956791629826298</v>
+      </c>
+      <c r="AG8" s="29" t="n">
+        <v>5.137100673502371</v>
+      </c>
+      <c r="AH8" s="29" t="n">
+        <v>9.893000904212974</v>
+      </c>
+      <c r="AI8" s="29" t="n">
+        <v>8.730834020622787</v>
+      </c>
+      <c r="AJ8" s="29" t="n">
+        <v>3.622227603086057</v>
+      </c>
+      <c r="AK8" s="29" t="n">
+        <v>2.106189759893085</v>
+      </c>
+      <c r="AL8" s="29" t="n">
+        <v>1.511040616056176</v>
+      </c>
+      <c r="AM8" s="29" t="n">
+        <v>1.24171517178803</v>
+      </c>
+      <c r="AN8" s="29" t="n">
+        <v>1.112447981369962</v>
+      </c>
+      <c r="AO8" s="27" t="n"/>
+      <c r="AP8" s="27" t="n"/>
+      <c r="AQ8" s="27" t="n"/>
+      <c r="AR8" s="27" t="n"/>
+      <c r="AS8" s="27" t="n"/>
+      <c r="AT8" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU8" s="32">
+        <f>IFERROR(IF($AQ8="","",INDEX($W8:$AB8,$AQ8-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV8" s="32">
+        <f>IF($AR8="","",IF($AS8="",1/$AR8,(1/$AR8)/((1/$AR8)+(1/$AS8))))</f>
+        <v/>
+      </c>
+      <c r="AW8" s="32">
+        <f>IF(OR($AU8="",$AV8=""),"",$AU8-$AV8)</f>
+        <v/>
+      </c>
+      <c r="AX8" s="33">
+        <f>IF($AW8="","",IF($AP8="","units?",IF(ISNUMBER(SEARCH("yellow",$AP8)),IF($AW8&gt;=0.05,"OVER",IF($AW8&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY8" s="34">
+        <f>IF(OR($AX8="",$AX8="skip",$AX8="units?",$AX8="UNITS?"),"",IF($AX8="OVER",$AT8*($AU8*$AR8-1),$AT8*((1-$AU8)*$AS8-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ8" s="27" t="n"/>
+      <c r="BA8" s="33">
+        <f>IF(OR($AX8="",$AX8="skip",$AX8="units?",$AX8="UNITS?",$AZ8="",$AQ8=""),"",IF($AX8="OVER",IF($AZ8&gt;$AQ8,"WON","LOST"),IF($AZ8&lt;$AQ8,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB8" s="34">
+        <f>IF($BA8="","",IF($BA8="WON",IF($AX8="OVER",$AT8*($AR8-1),$AT8*($AS8-1)),-$AT8))</f>
+        <v/>
+      </c>
+      <c r="BC8" s="34">
+        <f>IF(COUNT($BB$2:$BB8)=0,"",SUM($BB$2:$BB8))</f>
+        <v/>
+      </c>
+      <c r="BD8" s="27" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J9" s="29" t="n">
+        <v>4.086179518723705</v>
+      </c>
+      <c r="K9" s="30" t="n">
+        <v>0.05812913157032584</v>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N9" s="31" t="n">
+        <v>0.01980617743511015</v>
+      </c>
+      <c r="O9" s="31" t="n">
+        <v>0.07459100072827692</v>
+      </c>
+      <c r="P9" s="31" t="n">
+        <v>0.1433785383835565</v>
+      </c>
+      <c r="Q9" s="31" t="n">
+        <v>0.187478791108704</v>
+      </c>
+      <c r="R9" s="31" t="n">
+        <v>0.1875295346446647</v>
+      </c>
+      <c r="S9" s="31" t="n">
+        <v>0.1530026384062809</v>
+      </c>
+      <c r="T9" s="31" t="n">
+        <v>0.1060250371715355</v>
+      </c>
+      <c r="U9" s="31" t="n">
+        <v>0.06416208148731388</v>
+      </c>
+      <c r="V9" s="31" t="n">
+        <v>0.03460311695644641</v>
+      </c>
+      <c r="W9" s="28" t="n">
+        <v>0.9056028218366129</v>
+      </c>
+      <c r="X9" s="28" t="n">
+        <v>0.7622242834530565</v>
+      </c>
+      <c r="Y9" s="28" t="n">
+        <v>0.5747454923443525</v>
+      </c>
+      <c r="Z9" s="28" t="n">
+        <v>0.3872159576996879</v>
+      </c>
+      <c r="AA9" s="28" t="n">
+        <v>0.2342133192934069</v>
+      </c>
+      <c r="AB9" s="28" t="n">
+        <v>0.1281882821218715</v>
+      </c>
+      <c r="AC9" s="29" t="n">
+        <v>1.104236841899349</v>
+      </c>
+      <c r="AD9" s="29" t="n">
+        <v>1.311949804944239</v>
+      </c>
+      <c r="AE9" s="29" t="n">
+        <v>1.739900553062295</v>
+      </c>
+      <c r="AF9" s="29" t="n">
+        <v>2.582538193778593</v>
+      </c>
+      <c r="AG9" s="29" t="n">
+        <v>4.269612005913576</v>
+      </c>
+      <c r="AH9" s="29" t="n">
+        <v>7.801025050396396</v>
+      </c>
+      <c r="AI9" s="29" t="n">
+        <v>10.59353700456122</v>
+      </c>
+      <c r="AJ9" s="29" t="n">
+        <v>4.205643934218036</v>
+      </c>
+      <c r="AK9" s="29" t="n">
+        <v>2.351532980832636</v>
+      </c>
+      <c r="AL9" s="29" t="n">
+        <v>1.631896281512373</v>
+      </c>
+      <c r="AM9" s="29" t="n">
+        <v>1.305846687066035</v>
+      </c>
+      <c r="AN9" s="29" t="n">
+        <v>1.147036658825674</v>
+      </c>
+      <c r="AO9" s="27" t="n"/>
+      <c r="AP9" s="27" t="n"/>
+      <c r="AQ9" s="27" t="n"/>
+      <c r="AR9" s="27" t="n"/>
+      <c r="AS9" s="27" t="n"/>
+      <c r="AT9" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU9" s="32">
+        <f>IFERROR(IF($AQ9="","",INDEX($W9:$AB9,$AQ9-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV9" s="32">
+        <f>IF($AR9="","",IF($AS9="",1/$AR9,(1/$AR9)/((1/$AR9)+(1/$AS9))))</f>
+        <v/>
+      </c>
+      <c r="AW9" s="32">
+        <f>IF(OR($AU9="",$AV9=""),"",$AU9-$AV9)</f>
+        <v/>
+      </c>
+      <c r="AX9" s="33">
+        <f>IF($AW9="","",IF($AP9="","units?",IF(ISNUMBER(SEARCH("yellow",$AP9)),IF($AW9&gt;=0.05,"OVER",IF($AW9&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY9" s="34">
+        <f>IF(OR($AX9="",$AX9="skip",$AX9="units?",$AX9="UNITS?"),"",IF($AX9="OVER",$AT9*($AU9*$AR9-1),$AT9*((1-$AU9)*$AS9-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ9" s="27" t="n"/>
+      <c r="BA9" s="33">
+        <f>IF(OR($AX9="",$AX9="skip",$AX9="units?",$AX9="UNITS?",$AZ9="",$AQ9=""),"",IF($AX9="OVER",IF($AZ9&gt;$AQ9,"WON","LOST"),IF($AZ9&lt;$AQ9,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB9" s="34">
+        <f>IF($BA9="","",IF($BA9="WON",IF($AX9="OVER",$AT9*($AR9-1),$AT9*($AS9-1)),-$AT9))</f>
+        <v/>
+      </c>
+      <c r="BC9" s="34">
+        <f>IF(COUNT($BB$2:$BB9)=0,"",SUM($BB$2:$BB9))</f>
+        <v/>
+      </c>
+      <c r="BD9" s="27" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>Grimsby</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>Shrewsbury</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J10" s="29" t="n">
+        <v>3.856340505969337</v>
+      </c>
+      <c r="K10" s="30" t="n">
+        <v>-0.001388408922540774</v>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N10" s="31" t="n">
+        <v>0.02449071948701239</v>
+      </c>
+      <c r="O10" s="31" t="n">
+        <v>0.08743056798250627</v>
+      </c>
+      <c r="P10" s="31" t="n">
+        <v>0.1593077860561559</v>
+      </c>
+      <c r="Q10" s="31" t="n">
+        <v>0.1974608422653005</v>
+      </c>
+      <c r="R10" s="31" t="n">
+        <v>0.1872295976338018</v>
+      </c>
+      <c r="S10" s="31" t="n">
+        <v>0.1448037254532824</v>
+      </c>
+      <c r="T10" s="31" t="n">
+        <v>0.09511855327734098</v>
+      </c>
+      <c r="U10" s="31" t="n">
+        <v>0.05456463251545174</v>
+      </c>
+      <c r="V10" s="31" t="n">
+        <v>0.02789484792900001</v>
+      </c>
+      <c r="W10" s="28" t="n">
+        <v>0.8880787125304813</v>
+      </c>
+      <c r="X10" s="28" t="n">
+        <v>0.7287709264743254</v>
+      </c>
+      <c r="Y10" s="28" t="n">
+        <v>0.5313100842090249</v>
+      </c>
+      <c r="Z10" s="28" t="n">
+        <v>0.3440804865752231</v>
+      </c>
+      <c r="AA10" s="28" t="n">
+        <v>0.1992767611219406</v>
+      </c>
+      <c r="AB10" s="28" t="n">
+        <v>0.1041582078445996</v>
+      </c>
+      <c r="AC10" s="29" t="n">
+        <v>1.126026314886674</v>
+      </c>
+      <c r="AD10" s="29" t="n">
+        <v>1.372173290224181</v>
+      </c>
+      <c r="AE10" s="29" t="n">
+        <v>1.882140071722384</v>
+      </c>
+      <c r="AF10" s="29" t="n">
+        <v>2.906296750372037</v>
+      </c>
+      <c r="AG10" s="29" t="n">
+        <v>5.018146593561324</v>
+      </c>
+      <c r="AH10" s="29" t="n">
+        <v>9.60077962835118</v>
+      </c>
+      <c r="AI10" s="29" t="n">
+        <v>8.934850756361662</v>
+      </c>
+      <c r="AJ10" s="29" t="n">
+        <v>3.686920384312487</v>
+      </c>
+      <c r="AK10" s="29" t="n">
+        <v>2.133606818299835</v>
+      </c>
+      <c r="AL10" s="29" t="n">
+        <v>1.524577298788784</v>
+      </c>
+      <c r="AM10" s="29" t="n">
+        <v>1.248870959960097</v>
+      </c>
+      <c r="AN10" s="29" t="n">
+        <v>1.11626852950675</v>
+      </c>
+      <c r="AO10" s="27" t="n"/>
+      <c r="AP10" s="27" t="n"/>
+      <c r="AQ10" s="27" t="n"/>
+      <c r="AR10" s="27" t="n"/>
+      <c r="AS10" s="27" t="n"/>
+      <c r="AT10" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU10" s="32">
+        <f>IFERROR(IF($AQ10="","",INDEX($W10:$AB10,$AQ10-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV10" s="32">
+        <f>IF($AR10="","",IF($AS10="",1/$AR10,(1/$AR10)/((1/$AR10)+(1/$AS10))))</f>
+        <v/>
+      </c>
+      <c r="AW10" s="32">
+        <f>IF(OR($AU10="",$AV10=""),"",$AU10-$AV10)</f>
+        <v/>
+      </c>
+      <c r="AX10" s="33">
+        <f>IF($AW10="","",IF($AP10="","units?",IF(ISNUMBER(SEARCH("yellow",$AP10)),IF($AW10&gt;=0.05,"OVER",IF($AW10&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY10" s="34">
+        <f>IF(OR($AX10="",$AX10="skip",$AX10="units?",$AX10="UNITS?"),"",IF($AX10="OVER",$AT10*($AU10*$AR10-1),$AT10*((1-$AU10)*$AS10-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ10" s="27" t="n"/>
+      <c r="BA10" s="33">
+        <f>IF(OR($AX10="",$AX10="skip",$AX10="units?",$AX10="UNITS?",$AZ10="",$AQ10=""),"",IF($AX10="OVER",IF($AZ10&gt;$AQ10,"WON","LOST"),IF($AZ10&lt;$AQ10,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB10" s="34">
+        <f>IF($BA10="","",IF($BA10="WON",IF($AX10="OVER",$AT10*($AR10-1),$AT10*($AS10-1)),-$AT10))</f>
+        <v/>
+      </c>
+      <c r="BC10" s="34">
+        <f>IF(COUNT($BB$2:$BB10)=0,"",SUM($BB$2:$BB10))</f>
+        <v/>
+      </c>
+      <c r="BD10" s="27" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>Rochdale</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Swindon</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J11" s="29" t="n">
+        <v>3.303285143858103</v>
+      </c>
+      <c r="K11" s="30" t="n">
+        <v>-0.1446038470450092</v>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N11" s="31" t="n">
+        <v>0.04097747881596749</v>
+      </c>
+      <c r="O11" s="31" t="n">
+        <v>0.1266566689782702</v>
+      </c>
+      <c r="P11" s="31" t="n">
+        <v>0.1998125840724436</v>
+      </c>
+      <c r="Q11" s="31" t="n">
+        <v>0.2144311581412161</v>
+      </c>
+      <c r="R11" s="31" t="n">
+        <v>0.1760364013716943</v>
+      </c>
+      <c r="S11" s="31" t="n">
+        <v>0.1178769214898324</v>
+      </c>
+      <c r="T11" s="31" t="n">
+        <v>0.0670402087364015</v>
+      </c>
+      <c r="U11" s="31" t="n">
+        <v>0.03329679468494827</v>
+      </c>
+      <c r="V11" s="31" t="n">
+        <v>0.01473792233451729</v>
+      </c>
+      <c r="W11" s="28" t="n">
+        <v>0.8323658522057623</v>
+      </c>
+      <c r="X11" s="28" t="n">
+        <v>0.6325532681333186</v>
+      </c>
+      <c r="Y11" s="28" t="n">
+        <v>0.4181221099921025</v>
+      </c>
+      <c r="Z11" s="28" t="n">
+        <v>0.2420857086204082</v>
+      </c>
+      <c r="AA11" s="28" t="n">
+        <v>0.1242087871305758</v>
+      </c>
+      <c r="AB11" s="28" t="n">
+        <v>0.05716857839417433</v>
+      </c>
+      <c r="AC11" s="29" t="n">
+        <v>1.201394792145796</v>
+      </c>
+      <c r="AD11" s="29" t="n">
+        <v>1.580894527588208</v>
+      </c>
+      <c r="AE11" s="29" t="n">
+        <v>2.391645828102436</v>
+      </c>
+      <c r="AF11" s="29" t="n">
+        <v>4.130768419576579</v>
+      </c>
+      <c r="AG11" s="29" t="n">
+        <v>8.050960186486156</v>
+      </c>
+      <c r="AH11" s="29" t="n">
+        <v>17.492126410859</v>
+      </c>
+      <c r="AI11" s="29" t="n">
+        <v>5.965371692809562</v>
+      </c>
+      <c r="AJ11" s="29" t="n">
+        <v>2.721482906977723</v>
+      </c>
+      <c r="AK11" s="29" t="n">
+        <v>1.71857363404275</v>
+      </c>
+      <c r="AL11" s="29" t="n">
+        <v>1.31941040217061</v>
+      </c>
+      <c r="AM11" s="29" t="n">
+        <v>1.141824655586142</v>
+      </c>
+      <c r="AN11" s="29" t="n">
+        <v>1.060634994850729</v>
+      </c>
+      <c r="AO11" s="27" t="n"/>
+      <c r="AP11" s="27" t="n"/>
+      <c r="AQ11" s="27" t="n"/>
+      <c r="AR11" s="27" t="n"/>
+      <c r="AS11" s="27" t="n"/>
+      <c r="AT11" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU11" s="32">
+        <f>IFERROR(IF($AQ11="","",INDEX($W11:$AB11,$AQ11-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV11" s="32">
+        <f>IF($AR11="","",IF($AS11="",1/$AR11,(1/$AR11)/((1/$AR11)+(1/$AS11))))</f>
+        <v/>
+      </c>
+      <c r="AW11" s="32">
+        <f>IF(OR($AU11="",$AV11=""),"",$AU11-$AV11)</f>
+        <v/>
+      </c>
+      <c r="AX11" s="33">
+        <f>IF($AW11="","",IF($AP11="","units?",IF(ISNUMBER(SEARCH("yellow",$AP11)),IF($AW11&gt;=0.05,"OVER",IF($AW11&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY11" s="34">
+        <f>IF(OR($AX11="",$AX11="skip",$AX11="units?",$AX11="UNITS?"),"",IF($AX11="OVER",$AT11*($AU11*$AR11-1),$AT11*((1-$AU11)*$AS11-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ11" s="27" t="n"/>
+      <c r="BA11" s="33">
+        <f>IF(OR($AX11="",$AX11="skip",$AX11="units?",$AX11="UNITS?",$AZ11="",$AQ11=""),"",IF($AX11="OVER",IF($AZ11&gt;$AQ11,"WON","LOST"),IF($AZ11&lt;$AQ11,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB11" s="34">
+        <f>IF($BA11="","",IF($BA11="WON",IF($AX11="OVER",$AT11*($AR11-1),$AT11*($AS11-1)),-$AT11))</f>
+        <v/>
+      </c>
+      <c r="BC11" s="34">
+        <f>IF(COUNT($BB$2:$BB11)=0,"",SUM($BB$2:$BB11))</f>
+        <v/>
+      </c>
+      <c r="BD11" s="27" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Salford</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J12" s="29" t="n">
+        <v>3.824203463261887</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>-0.009710397943202942</v>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N12" s="31" t="n">
+        <v>0.02523050614990685</v>
+      </c>
+      <c r="O12" s="31" t="n">
+        <v>0.08937626504343038</v>
+      </c>
+      <c r="P12" s="31" t="n">
+        <v>0.1615959185326466</v>
+      </c>
+      <c r="Q12" s="31" t="n">
+        <v>0.1987507854614812</v>
+      </c>
+      <c r="R12" s="31" t="n">
+        <v>0.186997954357881</v>
+      </c>
+      <c r="S12" s="31" t="n">
+        <v>0.1435081514281418</v>
+      </c>
+      <c r="T12" s="31" t="n">
+        <v>0.09353982523960999</v>
+      </c>
+      <c r="U12" s="31" t="n">
+        <v>0.05324477986214632</v>
+      </c>
+      <c r="V12" s="31" t="n">
+        <v>0.02700998123674166</v>
+      </c>
+      <c r="W12" s="28" t="n">
+        <v>0.8853932288066628</v>
+      </c>
+      <c r="X12" s="28" t="n">
+        <v>0.7237973102740162</v>
+      </c>
+      <c r="Y12" s="28" t="n">
+        <v>0.525046524812535</v>
+      </c>
+      <c r="Z12" s="28" t="n">
+        <v>0.338048570454654</v>
+      </c>
+      <c r="AA12" s="28" t="n">
+        <v>0.1945404190265122</v>
+      </c>
+      <c r="AB12" s="28" t="n">
+        <v>0.1010005937869022</v>
+      </c>
+      <c r="AC12" s="29" t="n">
+        <v>1.129441662150279</v>
+      </c>
+      <c r="AD12" s="29" t="n">
+        <v>1.381602260474578</v>
+      </c>
+      <c r="AE12" s="29" t="n">
+        <v>1.904593122213397</v>
+      </c>
+      <c r="AF12" s="29" t="n">
+        <v>2.958154796084667</v>
+      </c>
+      <c r="AG12" s="29" t="n">
+        <v>5.14031996540379</v>
+      </c>
+      <c r="AH12" s="29" t="n">
+        <v>9.900931890656672</v>
+      </c>
+      <c r="AI12" s="29" t="n">
+        <v>8.725487940961523</v>
+      </c>
+      <c r="AJ12" s="29" t="n">
+        <v>3.620529550208521</v>
+      </c>
+      <c r="AK12" s="29" t="n">
+        <v>2.105469382249068</v>
+      </c>
+      <c r="AL12" s="29" t="n">
+        <v>1.51068485596721</v>
+      </c>
+      <c r="AM12" s="29" t="n">
+        <v>1.24152722696698</v>
+      </c>
+      <c r="AN12" s="29" t="n">
+        <v>1.11234778698281</v>
+      </c>
+      <c r="AO12" s="27" t="n"/>
+      <c r="AP12" s="27" t="n"/>
+      <c r="AQ12" s="27" t="n"/>
+      <c r="AR12" s="27" t="n"/>
+      <c r="AS12" s="27" t="n"/>
+      <c r="AT12" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU12" s="32">
+        <f>IFERROR(IF($AQ12="","",INDEX($W12:$AB12,$AQ12-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV12" s="32">
+        <f>IF($AR12="","",IF($AS12="",1/$AR12,(1/$AR12)/((1/$AR12)+(1/$AS12))))</f>
+        <v/>
+      </c>
+      <c r="AW12" s="32">
+        <f>IF(OR($AU12="",$AV12=""),"",$AU12-$AV12)</f>
+        <v/>
+      </c>
+      <c r="AX12" s="33">
+        <f>IF($AW12="","",IF($AP12="","units?",IF(ISNUMBER(SEARCH("yellow",$AP12)),IF($AW12&gt;=0.05,"OVER",IF($AW12&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY12" s="34">
+        <f>IF(OR($AX12="",$AX12="skip",$AX12="units?",$AX12="UNITS?"),"",IF($AX12="OVER",$AT12*($AU12*$AR12-1),$AT12*((1-$AU12)*$AS12-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ12" s="27" t="n"/>
+      <c r="BA12" s="33">
+        <f>IF(OR($AX12="",$AX12="skip",$AX12="units?",$AX12="UNITS?",$AZ12="",$AQ12=""),"",IF($AX12="OVER",IF($AZ12&gt;$AQ12,"WON","LOST"),IF($AZ12&lt;$AQ12,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB12" s="34">
+        <f>IF($BA12="","",IF($BA12="WON",IF($AX12="OVER",$AT12*($AR12-1),$AT12*($AS12-1)),-$AT12))</f>
+        <v/>
+      </c>
+      <c r="BC12" s="34">
+        <f>IF(COUNT($BB$2:$BB12)=0,"",SUM($BB$2:$BB12))</f>
+        <v/>
+      </c>
+      <c r="BD12" s="27" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>bets placed</t>
+        </is>
+      </c>
+      <c r="E15" s="37">
+        <f>COUNTIF($AX$2:$AX12,"OVER")+COUNTIF($AX$2:$AX12,"UNDER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>bets won</t>
+        </is>
+      </c>
+      <c r="E16" s="37">
+        <f>COUNTIF($BA$2:$BA12,"WON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t>total staked</t>
+        </is>
+      </c>
+      <c r="E17" s="38">
+        <f>SUMPRODUCT(($BA$2:$BA12&lt;&gt;"")*$AT$2:$AT12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>profit / loss EUR</t>
+        </is>
+      </c>
+      <c r="E18" s="38">
+        <f>IF(COUNT($BB$2:$BB12)=0,"",SUM($BB$2:$BB12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>return on stake</t>
+        </is>
+      </c>
+      <c r="E19" s="39">
+        <f>IF($E17=0,"",$E18/$E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>HOW TO USE THIS SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="inlineStr">
+        <is>
+          <t>1. Fill the yellow columns only. Everything green is computed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="inlineStr">
+        <is>
+          <t>2. 'Settles on' must say what the market actually pays out on. Write 'yellow cards' only if the bookmaker settles on yellows alone. If it says total cards or booking points, BET? shows UNITS? and gives no verdict -- on purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="45" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The model predicts yellows. Counting a red as two cards adds about 5-6 percentage points at every line, always upward, which is larger than the 5% edge threshold. Priced against the wrong market the model shows an OVER edge on nearly every game, and that looks identical to finding an edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="45" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The market to look for is 'Yellow Cards', as in the Chelsea screenshot -- not 'Cards' and not 'Booking Points'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="45" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="inlineStr">
+        <is>
+          <t>3. Record BOTH sides of the price. With one side only, the de-vig cannot run and the implied probability is overstated by the whole margin, which invents edge that is not there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="45" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="45" t="inlineStr">
+        <is>
+          <t>4. Record the price when you see it, before kick-off. A price looked up afterwards is not one you could have taken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="45" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="45" t="inlineStr">
+        <is>
+          <t>5. Stake is EUR 100 a bet. Change the column if you want; the P/L follows it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="45" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="44" t="inlineStr">
+        <is>
+          <t>WHAT THIS SHEET IS AND IS NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="45" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="45" t="inlineStr">
+        <is>
+          <t>11 fixtures. A sample this size tells you nothing about whether the model beats a bookmaker -- a verdict on profitability needs thousands of bets. Treat a single week as practice for the workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="45" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="45" t="inlineStr">
+        <is>
+          <t>The referee is 48% of the model's value. If the Referee column says 'not known', the EFL has not published appointments yet (they come one to three days ahead) and these are the weaker version of the model. Re-run run_week_sheet.py for the same dates once they are out and every unplayed row updates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="45" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="45" t="inlineStr">
+        <is>
+          <t>Model fingerprint d30beac40c73a847, frozen for the season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="45" t="inlineStr">
+        <is>
+          <t>Scoring these results against the model is a holdout look.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/forward_test_2026-09-18.xlsx
+++ b/forward_test_2026-09-18.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Read me" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Week 26 Sep" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Week 3 Oct" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Week 9-12 Oct" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -183,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -252,6 +253,12 @@
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -12442,134 +12449,134 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="42" t="inlineStr">
+      <c r="A25" s="44" t="inlineStr">
         <is>
           <t>HOW TO USE THIS SHEET</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr"/>
+      <c r="A26" s="45" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A27" s="45" t="inlineStr">
         <is>
           <t>1. Fill the yellow columns only. Everything green is computed.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="43" t="inlineStr"/>
+      <c r="A28" s="45" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="43" t="inlineStr">
+      <c r="A29" s="45" t="inlineStr">
         <is>
           <t>2. 'Settles on' must say what the market actually pays out on. Write 'yellow cards' only if the bookmaker settles on yellows alone. If it says total cards or booking points, BET? shows UNITS? and gives no verdict -- on purpose.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="43" t="inlineStr"/>
+      <c r="A30" s="45" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="43" t="inlineStr">
+      <c r="A31" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">   The model predicts yellows. Counting a red as two cards adds about 5-6 percentage points at every line, always upward, which is larger than the 5% edge threshold. Priced against the wrong market the model shows an OVER edge on nearly every game, and that looks identical to finding an edge.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="43" t="inlineStr"/>
+      <c r="A32" s="45" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">   The market to look for is 'Yellow Cards', as in the Chelsea screenshot -- not 'Cards' and not 'Booking Points'.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="43" t="inlineStr"/>
+      <c r="A34" s="45" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="43" t="inlineStr">
+      <c r="A35" s="45" t="inlineStr">
         <is>
           <t>3. Record BOTH sides of the price. With one side only, the de-vig cannot run and the implied probability is overstated by the whole margin, which invents edge that is not there.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="43" t="inlineStr"/>
+      <c r="A36" s="45" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="43" t="inlineStr">
+      <c r="A37" s="45" t="inlineStr">
         <is>
           <t>4. Record the price when you see it, before kick-off. A price looked up afterwards is not one you could have taken.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="43" t="inlineStr"/>
+      <c r="A38" s="45" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="43" t="inlineStr">
+      <c r="A39" s="45" t="inlineStr">
         <is>
           <t>5. Stake is EUR 100 a bet. Change the column if you want; the P/L follows it.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="43" t="inlineStr"/>
+      <c r="A40" s="45" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="42" t="inlineStr">
+      <c r="A41" s="44" t="inlineStr">
         <is>
           <t>WHAT THIS WEEK IS AND IS NOT</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="43" t="inlineStr"/>
+      <c r="A42" s="45" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="43" t="inlineStr">
+      <c r="A43" s="45" t="inlineStr">
         <is>
           <t>Fourteen fixtures, League One and League Two only -- 26 September starts a two-weekend international break, and seven more EFL matches are postponed. No Premier League or Championship football until 10 October.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="43" t="inlineStr"/>
+      <c r="A44" s="45" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="43" t="inlineStr">
+      <c r="A45" s="45" t="inlineStr">
         <is>
           <t>Fourteen matches is far too few to tell you anything about whether the model beats a bookmaker. Treat this as practice for the workflow. A verdict on profitability needs thousands of bets.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="43" t="inlineStr"/>
+      <c r="A46" s="45" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="43" t="inlineStr">
+      <c r="A47" s="45" t="inlineStr">
         <is>
           <t>Referees are not in yet. The EFL publishes appointments one to three days ahead, and the referee is 48% of the model's value -- so these numbers are the weaker version of the model. Re-run cards/run_week_sheet.py once the appointments are out.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="43" t="inlineStr"/>
+      <c r="A48" s="45" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="43" t="inlineStr">
+      <c r="A49" s="45" t="inlineStr">
         <is>
           <t>Model fingerprint d30beac40c73a847, frozen for the season.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="43" t="inlineStr">
+      <c r="A50" s="45" t="inlineStr">
         <is>
           <t>Scoring these results against the model is a holdout look.</t>
         </is>
@@ -15054,4 +15061,8640 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BD80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="7" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
+    <col width="9" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="11" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="8" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="9" customWidth="1" min="51" max="51"/>
+    <col width="14" customWidth="1" min="52" max="52"/>
+    <col width="8" customWidth="1" min="53" max="53"/>
+    <col width="9" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="34" customWidth="1" min="56" max="56"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>Div</t>
+        </is>
+      </c>
+      <c r="C1" s="24" t="inlineStr">
+        <is>
+          <t>League</t>
+        </is>
+      </c>
+      <c r="D1" s="24" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="E1" s="24" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F1" s="25" t="inlineStr">
+        <is>
+          <t>Referee</t>
+        </is>
+      </c>
+      <c r="G1" s="24" t="inlineStr">
+        <is>
+          <t>Ref matches</t>
+        </is>
+      </c>
+      <c r="H1" s="24" t="inlineStr">
+        <is>
+          <t>Ref vs avg</t>
+        </is>
+      </c>
+      <c r="I1" s="24" t="inlineStr">
+        <is>
+          <t>League avg</t>
+        </is>
+      </c>
+      <c r="J1" s="24" t="inlineStr">
+        <is>
+          <t>Model expects</t>
+        </is>
+      </c>
+      <c r="K1" s="24" t="inlineStr">
+        <is>
+          <t>vs league avg</t>
+        </is>
+      </c>
+      <c r="L1" s="24" t="inlineStr">
+        <is>
+          <t>Most likely</t>
+        </is>
+      </c>
+      <c r="M1" s="24" t="inlineStr">
+        <is>
+          <t>80% range</t>
+        </is>
+      </c>
+      <c r="N1" s="24" t="inlineStr">
+        <is>
+          <t>P(0)</t>
+        </is>
+      </c>
+      <c r="O1" s="24" t="inlineStr">
+        <is>
+          <t>P(1)</t>
+        </is>
+      </c>
+      <c r="P1" s="24" t="inlineStr">
+        <is>
+          <t>P(2)</t>
+        </is>
+      </c>
+      <c r="Q1" s="24" t="inlineStr">
+        <is>
+          <t>P(3)</t>
+        </is>
+      </c>
+      <c r="R1" s="24" t="inlineStr">
+        <is>
+          <t>P(4)</t>
+        </is>
+      </c>
+      <c r="S1" s="24" t="inlineStr">
+        <is>
+          <t>P(5)</t>
+        </is>
+      </c>
+      <c r="T1" s="24" t="inlineStr">
+        <is>
+          <t>P(6)</t>
+        </is>
+      </c>
+      <c r="U1" s="24" t="inlineStr">
+        <is>
+          <t>P(7)</t>
+        </is>
+      </c>
+      <c r="V1" s="24" t="inlineStr">
+        <is>
+          <t>P(8)</t>
+        </is>
+      </c>
+      <c r="W1" s="24" t="inlineStr">
+        <is>
+          <t>P(o1.5)</t>
+        </is>
+      </c>
+      <c r="X1" s="24" t="inlineStr">
+        <is>
+          <t>P(o2.5)</t>
+        </is>
+      </c>
+      <c r="Y1" s="24" t="inlineStr">
+        <is>
+          <t>P(o3.5)</t>
+        </is>
+      </c>
+      <c r="Z1" s="24" t="inlineStr">
+        <is>
+          <t>P(o4.5)</t>
+        </is>
+      </c>
+      <c r="AA1" s="24" t="inlineStr">
+        <is>
+          <t>P(o5.5)</t>
+        </is>
+      </c>
+      <c r="AB1" s="24" t="inlineStr">
+        <is>
+          <t>P(o6.5)</t>
+        </is>
+      </c>
+      <c r="AC1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 1.5</t>
+        </is>
+      </c>
+      <c r="AD1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 2.5</t>
+        </is>
+      </c>
+      <c r="AE1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 3.5</t>
+        </is>
+      </c>
+      <c r="AF1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 4.5</t>
+        </is>
+      </c>
+      <c r="AG1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 5.5</t>
+        </is>
+      </c>
+      <c r="AH1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 6.5</t>
+        </is>
+      </c>
+      <c r="AI1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 1.5</t>
+        </is>
+      </c>
+      <c r="AJ1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 2.5</t>
+        </is>
+      </c>
+      <c r="AK1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 3.5</t>
+        </is>
+      </c>
+      <c r="AL1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 4.5</t>
+        </is>
+      </c>
+      <c r="AM1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 5.5</t>
+        </is>
+      </c>
+      <c r="AN1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 6.5</t>
+        </is>
+      </c>
+      <c r="AO1" s="25" t="inlineStr">
+        <is>
+          <t>Bookmaker</t>
+        </is>
+      </c>
+      <c r="AP1" s="25" t="inlineStr">
+        <is>
+          <t>Settles on</t>
+        </is>
+      </c>
+      <c r="AQ1" s="25" t="inlineStr">
+        <is>
+          <t>Card line</t>
+        </is>
+      </c>
+      <c r="AR1" s="25" t="inlineStr">
+        <is>
+          <t>Over price</t>
+        </is>
+      </c>
+      <c r="AS1" s="25" t="inlineStr">
+        <is>
+          <t>Under price</t>
+        </is>
+      </c>
+      <c r="AT1" s="25" t="inlineStr">
+        <is>
+          <t>Stake EUR</t>
+        </is>
+      </c>
+      <c r="AU1" s="24" t="inlineStr">
+        <is>
+          <t>Model P(over)</t>
+        </is>
+      </c>
+      <c r="AV1" s="24" t="inlineStr">
+        <is>
+          <t>Implied P(over)</t>
+        </is>
+      </c>
+      <c r="AW1" s="24" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="AX1" s="24" t="inlineStr">
+        <is>
+          <t>BET?</t>
+        </is>
+      </c>
+      <c r="AY1" s="24" t="inlineStr">
+        <is>
+          <t>EV EUR</t>
+        </is>
+      </c>
+      <c r="AZ1" s="25" t="inlineStr">
+        <is>
+          <t>ACTUAL yellows</t>
+        </is>
+      </c>
+      <c r="BA1" s="24" t="inlineStr">
+        <is>
+          <t>Won?</t>
+        </is>
+      </c>
+      <c r="BB1" s="24" t="inlineStr">
+        <is>
+          <t>P/L EUR</t>
+        </is>
+      </c>
+      <c r="BC1" s="24" t="inlineStr">
+        <is>
+          <t>Running P/L</t>
+        </is>
+      </c>
+      <c r="BD1" s="25" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D2" s="26" t="inlineStr">
+        <is>
+          <t>West Ham</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="inlineStr">
+        <is>
+          <t>QPR</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G2" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="28" t="n"/>
+      <c r="I2" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J2" s="29" t="n">
+        <v>3.680958484454213</v>
+      </c>
+      <c r="K2" s="30" t="n">
+        <v>-0.0313267146173124</v>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N2" s="31" t="n">
+        <v>0.02881586815811756</v>
+      </c>
+      <c r="O2" s="31" t="n">
+        <v>0.09852542784242602</v>
+      </c>
+      <c r="P2" s="31" t="n">
+        <v>0.1719399899897411</v>
+      </c>
+      <c r="Q2" s="31" t="n">
+        <v>0.2041153873002563</v>
+      </c>
+      <c r="R2" s="31" t="n">
+        <v>0.1853634608696533</v>
+      </c>
+      <c r="S2" s="31" t="n">
+        <v>0.1373043277285688</v>
+      </c>
+      <c r="T2" s="31" t="n">
+        <v>0.08638226595685088</v>
+      </c>
+      <c r="U2" s="31" t="n">
+        <v>0.047459751058439</v>
+      </c>
+      <c r="V2" s="31" t="n">
+        <v>0.02323769700409085</v>
+      </c>
+      <c r="W2" s="28" t="n">
+        <v>0.8726587039994564</v>
+      </c>
+      <c r="X2" s="28" t="n">
+        <v>0.7007187140097153</v>
+      </c>
+      <c r="Y2" s="28" t="n">
+        <v>0.4966033267094589</v>
+      </c>
+      <c r="Z2" s="28" t="n">
+        <v>0.3112398658398057</v>
+      </c>
+      <c r="AA2" s="28" t="n">
+        <v>0.1739355381112369</v>
+      </c>
+      <c r="AB2" s="28" t="n">
+        <v>0.08755327215438602</v>
+      </c>
+      <c r="AC2" s="29" t="n">
+        <v>1.14592336662309</v>
+      </c>
+      <c r="AD2" s="29" t="n">
+        <v>1.427106169717818</v>
+      </c>
+      <c r="AE2" s="29" t="n">
+        <v>2.013679623586285</v>
+      </c>
+      <c r="AF2" s="29" t="n">
+        <v>3.212956018027258</v>
+      </c>
+      <c r="AG2" s="29" t="n">
+        <v>5.749256367381752</v>
+      </c>
+      <c r="AH2" s="29" t="n">
+        <v>11.42161766651807</v>
+      </c>
+      <c r="AI2" s="29" t="n">
+        <v>7.852912067077844</v>
+      </c>
+      <c r="AJ2" s="29" t="n">
+        <v>3.341338221971093</v>
+      </c>
+      <c r="AK2" s="29" t="n">
+        <v>1.986504983164318</v>
+      </c>
+      <c r="AL2" s="29" t="n">
+        <v>1.451884263335451</v>
+      </c>
+      <c r="AM2" s="29" t="n">
+        <v>1.210559279736523</v>
+      </c>
+      <c r="AN2" s="29" t="n">
+        <v>1.095954393262069</v>
+      </c>
+      <c r="AO2" s="27" t="n"/>
+      <c r="AP2" s="27" t="n"/>
+      <c r="AQ2" s="27" t="n"/>
+      <c r="AR2" s="27" t="n"/>
+      <c r="AS2" s="27" t="n"/>
+      <c r="AT2" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU2" s="32">
+        <f>IFERROR(IF($AQ2="","",INDEX($W2:$AB2,$AQ2-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV2" s="32">
+        <f>IF($AR2="","",IF($AS2="",1/$AR2,(1/$AR2)/((1/$AR2)+(1/$AS2))))</f>
+        <v/>
+      </c>
+      <c r="AW2" s="32">
+        <f>IF(OR($AU2="",$AV2=""),"",$AU2-$AV2)</f>
+        <v/>
+      </c>
+      <c r="AX2" s="33">
+        <f>IF($AW2="","",IF($AP2="","units?",IF(ISNUMBER(SEARCH("yellow",$AP2)),IF($AW2&gt;=0.05,"OVER",IF($AW2&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY2" s="34">
+        <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?"),"",IF($AX2="OVER",$AT2*($AU2*$AR2-1),$AT2*((1-$AU2)*$AS2-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ2" s="27" t="n"/>
+      <c r="BA2" s="33">
+        <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?",$AZ2="",$AQ2=""),"",IF($AX2="OVER",IF($AZ2&gt;$AQ2,"WON","LOST"),IF($AZ2&lt;$AQ2,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB2" s="34">
+        <f>IF($BA2="","",IF($BA2="WON",IF($AX2="OVER",$AT2*($AR2-1),$AT2*($AS2-1)),-$AT2))</f>
+        <v/>
+      </c>
+      <c r="BC2" s="34">
+        <f>IF(COUNT($BB$2:$BB2)=0,"",SUM($BB$2:$BB2))</f>
+        <v/>
+      </c>
+      <c r="BD2" s="27" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="28" t="n"/>
+      <c r="I3" s="29" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J3" s="29" t="n">
+        <v>4.034058155850071</v>
+      </c>
+      <c r="K3" s="30" t="n">
+        <v>0.0728878074069339</v>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N3" s="31" t="n">
+        <v>0.02078134705094173</v>
+      </c>
+      <c r="O3" s="31" t="n">
+        <v>0.07734253412337665</v>
+      </c>
+      <c r="P3" s="31" t="n">
+        <v>0.146918013206273</v>
+      </c>
+      <c r="Q3" s="31" t="n">
+        <v>0.1898462296004267</v>
+      </c>
+      <c r="R3" s="31" t="n">
+        <v>0.1876629080122233</v>
+      </c>
+      <c r="S3" s="31" t="n">
+        <v>0.15130964763128</v>
+      </c>
+      <c r="T3" s="31" t="n">
+        <v>0.1036179670628352</v>
+      </c>
+      <c r="U3" s="31" t="n">
+        <v>0.06196750528759579</v>
+      </c>
+      <c r="V3" s="31" t="n">
+        <v>0.0330262848759798</v>
+      </c>
+      <c r="W3" s="28" t="n">
+        <v>0.9018761188256816</v>
+      </c>
+      <c r="X3" s="28" t="n">
+        <v>0.7549581056194086</v>
+      </c>
+      <c r="Y3" s="28" t="n">
+        <v>0.5651118760189819</v>
+      </c>
+      <c r="Z3" s="28" t="n">
+        <v>0.3774489680067585</v>
+      </c>
+      <c r="AA3" s="28" t="n">
+        <v>0.2261393203754786</v>
+      </c>
+      <c r="AB3" s="28" t="n">
+        <v>0.1225213533126434</v>
+      </c>
+      <c r="AC3" s="29" t="n">
+        <v>1.108799733273882</v>
+      </c>
+      <c r="AD3" s="29" t="n">
+        <v>1.324576811026548</v>
+      </c>
+      <c r="AE3" s="29" t="n">
+        <v>1.769561112473259</v>
+      </c>
+      <c r="AF3" s="29" t="n">
+        <v>2.649364774477524</v>
+      </c>
+      <c r="AG3" s="29" t="n">
+        <v>4.422052734303853</v>
+      </c>
+      <c r="AH3" s="29" t="n">
+        <v>8.161842592843829</v>
+      </c>
+      <c r="AI3" s="29" t="n">
+        <v>10.19119900305907</v>
+      </c>
+      <c r="AJ3" s="29" t="n">
+        <v>4.080934823523815</v>
+      </c>
+      <c r="AK3" s="29" t="n">
+        <v>2.299441959568544</v>
+      </c>
+      <c r="AL3" s="29" t="n">
+        <v>1.606294020264119</v>
+      </c>
+      <c r="AM3" s="29" t="n">
+        <v>1.292222264717212</v>
+      </c>
+      <c r="AN3" s="29" t="n">
+        <v>1.139628871625747</v>
+      </c>
+      <c r="AO3" s="27" t="n"/>
+      <c r="AP3" s="27" t="n"/>
+      <c r="AQ3" s="27" t="n"/>
+      <c r="AR3" s="27" t="n"/>
+      <c r="AS3" s="27" t="n"/>
+      <c r="AT3" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU3" s="32">
+        <f>IFERROR(IF($AQ3="","",INDEX($W3:$AB3,$AQ3-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV3" s="32">
+        <f>IF($AR3="","",IF($AS3="",1/$AR3,(1/$AR3)/((1/$AR3)+(1/$AS3))))</f>
+        <v/>
+      </c>
+      <c r="AW3" s="32">
+        <f>IF(OR($AU3="",$AV3=""),"",$AU3-$AV3)</f>
+        <v/>
+      </c>
+      <c r="AX3" s="33">
+        <f>IF($AW3="","",IF($AP3="","units?",IF(ISNUMBER(SEARCH("yellow",$AP3)),IF($AW3&gt;=0.05,"OVER",IF($AW3&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY3" s="34">
+        <f>IF(OR($AX3="",$AX3="skip",$AX3="units?",$AX3="UNITS?"),"",IF($AX3="OVER",$AT3*($AU3*$AR3-1),$AT3*((1-$AU3)*$AS3-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ3" s="27" t="n"/>
+      <c r="BA3" s="33">
+        <f>IF(OR($AX3="",$AX3="skip",$AX3="units?",$AX3="UNITS?",$AZ3="",$AQ3=""),"",IF($AX3="OVER",IF($AZ3&gt;$AQ3,"WON","LOST"),IF($AZ3&lt;$AQ3,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB3" s="34">
+        <f>IF($BA3="","",IF($BA3="WON",IF($AX3="OVER",$AT3*($AR3-1),$AT3*($AS3-1)),-$AT3))</f>
+        <v/>
+      </c>
+      <c r="BC3" s="34">
+        <f>IF(COUNT($BB$2:$BB3)=0,"",SUM($BB$2:$BB3))</f>
+        <v/>
+      </c>
+      <c r="BD3" s="27" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="28" t="n"/>
+      <c r="I4" s="29" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J4" s="29" t="n">
+        <v>4.045690424097625</v>
+      </c>
+      <c r="K4" s="30" t="n">
+        <v>0.07598149577064506</v>
+      </c>
+      <c r="L4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N4" s="31" t="n">
+        <v>0.02055954570829664</v>
+      </c>
+      <c r="O4" s="31" t="n">
+        <v>0.07672055986705283</v>
+      </c>
+      <c r="P4" s="31" t="n">
+        <v>0.1461241370599246</v>
+      </c>
+      <c r="Q4" s="31" t="n">
+        <v>0.1893225895167784</v>
+      </c>
+      <c r="R4" s="31" t="n">
+        <v>0.1876430348670571</v>
+      </c>
+      <c r="S4" s="31" t="n">
+        <v>0.1516960154344922</v>
+      </c>
+      <c r="T4" s="31" t="n">
+        <v>0.1041588479736148</v>
+      </c>
+      <c r="U4" s="31" t="n">
+        <v>0.06245664621844852</v>
+      </c>
+      <c r="V4" s="31" t="n">
+        <v>0.03337551048129293</v>
+      </c>
+      <c r="W4" s="28" t="n">
+        <v>0.9027198944246505</v>
+      </c>
+      <c r="X4" s="28" t="n">
+        <v>0.756595757364726</v>
+      </c>
+      <c r="Y4" s="28" t="n">
+        <v>0.5672731678479476</v>
+      </c>
+      <c r="Z4" s="28" t="n">
+        <v>0.3796301329808904</v>
+      </c>
+      <c r="AA4" s="28" t="n">
+        <v>0.2279341175463983</v>
+      </c>
+      <c r="AB4" s="28" t="n">
+        <v>0.1237752695727835</v>
+      </c>
+      <c r="AC4" s="29" t="n">
+        <v>1.107763334093075</v>
+      </c>
+      <c r="AD4" s="29" t="n">
+        <v>1.321709764119042</v>
+      </c>
+      <c r="AE4" s="29" t="n">
+        <v>1.762819143718148</v>
+      </c>
+      <c r="AF4" s="29" t="n">
+        <v>2.634142848851088</v>
+      </c>
+      <c r="AG4" s="29" t="n">
+        <v>4.387232638819154</v>
+      </c>
+      <c r="AH4" s="29" t="n">
+        <v>8.079158328247232</v>
+      </c>
+      <c r="AI4" s="29" t="n">
+        <v>10.2795941069928</v>
+      </c>
+      <c r="AJ4" s="29" t="n">
+        <v>4.108391822481242</v>
+      </c>
+      <c r="AK4" s="29" t="n">
+        <v>2.31092672258562</v>
+      </c>
+      <c r="AL4" s="29" t="n">
+        <v>1.61194160639204</v>
+      </c>
+      <c r="AM4" s="29" t="n">
+        <v>1.295226253000626</v>
+      </c>
+      <c r="AN4" s="29" t="n">
+        <v>1.1412597308369</v>
+      </c>
+      <c r="AO4" s="27" t="n"/>
+      <c r="AP4" s="27" t="n"/>
+      <c r="AQ4" s="27" t="n"/>
+      <c r="AR4" s="27" t="n"/>
+      <c r="AS4" s="27" t="n"/>
+      <c r="AT4" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU4" s="32">
+        <f>IFERROR(IF($AQ4="","",INDEX($W4:$AB4,$AQ4-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV4" s="32">
+        <f>IF($AR4="","",IF($AS4="",1/$AR4,(1/$AR4)/((1/$AR4)+(1/$AS4))))</f>
+        <v/>
+      </c>
+      <c r="AW4" s="32">
+        <f>IF(OR($AU4="",$AV4=""),"",$AU4-$AV4)</f>
+        <v/>
+      </c>
+      <c r="AX4" s="33">
+        <f>IF($AW4="","",IF($AP4="","units?",IF(ISNUMBER(SEARCH("yellow",$AP4)),IF($AW4&gt;=0.05,"OVER",IF($AW4&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY4" s="34">
+        <f>IF(OR($AX4="",$AX4="skip",$AX4="units?",$AX4="UNITS?"),"",IF($AX4="OVER",$AT4*($AU4*$AR4-1),$AT4*((1-$AU4)*$AS4-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ4" s="27" t="n"/>
+      <c r="BA4" s="33">
+        <f>IF(OR($AX4="",$AX4="skip",$AX4="units?",$AX4="UNITS?",$AZ4="",$AQ4=""),"",IF($AX4="OVER",IF($AZ4&gt;$AQ4,"WON","LOST"),IF($AZ4&lt;$AQ4,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB4" s="34">
+        <f>IF($BA4="","",IF($BA4="WON",IF($AX4="OVER",$AT4*($AR4-1),$AT4*($AS4-1)),-$AT4))</f>
+        <v/>
+      </c>
+      <c r="BC4" s="34">
+        <f>IF(COUNT($BB$2:$BB4)=0,"",SUM($BB$2:$BB4))</f>
+        <v/>
+      </c>
+      <c r="BD4" s="27" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="29" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>4.154104403855049</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>0.1048150010252791</v>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N5" s="31" t="n">
+        <v>0.01860501762223355</v>
+      </c>
+      <c r="O5" s="31" t="n">
+        <v>0.07113946404091535</v>
+      </c>
+      <c r="P5" s="31" t="n">
+        <v>0.1388363024402334</v>
+      </c>
+      <c r="Q5" s="31" t="n">
+        <v>0.1843171596482752</v>
+      </c>
+      <c r="R5" s="31" t="n">
+        <v>0.1871880135443589</v>
+      </c>
+      <c r="S5" s="31" t="n">
+        <v>0.1550607978961152</v>
+      </c>
+      <c r="T5" s="31" t="n">
+        <v>0.1090953557106882</v>
+      </c>
+      <c r="U5" s="31" t="n">
+        <v>0.06703027614901548</v>
+      </c>
+      <c r="V5" s="31" t="n">
+        <v>0.03670308078133144</v>
+      </c>
+      <c r="W5" s="28" t="n">
+        <v>0.910255518336851</v>
+      </c>
+      <c r="X5" s="28" t="n">
+        <v>0.7714192158966177</v>
+      </c>
+      <c r="Y5" s="28" t="n">
+        <v>0.5871020562483424</v>
+      </c>
+      <c r="Z5" s="28" t="n">
+        <v>0.3999140427039836</v>
+      </c>
+      <c r="AA5" s="28" t="n">
+        <v>0.2448532448078684</v>
+      </c>
+      <c r="AB5" s="28" t="n">
+        <v>0.1357578890971802</v>
+      </c>
+      <c r="AC5" s="29" t="n">
+        <v>1.098592625757571</v>
+      </c>
+      <c r="AD5" s="29" t="n">
+        <v>1.296312017373982</v>
+      </c>
+      <c r="AE5" s="29" t="n">
+        <v>1.703281379033363</v>
+      </c>
+      <c r="AF5" s="29" t="n">
+        <v>2.500537348572679</v>
+      </c>
+      <c r="AG5" s="29" t="n">
+        <v>4.084079019596741</v>
+      </c>
+      <c r="AH5" s="29" t="n">
+        <v>7.366054427114473</v>
+      </c>
+      <c r="AI5" s="29" t="n">
+        <v>11.1427464003129</v>
+      </c>
+      <c r="AJ5" s="29" t="n">
+        <v>4.374820936600344</v>
+      </c>
+      <c r="AK5" s="29" t="n">
+        <v>2.421905982175252</v>
+      </c>
+      <c r="AL5" s="29" t="n">
+        <v>1.666427930601799</v>
+      </c>
+      <c r="AM5" s="29" t="n">
+        <v>1.324245907334357</v>
+      </c>
+      <c r="AN5" s="29" t="n">
+        <v>1.157083168460008</v>
+      </c>
+      <c r="AO5" s="27" t="n"/>
+      <c r="AP5" s="27" t="n"/>
+      <c r="AQ5" s="27" t="n"/>
+      <c r="AR5" s="27" t="n"/>
+      <c r="AS5" s="27" t="n"/>
+      <c r="AT5" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU5" s="32">
+        <f>IFERROR(IF($AQ5="","",INDEX($W5:$AB5,$AQ5-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV5" s="32">
+        <f>IF($AR5="","",IF($AS5="",1/$AR5,(1/$AR5)/((1/$AR5)+(1/$AS5))))</f>
+        <v/>
+      </c>
+      <c r="AW5" s="32">
+        <f>IF(OR($AU5="",$AV5=""),"",$AU5-$AV5)</f>
+        <v/>
+      </c>
+      <c r="AX5" s="33">
+        <f>IF($AW5="","",IF($AP5="","units?",IF(ISNUMBER(SEARCH("yellow",$AP5)),IF($AW5&gt;=0.05,"OVER",IF($AW5&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY5" s="34">
+        <f>IF(OR($AX5="",$AX5="skip",$AX5="units?",$AX5="UNITS?"),"",IF($AX5="OVER",$AT5*($AU5*$AR5-1),$AT5*((1-$AU5)*$AS5-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ5" s="27" t="n"/>
+      <c r="BA5" s="33">
+        <f>IF(OR($AX5="",$AX5="skip",$AX5="units?",$AX5="UNITS?",$AZ5="",$AQ5=""),"",IF($AX5="OVER",IF($AZ5&gt;$AQ5,"WON","LOST"),IF($AZ5&lt;$AQ5,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB5" s="34">
+        <f>IF($BA5="","",IF($BA5="WON",IF($AX5="OVER",$AT5*($AR5-1),$AT5*($AS5-1)),-$AT5))</f>
+        <v/>
+      </c>
+      <c r="BC5" s="34">
+        <f>IF(COUNT($BB$2:$BB5)=0,"",SUM($BB$2:$BB5))</f>
+        <v/>
+      </c>
+      <c r="BD5" s="27" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Ipswich</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n"/>
+      <c r="I6" s="29" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J6" s="29" t="n">
+        <v>3.653752358013483</v>
+      </c>
+      <c r="K6" s="30" t="n">
+        <v>-0.0282573515921587</v>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N6" s="31" t="n">
+        <v>0.02955354956511324</v>
+      </c>
+      <c r="O6" s="31" t="n">
+        <v>0.1003535717594683</v>
+      </c>
+      <c r="P6" s="31" t="n">
+        <v>0.1739273843046306</v>
+      </c>
+      <c r="Q6" s="31" t="n">
+        <v>0.2050564230945007</v>
+      </c>
+      <c r="R6" s="31" t="n">
+        <v>0.1849389234126393</v>
+      </c>
+      <c r="S6" s="31" t="n">
+        <v>0.1360488845354591</v>
+      </c>
+      <c r="T6" s="31" t="n">
+        <v>0.08500449957630916</v>
+      </c>
+      <c r="U6" s="31" t="n">
+        <v>0.04638198619458992</v>
+      </c>
+      <c r="V6" s="31" t="n">
+        <v>0.02255399784736755</v>
+      </c>
+      <c r="W6" s="28" t="n">
+        <v>0.8700928786754184</v>
+      </c>
+      <c r="X6" s="28" t="n">
+        <v>0.6961654943707878</v>
+      </c>
+      <c r="Y6" s="28" t="n">
+        <v>0.4911090712762871</v>
+      </c>
+      <c r="Z6" s="28" t="n">
+        <v>0.3061701478636478</v>
+      </c>
+      <c r="AA6" s="28" t="n">
+        <v>0.1701212633281888</v>
+      </c>
+      <c r="AB6" s="28" t="n">
+        <v>0.0851167637518796</v>
+      </c>
+      <c r="AC6" s="29" t="n">
+        <v>1.149302591146758</v>
+      </c>
+      <c r="AD6" s="29" t="n">
+        <v>1.436440053530412</v>
+      </c>
+      <c r="AE6" s="29" t="n">
+        <v>2.036207552430694</v>
+      </c>
+      <c r="AF6" s="29" t="n">
+        <v>3.266157745873212</v>
+      </c>
+      <c r="AG6" s="29" t="n">
+        <v>5.878159969167721</v>
+      </c>
+      <c r="AH6" s="29" t="n">
+        <v>11.74856697929751</v>
+      </c>
+      <c r="AI6" s="29" t="n">
+        <v>7.697807401192683</v>
+      </c>
+      <c r="AJ6" s="29" t="n">
+        <v>3.291265414140819</v>
+      </c>
+      <c r="AK6" s="29" t="n">
+        <v>1.965057625428651</v>
+      </c>
+      <c r="AL6" s="29" t="n">
+        <v>1.44127554748607</v>
+      </c>
+      <c r="AM6" s="29" t="n">
+        <v>1.204995327402232</v>
+      </c>
+      <c r="AN6" s="29" t="n">
+        <v>1.093035657862678</v>
+      </c>
+      <c r="AO6" s="27" t="n"/>
+      <c r="AP6" s="27" t="n"/>
+      <c r="AQ6" s="27" t="n"/>
+      <c r="AR6" s="27" t="n"/>
+      <c r="AS6" s="27" t="n"/>
+      <c r="AT6" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU6" s="32">
+        <f>IFERROR(IF($AQ6="","",INDEX($W6:$AB6,$AQ6-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV6" s="32">
+        <f>IF($AR6="","",IF($AS6="",1/$AR6,(1/$AR6)/((1/$AR6)+(1/$AS6))))</f>
+        <v/>
+      </c>
+      <c r="AW6" s="32">
+        <f>IF(OR($AU6="",$AV6=""),"",$AU6-$AV6)</f>
+        <v/>
+      </c>
+      <c r="AX6" s="33">
+        <f>IF($AW6="","",IF($AP6="","units?",IF(ISNUMBER(SEARCH("yellow",$AP6)),IF($AW6&gt;=0.05,"OVER",IF($AW6&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY6" s="34">
+        <f>IF(OR($AX6="",$AX6="skip",$AX6="units?",$AX6="UNITS?"),"",IF($AX6="OVER",$AT6*($AU6*$AR6-1),$AT6*((1-$AU6)*$AS6-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ6" s="27" t="n"/>
+      <c r="BA6" s="33">
+        <f>IF(OR($AX6="",$AX6="skip",$AX6="units?",$AX6="UNITS?",$AZ6="",$AQ6=""),"",IF($AX6="OVER",IF($AZ6&gt;$AQ6,"WON","LOST"),IF($AZ6&lt;$AQ6,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB6" s="34">
+        <f>IF($BA6="","",IF($BA6="WON",IF($AX6="OVER",$AT6*($AR6-1),$AT6*($AS6-1)),-$AT6))</f>
+        <v/>
+      </c>
+      <c r="BC6" s="34">
+        <f>IF(COUNT($BB$2:$BB6)=0,"",SUM($BB$2:$BB6))</f>
+        <v/>
+      </c>
+      <c r="BD6" s="27" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Man United</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="29" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J7" s="29" t="n">
+        <v>4.112334857894304</v>
+      </c>
+      <c r="K7" s="30" t="n">
+        <v>0.09370607922720842</v>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N7" s="31" t="n">
+        <v>0.01933455147421259</v>
+      </c>
+      <c r="O7" s="31" t="n">
+        <v>0.07324418694371206</v>
+      </c>
+      <c r="P7" s="31" t="n">
+        <v>0.1416198629665162</v>
+      </c>
+      <c r="Q7" s="31" t="n">
+        <v>0.1862710908021035</v>
+      </c>
+      <c r="R7" s="31" t="n">
+        <v>0.1874201502042903</v>
+      </c>
+      <c r="S7" s="31" t="n">
+        <v>0.1538150453843692</v>
+      </c>
+      <c r="T7" s="31" t="n">
+        <v>0.1072164994682711</v>
+      </c>
+      <c r="U7" s="31" t="n">
+        <v>0.0652656890064631</v>
+      </c>
+      <c r="V7" s="31" t="n">
+        <v>0.03540584760281584</v>
+      </c>
+      <c r="W7" s="28" t="n">
+        <v>0.9074212615820754</v>
+      </c>
+      <c r="X7" s="28" t="n">
+        <v>0.7658013986155592</v>
+      </c>
+      <c r="Y7" s="28" t="n">
+        <v>0.5795303078134557</v>
+      </c>
+      <c r="Z7" s="28" t="n">
+        <v>0.3921101576091653</v>
+      </c>
+      <c r="AA7" s="28" t="n">
+        <v>0.2382951122247962</v>
+      </c>
+      <c r="AB7" s="28" t="n">
+        <v>0.131078612756525</v>
+      </c>
+      <c r="AC7" s="29" t="n">
+        <v>1.102023990771954</v>
+      </c>
+      <c r="AD7" s="29" t="n">
+        <v>1.305821590046496</v>
+      </c>
+      <c r="AE7" s="29" t="n">
+        <v>1.725535293870927</v>
+      </c>
+      <c r="AF7" s="29" t="n">
+        <v>2.55030373632082</v>
+      </c>
+      <c r="AG7" s="29" t="n">
+        <v>4.196477177662998</v>
+      </c>
+      <c r="AH7" s="29" t="n">
+        <v>7.629009637578887</v>
+      </c>
+      <c r="AI7" s="29" t="n">
+        <v>10.80161619275625</v>
+      </c>
+      <c r="AJ7" s="29" t="n">
+        <v>4.269880324171893</v>
+      </c>
+      <c r="AK7" s="29" t="n">
+        <v>2.378292701192701</v>
+      </c>
+      <c r="AL7" s="29" t="n">
+        <v>1.645034889984333</v>
+      </c>
+      <c r="AM7" s="29" t="n">
+        <v>1.312844404767851</v>
+      </c>
+      <c r="AN7" s="29" t="n">
+        <v>1.150852096266559</v>
+      </c>
+      <c r="AO7" s="27" t="n"/>
+      <c r="AP7" s="27" t="n"/>
+      <c r="AQ7" s="27" t="n"/>
+      <c r="AR7" s="27" t="n"/>
+      <c r="AS7" s="27" t="n"/>
+      <c r="AT7" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU7" s="32">
+        <f>IFERROR(IF($AQ7="","",INDEX($W7:$AB7,$AQ7-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV7" s="32">
+        <f>IF($AR7="","",IF($AS7="",1/$AR7,(1/$AR7)/((1/$AR7)+(1/$AS7))))</f>
+        <v/>
+      </c>
+      <c r="AW7" s="32">
+        <f>IF(OR($AU7="",$AV7=""),"",$AU7-$AV7)</f>
+        <v/>
+      </c>
+      <c r="AX7" s="33">
+        <f>IF($AW7="","",IF($AP7="","units?",IF(ISNUMBER(SEARCH("yellow",$AP7)),IF($AW7&gt;=0.05,"OVER",IF($AW7&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY7" s="34">
+        <f>IF(OR($AX7="",$AX7="skip",$AX7="units?",$AX7="UNITS?"),"",IF($AX7="OVER",$AT7*($AU7*$AR7-1),$AT7*((1-$AU7)*$AS7-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ7" s="27" t="n"/>
+      <c r="BA7" s="33">
+        <f>IF(OR($AX7="",$AX7="skip",$AX7="units?",$AX7="UNITS?",$AZ7="",$AQ7=""),"",IF($AX7="OVER",IF($AZ7&gt;$AQ7,"WON","LOST"),IF($AZ7&lt;$AQ7,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB7" s="34">
+        <f>IF($BA7="","",IF($BA7="WON",IF($AX7="OVER",$AT7*($AR7-1),$AT7*($AS7-1)),-$AT7))</f>
+        <v/>
+      </c>
+      <c r="BC7" s="34">
+        <f>IF(COUNT($BB$2:$BB7)=0,"",SUM($BB$2:$BB7))</f>
+        <v/>
+      </c>
+      <c r="BD7" s="27" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="29" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J8" s="29" t="n">
+        <v>3.97944764177028</v>
+      </c>
+      <c r="K8" s="30" t="n">
+        <v>0.05836373451337229</v>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N8" s="31" t="n">
+        <v>0.02185576267863817</v>
+      </c>
+      <c r="O8" s="31" t="n">
+        <v>0.08032426013900154</v>
+      </c>
+      <c r="P8" s="31" t="n">
+        <v>0.1506743922528984</v>
+      </c>
+      <c r="Q8" s="31" t="n">
+        <v>0.1922659788846428</v>
+      </c>
+      <c r="R8" s="31" t="n">
+        <v>0.1876786946883841</v>
+      </c>
+      <c r="S8" s="31" t="n">
+        <v>0.1494304889963298</v>
+      </c>
+      <c r="T8" s="31" t="n">
+        <v>0.1010517247539828</v>
+      </c>
+      <c r="U8" s="31" t="n">
+        <v>0.05967724159377383</v>
+      </c>
+      <c r="V8" s="31" t="n">
+        <v>0.03140801693773256</v>
+      </c>
+      <c r="W8" s="28" t="n">
+        <v>0.8978199771823603</v>
+      </c>
+      <c r="X8" s="28" t="n">
+        <v>0.7471455849294619</v>
+      </c>
+      <c r="Y8" s="28" t="n">
+        <v>0.5548796060448191</v>
+      </c>
+      <c r="Z8" s="28" t="n">
+        <v>0.3672009113564351</v>
+      </c>
+      <c r="AA8" s="28" t="n">
+        <v>0.2177704223601052</v>
+      </c>
+      <c r="AB8" s="28" t="n">
+        <v>0.1167186976061224</v>
+      </c>
+      <c r="AC8" s="29" t="n">
+        <v>1.11380903233888</v>
+      </c>
+      <c r="AD8" s="29" t="n">
+        <v>1.338427235830364</v>
+      </c>
+      <c r="AE8" s="29" t="n">
+        <v>1.802192744346829</v>
+      </c>
+      <c r="AF8" s="29" t="n">
+        <v>2.723304787850373</v>
+      </c>
+      <c r="AG8" s="29" t="n">
+        <v>4.591991828653386</v>
+      </c>
+      <c r="AH8" s="29" t="n">
+        <v>8.567607594239858</v>
+      </c>
+      <c r="AI8" s="29" t="n">
+        <v>9.78664882258537</v>
+      </c>
+      <c r="AJ8" s="29" t="n">
+        <v>3.954844924187038</v>
+      </c>
+      <c r="AK8" s="29" t="n">
+        <v>2.246583202163255</v>
+      </c>
+      <c r="AL8" s="29" t="n">
+        <v>1.580280404865228</v>
+      </c>
+      <c r="AM8" s="29" t="n">
+        <v>1.278397069843807</v>
+      </c>
+      <c r="AN8" s="29" t="n">
+        <v>1.132142158211422</v>
+      </c>
+      <c r="AO8" s="27" t="n"/>
+      <c r="AP8" s="27" t="n"/>
+      <c r="AQ8" s="27" t="n"/>
+      <c r="AR8" s="27" t="n"/>
+      <c r="AS8" s="27" t="n"/>
+      <c r="AT8" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU8" s="32">
+        <f>IFERROR(IF($AQ8="","",INDEX($W8:$AB8,$AQ8-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV8" s="32">
+        <f>IF($AR8="","",IF($AS8="",1/$AR8,(1/$AR8)/((1/$AR8)+(1/$AS8))))</f>
+        <v/>
+      </c>
+      <c r="AW8" s="32">
+        <f>IF(OR($AU8="",$AV8=""),"",$AU8-$AV8)</f>
+        <v/>
+      </c>
+      <c r="AX8" s="33">
+        <f>IF($AW8="","",IF($AP8="","units?",IF(ISNUMBER(SEARCH("yellow",$AP8)),IF($AW8&gt;=0.05,"OVER",IF($AW8&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY8" s="34">
+        <f>IF(OR($AX8="",$AX8="skip",$AX8="units?",$AX8="UNITS?"),"",IF($AX8="OVER",$AT8*($AU8*$AR8-1),$AT8*((1-$AU8)*$AS8-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ8" s="27" t="n"/>
+      <c r="BA8" s="33">
+        <f>IF(OR($AX8="",$AX8="skip",$AX8="units?",$AX8="UNITS?",$AZ8="",$AQ8=""),"",IF($AX8="OVER",IF($AZ8&gt;$AQ8,"WON","LOST"),IF($AZ8&lt;$AQ8,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB8" s="34">
+        <f>IF($BA8="","",IF($BA8="WON",IF($AX8="OVER",$AT8*($AR8-1),$AT8*($AS8-1)),-$AT8))</f>
+        <v/>
+      </c>
+      <c r="BC8" s="34">
+        <f>IF(COUNT($BB$2:$BB8)=0,"",SUM($BB$2:$BB8))</f>
+        <v/>
+      </c>
+      <c r="BD8" s="27" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Blackburn</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J9" s="29" t="n">
+        <v>3.82726518543982</v>
+      </c>
+      <c r="K9" s="30" t="n">
+        <v>0.007175048799952677</v>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N9" s="31" t="n">
+        <v>0.02515905347471542</v>
+      </c>
+      <c r="O9" s="31" t="n">
+        <v>0.08918924327982602</v>
+      </c>
+      <c r="P9" s="31" t="n">
+        <v>0.1613773601373051</v>
+      </c>
+      <c r="Q9" s="31" t="n">
+        <v>0.1986291641734674</v>
+      </c>
+      <c r="R9" s="31" t="n">
+        <v>0.1870221129011488</v>
+      </c>
+      <c r="S9" s="31" t="n">
+        <v>0.1436331271025355</v>
+      </c>
+      <c r="T9" s="31" t="n">
+        <v>0.09369071253827316</v>
+      </c>
+      <c r="U9" s="31" t="n">
+        <v>0.05337021662527235</v>
+      </c>
+      <c r="V9" s="31" t="n">
+        <v>0.0270936898092633</v>
+      </c>
+      <c r="W9" s="28" t="n">
+        <v>0.8856517032454585</v>
+      </c>
+      <c r="X9" s="28" t="n">
+        <v>0.7242743431081534</v>
+      </c>
+      <c r="Y9" s="28" t="n">
+        <v>0.525645178934686</v>
+      </c>
+      <c r="Z9" s="28" t="n">
+        <v>0.3386230660335372</v>
+      </c>
+      <c r="AA9" s="28" t="n">
+        <v>0.1949899389310017</v>
+      </c>
+      <c r="AB9" s="28" t="n">
+        <v>0.1012992263927286</v>
+      </c>
+      <c r="AC9" s="29" t="n">
+        <v>1.129112038440748</v>
+      </c>
+      <c r="AD9" s="29" t="n">
+        <v>1.380692288102594</v>
+      </c>
+      <c r="AE9" s="29" t="n">
+        <v>1.902423992600254</v>
+      </c>
+      <c r="AF9" s="29" t="n">
+        <v>2.953136098238978</v>
+      </c>
+      <c r="AG9" s="29" t="n">
+        <v>5.128469732758139</v>
+      </c>
+      <c r="AH9" s="29" t="n">
+        <v>9.8717437004216</v>
+      </c>
+      <c r="AI9" s="29" t="n">
+        <v>8.745211152087261</v>
+      </c>
+      <c r="AJ9" s="29" t="n">
+        <v>3.626793426743925</v>
+      </c>
+      <c r="AK9" s="29" t="n">
+        <v>2.10812656600429</v>
+      </c>
+      <c r="AL9" s="29" t="n">
+        <v>1.511997090679773</v>
+      </c>
+      <c r="AM9" s="29" t="n">
+        <v>1.242220499296703</v>
+      </c>
+      <c r="AN9" s="29" t="n">
+        <v>1.112717413145341</v>
+      </c>
+      <c r="AO9" s="27" t="n"/>
+      <c r="AP9" s="27" t="n"/>
+      <c r="AQ9" s="27" t="n"/>
+      <c r="AR9" s="27" t="n"/>
+      <c r="AS9" s="27" t="n"/>
+      <c r="AT9" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU9" s="32">
+        <f>IFERROR(IF($AQ9="","",INDEX($W9:$AB9,$AQ9-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV9" s="32">
+        <f>IF($AR9="","",IF($AS9="",1/$AR9,(1/$AR9)/((1/$AR9)+(1/$AS9))))</f>
+        <v/>
+      </c>
+      <c r="AW9" s="32">
+        <f>IF(OR($AU9="",$AV9=""),"",$AU9-$AV9)</f>
+        <v/>
+      </c>
+      <c r="AX9" s="33">
+        <f>IF($AW9="","",IF($AP9="","units?",IF(ISNUMBER(SEARCH("yellow",$AP9)),IF($AW9&gt;=0.05,"OVER",IF($AW9&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY9" s="34">
+        <f>IF(OR($AX9="",$AX9="skip",$AX9="units?",$AX9="UNITS?"),"",IF($AX9="OVER",$AT9*($AU9*$AR9-1),$AT9*((1-$AU9)*$AS9-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ9" s="27" t="n"/>
+      <c r="BA9" s="33">
+        <f>IF(OR($AX9="",$AX9="skip",$AX9="units?",$AX9="UNITS?",$AZ9="",$AQ9=""),"",IF($AX9="OVER",IF($AZ9&gt;$AQ9,"WON","LOST"),IF($AZ9&lt;$AQ9,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB9" s="34">
+        <f>IF($BA9="","",IF($BA9="WON",IF($AX9="OVER",$AT9*($AR9-1),$AT9*($AS9-1)),-$AT9))</f>
+        <v/>
+      </c>
+      <c r="BC9" s="34">
+        <f>IF(COUNT($BB$2:$BB9)=0,"",SUM($BB$2:$BB9))</f>
+        <v/>
+      </c>
+      <c r="BD9" s="27" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>Bolton</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>Stoke</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J10" s="29" t="n">
+        <v>4.102630309733895</v>
+      </c>
+      <c r="K10" s="30" t="n">
+        <v>0.07963955519313037</v>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N10" s="31" t="n">
+        <v>0.01950818887226139</v>
+      </c>
+      <c r="O10" s="31" t="n">
+        <v>0.07374128487759458</v>
+      </c>
+      <c r="P10" s="31" t="n">
+        <v>0.1422710039284716</v>
+      </c>
+      <c r="Q10" s="31" t="n">
+        <v>0.1867206593298659</v>
+      </c>
+      <c r="R10" s="31" t="n">
+        <v>0.1874640020257447</v>
+      </c>
+      <c r="S10" s="31" t="n">
+        <v>0.1535165170776964</v>
+      </c>
+      <c r="T10" s="31" t="n">
+        <v>0.1067757431348275</v>
+      </c>
+      <c r="U10" s="31" t="n">
+        <v>0.06485606485611646</v>
+      </c>
+      <c r="V10" s="31" t="n">
+        <v>0.03510713190200197</v>
+      </c>
+      <c r="W10" s="28" t="n">
+        <v>0.9067505262501441</v>
+      </c>
+      <c r="X10" s="28" t="n">
+        <v>0.7644795223216725</v>
+      </c>
+      <c r="Y10" s="28" t="n">
+        <v>0.5777588629918066</v>
+      </c>
+      <c r="Z10" s="28" t="n">
+        <v>0.3902948609660619</v>
+      </c>
+      <c r="AA10" s="28" t="n">
+        <v>0.2367783438883655</v>
+      </c>
+      <c r="AB10" s="28" t="n">
+        <v>0.130002600753538</v>
+      </c>
+      <c r="AC10" s="29" t="n">
+        <v>1.102839172462891</v>
+      </c>
+      <c r="AD10" s="29" t="n">
+        <v>1.308079511355736</v>
+      </c>
+      <c r="AE10" s="29" t="n">
+        <v>1.730825893040747</v>
+      </c>
+      <c r="AF10" s="29" t="n">
+        <v>2.562165429298222</v>
+      </c>
+      <c r="AG10" s="29" t="n">
+        <v>4.223359212578464</v>
+      </c>
+      <c r="AH10" s="29" t="n">
+        <v>7.692153804644446</v>
+      </c>
+      <c r="AI10" s="29" t="n">
+        <v>10.72392110954455</v>
+      </c>
+      <c r="AJ10" s="29" t="n">
+        <v>4.245915301538213</v>
+      </c>
+      <c r="AK10" s="29" t="n">
+        <v>2.368314956438258</v>
+      </c>
+      <c r="AL10" s="29" t="n">
+        <v>1.640137069509491</v>
+      </c>
+      <c r="AM10" s="29" t="n">
+        <v>1.310235358224338</v>
+      </c>
+      <c r="AN10" s="29" t="n">
+        <v>1.149428723426229</v>
+      </c>
+      <c r="AO10" s="27" t="n"/>
+      <c r="AP10" s="27" t="n"/>
+      <c r="AQ10" s="27" t="n"/>
+      <c r="AR10" s="27" t="n"/>
+      <c r="AS10" s="27" t="n"/>
+      <c r="AT10" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU10" s="32">
+        <f>IFERROR(IF($AQ10="","",INDEX($W10:$AB10,$AQ10-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV10" s="32">
+        <f>IF($AR10="","",IF($AS10="",1/$AR10,(1/$AR10)/((1/$AR10)+(1/$AS10))))</f>
+        <v/>
+      </c>
+      <c r="AW10" s="32">
+        <f>IF(OR($AU10="",$AV10=""),"",$AU10-$AV10)</f>
+        <v/>
+      </c>
+      <c r="AX10" s="33">
+        <f>IF($AW10="","",IF($AP10="","units?",IF(ISNUMBER(SEARCH("yellow",$AP10)),IF($AW10&gt;=0.05,"OVER",IF($AW10&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY10" s="34">
+        <f>IF(OR($AX10="",$AX10="skip",$AX10="units?",$AX10="UNITS?"),"",IF($AX10="OVER",$AT10*($AU10*$AR10-1),$AT10*((1-$AU10)*$AS10-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ10" s="27" t="n"/>
+      <c r="BA10" s="33">
+        <f>IF(OR($AX10="",$AX10="skip",$AX10="units?",$AX10="UNITS?",$AZ10="",$AQ10=""),"",IF($AX10="OVER",IF($AZ10&gt;$AQ10,"WON","LOST"),IF($AZ10&lt;$AQ10,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB10" s="34">
+        <f>IF($BA10="","",IF($BA10="WON",IF($AX10="OVER",$AT10*($AR10-1),$AT10*($AS10-1)),-$AT10))</f>
+        <v/>
+      </c>
+      <c r="BC10" s="34">
+        <f>IF(COUNT($BB$2:$BB10)=0,"",SUM($BB$2:$BB10))</f>
+        <v/>
+      </c>
+      <c r="BD10" s="27" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>Charlton</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J11" s="29" t="n">
+        <v>3.876203599758738</v>
+      </c>
+      <c r="K11" s="30" t="n">
+        <v>0.02005357888387826</v>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N11" s="31" t="n">
+        <v>0.02404458504217603</v>
+      </c>
+      <c r="O11" s="31" t="n">
+        <v>0.08624703067548509</v>
+      </c>
+      <c r="P11" s="31" t="n">
+        <v>0.1579003033260044</v>
+      </c>
+      <c r="Q11" s="31" t="n">
+        <v>0.1966491425545706</v>
+      </c>
+      <c r="R11" s="31" t="n">
+        <v>0.1873487007960487</v>
+      </c>
+      <c r="S11" s="31" t="n">
+        <v>0.145586473693043</v>
+      </c>
+      <c r="T11" s="31" t="n">
+        <v>0.09608854950452851</v>
+      </c>
+      <c r="U11" s="31" t="n">
+        <v>0.0553837994341324</v>
+      </c>
+      <c r="V11" s="31" t="n">
+        <v>0.02844858167493074</v>
+      </c>
+      <c r="W11" s="28" t="n">
+        <v>0.8897083842823389</v>
+      </c>
+      <c r="X11" s="28" t="n">
+        <v>0.7318080809563344</v>
+      </c>
+      <c r="Y11" s="28" t="n">
+        <v>0.5351589384017639</v>
+      </c>
+      <c r="Z11" s="28" t="n">
+        <v>0.3478102376057153</v>
+      </c>
+      <c r="AA11" s="28" t="n">
+        <v>0.2022237639126723</v>
+      </c>
+      <c r="AB11" s="28" t="n">
+        <v>0.1061352144081438</v>
+      </c>
+      <c r="AC11" s="29" t="n">
+        <v>1.123963781466019</v>
+      </c>
+      <c r="AD11" s="29" t="n">
+        <v>1.36647848803909</v>
+      </c>
+      <c r="AE11" s="29" t="n">
+        <v>1.868603751600356</v>
+      </c>
+      <c r="AF11" s="29" t="n">
+        <v>2.875131010760012</v>
+      </c>
+      <c r="AG11" s="29" t="n">
+        <v>4.94501724550947</v>
+      </c>
+      <c r="AH11" s="29" t="n">
+        <v>9.421943561111512</v>
+      </c>
+      <c r="AI11" s="29" t="n">
+        <v>9.066872341048395</v>
+      </c>
+      <c r="AJ11" s="29" t="n">
+        <v>3.728673121717681</v>
+      </c>
+      <c r="AK11" s="29" t="n">
+        <v>2.151272945986652</v>
+      </c>
+      <c r="AL11" s="29" t="n">
+        <v>1.533296070654119</v>
+      </c>
+      <c r="AM11" s="29" t="n">
+        <v>1.253484316485125</v>
+      </c>
+      <c r="AN11" s="29" t="n">
+        <v>1.118737437830564</v>
+      </c>
+      <c r="AO11" s="27" t="n"/>
+      <c r="AP11" s="27" t="n"/>
+      <c r="AQ11" s="27" t="n"/>
+      <c r="AR11" s="27" t="n"/>
+      <c r="AS11" s="27" t="n"/>
+      <c r="AT11" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU11" s="32">
+        <f>IFERROR(IF($AQ11="","",INDEX($W11:$AB11,$AQ11-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV11" s="32">
+        <f>IF($AR11="","",IF($AS11="",1/$AR11,(1/$AR11)/((1/$AR11)+(1/$AS11))))</f>
+        <v/>
+      </c>
+      <c r="AW11" s="32">
+        <f>IF(OR($AU11="",$AV11=""),"",$AU11-$AV11)</f>
+        <v/>
+      </c>
+      <c r="AX11" s="33">
+        <f>IF($AW11="","",IF($AP11="","units?",IF(ISNUMBER(SEARCH("yellow",$AP11)),IF($AW11&gt;=0.05,"OVER",IF($AW11&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY11" s="34">
+        <f>IF(OR($AX11="",$AX11="skip",$AX11="units?",$AX11="UNITS?"),"",IF($AX11="OVER",$AT11*($AU11*$AR11-1),$AT11*((1-$AU11)*$AS11-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ11" s="27" t="n"/>
+      <c r="BA11" s="33">
+        <f>IF(OR($AX11="",$AX11="skip",$AX11="units?",$AX11="UNITS?",$AZ11="",$AQ11=""),"",IF($AX11="OVER",IF($AZ11&gt;$AQ11,"WON","LOST"),IF($AZ11&lt;$AQ11,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB11" s="34">
+        <f>IF($BA11="","",IF($BA11="WON",IF($AX11="OVER",$AT11*($AR11-1),$AT11*($AS11-1)),-$AT11))</f>
+        <v/>
+      </c>
+      <c r="BC11" s="34">
+        <f>IF(COUNT($BB$2:$BB11)=0,"",SUM($BB$2:$BB11))</f>
+        <v/>
+      </c>
+      <c r="BD11" s="27" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J12" s="29" t="n">
+        <v>3.85662576278191</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>0.01490151652155536</v>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N12" s="31" t="n">
+        <v>0.02448425304456275</v>
+      </c>
+      <c r="O12" s="31" t="n">
+        <v>0.08741346852750131</v>
+      </c>
+      <c r="P12" s="31" t="n">
+        <v>0.1592875358157395</v>
+      </c>
+      <c r="Q12" s="31" t="n">
+        <v>0.1974492620444453</v>
+      </c>
+      <c r="R12" s="31" t="n">
+        <v>0.1872314375979557</v>
+      </c>
+      <c r="S12" s="31" t="n">
+        <v>0.1448150643054013</v>
+      </c>
+      <c r="T12" s="31" t="n">
+        <v>0.09513251547531616</v>
+      </c>
+      <c r="U12" s="31" t="n">
+        <v>0.05457637888201127</v>
+      </c>
+      <c r="V12" s="31" t="n">
+        <v>0.02790276354100892</v>
+      </c>
+      <c r="W12" s="28" t="n">
+        <v>0.888102278427936</v>
+      </c>
+      <c r="X12" s="28" t="n">
+        <v>0.7288147426121964</v>
+      </c>
+      <c r="Y12" s="28" t="n">
+        <v>0.531365480567751</v>
+      </c>
+      <c r="Z12" s="28" t="n">
+        <v>0.3441340429697954</v>
+      </c>
+      <c r="AA12" s="28" t="n">
+        <v>0.1993189786643942</v>
+      </c>
+      <c r="AB12" s="28" t="n">
+        <v>0.104186463189078</v>
+      </c>
+      <c r="AC12" s="29" t="n">
+        <v>1.125996435647185</v>
+      </c>
+      <c r="AD12" s="29" t="n">
+        <v>1.37209079555091</v>
+      </c>
+      <c r="AE12" s="29" t="n">
+        <v>1.881943853280654</v>
+      </c>
+      <c r="AF12" s="29" t="n">
+        <v>2.905844453429357</v>
+      </c>
+      <c r="AG12" s="29" t="n">
+        <v>5.017083705228906</v>
+      </c>
+      <c r="AH12" s="29" t="n">
+        <v>9.598175899158763</v>
+      </c>
+      <c r="AI12" s="29" t="n">
+        <v>8.9367324548783</v>
+      </c>
+      <c r="AJ12" s="29" t="n">
+        <v>3.68751609004308</v>
+      </c>
+      <c r="AK12" s="29" t="n">
+        <v>2.133859027737651</v>
+      </c>
+      <c r="AL12" s="29" t="n">
+        <v>1.524701792006483</v>
+      </c>
+      <c r="AM12" s="29" t="n">
+        <v>1.248936809232611</v>
+      </c>
+      <c r="AN12" s="29" t="n">
+        <v>1.116303738342669</v>
+      </c>
+      <c r="AO12" s="27" t="n"/>
+      <c r="AP12" s="27" t="n"/>
+      <c r="AQ12" s="27" t="n"/>
+      <c r="AR12" s="27" t="n"/>
+      <c r="AS12" s="27" t="n"/>
+      <c r="AT12" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU12" s="32">
+        <f>IFERROR(IF($AQ12="","",INDEX($W12:$AB12,$AQ12-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV12" s="32">
+        <f>IF($AR12="","",IF($AS12="",1/$AR12,(1/$AR12)/((1/$AR12)+(1/$AS12))))</f>
+        <v/>
+      </c>
+      <c r="AW12" s="32">
+        <f>IF(OR($AU12="",$AV12=""),"",$AU12-$AV12)</f>
+        <v/>
+      </c>
+      <c r="AX12" s="33">
+        <f>IF($AW12="","",IF($AP12="","units?",IF(ISNUMBER(SEARCH("yellow",$AP12)),IF($AW12&gt;=0.05,"OVER",IF($AW12&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY12" s="34">
+        <f>IF(OR($AX12="",$AX12="skip",$AX12="units?",$AX12="UNITS?"),"",IF($AX12="OVER",$AT12*($AU12*$AR12-1),$AT12*((1-$AU12)*$AS12-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ12" s="27" t="n"/>
+      <c r="BA12" s="33">
+        <f>IF(OR($AX12="",$AX12="skip",$AX12="units?",$AX12="UNITS?",$AZ12="",$AQ12=""),"",IF($AX12="OVER",IF($AZ12&gt;$AQ12,"WON","LOST"),IF($AZ12&lt;$AQ12,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB12" s="34">
+        <f>IF($BA12="","",IF($BA12="WON",IF($AX12="OVER",$AT12*($AR12-1),$AT12*($AS12-1)),-$AT12))</f>
+        <v/>
+      </c>
+      <c r="BC12" s="34">
+        <f>IF(COUNT($BB$2:$BB12)=0,"",SUM($BB$2:$BB12))</f>
+        <v/>
+      </c>
+      <c r="BD12" s="27" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>Wolves</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="28" t="n"/>
+      <c r="I13" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J13" s="29" t="n">
+        <v>3.65568217096774</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>-0.03797837606112098</v>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N13" s="31" t="n">
+        <v>0.02950059401849882</v>
+      </c>
+      <c r="O13" s="31" t="n">
+        <v>0.100222922889695</v>
+      </c>
+      <c r="P13" s="31" t="n">
+        <v>0.1737862109145296</v>
+      </c>
+      <c r="Q13" s="31" t="n">
+        <v>0.2049905520176011</v>
+      </c>
+      <c r="R13" s="31" t="n">
+        <v>0.1849702618627887</v>
+      </c>
+      <c r="S13" s="31" t="n">
+        <v>0.1361387285938756</v>
+      </c>
+      <c r="T13" s="31" t="n">
+        <v>0.08510238645760006</v>
+      </c>
+      <c r="U13" s="31" t="n">
+        <v>0.04645818990554509</v>
+      </c>
+      <c r="V13" s="31" t="n">
+        <v>0.02260214184116257</v>
+      </c>
+      <c r="W13" s="28" t="n">
+        <v>0.8702764830918062</v>
+      </c>
+      <c r="X13" s="28" t="n">
+        <v>0.6964902721772767</v>
+      </c>
+      <c r="Y13" s="28" t="n">
+        <v>0.4914997201596756</v>
+      </c>
+      <c r="Z13" s="28" t="n">
+        <v>0.3065294582968868</v>
+      </c>
+      <c r="AA13" s="28" t="n">
+        <v>0.1703907297030112</v>
+      </c>
+      <c r="AB13" s="28" t="n">
+        <v>0.08528834324541112</v>
+      </c>
+      <c r="AC13" s="29" t="n">
+        <v>1.149060119891243</v>
+      </c>
+      <c r="AD13" s="29" t="n">
+        <v>1.435770232474218</v>
+      </c>
+      <c r="AE13" s="29" t="n">
+        <v>2.034589154344026</v>
+      </c>
+      <c r="AF13" s="29" t="n">
+        <v>3.262329191967766</v>
+      </c>
+      <c r="AG13" s="29" t="n">
+        <v>5.868863885629148</v>
+      </c>
+      <c r="AH13" s="29" t="n">
+        <v>11.72493170752035</v>
+      </c>
+      <c r="AI13" s="29" t="n">
+        <v>7.708702506945648</v>
+      </c>
+      <c r="AJ13" s="29" t="n">
+        <v>3.294787311015246</v>
+      </c>
+      <c r="AK13" s="29" t="n">
+        <v>1.96656725599839</v>
+      </c>
+      <c r="AL13" s="29" t="n">
+        <v>1.44202232086755</v>
+      </c>
+      <c r="AM13" s="29" t="n">
+        <v>1.205386723369199</v>
+      </c>
+      <c r="AN13" s="29" t="n">
+        <v>1.093240686959228</v>
+      </c>
+      <c r="AO13" s="27" t="n"/>
+      <c r="AP13" s="27" t="n"/>
+      <c r="AQ13" s="27" t="n"/>
+      <c r="AR13" s="27" t="n"/>
+      <c r="AS13" s="27" t="n"/>
+      <c r="AT13" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU13" s="32">
+        <f>IFERROR(IF($AQ13="","",INDEX($W13:$AB13,$AQ13-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV13" s="32">
+        <f>IF($AR13="","",IF($AS13="",1/$AR13,(1/$AR13)/((1/$AR13)+(1/$AS13))))</f>
+        <v/>
+      </c>
+      <c r="AW13" s="32">
+        <f>IF(OR($AU13="",$AV13=""),"",$AU13-$AV13)</f>
+        <v/>
+      </c>
+      <c r="AX13" s="33">
+        <f>IF($AW13="","",IF($AP13="","units?",IF(ISNUMBER(SEARCH("yellow",$AP13)),IF($AW13&gt;=0.05,"OVER",IF($AW13&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY13" s="34">
+        <f>IF(OR($AX13="",$AX13="skip",$AX13="units?",$AX13="UNITS?"),"",IF($AX13="OVER",$AT13*($AU13*$AR13-1),$AT13*((1-$AU13)*$AS13-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ13" s="27" t="n"/>
+      <c r="BA13" s="33">
+        <f>IF(OR($AX13="",$AX13="skip",$AX13="units?",$AX13="UNITS?",$AZ13="",$AQ13=""),"",IF($AX13="OVER",IF($AZ13&gt;$AQ13,"WON","LOST"),IF($AZ13&lt;$AQ13,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB13" s="34">
+        <f>IF($BA13="","",IF($BA13="WON",IF($AX13="OVER",$AT13*($AR13-1),$AT13*($AS13-1)),-$AT13))</f>
+        <v/>
+      </c>
+      <c r="BC13" s="34">
+        <f>IF(COUNT($BB$2:$BB13)=0,"",SUM($BB$2:$BB13))</f>
+        <v/>
+      </c>
+      <c r="BD13" s="27" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Preston</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J14" s="29" t="n">
+        <v>3.650253958411302</v>
+      </c>
+      <c r="K14" s="30" t="n">
+        <v>-0.0394068530496573</v>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N14" s="31" t="n">
+        <v>0.02964979586632546</v>
+      </c>
+      <c r="O14" s="31" t="n">
+        <v>0.1005907947055463</v>
+      </c>
+      <c r="P14" s="31" t="n">
+        <v>0.1741833815220949</v>
+      </c>
+      <c r="Q14" s="31" t="n">
+        <v>0.2051754886116714</v>
+      </c>
+      <c r="R14" s="31" t="n">
+        <v>0.1848816340758105</v>
+      </c>
+      <c r="S14" s="31" t="n">
+        <v>0.1358857069703855</v>
+      </c>
+      <c r="T14" s="31" t="n">
+        <v>0.08482698962813989</v>
+      </c>
+      <c r="U14" s="31" t="n">
+        <v>0.04624394001427239</v>
+      </c>
+      <c r="V14" s="31" t="n">
+        <v>0.02246685945525516</v>
+      </c>
+      <c r="W14" s="28" t="n">
+        <v>0.8697594094281282</v>
+      </c>
+      <c r="X14" s="28" t="n">
+        <v>0.6955760279060333</v>
+      </c>
+      <c r="Y14" s="28" t="n">
+        <v>0.490400539294362</v>
+      </c>
+      <c r="Z14" s="28" t="n">
+        <v>0.3055189052185515</v>
+      </c>
+      <c r="AA14" s="28" t="n">
+        <v>0.169633198248166</v>
+      </c>
+      <c r="AB14" s="28" t="n">
+        <v>0.08480620862002608</v>
+      </c>
+      <c r="AC14" s="29" t="n">
+        <v>1.149743238371524</v>
+      </c>
+      <c r="AD14" s="29" t="n">
+        <v>1.437657365810042</v>
+      </c>
+      <c r="AE14" s="29" t="n">
+        <v>2.039149470428604</v>
+      </c>
+      <c r="AF14" s="29" t="n">
+        <v>3.273119872188121</v>
+      </c>
+      <c r="AG14" s="29" t="n">
+        <v>5.895072487739359</v>
+      </c>
+      <c r="AH14" s="29" t="n">
+        <v>11.79158951062765</v>
+      </c>
+      <c r="AI14" s="29" t="n">
+        <v>7.678097861880944</v>
+      </c>
+      <c r="AJ14" s="29" t="n">
+        <v>3.284892425263178</v>
+      </c>
+      <c r="AK14" s="29" t="n">
+        <v>1.962325467564876</v>
+      </c>
+      <c r="AL14" s="29" t="n">
+        <v>1.439924005871891</v>
+      </c>
+      <c r="AM14" s="29" t="n">
+        <v>1.204287066740011</v>
+      </c>
+      <c r="AN14" s="29" t="n">
+        <v>1.092664755179503</v>
+      </c>
+      <c r="AO14" s="27" t="n"/>
+      <c r="AP14" s="27" t="n"/>
+      <c r="AQ14" s="27" t="n"/>
+      <c r="AR14" s="27" t="n"/>
+      <c r="AS14" s="27" t="n"/>
+      <c r="AT14" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU14" s="32">
+        <f>IFERROR(IF($AQ14="","",INDEX($W14:$AB14,$AQ14-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV14" s="32">
+        <f>IF($AR14="","",IF($AS14="",1/$AR14,(1/$AR14)/((1/$AR14)+(1/$AS14))))</f>
+        <v/>
+      </c>
+      <c r="AW14" s="32">
+        <f>IF(OR($AU14="",$AV14=""),"",$AU14-$AV14)</f>
+        <v/>
+      </c>
+      <c r="AX14" s="33">
+        <f>IF($AW14="","",IF($AP14="","units?",IF(ISNUMBER(SEARCH("yellow",$AP14)),IF($AW14&gt;=0.05,"OVER",IF($AW14&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY14" s="34">
+        <f>IF(OR($AX14="",$AX14="skip",$AX14="units?",$AX14="UNITS?"),"",IF($AX14="OVER",$AT14*($AU14*$AR14-1),$AT14*((1-$AU14)*$AS14-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ14" s="27" t="n"/>
+      <c r="BA14" s="33">
+        <f>IF(OR($AX14="",$AX14="skip",$AX14="units?",$AX14="UNITS?",$AZ14="",$AQ14=""),"",IF($AX14="OVER",IF($AZ14&gt;$AQ14,"WON","LOST"),IF($AZ14&lt;$AQ14,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB14" s="34">
+        <f>IF($BA14="","",IF($BA14="WON",IF($AX14="OVER",$AT14*($AR14-1),$AT14*($AS14-1)),-$AT14))</f>
+        <v/>
+      </c>
+      <c r="BC14" s="34">
+        <f>IF(COUNT($BB$2:$BB14)=0,"",SUM($BB$2:$BB14))</f>
+        <v/>
+      </c>
+      <c r="BD14" s="27" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J15" s="29" t="n">
+        <v>4.06964045685306</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>0.07095801496133158</v>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N15" s="31" t="n">
+        <v>0.02011045049637343</v>
+      </c>
+      <c r="O15" s="31" t="n">
+        <v>0.07545428475033521</v>
+      </c>
+      <c r="P15" s="31" t="n">
+        <v>0.1444967105814066</v>
+      </c>
+      <c r="Q15" s="31" t="n">
+        <v>0.1882358308061813</v>
+      </c>
+      <c r="R15" s="31" t="n">
+        <v>0.1875841611644583</v>
+      </c>
+      <c r="S15" s="31" t="n">
+        <v>0.1524760906361604</v>
+      </c>
+      <c r="T15" s="31" t="n">
+        <v>0.1052658740420429</v>
+      </c>
+      <c r="U15" s="31" t="n">
+        <v>0.06346495125837635</v>
+      </c>
+      <c r="V15" s="31" t="n">
+        <v>0.03409942579512823</v>
+      </c>
+      <c r="W15" s="28" t="n">
+        <v>0.9044352647532914</v>
+      </c>
+      <c r="X15" s="28" t="n">
+        <v>0.7599385541718847</v>
+      </c>
+      <c r="Y15" s="28" t="n">
+        <v>0.5717027233657034</v>
+      </c>
+      <c r="Z15" s="28" t="n">
+        <v>0.3841185622012451</v>
+      </c>
+      <c r="AA15" s="28" t="n">
+        <v>0.2316424715650847</v>
+      </c>
+      <c r="AB15" s="28" t="n">
+        <v>0.1263765975230418</v>
+      </c>
+      <c r="AC15" s="29" t="n">
+        <v>1.105662327610342</v>
+      </c>
+      <c r="AD15" s="29" t="n">
+        <v>1.315895863567172</v>
+      </c>
+      <c r="AE15" s="29" t="n">
+        <v>1.749160812306164</v>
+      </c>
+      <c r="AF15" s="29" t="n">
+        <v>2.603362863459033</v>
+      </c>
+      <c r="AG15" s="29" t="n">
+        <v>4.316997626745792</v>
+      </c>
+      <c r="AH15" s="29" t="n">
+        <v>7.912857440379132</v>
+      </c>
+      <c r="AI15" s="29" t="n">
+        <v>10.46411102817806</v>
+      </c>
+      <c r="AJ15" s="29" t="n">
+        <v>4.165600171866011</v>
+      </c>
+      <c r="AK15" s="29" t="n">
+        <v>2.334826893736833</v>
+      </c>
+      <c r="AL15" s="29" t="n">
+        <v>1.623689136620415</v>
+      </c>
+      <c r="AM15" s="29" t="n">
+        <v>1.301477454170225</v>
+      </c>
+      <c r="AN15" s="29" t="n">
+        <v>1.144657980961511</v>
+      </c>
+      <c r="AO15" s="27" t="n"/>
+      <c r="AP15" s="27" t="n"/>
+      <c r="AQ15" s="27" t="n"/>
+      <c r="AR15" s="27" t="n"/>
+      <c r="AS15" s="27" t="n"/>
+      <c r="AT15" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU15" s="32">
+        <f>IFERROR(IF($AQ15="","",INDEX($W15:$AB15,$AQ15-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV15" s="32">
+        <f>IF($AR15="","",IF($AS15="",1/$AR15,(1/$AR15)/((1/$AR15)+(1/$AS15))))</f>
+        <v/>
+      </c>
+      <c r="AW15" s="32">
+        <f>IF(OR($AU15="",$AV15=""),"",$AU15-$AV15)</f>
+        <v/>
+      </c>
+      <c r="AX15" s="33">
+        <f>IF($AW15="","",IF($AP15="","units?",IF(ISNUMBER(SEARCH("yellow",$AP15)),IF($AW15&gt;=0.05,"OVER",IF($AW15&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY15" s="34">
+        <f>IF(OR($AX15="",$AX15="skip",$AX15="units?",$AX15="UNITS?"),"",IF($AX15="OVER",$AT15*($AU15*$AR15-1),$AT15*((1-$AU15)*$AS15-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ15" s="27" t="n"/>
+      <c r="BA15" s="33">
+        <f>IF(OR($AX15="",$AX15="skip",$AX15="units?",$AX15="UNITS?",$AZ15="",$AQ15=""),"",IF($AX15="OVER",IF($AZ15&gt;$AQ15,"WON","LOST"),IF($AZ15&lt;$AQ15,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB15" s="34">
+        <f>IF($BA15="","",IF($BA15="WON",IF($AX15="OVER",$AT15*($AR15-1),$AT15*($AS15-1)),-$AT15))</f>
+        <v/>
+      </c>
+      <c r="BC15" s="34">
+        <f>IF(COUNT($BB$2:$BB15)=0,"",SUM($BB$2:$BB15))</f>
+        <v/>
+      </c>
+      <c r="BD15" s="27" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>Norwich</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J16" s="29" t="n">
+        <v>3.895585812433445</v>
+      </c>
+      <c r="K16" s="30" t="n">
+        <v>0.02515416116669633</v>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N16" s="31" t="n">
+        <v>0.02361724683203562</v>
+      </c>
+      <c r="O16" s="31" t="n">
+        <v>0.08510602661335402</v>
+      </c>
+      <c r="P16" s="31" t="n">
+        <v>0.156532062568314</v>
+      </c>
+      <c r="Q16" s="31" t="n">
+        <v>0.1958468457685668</v>
+      </c>
+      <c r="R16" s="31" t="n">
+        <v>0.1874473869812761</v>
+      </c>
+      <c r="S16" s="31" t="n">
+        <v>0.146336920873988</v>
+      </c>
+      <c r="T16" s="31" t="n">
+        <v>0.09703059712052897</v>
+      </c>
+      <c r="U16" s="31" t="n">
+        <v>0.05618546674722757</v>
+      </c>
+      <c r="V16" s="31" t="n">
+        <v>0.02899386063646728</v>
+      </c>
+      <c r="W16" s="28" t="n">
+        <v>0.8912767265546103</v>
+      </c>
+      <c r="X16" s="28" t="n">
+        <v>0.7347446639862963</v>
+      </c>
+      <c r="Y16" s="28" t="n">
+        <v>0.5388978182177295</v>
+      </c>
+      <c r="Z16" s="28" t="n">
+        <v>0.3514504312364535</v>
+      </c>
+      <c r="AA16" s="28" t="n">
+        <v>0.2051135103624655</v>
+      </c>
+      <c r="AB16" s="28" t="n">
+        <v>0.1080829132419365</v>
+      </c>
+      <c r="AC16" s="29" t="n">
+        <v>1.121985989542977</v>
+      </c>
+      <c r="AD16" s="29" t="n">
+        <v>1.361017029473318</v>
+      </c>
+      <c r="AE16" s="29" t="n">
+        <v>1.855639355355439</v>
+      </c>
+      <c r="AF16" s="29" t="n">
+        <v>2.845351466725635</v>
+      </c>
+      <c r="AG16" s="29" t="n">
+        <v>4.875349255311628</v>
+      </c>
+      <c r="AH16" s="29" t="n">
+        <v>9.252156238253548</v>
+      </c>
+      <c r="AI16" s="29" t="n">
+        <v>9.197662729519337</v>
+      </c>
+      <c r="AJ16" s="29" t="n">
+        <v>3.769952435370943</v>
+      </c>
+      <c r="AK16" s="29" t="n">
+        <v>2.168716695580924</v>
+      </c>
+      <c r="AL16" s="29" t="n">
+        <v>1.541902189383134</v>
+      </c>
+      <c r="AM16" s="29" t="n">
+        <v>1.258041258766389</v>
+      </c>
+      <c r="AN16" s="29" t="n">
+        <v>1.121180449221795</v>
+      </c>
+      <c r="AO16" s="27" t="n"/>
+      <c r="AP16" s="27" t="n"/>
+      <c r="AQ16" s="27" t="n"/>
+      <c r="AR16" s="27" t="n"/>
+      <c r="AS16" s="27" t="n"/>
+      <c r="AT16" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU16" s="32">
+        <f>IFERROR(IF($AQ16="","",INDEX($W16:$AB16,$AQ16-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV16" s="32">
+        <f>IF($AR16="","",IF($AS16="",1/$AR16,(1/$AR16)/((1/$AR16)+(1/$AS16))))</f>
+        <v/>
+      </c>
+      <c r="AW16" s="32">
+        <f>IF(OR($AU16="",$AV16=""),"",$AU16-$AV16)</f>
+        <v/>
+      </c>
+      <c r="AX16" s="33">
+        <f>IF($AW16="","",IF($AP16="","units?",IF(ISNUMBER(SEARCH("yellow",$AP16)),IF($AW16&gt;=0.05,"OVER",IF($AW16&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY16" s="34">
+        <f>IF(OR($AX16="",$AX16="skip",$AX16="units?",$AX16="UNITS?"),"",IF($AX16="OVER",$AT16*($AU16*$AR16-1),$AT16*((1-$AU16)*$AS16-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ16" s="27" t="n"/>
+      <c r="BA16" s="33">
+        <f>IF(OR($AX16="",$AX16="skip",$AX16="units?",$AX16="UNITS?",$AZ16="",$AQ16=""),"",IF($AX16="OVER",IF($AZ16&gt;$AQ16,"WON","LOST"),IF($AZ16&lt;$AQ16,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB16" s="34">
+        <f>IF($BA16="","",IF($BA16="WON",IF($AX16="OVER",$AT16*($AR16-1),$AT16*($AS16-1)),-$AT16))</f>
+        <v/>
+      </c>
+      <c r="BC16" s="34">
+        <f>IF(COUNT($BB$2:$BB16)=0,"",SUM($BB$2:$BB16))</f>
+        <v/>
+      </c>
+      <c r="BD16" s="27" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J17" s="29" t="n">
+        <v>4.253769785705054</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>0.11941310150133</v>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N17" s="31" t="n">
+        <v>0.01697566966344017</v>
+      </c>
+      <c r="O17" s="31" t="n">
+        <v>0.06634007646816818</v>
+      </c>
+      <c r="P17" s="31" t="n">
+        <v>0.1323234960739294</v>
+      </c>
+      <c r="Q17" s="31" t="n">
+        <v>0.1795429043527981</v>
+      </c>
+      <c r="R17" s="31" t="n">
+        <v>0.186358437947825</v>
+      </c>
+      <c r="S17" s="31" t="n">
+        <v>0.1577762354059716</v>
+      </c>
+      <c r="T17" s="31" t="n">
+        <v>0.1134525826736359</v>
+      </c>
+      <c r="U17" s="31" t="n">
+        <v>0.07124389940040823</v>
+      </c>
+      <c r="V17" s="31" t="n">
+        <v>0.03987013826605843</v>
+      </c>
+      <c r="W17" s="28" t="n">
+        <v>0.9166842538683917</v>
+      </c>
+      <c r="X17" s="28" t="n">
+        <v>0.7843607577944622</v>
+      </c>
+      <c r="Y17" s="28" t="n">
+        <v>0.6048178534416642</v>
+      </c>
+      <c r="Z17" s="28" t="n">
+        <v>0.4184594154938391</v>
+      </c>
+      <c r="AA17" s="28" t="n">
+        <v>0.2606831800878675</v>
+      </c>
+      <c r="AB17" s="28" t="n">
+        <v>0.1472305974142316</v>
+      </c>
+      <c r="AC17" s="29" t="n">
+        <v>1.090888161087111</v>
+      </c>
+      <c r="AD17" s="29" t="n">
+        <v>1.274923547694931</v>
+      </c>
+      <c r="AE17" s="29" t="n">
+        <v>1.653390346051436</v>
+      </c>
+      <c r="AF17" s="29" t="n">
+        <v>2.389718006033784</v>
+      </c>
+      <c r="AG17" s="29" t="n">
+        <v>3.836074117489797</v>
+      </c>
+      <c r="AH17" s="29" t="n">
+        <v>6.792066442456329</v>
+      </c>
+      <c r="AI17" s="29" t="n">
+        <v>12.00253309164833</v>
+      </c>
+      <c r="AJ17" s="29" t="n">
+        <v>4.637374857062632</v>
+      </c>
+      <c r="AK17" s="29" t="n">
+        <v>2.5304786886479</v>
+      </c>
+      <c r="AL17" s="29" t="n">
+        <v>1.719570442102835</v>
+      </c>
+      <c r="AM17" s="29" t="n">
+        <v>1.352600093852659</v>
+      </c>
+      <c r="AN17" s="29" t="n">
+        <v>1.17264995316178</v>
+      </c>
+      <c r="AO17" s="27" t="n"/>
+      <c r="AP17" s="27" t="n"/>
+      <c r="AQ17" s="27" t="n"/>
+      <c r="AR17" s="27" t="n"/>
+      <c r="AS17" s="27" t="n"/>
+      <c r="AT17" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU17" s="32">
+        <f>IFERROR(IF($AQ17="","",INDEX($W17:$AB17,$AQ17-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV17" s="32">
+        <f>IF($AR17="","",IF($AS17="",1/$AR17,(1/$AR17)/((1/$AR17)+(1/$AS17))))</f>
+        <v/>
+      </c>
+      <c r="AW17" s="32">
+        <f>IF(OR($AU17="",$AV17=""),"",$AU17-$AV17)</f>
+        <v/>
+      </c>
+      <c r="AX17" s="33">
+        <f>IF($AW17="","",IF($AP17="","units?",IF(ISNUMBER(SEARCH("yellow",$AP17)),IF($AW17&gt;=0.05,"OVER",IF($AW17&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY17" s="34">
+        <f>IF(OR($AX17="",$AX17="skip",$AX17="units?",$AX17="UNITS?"),"",IF($AX17="OVER",$AT17*($AU17*$AR17-1),$AT17*((1-$AU17)*$AS17-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ17" s="27" t="n"/>
+      <c r="BA17" s="33">
+        <f>IF(OR($AX17="",$AX17="skip",$AX17="units?",$AX17="UNITS?",$AZ17="",$AQ17=""),"",IF($AX17="OVER",IF($AZ17&gt;$AQ17,"WON","LOST"),IF($AZ17&lt;$AQ17,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB17" s="34">
+        <f>IF($BA17="","",IF($BA17="WON",IF($AX17="OVER",$AT17*($AR17-1),$AT17*($AS17-1)),-$AT17))</f>
+        <v/>
+      </c>
+      <c r="BC17" s="34">
+        <f>IF(COUNT($BB$2:$BB17)=0,"",SUM($BB$2:$BB17))</f>
+        <v/>
+      </c>
+      <c r="BD17" s="27" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>West Brom</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J18" s="29" t="n">
+        <v>3.829591266483753</v>
+      </c>
+      <c r="K18" s="30" t="n">
+        <v>0.007787175390461476</v>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N18" s="31" t="n">
+        <v>0.02510490686416387</v>
+      </c>
+      <c r="O18" s="31" t="n">
+        <v>0.08904739101671039</v>
+      </c>
+      <c r="P18" s="31" t="n">
+        <v>0.1612113933008812</v>
+      </c>
+      <c r="Q18" s="31" t="n">
+        <v>0.1985365833913783</v>
+      </c>
+      <c r="R18" s="31" t="n">
+        <v>0.1870401715115373</v>
+      </c>
+      <c r="S18" s="31" t="n">
+        <v>0.1437278578533623</v>
+      </c>
+      <c r="T18" s="31" t="n">
+        <v>0.09380527976312002</v>
+      </c>
+      <c r="U18" s="31" t="n">
+        <v>0.05346555887550904</v>
+      </c>
+      <c r="V18" s="31" t="n">
+        <v>0.02715736965500318</v>
+      </c>
+      <c r="W18" s="28" t="n">
+        <v>0.8858477021191258</v>
+      </c>
+      <c r="X18" s="28" t="n">
+        <v>0.7246363088182445</v>
+      </c>
+      <c r="Y18" s="28" t="n">
+        <v>0.5260997254268661</v>
+      </c>
+      <c r="Z18" s="28" t="n">
+        <v>0.3390595539153288</v>
+      </c>
+      <c r="AA18" s="28" t="n">
+        <v>0.1953316960619665</v>
+      </c>
+      <c r="AB18" s="28" t="n">
+        <v>0.1015264162988465</v>
+      </c>
+      <c r="AC18" s="29" t="n">
+        <v>1.128862215940504</v>
+      </c>
+      <c r="AD18" s="29" t="n">
+        <v>1.380002613491485</v>
+      </c>
+      <c r="AE18" s="29" t="n">
+        <v>1.900780311543826</v>
+      </c>
+      <c r="AF18" s="29" t="n">
+        <v>2.949334382271156</v>
+      </c>
+      <c r="AG18" s="29" t="n">
+        <v>5.119496836206053</v>
+      </c>
+      <c r="AH18" s="29" t="n">
+        <v>9.849653286849655</v>
+      </c>
+      <c r="AI18" s="29" t="n">
+        <v>8.760226631999725</v>
+      </c>
+      <c r="AJ18" s="29" t="n">
+        <v>3.631560848521397</v>
+      </c>
+      <c r="AK18" s="29" t="n">
+        <v>2.110148598037321</v>
+      </c>
+      <c r="AL18" s="29" t="n">
+        <v>1.512995619989479</v>
+      </c>
+      <c r="AM18" s="29" t="n">
+        <v>1.242748092730901</v>
+      </c>
+      <c r="AN18" s="29" t="n">
+        <v>1.112998777193449</v>
+      </c>
+      <c r="AO18" s="27" t="n"/>
+      <c r="AP18" s="27" t="n"/>
+      <c r="AQ18" s="27" t="n"/>
+      <c r="AR18" s="27" t="n"/>
+      <c r="AS18" s="27" t="n"/>
+      <c r="AT18" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU18" s="32">
+        <f>IFERROR(IF($AQ18="","",INDEX($W18:$AB18,$AQ18-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV18" s="32">
+        <f>IF($AR18="","",IF($AS18="",1/$AR18,(1/$AR18)/((1/$AR18)+(1/$AS18))))</f>
+        <v/>
+      </c>
+      <c r="AW18" s="32">
+        <f>IF(OR($AU18="",$AV18=""),"",$AU18-$AV18)</f>
+        <v/>
+      </c>
+      <c r="AX18" s="33">
+        <f>IF($AW18="","",IF($AP18="","units?",IF(ISNUMBER(SEARCH("yellow",$AP18)),IF($AW18&gt;=0.05,"OVER",IF($AW18&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY18" s="34">
+        <f>IF(OR($AX18="",$AX18="skip",$AX18="units?",$AX18="UNITS?"),"",IF($AX18="OVER",$AT18*($AU18*$AR18-1),$AT18*((1-$AU18)*$AS18-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ18" s="27" t="n"/>
+      <c r="BA18" s="33">
+        <f>IF(OR($AX18="",$AX18="skip",$AX18="units?",$AX18="UNITS?",$AZ18="",$AQ18=""),"",IF($AX18="OVER",IF($AZ18&gt;$AQ18,"WON","LOST"),IF($AZ18&lt;$AQ18,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB18" s="34">
+        <f>IF($BA18="","",IF($BA18="WON",IF($AX18="OVER",$AT18*($AR18-1),$AT18*($AS18-1)),-$AT18))</f>
+        <v/>
+      </c>
+      <c r="BC18" s="34">
+        <f>IF(COUNT($BB$2:$BB18)=0,"",SUM($BB$2:$BB18))</f>
+        <v/>
+      </c>
+      <c r="BD18" s="27" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>Bradford</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>Leyton Orient</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J19" s="29" t="n">
+        <v>4.422633054084677</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>0.1949350177185305</v>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N19" s="31" t="n">
+        <v>0.01453988771129786</v>
+      </c>
+      <c r="O19" s="31" t="n">
+        <v>0.05888676514046162</v>
+      </c>
+      <c r="P19" s="31" t="n">
+        <v>0.1217268235719875</v>
+      </c>
+      <c r="Q19" s="31" t="n">
+        <v>0.1711690190126045</v>
+      </c>
+      <c r="R19" s="31" t="n">
+        <v>0.1841253434023059</v>
+      </c>
+      <c r="S19" s="31" t="n">
+        <v>0.1615525027850394</v>
+      </c>
+      <c r="T19" s="31" t="n">
+        <v>0.1203910163098586</v>
+      </c>
+      <c r="U19" s="31" t="n">
+        <v>0.07834927253624274</v>
+      </c>
+      <c r="V19" s="31" t="n">
+        <v>0.0454404497610952</v>
+      </c>
+      <c r="W19" s="28" t="n">
+        <v>0.9265733471482405</v>
+      </c>
+      <c r="X19" s="28" t="n">
+        <v>0.804846523576253</v>
+      </c>
+      <c r="Y19" s="28" t="n">
+        <v>0.6336775045636486</v>
+      </c>
+      <c r="Z19" s="28" t="n">
+        <v>0.4495521611613427</v>
+      </c>
+      <c r="AA19" s="28" t="n">
+        <v>0.2879996583763033</v>
+      </c>
+      <c r="AB19" s="28" t="n">
+        <v>0.1676086420664447</v>
+      </c>
+      <c r="AC19" s="29" t="n">
+        <v>1.07924537553098</v>
+      </c>
+      <c r="AD19" s="29" t="n">
+        <v>1.242472907202981</v>
+      </c>
+      <c r="AE19" s="29" t="n">
+        <v>1.578089789834976</v>
+      </c>
+      <c r="AF19" s="29" t="n">
+        <v>2.224435975163967</v>
+      </c>
+      <c r="AG19" s="29" t="n">
+        <v>3.472226340954161</v>
+      </c>
+      <c r="AH19" s="29" t="n">
+        <v>5.966279469071605</v>
+      </c>
+      <c r="AI19" s="29" t="n">
+        <v>13.6190328874025</v>
+      </c>
+      <c r="AJ19" s="29" t="n">
+        <v>5.124172104567829</v>
+      </c>
+      <c r="AK19" s="29" t="n">
+        <v>2.729835083725427</v>
+      </c>
+      <c r="AL19" s="29" t="n">
+        <v>1.816702563697614</v>
+      </c>
+      <c r="AM19" s="29" t="n">
+        <v>1.404493708134364</v>
+      </c>
+      <c r="AN19" s="29" t="n">
+        <v>1.201357979595727</v>
+      </c>
+      <c r="AO19" s="27" t="n"/>
+      <c r="AP19" s="27" t="n"/>
+      <c r="AQ19" s="27" t="n"/>
+      <c r="AR19" s="27" t="n"/>
+      <c r="AS19" s="27" t="n"/>
+      <c r="AT19" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU19" s="32">
+        <f>IFERROR(IF($AQ19="","",INDEX($W19:$AB19,$AQ19-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV19" s="32">
+        <f>IF($AR19="","",IF($AS19="",1/$AR19,(1/$AR19)/((1/$AR19)+(1/$AS19))))</f>
+        <v/>
+      </c>
+      <c r="AW19" s="32">
+        <f>IF(OR($AU19="",$AV19=""),"",$AU19-$AV19)</f>
+        <v/>
+      </c>
+      <c r="AX19" s="33">
+        <f>IF($AW19="","",IF($AP19="","units?",IF(ISNUMBER(SEARCH("yellow",$AP19)),IF($AW19&gt;=0.05,"OVER",IF($AW19&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY19" s="34">
+        <f>IF(OR($AX19="",$AX19="skip",$AX19="units?",$AX19="UNITS?"),"",IF($AX19="OVER",$AT19*($AU19*$AR19-1),$AT19*((1-$AU19)*$AS19-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ19" s="27" t="n"/>
+      <c r="BA19" s="33">
+        <f>IF(OR($AX19="",$AX19="skip",$AX19="units?",$AX19="UNITS?",$AZ19="",$AQ19=""),"",IF($AX19="OVER",IF($AZ19&gt;$AQ19,"WON","LOST"),IF($AZ19&lt;$AQ19,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB19" s="34">
+        <f>IF($BA19="","",IF($BA19="WON",IF($AX19="OVER",$AT19*($AR19-1),$AT19*($AS19-1)),-$AT19))</f>
+        <v/>
+      </c>
+      <c r="BC19" s="34">
+        <f>IF(COUNT($BB$2:$BB19)=0,"",SUM($BB$2:$BB19))</f>
+        <v/>
+      </c>
+      <c r="BD19" s="27" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>Cambridge</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>Blackpool</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="28" t="n"/>
+      <c r="I20" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J20" s="29" t="n">
+        <v>3.304967019364976</v>
+      </c>
+      <c r="K20" s="30" t="n">
+        <v>-0.1070430724075997</v>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N20" s="31" t="n">
+        <v>0.04091304304132944</v>
+      </c>
+      <c r="O20" s="31" t="n">
+        <v>0.1265177495756873</v>
+      </c>
+      <c r="P20" s="31" t="n">
+        <v>0.1996885118904333</v>
+      </c>
+      <c r="Q20" s="31" t="n">
+        <v>0.2144000998973931</v>
+      </c>
+      <c r="R20" s="31" t="n">
+        <v>0.1760947555502536</v>
+      </c>
+      <c r="S20" s="31" t="n">
+        <v>0.1179721714210629</v>
+      </c>
+      <c r="T20" s="31" t="n">
+        <v>0.06712634394193152</v>
+      </c>
+      <c r="U20" s="31" t="n">
+        <v>0.03335545829453064</v>
+      </c>
+      <c r="V20" s="31" t="n">
+        <v>0.01477092168213912</v>
+      </c>
+      <c r="W20" s="28" t="n">
+        <v>0.8325692073829832</v>
+      </c>
+      <c r="X20" s="28" t="n">
+        <v>0.63288069549255</v>
+      </c>
+      <c r="Y20" s="28" t="n">
+        <v>0.4184805955951568</v>
+      </c>
+      <c r="Z20" s="28" t="n">
+        <v>0.2423858400449033</v>
+      </c>
+      <c r="AA20" s="28" t="n">
+        <v>0.1244136686238404</v>
+      </c>
+      <c r="AB20" s="28" t="n">
+        <v>0.05728732468190889</v>
+      </c>
+      <c r="AC20" s="29" t="n">
+        <v>1.201101351253792</v>
+      </c>
+      <c r="AD20" s="29" t="n">
+        <v>1.580076635489305</v>
+      </c>
+      <c r="AE20" s="29" t="n">
+        <v>2.38959705784641</v>
+      </c>
+      <c r="AF20" s="29" t="n">
+        <v>4.125653544013729</v>
+      </c>
+      <c r="AG20" s="29" t="n">
+        <v>8.03770205525776</v>
+      </c>
+      <c r="AH20" s="29" t="n">
+        <v>17.45586838890726</v>
+      </c>
+      <c r="AI20" s="29" t="n">
+        <v>5.972617010106451</v>
+      </c>
+      <c r="AJ20" s="29" t="n">
+        <v>2.723910150520856</v>
+      </c>
+      <c r="AK20" s="29" t="n">
+        <v>1.719633072302121</v>
+      </c>
+      <c r="AL20" s="29" t="n">
+        <v>1.319933091085929</v>
+      </c>
+      <c r="AM20" s="29" t="n">
+        <v>1.142091835111564</v>
+      </c>
+      <c r="AN20" s="29" t="n">
+        <v>1.06076859490892</v>
+      </c>
+      <c r="AO20" s="27" t="n"/>
+      <c r="AP20" s="27" t="n"/>
+      <c r="AQ20" s="27" t="n"/>
+      <c r="AR20" s="27" t="n"/>
+      <c r="AS20" s="27" t="n"/>
+      <c r="AT20" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU20" s="32">
+        <f>IFERROR(IF($AQ20="","",INDEX($W20:$AB20,$AQ20-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV20" s="32">
+        <f>IF($AR20="","",IF($AS20="",1/$AR20,(1/$AR20)/((1/$AR20)+(1/$AS20))))</f>
+        <v/>
+      </c>
+      <c r="AW20" s="32">
+        <f>IF(OR($AU20="",$AV20=""),"",$AU20-$AV20)</f>
+        <v/>
+      </c>
+      <c r="AX20" s="33">
+        <f>IF($AW20="","",IF($AP20="","units?",IF(ISNUMBER(SEARCH("yellow",$AP20)),IF($AW20&gt;=0.05,"OVER",IF($AW20&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY20" s="34">
+        <f>IF(OR($AX20="",$AX20="skip",$AX20="units?",$AX20="UNITS?"),"",IF($AX20="OVER",$AT20*($AU20*$AR20-1),$AT20*((1-$AU20)*$AS20-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ20" s="27" t="n"/>
+      <c r="BA20" s="33">
+        <f>IF(OR($AX20="",$AX20="skip",$AX20="units?",$AX20="UNITS?",$AZ20="",$AQ20=""),"",IF($AX20="OVER",IF($AZ20&gt;$AQ20,"WON","LOST"),IF($AZ20&lt;$AQ20,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB20" s="34">
+        <f>IF($BA20="","",IF($BA20="WON",IF($AX20="OVER",$AT20*($AR20-1),$AT20*($AS20-1)),-$AT20))</f>
+        <v/>
+      </c>
+      <c r="BC20" s="34">
+        <f>IF(COUNT($BB$2:$BB20)=0,"",SUM($BB$2:$BB20))</f>
+        <v/>
+      </c>
+      <c r="BD20" s="27" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Doncaster</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>Burton</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="28" t="n"/>
+      <c r="I21" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J21" s="29" t="n">
+        <v>3.751537810186114</v>
+      </c>
+      <c r="K21" s="30" t="n">
+        <v>0.01361425306270769</v>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N21" s="31" t="n">
+        <v>0.02698852415595826</v>
+      </c>
+      <c r="O21" s="31" t="n">
+        <v>0.09391874196612711</v>
+      </c>
+      <c r="P21" s="31" t="n">
+        <v>0.166815861889491</v>
+      </c>
+      <c r="Q21" s="31" t="n">
+        <v>0.2015545939750033</v>
+      </c>
+      <c r="R21" s="31" t="n">
+        <v>0.1862934539833346</v>
+      </c>
+      <c r="S21" s="31" t="n">
+        <v>0.1404475607420343</v>
+      </c>
+      <c r="T21" s="31" t="n">
+        <v>0.08993134244532287</v>
+      </c>
+      <c r="U21" s="31" t="n">
+        <v>0.05028847310928548</v>
+      </c>
+      <c r="V21" s="31" t="n">
+        <v>0.02506066480386158</v>
+      </c>
+      <c r="W21" s="28" t="n">
+        <v>0.8790927338779146</v>
+      </c>
+      <c r="X21" s="28" t="n">
+        <v>0.7122768719884236</v>
+      </c>
+      <c r="Y21" s="28" t="n">
+        <v>0.5107222780134203</v>
+      </c>
+      <c r="Z21" s="28" t="n">
+        <v>0.3244288240300858</v>
+      </c>
+      <c r="AA21" s="28" t="n">
+        <v>0.1839812632880514</v>
+      </c>
+      <c r="AB21" s="28" t="n">
+        <v>0.09404992084272856</v>
+      </c>
+      <c r="AC21" s="29" t="n">
+        <v>1.137536418471725</v>
+      </c>
+      <c r="AD21" s="29" t="n">
+        <v>1.403948435400346</v>
+      </c>
+      <c r="AE21" s="29" t="n">
+        <v>1.958011316619564</v>
+      </c>
+      <c r="AF21" s="29" t="n">
+        <v>3.082340180437437</v>
+      </c>
+      <c r="AG21" s="29" t="n">
+        <v>5.43533608873173</v>
+      </c>
+      <c r="AH21" s="29" t="n">
+        <v>10.63265116057048</v>
+      </c>
+      <c r="AI21" s="29" t="n">
+        <v>8.27080151651313</v>
+      </c>
+      <c r="AJ21" s="29" t="n">
+        <v>3.475563493664525</v>
+      </c>
+      <c r="AK21" s="29" t="n">
+        <v>2.043829005620307</v>
+      </c>
+      <c r="AL21" s="29" t="n">
+        <v>1.480228931561955</v>
+      </c>
+      <c r="AM21" s="29" t="n">
+        <v>1.225462057439247</v>
+      </c>
+      <c r="AN21" s="29" t="n">
+        <v>1.103813579805871</v>
+      </c>
+      <c r="AO21" s="27" t="n"/>
+      <c r="AP21" s="27" t="n"/>
+      <c r="AQ21" s="27" t="n"/>
+      <c r="AR21" s="27" t="n"/>
+      <c r="AS21" s="27" t="n"/>
+      <c r="AT21" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU21" s="32">
+        <f>IFERROR(IF($AQ21="","",INDEX($W21:$AB21,$AQ21-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV21" s="32">
+        <f>IF($AR21="","",IF($AS21="",1/$AR21,(1/$AR21)/((1/$AR21)+(1/$AS21))))</f>
+        <v/>
+      </c>
+      <c r="AW21" s="32">
+        <f>IF(OR($AU21="",$AV21=""),"",$AU21-$AV21)</f>
+        <v/>
+      </c>
+      <c r="AX21" s="33">
+        <f>IF($AW21="","",IF($AP21="","units?",IF(ISNUMBER(SEARCH("yellow",$AP21)),IF($AW21&gt;=0.05,"OVER",IF($AW21&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY21" s="34">
+        <f>IF(OR($AX21="",$AX21="skip",$AX21="units?",$AX21="UNITS?"),"",IF($AX21="OVER",$AT21*($AU21*$AR21-1),$AT21*((1-$AU21)*$AS21-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ21" s="27" t="n"/>
+      <c r="BA21" s="33">
+        <f>IF(OR($AX21="",$AX21="skip",$AX21="units?",$AX21="UNITS?",$AZ21="",$AQ21=""),"",IF($AX21="OVER",IF($AZ21&gt;$AQ21,"WON","LOST"),IF($AZ21&lt;$AQ21,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB21" s="34">
+        <f>IF($BA21="","",IF($BA21="WON",IF($AX21="OVER",$AT21*($AR21-1),$AT21*($AS21-1)),-$AT21))</f>
+        <v/>
+      </c>
+      <c r="BC21" s="34">
+        <f>IF(COUNT($BB$2:$BB21)=0,"",SUM($BB$2:$BB21))</f>
+        <v/>
+      </c>
+      <c r="BD21" s="27" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>Huddersfield</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>Sheffield Weds</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J22" s="29" t="n">
+        <v>3.727834213470797</v>
+      </c>
+      <c r="K22" s="30" t="n">
+        <v>0.007209865130308302</v>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N22" s="31" t="n">
+        <v>0.02758864806028996</v>
+      </c>
+      <c r="O22" s="31" t="n">
+        <v>0.09544419226960904</v>
+      </c>
+      <c r="P22" s="31" t="n">
+        <v>0.168531288615778</v>
+      </c>
+      <c r="Q22" s="31" t="n">
+        <v>0.2024332541864932</v>
+      </c>
+      <c r="R22" s="31" t="n">
+        <v>0.1860084644501721</v>
+      </c>
+      <c r="S22" s="31" t="n">
+        <v>0.139410431385298</v>
+      </c>
+      <c r="T22" s="31" t="n">
+        <v>0.08874381691624157</v>
+      </c>
+      <c r="U22" s="31" t="n">
+        <v>0.04933344396482444</v>
+      </c>
+      <c r="V22" s="31" t="n">
+        <v>0.02444058125459321</v>
+      </c>
+      <c r="W22" s="28" t="n">
+        <v>0.876967159670101</v>
+      </c>
+      <c r="X22" s="28" t="n">
+        <v>0.708435871054323</v>
+      </c>
+      <c r="Y22" s="28" t="n">
+        <v>0.5060026168678298</v>
+      </c>
+      <c r="Z22" s="28" t="n">
+        <v>0.3199941524176576</v>
+      </c>
+      <c r="AA22" s="28" t="n">
+        <v>0.1805837210323595</v>
+      </c>
+      <c r="AB22" s="28" t="n">
+        <v>0.09183990411611798</v>
+      </c>
+      <c r="AC22" s="29" t="n">
+        <v>1.140293554864907</v>
+      </c>
+      <c r="AD22" s="29" t="n">
+        <v>1.411560369623519</v>
+      </c>
+      <c r="AE22" s="29" t="n">
+        <v>1.976274364330421</v>
+      </c>
+      <c r="AF22" s="29" t="n">
+        <v>3.125057106339856</v>
+      </c>
+      <c r="AG22" s="29" t="n">
+        <v>5.53759770971164</v>
+      </c>
+      <c r="AH22" s="29" t="n">
+        <v>10.8885131101144</v>
+      </c>
+      <c r="AI22" s="29" t="n">
+        <v>8.12791119280519</v>
+      </c>
+      <c r="AJ22" s="29" t="n">
+        <v>3.429777193841002</v>
+      </c>
+      <c r="AK22" s="29" t="n">
+        <v>2.024302221318544</v>
+      </c>
+      <c r="AL22" s="29" t="n">
+        <v>1.470575589247281</v>
+      </c>
+      <c r="AM22" s="29" t="n">
+        <v>1.220380929287702</v>
+      </c>
+      <c r="AN22" s="29" t="n">
+        <v>1.101127438358468</v>
+      </c>
+      <c r="AO22" s="27" t="n"/>
+      <c r="AP22" s="27" t="n"/>
+      <c r="AQ22" s="27" t="n"/>
+      <c r="AR22" s="27" t="n"/>
+      <c r="AS22" s="27" t="n"/>
+      <c r="AT22" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU22" s="32">
+        <f>IFERROR(IF($AQ22="","",INDEX($W22:$AB22,$AQ22-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV22" s="32">
+        <f>IF($AR22="","",IF($AS22="",1/$AR22,(1/$AR22)/((1/$AR22)+(1/$AS22))))</f>
+        <v/>
+      </c>
+      <c r="AW22" s="32">
+        <f>IF(OR($AU22="",$AV22=""),"",$AU22-$AV22)</f>
+        <v/>
+      </c>
+      <c r="AX22" s="33">
+        <f>IF($AW22="","",IF($AP22="","units?",IF(ISNUMBER(SEARCH("yellow",$AP22)),IF($AW22&gt;=0.05,"OVER",IF($AW22&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY22" s="34">
+        <f>IF(OR($AX22="",$AX22="skip",$AX22="units?",$AX22="UNITS?"),"",IF($AX22="OVER",$AT22*($AU22*$AR22-1),$AT22*((1-$AU22)*$AS22-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ22" s="27" t="n"/>
+      <c r="BA22" s="33">
+        <f>IF(OR($AX22="",$AX22="skip",$AX22="units?",$AX22="UNITS?",$AZ22="",$AQ22=""),"",IF($AX22="OVER",IF($AZ22&gt;$AQ22,"WON","LOST"),IF($AZ22&lt;$AQ22,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB22" s="34">
+        <f>IF($BA22="","",IF($BA22="WON",IF($AX22="OVER",$AT22*($AR22-1),$AT22*($AS22-1)),-$AT22))</f>
+        <v/>
+      </c>
+      <c r="BC22" s="34">
+        <f>IF(COUNT($BB$2:$BB22)=0,"",SUM($BB$2:$BB22))</f>
+        <v/>
+      </c>
+      <c r="BD22" s="27" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>Leicester</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>Peterboro</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="28" t="n"/>
+      <c r="I23" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J23" s="29" t="n">
+        <v>3.491005693051016</v>
+      </c>
+      <c r="K23" s="30" t="n">
+        <v>-0.05677796492099896</v>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N23" s="31" t="n">
+        <v>0.03438748136678211</v>
+      </c>
+      <c r="O23" s="31" t="n">
+        <v>0.1119189549072325</v>
+      </c>
+      <c r="P23" s="31" t="n">
+        <v>0.1859169006309555</v>
+      </c>
+      <c r="Q23" s="31" t="n">
+        <v>0.2100895138145329</v>
+      </c>
+      <c r="R23" s="31" t="n">
+        <v>0.1816098572778559</v>
+      </c>
+      <c r="S23" s="31" t="n">
+        <v>0.1280519424499047</v>
+      </c>
+      <c r="T23" s="31" t="n">
+        <v>0.07668548945379626</v>
+      </c>
+      <c r="U23" s="31" t="n">
+        <v>0.04010520259685797</v>
+      </c>
+      <c r="V23" s="31" t="n">
+        <v>0.01869196677375093</v>
+      </c>
+      <c r="W23" s="28" t="n">
+        <v>0.8536935637259854</v>
+      </c>
+      <c r="X23" s="28" t="n">
+        <v>0.6677766630950299</v>
+      </c>
+      <c r="Y23" s="28" t="n">
+        <v>0.457687149280497</v>
+      </c>
+      <c r="Z23" s="28" t="n">
+        <v>0.2760772920026412</v>
+      </c>
+      <c r="AA23" s="28" t="n">
+        <v>0.1480253495527365</v>
+      </c>
+      <c r="AB23" s="28" t="n">
+        <v>0.07133986009894022</v>
+      </c>
+      <c r="AC23" s="29" t="n">
+        <v>1.171380507585712</v>
+      </c>
+      <c r="AD23" s="29" t="n">
+        <v>1.497506659434866</v>
+      </c>
+      <c r="AE23" s="29" t="n">
+        <v>2.184898574434613</v>
+      </c>
+      <c r="AF23" s="29" t="n">
+        <v>3.622174039545538</v>
+      </c>
+      <c r="AG23" s="29" t="n">
+        <v>6.755599652502313</v>
+      </c>
+      <c r="AH23" s="29" t="n">
+        <v>14.0174090419173</v>
+      </c>
+      <c r="AI23" s="29" t="n">
+        <v>6.83496929777661</v>
+      </c>
+      <c r="AJ23" s="29" t="n">
+        <v>3.010023345488346</v>
+      </c>
+      <c r="AK23" s="29" t="n">
+        <v>1.843954091578818</v>
+      </c>
+      <c r="AL23" s="29" t="n">
+        <v>1.381362939651906</v>
+      </c>
+      <c r="AM23" s="29" t="n">
+        <v>1.173743842583846</v>
+      </c>
+      <c r="AN23" s="29" t="n">
+        <v>1.076820202605596</v>
+      </c>
+      <c r="AO23" s="27" t="n"/>
+      <c r="AP23" s="27" t="n"/>
+      <c r="AQ23" s="27" t="n"/>
+      <c r="AR23" s="27" t="n"/>
+      <c r="AS23" s="27" t="n"/>
+      <c r="AT23" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU23" s="32">
+        <f>IFERROR(IF($AQ23="","",INDEX($W23:$AB23,$AQ23-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV23" s="32">
+        <f>IF($AR23="","",IF($AS23="",1/$AR23,(1/$AR23)/((1/$AR23)+(1/$AS23))))</f>
+        <v/>
+      </c>
+      <c r="AW23" s="32">
+        <f>IF(OR($AU23="",$AV23=""),"",$AU23-$AV23)</f>
+        <v/>
+      </c>
+      <c r="AX23" s="33">
+        <f>IF($AW23="","",IF($AP23="","units?",IF(ISNUMBER(SEARCH("yellow",$AP23)),IF($AW23&gt;=0.05,"OVER",IF($AW23&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY23" s="34">
+        <f>IF(OR($AX23="",$AX23="skip",$AX23="units?",$AX23="UNITS?"),"",IF($AX23="OVER",$AT23*($AU23*$AR23-1),$AT23*((1-$AU23)*$AS23-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ23" s="27" t="n"/>
+      <c r="BA23" s="33">
+        <f>IF(OR($AX23="",$AX23="skip",$AX23="units?",$AX23="UNITS?",$AZ23="",$AQ23=""),"",IF($AX23="OVER",IF($AZ23&gt;$AQ23,"WON","LOST"),IF($AZ23&lt;$AQ23,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB23" s="34">
+        <f>IF($BA23="","",IF($BA23="WON",IF($AX23="OVER",$AT23*($AR23-1),$AT23*($AS23-1)),-$AT23))</f>
+        <v/>
+      </c>
+      <c r="BC23" s="34">
+        <f>IF(COUNT($BB$2:$BB23)=0,"",SUM($BB$2:$BB23))</f>
+        <v/>
+      </c>
+      <c r="BD23" s="27" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="28" t="n"/>
+      <c r="I24" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J24" s="29" t="n">
+        <v>3.472278285505998</v>
+      </c>
+      <c r="K24" s="30" t="n">
+        <v>-0.06183785453719925</v>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N24" s="31" t="n">
+        <v>0.03499325045665005</v>
+      </c>
+      <c r="O24" s="31" t="n">
+        <v>0.1133207131136989</v>
+      </c>
+      <c r="P24" s="31" t="n">
+        <v>0.1873036580107105</v>
+      </c>
+      <c r="Q24" s="31" t="n">
+        <v>0.2105976399991977</v>
+      </c>
+      <c r="R24" s="31" t="n">
+        <v>0.1811382955365963</v>
+      </c>
+      <c r="S24" s="31" t="n">
+        <v>0.1270804564707207</v>
+      </c>
+      <c r="T24" s="31" t="n">
+        <v>0.07572295001686584</v>
+      </c>
+      <c r="U24" s="31" t="n">
+        <v>0.03940367979903716</v>
+      </c>
+      <c r="V24" s="31" t="n">
+        <v>0.01827312405832273</v>
+      </c>
+      <c r="W24" s="28" t="n">
+        <v>0.851686036429651</v>
+      </c>
+      <c r="X24" s="28" t="n">
+        <v>0.6643823784189405</v>
+      </c>
+      <c r="Y24" s="28" t="n">
+        <v>0.4537847384197429</v>
+      </c>
+      <c r="Z24" s="28" t="n">
+        <v>0.2726464428831465</v>
+      </c>
+      <c r="AA24" s="28" t="n">
+        <v>0.1455659864124258</v>
+      </c>
+      <c r="AB24" s="28" t="n">
+        <v>0.06984303639556</v>
+      </c>
+      <c r="AC24" s="29" t="n">
+        <v>1.174141593529108</v>
+      </c>
+      <c r="AD24" s="29" t="n">
+        <v>1.505157319764777</v>
+      </c>
+      <c r="AE24" s="29" t="n">
+        <v>2.203688038258831</v>
+      </c>
+      <c r="AF24" s="29" t="n">
+        <v>3.667753701186521</v>
+      </c>
+      <c r="AG24" s="29" t="n">
+        <v>6.869736705982559</v>
+      </c>
+      <c r="AH24" s="29" t="n">
+        <v>14.31781966546304</v>
+      </c>
+      <c r="AI24" s="29" t="n">
+        <v>6.742453481297972</v>
+      </c>
+      <c r="AJ24" s="29" t="n">
+        <v>2.979581332139548</v>
+      </c>
+      <c r="AK24" s="29" t="n">
+        <v>1.830780042847753</v>
+      </c>
+      <c r="AL24" s="29" t="n">
+        <v>1.374847198058515</v>
+      </c>
+      <c r="AM24" s="29" t="n">
+        <v>1.170365392877125</v>
+      </c>
+      <c r="AN24" s="29" t="n">
+        <v>1.075087366034343</v>
+      </c>
+      <c r="AO24" s="27" t="n"/>
+      <c r="AP24" s="27" t="n"/>
+      <c r="AQ24" s="27" t="n"/>
+      <c r="AR24" s="27" t="n"/>
+      <c r="AS24" s="27" t="n"/>
+      <c r="AT24" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU24" s="32">
+        <f>IFERROR(IF($AQ24="","",INDEX($W24:$AB24,$AQ24-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV24" s="32">
+        <f>IF($AR24="","",IF($AS24="",1/$AR24,(1/$AR24)/((1/$AR24)+(1/$AS24))))</f>
+        <v/>
+      </c>
+      <c r="AW24" s="32">
+        <f>IF(OR($AU24="",$AV24=""),"",$AU24-$AV24)</f>
+        <v/>
+      </c>
+      <c r="AX24" s="33">
+        <f>IF($AW24="","",IF($AP24="","units?",IF(ISNUMBER(SEARCH("yellow",$AP24)),IF($AW24&gt;=0.05,"OVER",IF($AW24&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY24" s="34">
+        <f>IF(OR($AX24="",$AX24="skip",$AX24="units?",$AX24="UNITS?"),"",IF($AX24="OVER",$AT24*($AU24*$AR24-1),$AT24*((1-$AU24)*$AS24-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ24" s="27" t="n"/>
+      <c r="BA24" s="33">
+        <f>IF(OR($AX24="",$AX24="skip",$AX24="units?",$AX24="UNITS?",$AZ24="",$AQ24=""),"",IF($AX24="OVER",IF($AZ24&gt;$AQ24,"WON","LOST"),IF($AZ24&lt;$AQ24,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB24" s="34">
+        <f>IF($BA24="","",IF($BA24="WON",IF($AX24="OVER",$AT24*($AR24-1),$AT24*($AS24-1)),-$AT24))</f>
+        <v/>
+      </c>
+      <c r="BC24" s="34">
+        <f>IF(COUNT($BB$2:$BB24)=0,"",SUM($BB$2:$BB24))</f>
+        <v/>
+      </c>
+      <c r="BD24" s="27" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Mansfield</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J25" s="29" t="n">
+        <v>3.720226171894756</v>
+      </c>
+      <c r="K25" s="30" t="n">
+        <v>0.005154276257278712</v>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N25" s="31" t="n">
+        <v>0.02778414135832455</v>
+      </c>
+      <c r="O25" s="31" t="n">
+        <v>0.09593843180147762</v>
+      </c>
+      <c r="P25" s="31" t="n">
+        <v>0.1690830983031342</v>
+      </c>
+      <c r="Q25" s="31" t="n">
+        <v>0.2027113471990683</v>
+      </c>
+      <c r="R25" s="31" t="n">
+        <v>0.1859111590185598</v>
+      </c>
+      <c r="S25" s="31" t="n">
+        <v>0.1390735592131372</v>
+      </c>
+      <c r="T25" s="31" t="n">
+        <v>0.08836167703392608</v>
+      </c>
+      <c r="U25" s="31" t="n">
+        <v>0.04902796054473706</v>
+      </c>
+      <c r="V25" s="31" t="n">
+        <v>0.02424322940484183</v>
+      </c>
+      <c r="W25" s="28" t="n">
+        <v>0.8762774268401978</v>
+      </c>
+      <c r="X25" s="28" t="n">
+        <v>0.7071943285370637</v>
+      </c>
+      <c r="Y25" s="28" t="n">
+        <v>0.5044829813379953</v>
+      </c>
+      <c r="Z25" s="28" t="n">
+        <v>0.3185718223194355</v>
+      </c>
+      <c r="AA25" s="28" t="n">
+        <v>0.1794982631062984</v>
+      </c>
+      <c r="AB25" s="28" t="n">
+        <v>0.09113658607237229</v>
+      </c>
+      <c r="AC25" s="29" t="n">
+        <v>1.141191099268571</v>
+      </c>
+      <c r="AD25" s="29" t="n">
+        <v>1.414038489347968</v>
+      </c>
+      <c r="AE25" s="29" t="n">
+        <v>1.982227422910856</v>
+      </c>
+      <c r="AF25" s="29" t="n">
+        <v>3.139009573160833</v>
+      </c>
+      <c r="AG25" s="29" t="n">
+        <v>5.571084548087259</v>
+      </c>
+      <c r="AH25" s="29" t="n">
+        <v>10.97254179793274</v>
+      </c>
+      <c r="AI25" s="29" t="n">
+        <v>8.082599435661454</v>
+      </c>
+      <c r="AJ25" s="29" t="n">
+        <v>3.41523439421009</v>
+      </c>
+      <c r="AK25" s="29" t="n">
+        <v>2.018094156887286</v>
+      </c>
+      <c r="AL25" s="29" t="n">
+        <v>1.467506089055175</v>
+      </c>
+      <c r="AM25" s="29" t="n">
+        <v>1.218766463293365</v>
+      </c>
+      <c r="AN25" s="29" t="n">
+        <v>1.100275338049453</v>
+      </c>
+      <c r="AO25" s="27" t="n"/>
+      <c r="AP25" s="27" t="n"/>
+      <c r="AQ25" s="27" t="n"/>
+      <c r="AR25" s="27" t="n"/>
+      <c r="AS25" s="27" t="n"/>
+      <c r="AT25" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU25" s="32">
+        <f>IFERROR(IF($AQ25="","",INDEX($W25:$AB25,$AQ25-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV25" s="32">
+        <f>IF($AR25="","",IF($AS25="",1/$AR25,(1/$AR25)/((1/$AR25)+(1/$AS25))))</f>
+        <v/>
+      </c>
+      <c r="AW25" s="32">
+        <f>IF(OR($AU25="",$AV25=""),"",$AU25-$AV25)</f>
+        <v/>
+      </c>
+      <c r="AX25" s="33">
+        <f>IF($AW25="","",IF($AP25="","units?",IF(ISNUMBER(SEARCH("yellow",$AP25)),IF($AW25&gt;=0.05,"OVER",IF($AW25&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY25" s="34">
+        <f>IF(OR($AX25="",$AX25="skip",$AX25="units?",$AX25="UNITS?"),"",IF($AX25="OVER",$AT25*($AU25*$AR25-1),$AT25*((1-$AU25)*$AS25-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ25" s="27" t="n"/>
+      <c r="BA25" s="33">
+        <f>IF(OR($AX25="",$AX25="skip",$AX25="units?",$AX25="UNITS?",$AZ25="",$AQ25=""),"",IF($AX25="OVER",IF($AZ25&gt;$AQ25,"WON","LOST"),IF($AZ25&lt;$AQ25,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB25" s="34">
+        <f>IF($BA25="","",IF($BA25="WON",IF($AX25="OVER",$AT25*($AR25-1),$AT25*($AS25-1)),-$AT25))</f>
+        <v/>
+      </c>
+      <c r="BC25" s="34">
+        <f>IF(COUNT($BB$2:$BB25)=0,"",SUM($BB$2:$BB25))</f>
+        <v/>
+      </c>
+      <c r="BD25" s="27" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>Oxford</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J26" s="29" t="n">
+        <v>4.063091839379347</v>
+      </c>
+      <c r="K26" s="30" t="n">
+        <v>0.09779189449069325</v>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N26" s="31" t="n">
+        <v>0.02023224186923879</v>
+      </c>
+      <c r="O26" s="31" t="n">
+        <v>0.07579861360626976</v>
+      </c>
+      <c r="P26" s="31" t="n">
+        <v>0.1449407362162883</v>
+      </c>
+      <c r="Q26" s="31" t="n">
+        <v>0.1885341139498504</v>
+      </c>
+      <c r="R26" s="31" t="n">
+        <v>0.1876026468073211</v>
+      </c>
+      <c r="S26" s="31" t="n">
+        <v>0.152264861235052</v>
+      </c>
+      <c r="T26" s="31" t="n">
+        <v>0.1049640767556764</v>
+      </c>
+      <c r="U26" s="31" t="n">
+        <v>0.06318910249377363</v>
+      </c>
+      <c r="V26" s="31" t="n">
+        <v>0.03390083917040931</v>
+      </c>
+      <c r="W26" s="28" t="n">
+        <v>0.9039691445244915</v>
+      </c>
+      <c r="X26" s="28" t="n">
+        <v>0.7590284083082032</v>
+      </c>
+      <c r="Y26" s="28" t="n">
+        <v>0.5704942943583527</v>
+      </c>
+      <c r="Z26" s="28" t="n">
+        <v>0.3828916475510317</v>
+      </c>
+      <c r="AA26" s="28" t="n">
+        <v>0.2306267863159797</v>
+      </c>
+      <c r="AB26" s="28" t="n">
+        <v>0.1256627095603033</v>
+      </c>
+      <c r="AC26" s="29" t="n">
+        <v>1.106232448371922</v>
+      </c>
+      <c r="AD26" s="29" t="n">
+        <v>1.317473745454268</v>
+      </c>
+      <c r="AE26" s="29" t="n">
+        <v>1.752865909245809</v>
+      </c>
+      <c r="AF26" s="29" t="n">
+        <v>2.611704920689659</v>
+      </c>
+      <c r="AG26" s="29" t="n">
+        <v>4.336009775681083</v>
+      </c>
+      <c r="AH26" s="29" t="n">
+        <v>7.957810264469249</v>
+      </c>
+      <c r="AI26" s="29" t="n">
+        <v>10.41331970904954</v>
+      </c>
+      <c r="AJ26" s="29" t="n">
+        <v>4.149866766365564</v>
+      </c>
+      <c r="AK26" s="29" t="n">
+        <v>2.328257778336332</v>
+      </c>
+      <c r="AL26" s="29" t="n">
+        <v>1.620460970964892</v>
+      </c>
+      <c r="AM26" s="29" t="n">
+        <v>1.29975931344381</v>
+      </c>
+      <c r="AN26" s="29" t="n">
+        <v>1.143723378762798</v>
+      </c>
+      <c r="AO26" s="27" t="n"/>
+      <c r="AP26" s="27" t="n"/>
+      <c r="AQ26" s="27" t="n"/>
+      <c r="AR26" s="27" t="n"/>
+      <c r="AS26" s="27" t="n"/>
+      <c r="AT26" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU26" s="32">
+        <f>IFERROR(IF($AQ26="","",INDEX($W26:$AB26,$AQ26-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV26" s="32">
+        <f>IF($AR26="","",IF($AS26="",1/$AR26,(1/$AR26)/((1/$AR26)+(1/$AS26))))</f>
+        <v/>
+      </c>
+      <c r="AW26" s="32">
+        <f>IF(OR($AU26="",$AV26=""),"",$AU26-$AV26)</f>
+        <v/>
+      </c>
+      <c r="AX26" s="33">
+        <f>IF($AW26="","",IF($AP26="","units?",IF(ISNUMBER(SEARCH("yellow",$AP26)),IF($AW26&gt;=0.05,"OVER",IF($AW26&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY26" s="34">
+        <f>IF(OR($AX26="",$AX26="skip",$AX26="units?",$AX26="UNITS?"),"",IF($AX26="OVER",$AT26*($AU26*$AR26-1),$AT26*((1-$AU26)*$AS26-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ26" s="27" t="n"/>
+      <c r="BA26" s="33">
+        <f>IF(OR($AX26="",$AX26="skip",$AX26="units?",$AX26="UNITS?",$AZ26="",$AQ26=""),"",IF($AX26="OVER",IF($AZ26&gt;$AQ26,"WON","LOST"),IF($AZ26&lt;$AQ26,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB26" s="34">
+        <f>IF($BA26="","",IF($BA26="WON",IF($AX26="OVER",$AT26*($AR26-1),$AT26*($AS26-1)),-$AT26))</f>
+        <v/>
+      </c>
+      <c r="BC26" s="34">
+        <f>IF(COUNT($BB$2:$BB26)=0,"",SUM($BB$2:$BB26))</f>
+        <v/>
+      </c>
+      <c r="BD26" s="27" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Plymouth</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="28" t="n"/>
+      <c r="I27" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J27" s="29" t="n">
+        <v>3.905587086700044</v>
+      </c>
+      <c r="K27" s="30" t="n">
+        <v>0.05523626255560199</v>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N27" s="31" t="n">
+        <v>0.02339977957071827</v>
+      </c>
+      <c r="O27" s="31" t="n">
+        <v>0.08452258816652532</v>
+      </c>
+      <c r="P27" s="31" t="n">
+        <v>0.1558280925392635</v>
+      </c>
+      <c r="Q27" s="31" t="n">
+        <v>0.1954289967925902</v>
+      </c>
+      <c r="R27" s="31" t="n">
+        <v>0.187491587602921</v>
+      </c>
+      <c r="S27" s="31" t="n">
+        <v>0.1467189745485605</v>
+      </c>
+      <c r="T27" s="31" t="n">
+        <v>0.09751491551459879</v>
+      </c>
+      <c r="U27" s="31" t="n">
+        <v>0.05659998451145157</v>
+      </c>
+      <c r="V27" s="31" t="n">
+        <v>0.02927711919935828</v>
+      </c>
+      <c r="W27" s="28" t="n">
+        <v>0.8920776322627564</v>
+      </c>
+      <c r="X27" s="28" t="n">
+        <v>0.7362495397234929</v>
+      </c>
+      <c r="Y27" s="28" t="n">
+        <v>0.5408205429309028</v>
+      </c>
+      <c r="Z27" s="28" t="n">
+        <v>0.3533289553279817</v>
+      </c>
+      <c r="AA27" s="28" t="n">
+        <v>0.2066099807794212</v>
+      </c>
+      <c r="AB27" s="28" t="n">
+        <v>0.1090950652648224</v>
+      </c>
+      <c r="AC27" s="29" t="n">
+        <v>1.120978672521469</v>
+      </c>
+      <c r="AD27" s="29" t="n">
+        <v>1.358235144534775</v>
+      </c>
+      <c r="AE27" s="29" t="n">
+        <v>1.849042187969852</v>
+      </c>
+      <c r="AF27" s="29" t="n">
+        <v>2.830223747362393</v>
+      </c>
+      <c r="AG27" s="29" t="n">
+        <v>4.840037234540038</v>
+      </c>
+      <c r="AH27" s="29" t="n">
+        <v>9.166317445913378</v>
+      </c>
+      <c r="AI27" s="29" t="n">
+        <v>9.265919762200543</v>
+      </c>
+      <c r="AJ27" s="29" t="n">
+        <v>3.791462577739708</v>
+      </c>
+      <c r="AK27" s="29" t="n">
+        <v>2.17779777515073</v>
+      </c>
+      <c r="AL27" s="29" t="n">
+        <v>1.546381283403813</v>
+      </c>
+      <c r="AM27" s="29" t="n">
+        <v>1.260414141562297</v>
+      </c>
+      <c r="AN27" s="29" t="n">
+        <v>1.122454215945331</v>
+      </c>
+      <c r="AO27" s="27" t="n"/>
+      <c r="AP27" s="27" t="n"/>
+      <c r="AQ27" s="27" t="n"/>
+      <c r="AR27" s="27" t="n"/>
+      <c r="AS27" s="27" t="n"/>
+      <c r="AT27" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU27" s="32">
+        <f>IFERROR(IF($AQ27="","",INDEX($W27:$AB27,$AQ27-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV27" s="32">
+        <f>IF($AR27="","",IF($AS27="",1/$AR27,(1/$AR27)/((1/$AR27)+(1/$AS27))))</f>
+        <v/>
+      </c>
+      <c r="AW27" s="32">
+        <f>IF(OR($AU27="",$AV27=""),"",$AU27-$AV27)</f>
+        <v/>
+      </c>
+      <c r="AX27" s="33">
+        <f>IF($AW27="","",IF($AP27="","units?",IF(ISNUMBER(SEARCH("yellow",$AP27)),IF($AW27&gt;=0.05,"OVER",IF($AW27&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY27" s="34">
+        <f>IF(OR($AX27="",$AX27="skip",$AX27="units?",$AX27="UNITS?"),"",IF($AX27="OVER",$AT27*($AU27*$AR27-1),$AT27*((1-$AU27)*$AS27-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ27" s="27" t="n"/>
+      <c r="BA27" s="33">
+        <f>IF(OR($AX27="",$AX27="skip",$AX27="units?",$AX27="UNITS?",$AZ27="",$AQ27=""),"",IF($AX27="OVER",IF($AZ27&gt;$AQ27,"WON","LOST"),IF($AZ27&lt;$AQ27,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB27" s="34">
+        <f>IF($BA27="","",IF($BA27="WON",IF($AX27="OVER",$AT27*($AR27-1),$AT27*($AS27-1)),-$AT27))</f>
+        <v/>
+      </c>
+      <c r="BC27" s="34">
+        <f>IF(COUNT($BB$2:$BB27)=0,"",SUM($BB$2:$BB27))</f>
+        <v/>
+      </c>
+      <c r="BD27" s="27" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Stevenage</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>Wigan</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="28" t="n"/>
+      <c r="I28" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J28" s="29" t="n">
+        <v>3.687241410001837</v>
+      </c>
+      <c r="K28" s="30" t="n">
+        <v>-0.003757755682733621</v>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N28" s="31" t="n">
+        <v>0.02864819776725999</v>
+      </c>
+      <c r="O28" s="31" t="n">
+        <v>0.09810742049908044</v>
+      </c>
+      <c r="P28" s="31" t="n">
+        <v>0.1714819268638018</v>
+      </c>
+      <c r="Q28" s="31" t="n">
+        <v>0.2038943226139211</v>
+      </c>
+      <c r="R28" s="31" t="n">
+        <v>0.185456238605217</v>
+      </c>
+      <c r="S28" s="31" t="n">
+        <v>0.1375908247497438</v>
+      </c>
+      <c r="T28" s="31" t="n">
+        <v>0.0866997349968803</v>
+      </c>
+      <c r="U28" s="31" t="n">
+        <v>0.04770968660557076</v>
+      </c>
+      <c r="V28" s="31" t="n">
+        <v>0.0233971049209775</v>
+      </c>
+      <c r="W28" s="28" t="n">
+        <v>0.8732443817336596</v>
+      </c>
+      <c r="X28" s="28" t="n">
+        <v>0.7017624548698578</v>
+      </c>
+      <c r="Y28" s="28" t="n">
+        <v>0.4978681322559366</v>
+      </c>
+      <c r="Z28" s="28" t="n">
+        <v>0.3124118936507196</v>
+      </c>
+      <c r="AA28" s="28" t="n">
+        <v>0.1748210689009758</v>
+      </c>
+      <c r="AB28" s="28" t="n">
+        <v>0.08812133390409549</v>
+      </c>
+      <c r="AC28" s="29" t="n">
+        <v>1.145154805364669</v>
+      </c>
+      <c r="AD28" s="29" t="n">
+        <v>1.42498361526829</v>
+      </c>
+      <c r="AE28" s="29" t="n">
+        <v>2.008563985545343</v>
+      </c>
+      <c r="AF28" s="29" t="n">
+        <v>3.200902463457465</v>
+      </c>
+      <c r="AG28" s="29" t="n">
+        <v>5.720134342425464</v>
+      </c>
+      <c r="AH28" s="29" t="n">
+        <v>11.3479898192227</v>
+      </c>
+      <c r="AI28" s="29" t="n">
+        <v>7.889196657924765</v>
+      </c>
+      <c r="AJ28" s="29" t="n">
+        <v>3.353031891285281</v>
+      </c>
+      <c r="AK28" s="29" t="n">
+        <v>1.9915087335379</v>
+      </c>
+      <c r="AL28" s="29" t="n">
+        <v>1.454359071609684</v>
+      </c>
+      <c r="AM28" s="29" t="n">
+        <v>1.2118583767864</v>
+      </c>
+      <c r="AN28" s="29" t="n">
+        <v>1.096637126385878</v>
+      </c>
+      <c r="AO28" s="27" t="n"/>
+      <c r="AP28" s="27" t="n"/>
+      <c r="AQ28" s="27" t="n"/>
+      <c r="AR28" s="27" t="n"/>
+      <c r="AS28" s="27" t="n"/>
+      <c r="AT28" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU28" s="32">
+        <f>IFERROR(IF($AQ28="","",INDEX($W28:$AB28,$AQ28-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV28" s="32">
+        <f>IF($AR28="","",IF($AS28="",1/$AR28,(1/$AR28)/((1/$AR28)+(1/$AS28))))</f>
+        <v/>
+      </c>
+      <c r="AW28" s="32">
+        <f>IF(OR($AU28="",$AV28=""),"",$AU28-$AV28)</f>
+        <v/>
+      </c>
+      <c r="AX28" s="33">
+        <f>IF($AW28="","",IF($AP28="","units?",IF(ISNUMBER(SEARCH("yellow",$AP28)),IF($AW28&gt;=0.05,"OVER",IF($AW28&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY28" s="34">
+        <f>IF(OR($AX28="",$AX28="skip",$AX28="units?",$AX28="UNITS?"),"",IF($AX28="OVER",$AT28*($AU28*$AR28-1),$AT28*((1-$AU28)*$AS28-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ28" s="27" t="n"/>
+      <c r="BA28" s="33">
+        <f>IF(OR($AX28="",$AX28="skip",$AX28="units?",$AX28="UNITS?",$AZ28="",$AQ28=""),"",IF($AX28="OVER",IF($AZ28&gt;$AQ28,"WON","LOST"),IF($AZ28&lt;$AQ28,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB28" s="34">
+        <f>IF($BA28="","",IF($BA28="WON",IF($AX28="OVER",$AT28*($AR28-1),$AT28*($AS28-1)),-$AT28))</f>
+        <v/>
+      </c>
+      <c r="BC28" s="34">
+        <f>IF(COUNT($BB$2:$BB28)=0,"",SUM($BB$2:$BB28))</f>
+        <v/>
+      </c>
+      <c r="BD28" s="27" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Stockport</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="28" t="n"/>
+      <c r="I29" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J29" s="29" t="n">
+        <v>3.689875699743188</v>
+      </c>
+      <c r="K29" s="30" t="n">
+        <v>-0.003046006591126416</v>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N29" s="31" t="n">
+        <v>0.0285781939667812</v>
+      </c>
+      <c r="O29" s="31" t="n">
+        <v>0.09793262390799831</v>
+      </c>
+      <c r="P29" s="31" t="n">
+        <v>0.1712899760041503</v>
+      </c>
+      <c r="Q29" s="31" t="n">
+        <v>0.2038012235013743</v>
+      </c>
+      <c r="R29" s="31" t="n">
+        <v>0.1854945529805977</v>
+      </c>
+      <c r="S29" s="31" t="n">
+        <v>0.1377105611340274</v>
+      </c>
+      <c r="T29" s="31" t="n">
+        <v>0.0868327597501516</v>
+      </c>
+      <c r="U29" s="31" t="n">
+        <v>0.04781459240678601</v>
+      </c>
+      <c r="V29" s="31" t="n">
+        <v>0.02346410951214777</v>
+      </c>
+      <c r="W29" s="28" t="n">
+        <v>0.8734891821252204</v>
+      </c>
+      <c r="X29" s="28" t="n">
+        <v>0.7021992061210702</v>
+      </c>
+      <c r="Y29" s="28" t="n">
+        <v>0.4983979826196959</v>
+      </c>
+      <c r="Z29" s="28" t="n">
+        <v>0.3129034296390982</v>
+      </c>
+      <c r="AA29" s="28" t="n">
+        <v>0.1751928685050708</v>
+      </c>
+      <c r="AB29" s="28" t="n">
+        <v>0.08836010875491918</v>
+      </c>
+      <c r="AC29" s="29" t="n">
+        <v>1.144833869112123</v>
+      </c>
+      <c r="AD29" s="29" t="n">
+        <v>1.424097309257829</v>
+      </c>
+      <c r="AE29" s="29" t="n">
+        <v>2.006428667194371</v>
+      </c>
+      <c r="AF29" s="29" t="n">
+        <v>3.195874206790883</v>
+      </c>
+      <c r="AG29" s="29" t="n">
+        <v>5.70799490032356</v>
+      </c>
+      <c r="AH29" s="29" t="n">
+        <v>11.31732423251831</v>
+      </c>
+      <c r="AI29" s="29" t="n">
+        <v>7.904462375619135</v>
+      </c>
+      <c r="AJ29" s="29" t="n">
+        <v>3.357949409653178</v>
+      </c>
+      <c r="AK29" s="29" t="n">
+        <v>1.993612396582171</v>
+      </c>
+      <c r="AL29" s="29" t="n">
+        <v>1.455399492788537</v>
+      </c>
+      <c r="AM29" s="29" t="n">
+        <v>1.212404648087294</v>
+      </c>
+      <c r="AN29" s="29" t="n">
+        <v>1.096924355333157</v>
+      </c>
+      <c r="AO29" s="27" t="n"/>
+      <c r="AP29" s="27" t="n"/>
+      <c r="AQ29" s="27" t="n"/>
+      <c r="AR29" s="27" t="n"/>
+      <c r="AS29" s="27" t="n"/>
+      <c r="AT29" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU29" s="32">
+        <f>IFERROR(IF($AQ29="","",INDEX($W29:$AB29,$AQ29-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV29" s="32">
+        <f>IF($AR29="","",IF($AS29="",1/$AR29,(1/$AR29)/((1/$AR29)+(1/$AS29))))</f>
+        <v/>
+      </c>
+      <c r="AW29" s="32">
+        <f>IF(OR($AU29="",$AV29=""),"",$AU29-$AV29)</f>
+        <v/>
+      </c>
+      <c r="AX29" s="33">
+        <f>IF($AW29="","",IF($AP29="","units?",IF(ISNUMBER(SEARCH("yellow",$AP29)),IF($AW29&gt;=0.05,"OVER",IF($AW29&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY29" s="34">
+        <f>IF(OR($AX29="",$AX29="skip",$AX29="units?",$AX29="UNITS?"),"",IF($AX29="OVER",$AT29*($AU29*$AR29-1),$AT29*((1-$AU29)*$AS29-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ29" s="27" t="n"/>
+      <c r="BA29" s="33">
+        <f>IF(OR($AX29="",$AX29="skip",$AX29="units?",$AX29="UNITS?",$AZ29="",$AQ29=""),"",IF($AX29="OVER",IF($AZ29&gt;$AQ29,"WON","LOST"),IF($AZ29&lt;$AQ29,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB29" s="34">
+        <f>IF($BA29="","",IF($BA29="WON",IF($AX29="OVER",$AT29*($AR29-1),$AT29*($AS29-1)),-$AT29))</f>
+        <v/>
+      </c>
+      <c r="BC29" s="34">
+        <f>IF(COUNT($BB$2:$BB29)=0,"",SUM($BB$2:$BB29))</f>
+        <v/>
+      </c>
+      <c r="BD29" s="27" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>Wycombe</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
+        <is>
+          <t>Luton</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="28" t="n"/>
+      <c r="I30" s="29" t="n">
+        <v>3.701149425287356</v>
+      </c>
+      <c r="J30" s="29" t="n">
+        <v>4.139827153780002</v>
+      </c>
+      <c r="K30" s="30" t="n">
+        <v>0.1185247278846591</v>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M30" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N30" s="31" t="n">
+        <v>0.01885116447885393</v>
+      </c>
+      <c r="O30" s="31" t="n">
+        <v>0.07185255785092022</v>
+      </c>
+      <c r="P30" s="31" t="n">
+        <v>0.1397842465784372</v>
+      </c>
+      <c r="Q30" s="31" t="n">
+        <v>0.1849884048729343</v>
+      </c>
+      <c r="R30" s="31" t="n">
+        <v>0.1872752221578901</v>
+      </c>
+      <c r="S30" s="31" t="n">
+        <v>0.1546421385281964</v>
+      </c>
+      <c r="T30" s="31" t="n">
+        <v>0.1084565142440871</v>
+      </c>
+      <c r="U30" s="31" t="n">
+        <v>0.06642689234202996</v>
+      </c>
+      <c r="V30" s="31" t="n">
+        <v>0.03625759498163808</v>
+      </c>
+      <c r="W30" s="28" t="n">
+        <v>0.9092962776702258</v>
+      </c>
+      <c r="X30" s="28" t="n">
+        <v>0.7695120310917887</v>
+      </c>
+      <c r="Y30" s="28" t="n">
+        <v>0.5845236262188543</v>
+      </c>
+      <c r="Z30" s="28" t="n">
+        <v>0.3972484040609643</v>
+      </c>
+      <c r="AA30" s="28" t="n">
+        <v>0.2426062655327679</v>
+      </c>
+      <c r="AB30" s="28" t="n">
+        <v>0.1341497512886808</v>
+      </c>
+      <c r="AC30" s="29" t="n">
+        <v>1.099751560142941</v>
+      </c>
+      <c r="AD30" s="29" t="n">
+        <v>1.299524841192143</v>
+      </c>
+      <c r="AE30" s="29" t="n">
+        <v>1.710794833852593</v>
+      </c>
+      <c r="AF30" s="29" t="n">
+        <v>2.517316595302252</v>
+      </c>
+      <c r="AG30" s="29" t="n">
+        <v>4.121905086845064</v>
+      </c>
+      <c r="AH30" s="29" t="n">
+        <v>7.454355974526338</v>
+      </c>
+      <c r="AI30" s="29" t="n">
+        <v>11.02490586179331</v>
+      </c>
+      <c r="AJ30" s="29" t="n">
+        <v>4.338621250978338</v>
+      </c>
+      <c r="AK30" s="29" t="n">
+        <v>2.406875728935565</v>
+      </c>
+      <c r="AL30" s="29" t="n">
+        <v>1.659058236821563</v>
+      </c>
+      <c r="AM30" s="29" t="n">
+        <v>1.320317233286096</v>
+      </c>
+      <c r="AN30" s="29" t="n">
+        <v>1.154934125720171</v>
+      </c>
+      <c r="AO30" s="27" t="n"/>
+      <c r="AP30" s="27" t="n"/>
+      <c r="AQ30" s="27" t="n"/>
+      <c r="AR30" s="27" t="n"/>
+      <c r="AS30" s="27" t="n"/>
+      <c r="AT30" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU30" s="32">
+        <f>IFERROR(IF($AQ30="","",INDEX($W30:$AB30,$AQ30-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV30" s="32">
+        <f>IF($AR30="","",IF($AS30="",1/$AR30,(1/$AR30)/((1/$AR30)+(1/$AS30))))</f>
+        <v/>
+      </c>
+      <c r="AW30" s="32">
+        <f>IF(OR($AU30="",$AV30=""),"",$AU30-$AV30)</f>
+        <v/>
+      </c>
+      <c r="AX30" s="33">
+        <f>IF($AW30="","",IF($AP30="","units?",IF(ISNUMBER(SEARCH("yellow",$AP30)),IF($AW30&gt;=0.05,"OVER",IF($AW30&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY30" s="34">
+        <f>IF(OR($AX30="",$AX30="skip",$AX30="units?",$AX30="UNITS?"),"",IF($AX30="OVER",$AT30*($AU30*$AR30-1),$AT30*((1-$AU30)*$AS30-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ30" s="27" t="n"/>
+      <c r="BA30" s="33">
+        <f>IF(OR($AX30="",$AX30="skip",$AX30="units?",$AX30="UNITS?",$AZ30="",$AQ30=""),"",IF($AX30="OVER",IF($AZ30&gt;$AQ30,"WON","LOST"),IF($AZ30&lt;$AQ30,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB30" s="34">
+        <f>IF($BA30="","",IF($BA30="WON",IF($AX30="OVER",$AT30*($AR30-1),$AT30*($AS30-1)),-$AT30))</f>
+        <v/>
+      </c>
+      <c r="BC30" s="34">
+        <f>IF(COUNT($BB$2:$BB30)=0,"",SUM($BB$2:$BB30))</f>
+        <v/>
+      </c>
+      <c r="BD30" s="27" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>Bristol Rvs</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="inlineStr">
+        <is>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="28" t="n"/>
+      <c r="I31" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J31" s="29" t="n">
+        <v>4.087945917612043</v>
+      </c>
+      <c r="K31" s="30" t="n">
+        <v>0.05858654615849046</v>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M31" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N31" s="31" t="n">
+        <v>0.01977395955539378</v>
+      </c>
+      <c r="O31" s="31" t="n">
+        <v>0.074499335769557</v>
+      </c>
+      <c r="P31" s="31" t="n">
+        <v>0.1432593928996627</v>
+      </c>
+      <c r="Q31" s="31" t="n">
+        <v>0.1873976294049084</v>
+      </c>
+      <c r="R31" s="31" t="n">
+        <v>0.1875230313641918</v>
+      </c>
+      <c r="S31" s="31" t="n">
+        <v>0.1530582874008297</v>
+      </c>
+      <c r="T31" s="31" t="n">
+        <v>0.1061058561041565</v>
+      </c>
+      <c r="U31" s="31" t="n">
+        <v>0.06423657183956694</v>
+      </c>
+      <c r="V31" s="31" t="n">
+        <v>0.03465709225701136</v>
+      </c>
+      <c r="W31" s="28" t="n">
+        <v>0.9057267046750492</v>
+      </c>
+      <c r="X31" s="28" t="n">
+        <v>0.7624673117753865</v>
+      </c>
+      <c r="Y31" s="28" t="n">
+        <v>0.5750696823704781</v>
+      </c>
+      <c r="Z31" s="28" t="n">
+        <v>0.3875466510062863</v>
+      </c>
+      <c r="AA31" s="28" t="n">
+        <v>0.2344883636054567</v>
+      </c>
+      <c r="AB31" s="28" t="n">
+        <v>0.1283825075013001</v>
+      </c>
+      <c r="AC31" s="29" t="n">
+        <v>1.104085807383557</v>
+      </c>
+      <c r="AD31" s="29" t="n">
+        <v>1.311531634938584</v>
+      </c>
+      <c r="AE31" s="29" t="n">
+        <v>1.738919700788136</v>
+      </c>
+      <c r="AF31" s="29" t="n">
+        <v>2.580334515608495</v>
+      </c>
+      <c r="AG31" s="29" t="n">
+        <v>4.264603942917061</v>
+      </c>
+      <c r="AH31" s="29" t="n">
+        <v>7.789223154017874</v>
+      </c>
+      <c r="AI31" s="29" t="n">
+        <v>10.60745778062704</v>
+      </c>
+      <c r="AJ31" s="29" t="n">
+        <v>4.209946881308349</v>
+      </c>
+      <c r="AK31" s="29" t="n">
+        <v>2.353327024483709</v>
+      </c>
+      <c r="AL31" s="29" t="n">
+        <v>1.632777421566951</v>
+      </c>
+      <c r="AM31" s="29" t="n">
+        <v>1.306315870925052</v>
+      </c>
+      <c r="AN31" s="29" t="n">
+        <v>1.147292256759626</v>
+      </c>
+      <c r="AO31" s="27" t="n"/>
+      <c r="AP31" s="27" t="n"/>
+      <c r="AQ31" s="27" t="n"/>
+      <c r="AR31" s="27" t="n"/>
+      <c r="AS31" s="27" t="n"/>
+      <c r="AT31" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU31" s="32">
+        <f>IFERROR(IF($AQ31="","",INDEX($W31:$AB31,$AQ31-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV31" s="32">
+        <f>IF($AR31="","",IF($AS31="",1/$AR31,(1/$AR31)/((1/$AR31)+(1/$AS31))))</f>
+        <v/>
+      </c>
+      <c r="AW31" s="32">
+        <f>IF(OR($AU31="",$AV31=""),"",$AU31-$AV31)</f>
+        <v/>
+      </c>
+      <c r="AX31" s="33">
+        <f>IF($AW31="","",IF($AP31="","units?",IF(ISNUMBER(SEARCH("yellow",$AP31)),IF($AW31&gt;=0.05,"OVER",IF($AW31&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY31" s="34">
+        <f>IF(OR($AX31="",$AX31="skip",$AX31="units?",$AX31="UNITS?"),"",IF($AX31="OVER",$AT31*($AU31*$AR31-1),$AT31*((1-$AU31)*$AS31-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ31" s="27" t="n"/>
+      <c r="BA31" s="33">
+        <f>IF(OR($AX31="",$AX31="skip",$AX31="units?",$AX31="UNITS?",$AZ31="",$AQ31=""),"",IF($AX31="OVER",IF($AZ31&gt;$AQ31,"WON","LOST"),IF($AZ31&lt;$AQ31,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB31" s="34">
+        <f>IF($BA31="","",IF($BA31="WON",IF($AX31="OVER",$AT31*($AR31-1),$AT31*($AS31-1)),-$AT31))</f>
+        <v/>
+      </c>
+      <c r="BC31" s="34">
+        <f>IF(COUNT($BB$2:$BB31)=0,"",SUM($BB$2:$BB31))</f>
+        <v/>
+      </c>
+      <c r="BD31" s="27" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
+        <is>
+          <t>Salford</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J32" s="29" t="n">
+        <v>3.574398039143975</v>
+      </c>
+      <c r="K32" s="30" t="n">
+        <v>-0.07439830391313051</v>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N32" s="31" t="n">
+        <v>0.03181727032750714</v>
+      </c>
+      <c r="O32" s="31" t="n">
+        <v>0.1058563003527647</v>
+      </c>
+      <c r="P32" s="31" t="n">
+        <v>0.1797556093991574</v>
+      </c>
+      <c r="Q32" s="31" t="n">
+        <v>0.2076435630784699</v>
+      </c>
+      <c r="R32" s="31" t="n">
+        <v>0.1834864631061332</v>
+      </c>
+      <c r="S32" s="31" t="n">
+        <v>0.1322517107267</v>
+      </c>
+      <c r="T32" s="31" t="n">
+        <v>0.08096155430474</v>
+      </c>
+      <c r="U32" s="31" t="n">
+        <v>0.04328295204817534</v>
+      </c>
+      <c r="V32" s="31" t="n">
+        <v>0.02062156753837311</v>
+      </c>
+      <c r="W32" s="28" t="n">
+        <v>0.8623264293197281</v>
+      </c>
+      <c r="X32" s="28" t="n">
+        <v>0.6825708199205707</v>
+      </c>
+      <c r="Y32" s="28" t="n">
+        <v>0.4749272568421008</v>
+      </c>
+      <c r="Z32" s="28" t="n">
+        <v>0.2914407937359675</v>
+      </c>
+      <c r="AA32" s="28" t="n">
+        <v>0.1591890830092676</v>
+      </c>
+      <c r="AB32" s="28" t="n">
+        <v>0.07822752870452754</v>
+      </c>
+      <c r="AC32" s="29" t="n">
+        <v>1.159653660144546</v>
+      </c>
+      <c r="AD32" s="29" t="n">
+        <v>1.465049443684639</v>
+      </c>
+      <c r="AE32" s="29" t="n">
+        <v>2.105585614624916</v>
+      </c>
+      <c r="AF32" s="29" t="n">
+        <v>3.431228645726088</v>
+      </c>
+      <c r="AG32" s="29" t="n">
+        <v>6.28183780631353</v>
+      </c>
+      <c r="AH32" s="29" t="n">
+        <v>12.78322371370174</v>
+      </c>
+      <c r="AI32" s="29" t="n">
+        <v>7.263558249116412</v>
+      </c>
+      <c r="AJ32" s="29" t="n">
+        <v>3.150308990968546</v>
+      </c>
+      <c r="AK32" s="29" t="n">
+        <v>1.904498020570992</v>
+      </c>
+      <c r="AL32" s="29" t="n">
+        <v>1.411314666663673</v>
+      </c>
+      <c r="AM32" s="29" t="n">
+        <v>1.189328040100866</v>
+      </c>
+      <c r="AN32" s="29" t="n">
+        <v>1.084866418927206</v>
+      </c>
+      <c r="AO32" s="27" t="n"/>
+      <c r="AP32" s="27" t="n"/>
+      <c r="AQ32" s="27" t="n"/>
+      <c r="AR32" s="27" t="n"/>
+      <c r="AS32" s="27" t="n"/>
+      <c r="AT32" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU32" s="32">
+        <f>IFERROR(IF($AQ32="","",INDEX($W32:$AB32,$AQ32-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV32" s="32">
+        <f>IF($AR32="","",IF($AS32="",1/$AR32,(1/$AR32)/((1/$AR32)+(1/$AS32))))</f>
+        <v/>
+      </c>
+      <c r="AW32" s="32">
+        <f>IF(OR($AU32="",$AV32=""),"",$AU32-$AV32)</f>
+        <v/>
+      </c>
+      <c r="AX32" s="33">
+        <f>IF($AW32="","",IF($AP32="","units?",IF(ISNUMBER(SEARCH("yellow",$AP32)),IF($AW32&gt;=0.05,"OVER",IF($AW32&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY32" s="34">
+        <f>IF(OR($AX32="",$AX32="skip",$AX32="units?",$AX32="UNITS?"),"",IF($AX32="OVER",$AT32*($AU32*$AR32-1),$AT32*((1-$AU32)*$AS32-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ32" s="27" t="n"/>
+      <c r="BA32" s="33">
+        <f>IF(OR($AX32="",$AX32="skip",$AX32="units?",$AX32="UNITS?",$AZ32="",$AQ32=""),"",IF($AX32="OVER",IF($AZ32&gt;$AQ32,"WON","LOST"),IF($AZ32&lt;$AQ32,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB32" s="34">
+        <f>IF($BA32="","",IF($BA32="WON",IF($AX32="OVER",$AT32*($AR32-1),$AT32*($AS32-1)),-$AT32))</f>
+        <v/>
+      </c>
+      <c r="BC32" s="34">
+        <f>IF(COUNT($BB$2:$BB32)=0,"",SUM($BB$2:$BB32))</f>
+        <v/>
+      </c>
+      <c r="BD32" s="27" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Crawley Town</t>
+        </is>
+      </c>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="28" t="n"/>
+      <c r="I33" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J33" s="29" t="n">
+        <v>4.074525999145339</v>
+      </c>
+      <c r="K33" s="30" t="n">
+        <v>0.05511141575664436</v>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N33" s="31" t="n">
+        <v>0.02002007667814214</v>
+      </c>
+      <c r="O33" s="31" t="n">
+        <v>0.0751983312499383</v>
+      </c>
+      <c r="P33" s="31" t="n">
+        <v>0.1441659228639918</v>
+      </c>
+      <c r="Q33" s="31" t="n">
+        <v>0.1880127536891033</v>
+      </c>
+      <c r="R33" s="31" t="n">
+        <v>0.187569205978641</v>
+      </c>
+      <c r="S33" s="31" t="n">
+        <v>0.1526326632537153</v>
+      </c>
+      <c r="T33" s="31" t="n">
+        <v>0.1054905833366318</v>
+      </c>
+      <c r="U33" s="31" t="n">
+        <v>0.06367081415485129</v>
+      </c>
+      <c r="V33" s="31" t="n">
+        <v>0.03424789454617099</v>
+      </c>
+      <c r="W33" s="28" t="n">
+        <v>0.9047815920719195</v>
+      </c>
+      <c r="X33" s="28" t="n">
+        <v>0.7606156692079278</v>
+      </c>
+      <c r="Y33" s="28" t="n">
+        <v>0.5726029155188245</v>
+      </c>
+      <c r="Z33" s="28" t="n">
+        <v>0.3850337095401835</v>
+      </c>
+      <c r="AA33" s="28" t="n">
+        <v>0.2324010462864682</v>
+      </c>
+      <c r="AB33" s="28" t="n">
+        <v>0.1269104629498363</v>
+      </c>
+      <c r="AC33" s="29" t="n">
+        <v>1.105239108269249</v>
+      </c>
+      <c r="AD33" s="29" t="n">
+        <v>1.314724427175365</v>
+      </c>
+      <c r="AE33" s="29" t="n">
+        <v>1.746410947093972</v>
+      </c>
+      <c r="AF33" s="29" t="n">
+        <v>2.597175195891872</v>
+      </c>
+      <c r="AG33" s="29" t="n">
+        <v>4.302906617586197</v>
+      </c>
+      <c r="AH33" s="29" t="n">
+        <v>7.879570972767377</v>
+      </c>
+      <c r="AI33" s="29" t="n">
+        <v>10.50217097470598</v>
+      </c>
+      <c r="AJ33" s="29" t="n">
+        <v>4.177382858314957</v>
+      </c>
+      <c r="AK33" s="29" t="n">
+        <v>2.339744552104086</v>
+      </c>
+      <c r="AL33" s="29" t="n">
+        <v>1.626105390674812</v>
+      </c>
+      <c r="AM33" s="29" t="n">
+        <v>1.302763630880613</v>
+      </c>
+      <c r="AN33" s="29" t="n">
+        <v>1.145357901525906</v>
+      </c>
+      <c r="AO33" s="27" t="n"/>
+      <c r="AP33" s="27" t="n"/>
+      <c r="AQ33" s="27" t="n"/>
+      <c r="AR33" s="27" t="n"/>
+      <c r="AS33" s="27" t="n"/>
+      <c r="AT33" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU33" s="32">
+        <f>IFERROR(IF($AQ33="","",INDEX($W33:$AB33,$AQ33-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV33" s="32">
+        <f>IF($AR33="","",IF($AS33="",1/$AR33,(1/$AR33)/((1/$AR33)+(1/$AS33))))</f>
+        <v/>
+      </c>
+      <c r="AW33" s="32">
+        <f>IF(OR($AU33="",$AV33=""),"",$AU33-$AV33)</f>
+        <v/>
+      </c>
+      <c r="AX33" s="33">
+        <f>IF($AW33="","",IF($AP33="","units?",IF(ISNUMBER(SEARCH("yellow",$AP33)),IF($AW33&gt;=0.05,"OVER",IF($AW33&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY33" s="34">
+        <f>IF(OR($AX33="",$AX33="skip",$AX33="units?",$AX33="UNITS?"),"",IF($AX33="OVER",$AT33*($AU33*$AR33-1),$AT33*((1-$AU33)*$AS33-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ33" s="27" t="n"/>
+      <c r="BA33" s="33">
+        <f>IF(OR($AX33="",$AX33="skip",$AX33="units?",$AX33="UNITS?",$AZ33="",$AQ33=""),"",IF($AX33="OVER",IF($AZ33&gt;$AQ33,"WON","LOST"),IF($AZ33&lt;$AQ33,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB33" s="34">
+        <f>IF($BA33="","",IF($BA33="WON",IF($AX33="OVER",$AT33*($AR33-1),$AT33*($AS33-1)),-$AT33))</f>
+        <v/>
+      </c>
+      <c r="BC33" s="34">
+        <f>IF(COUNT($BB$2:$BB33)=0,"",SUM($BB$2:$BB33))</f>
+        <v/>
+      </c>
+      <c r="BD33" s="27" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="28" t="n"/>
+      <c r="I34" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J34" s="29" t="n">
+        <v>3.806749875223653</v>
+      </c>
+      <c r="K34" s="30" t="n">
+        <v>-0.01423005985943993</v>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N34" s="31" t="n">
+        <v>0.02564180263916173</v>
+      </c>
+      <c r="O34" s="31" t="n">
+        <v>0.09044909687155508</v>
+      </c>
+      <c r="P34" s="31" t="n">
+        <v>0.1628440380763715</v>
+      </c>
+      <c r="Q34" s="31" t="n">
+        <v>0.1994388549325432</v>
+      </c>
+      <c r="R34" s="31" t="n">
+        <v>0.1868517702483258</v>
+      </c>
+      <c r="S34" s="31" t="n">
+        <v>0.1427895332652887</v>
+      </c>
+      <c r="T34" s="31" t="n">
+        <v>0.09267781810689228</v>
+      </c>
+      <c r="U34" s="31" t="n">
+        <v>0.0525310068730088</v>
+      </c>
+      <c r="V34" s="31" t="n">
+        <v>0.02653520300556879</v>
+      </c>
+      <c r="W34" s="28" t="n">
+        <v>0.8839091004892832</v>
+      </c>
+      <c r="X34" s="28" t="n">
+        <v>0.7210650624129117</v>
+      </c>
+      <c r="Y34" s="28" t="n">
+        <v>0.5216262074803685</v>
+      </c>
+      <c r="Z34" s="28" t="n">
+        <v>0.3347744372320427</v>
+      </c>
+      <c r="AA34" s="28" t="n">
+        <v>0.1919849039667539</v>
+      </c>
+      <c r="AB34" s="28" t="n">
+        <v>0.0993070858598617</v>
+      </c>
+      <c r="AC34" s="29" t="n">
+        <v>1.131338052121486</v>
+      </c>
+      <c r="AD34" s="29" t="n">
+        <v>1.386837405009867</v>
+      </c>
+      <c r="AE34" s="29" t="n">
+        <v>1.917081591491231</v>
+      </c>
+      <c r="AF34" s="29" t="n">
+        <v>2.987085896605865</v>
+      </c>
+      <c r="AG34" s="29" t="n">
+        <v>5.208742871643544</v>
+      </c>
+      <c r="AH34" s="29" t="n">
+        <v>10.06977489412146</v>
+      </c>
+      <c r="AI34" s="29" t="n">
+        <v>8.613939630191993</v>
+      </c>
+      <c r="AJ34" s="29" t="n">
+        <v>3.585065422963671</v>
+      </c>
+      <c r="AK34" s="29" t="n">
+        <v>2.090415519489317</v>
+      </c>
+      <c r="AL34" s="29" t="n">
+        <v>1.503249508090263</v>
+      </c>
+      <c r="AM34" s="29" t="n">
+        <v>1.237600640024249</v>
+      </c>
+      <c r="AN34" s="29" t="n">
+        <v>1.110256319663253</v>
+      </c>
+      <c r="AO34" s="27" t="n"/>
+      <c r="AP34" s="27" t="n"/>
+      <c r="AQ34" s="27" t="n"/>
+      <c r="AR34" s="27" t="n"/>
+      <c r="AS34" s="27" t="n"/>
+      <c r="AT34" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU34" s="32">
+        <f>IFERROR(IF($AQ34="","",INDEX($W34:$AB34,$AQ34-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV34" s="32">
+        <f>IF($AR34="","",IF($AS34="",1/$AR34,(1/$AR34)/((1/$AR34)+(1/$AS34))))</f>
+        <v/>
+      </c>
+      <c r="AW34" s="32">
+        <f>IF(OR($AU34="",$AV34=""),"",$AU34-$AV34)</f>
+        <v/>
+      </c>
+      <c r="AX34" s="33">
+        <f>IF($AW34="","",IF($AP34="","units?",IF(ISNUMBER(SEARCH("yellow",$AP34)),IF($AW34&gt;=0.05,"OVER",IF($AW34&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY34" s="34">
+        <f>IF(OR($AX34="",$AX34="skip",$AX34="units?",$AX34="UNITS?"),"",IF($AX34="OVER",$AT34*($AU34*$AR34-1),$AT34*((1-$AU34)*$AS34-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ34" s="27" t="n"/>
+      <c r="BA34" s="33">
+        <f>IF(OR($AX34="",$AX34="skip",$AX34="units?",$AX34="UNITS?",$AZ34="",$AQ34=""),"",IF($AX34="OVER",IF($AZ34&gt;$AQ34,"WON","LOST"),IF($AZ34&lt;$AQ34,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB34" s="34">
+        <f>IF($BA34="","",IF($BA34="WON",IF($AX34="OVER",$AT34*($AR34-1),$AT34*($AS34-1)),-$AT34))</f>
+        <v/>
+      </c>
+      <c r="BC34" s="34">
+        <f>IF(COUNT($BB$2:$BB34)=0,"",SUM($BB$2:$BB34))</f>
+        <v/>
+      </c>
+      <c r="BD34" s="27" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="E35" s="26" t="inlineStr">
+        <is>
+          <t>Colchester</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="28" t="n"/>
+      <c r="I35" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J35" s="29" t="n">
+        <v>3.921896165526225</v>
+      </c>
+      <c r="K35" s="30" t="n">
+        <v>0.01558743680293406</v>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N35" s="31" t="n">
+        <v>0.02304953046231673</v>
+      </c>
+      <c r="O35" s="31" t="n">
+        <v>0.08357889320617054</v>
+      </c>
+      <c r="P35" s="31" t="n">
+        <v>0.1546831812101759</v>
+      </c>
+      <c r="Q35" s="31" t="n">
+        <v>0.1947421028426255</v>
+      </c>
+      <c r="R35" s="31" t="n">
+        <v>0.1875539223814013</v>
+      </c>
+      <c r="S35" s="31" t="n">
+        <v>0.1473344002552242</v>
+      </c>
+      <c r="T35" s="31" t="n">
+        <v>0.09830201892790381</v>
+      </c>
+      <c r="U35" s="31" t="n">
+        <v>0.05727712531219459</v>
+      </c>
+      <c r="V35" s="31" t="n">
+        <v>0.02974176608130422</v>
+      </c>
+      <c r="W35" s="28" t="n">
+        <v>0.8933715763315128</v>
+      </c>
+      <c r="X35" s="28" t="n">
+        <v>0.7386883951213368</v>
+      </c>
+      <c r="Y35" s="28" t="n">
+        <v>0.5439462922787113</v>
+      </c>
+      <c r="Z35" s="28" t="n">
+        <v>0.35639236989731</v>
+      </c>
+      <c r="AA35" s="28" t="n">
+        <v>0.2090579696420859</v>
+      </c>
+      <c r="AB35" s="28" t="n">
+        <v>0.1107559507141821</v>
+      </c>
+      <c r="AC35" s="29" t="n">
+        <v>1.119355066238328</v>
+      </c>
+      <c r="AD35" s="29" t="n">
+        <v>1.353750792085667</v>
+      </c>
+      <c r="AE35" s="29" t="n">
+        <v>1.838416796281079</v>
+      </c>
+      <c r="AF35" s="29" t="n">
+        <v>2.805896210090405</v>
+      </c>
+      <c r="AG35" s="29" t="n">
+        <v>4.783362249772313</v>
+      </c>
+      <c r="AH35" s="29" t="n">
+        <v>9.028860242287205</v>
+      </c>
+      <c r="AI35" s="29" t="n">
+        <v>9.378362406529115</v>
+      </c>
+      <c r="AJ35" s="29" t="n">
+        <v>3.826848794045475</v>
+      </c>
+      <c r="AK35" s="29" t="n">
+        <v>2.192724196885901</v>
+      </c>
+      <c r="AL35" s="29" t="n">
+        <v>1.553741679290605</v>
+      </c>
+      <c r="AM35" s="29" t="n">
+        <v>1.264315160426465</v>
+      </c>
+      <c r="AN35" s="29" t="n">
+        <v>1.124550679651029</v>
+      </c>
+      <c r="AO35" s="27" t="n"/>
+      <c r="AP35" s="27" t="n"/>
+      <c r="AQ35" s="27" t="n"/>
+      <c r="AR35" s="27" t="n"/>
+      <c r="AS35" s="27" t="n"/>
+      <c r="AT35" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU35" s="32">
+        <f>IFERROR(IF($AQ35="","",INDEX($W35:$AB35,$AQ35-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV35" s="32">
+        <f>IF($AR35="","",IF($AS35="",1/$AR35,(1/$AR35)/((1/$AR35)+(1/$AS35))))</f>
+        <v/>
+      </c>
+      <c r="AW35" s="32">
+        <f>IF(OR($AU35="",$AV35=""),"",$AU35-$AV35)</f>
+        <v/>
+      </c>
+      <c r="AX35" s="33">
+        <f>IF($AW35="","",IF($AP35="","units?",IF(ISNUMBER(SEARCH("yellow",$AP35)),IF($AW35&gt;=0.05,"OVER",IF($AW35&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY35" s="34">
+        <f>IF(OR($AX35="",$AX35="skip",$AX35="units?",$AX35="UNITS?"),"",IF($AX35="OVER",$AT35*($AU35*$AR35-1),$AT35*((1-$AU35)*$AS35-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ35" s="27" t="n"/>
+      <c r="BA35" s="33">
+        <f>IF(OR($AX35="",$AX35="skip",$AX35="units?",$AX35="UNITS?",$AZ35="",$AQ35=""),"",IF($AX35="OVER",IF($AZ35&gt;$AQ35,"WON","LOST"),IF($AZ35&lt;$AQ35,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB35" s="34">
+        <f>IF($BA35="","",IF($BA35="WON",IF($AX35="OVER",$AT35*($AR35-1),$AT35*($AS35-1)),-$AT35))</f>
+        <v/>
+      </c>
+      <c r="BC35" s="34">
+        <f>IF(COUNT($BB$2:$BB35)=0,"",SUM($BB$2:$BB35))</f>
+        <v/>
+      </c>
+      <c r="BD35" s="27" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>Oldham</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
+        <is>
+          <t>Accrington</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="28" t="n"/>
+      <c r="I36" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J36" s="29" t="n">
+        <v>4.029690319136806</v>
+      </c>
+      <c r="K36" s="30" t="n">
+        <v>0.04350107437702411</v>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N36" s="31" t="n">
+        <v>0.02086526139463974</v>
+      </c>
+      <c r="O36" s="31" t="n">
+        <v>0.07757726376200423</v>
+      </c>
+      <c r="P36" s="31" t="n">
+        <v>0.1472166842100203</v>
+      </c>
+      <c r="Q36" s="31" t="n">
+        <v>0.190042128842722</v>
+      </c>
+      <c r="R36" s="31" t="n">
+        <v>0.187668886613492</v>
+      </c>
+      <c r="S36" s="31" t="n">
+        <v>0.1511633057278256</v>
+      </c>
+      <c r="T36" s="31" t="n">
+        <v>0.1034143373564752</v>
+      </c>
+      <c r="U36" s="31" t="n">
+        <v>0.06178394338406961</v>
+      </c>
+      <c r="V36" s="31" t="n">
+        <v>0.03289555812590347</v>
+      </c>
+      <c r="W36" s="28" t="n">
+        <v>0.901557474843356</v>
+      </c>
+      <c r="X36" s="28" t="n">
+        <v>0.7543407906333357</v>
+      </c>
+      <c r="Y36" s="28" t="n">
+        <v>0.5642986617906138</v>
+      </c>
+      <c r="Z36" s="28" t="n">
+        <v>0.3766297751771218</v>
+      </c>
+      <c r="AA36" s="28" t="n">
+        <v>0.2254664694492962</v>
+      </c>
+      <c r="AB36" s="28" t="n">
+        <v>0.122052132092821</v>
+      </c>
+      <c r="AC36" s="29" t="n">
+        <v>1.109191624387284</v>
+      </c>
+      <c r="AD36" s="29" t="n">
+        <v>1.325660778811141</v>
+      </c>
+      <c r="AE36" s="29" t="n">
+        <v>1.772111237738599</v>
+      </c>
+      <c r="AF36" s="29" t="n">
+        <v>2.655127305135976</v>
+      </c>
+      <c r="AG36" s="29" t="n">
+        <v>4.435249296458621</v>
+      </c>
+      <c r="AH36" s="29" t="n">
+        <v>8.193220248209162</v>
+      </c>
+      <c r="AI36" s="29" t="n">
+        <v>10.1582115900499</v>
+      </c>
+      <c r="AJ36" s="29" t="n">
+        <v>4.070679876313641</v>
+      </c>
+      <c r="AK36" s="29" t="n">
+        <v>2.295150168943083</v>
+      </c>
+      <c r="AL36" s="29" t="n">
+        <v>1.604183132558402</v>
+      </c>
+      <c r="AM36" s="29" t="n">
+        <v>1.291099688465374</v>
+      </c>
+      <c r="AN36" s="29" t="n">
+        <v>1.139019794402787</v>
+      </c>
+      <c r="AO36" s="27" t="n"/>
+      <c r="AP36" s="27" t="n"/>
+      <c r="AQ36" s="27" t="n"/>
+      <c r="AR36" s="27" t="n"/>
+      <c r="AS36" s="27" t="n"/>
+      <c r="AT36" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU36" s="32">
+        <f>IFERROR(IF($AQ36="","",INDEX($W36:$AB36,$AQ36-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV36" s="32">
+        <f>IF($AR36="","",IF($AS36="",1/$AR36,(1/$AR36)/((1/$AR36)+(1/$AS36))))</f>
+        <v/>
+      </c>
+      <c r="AW36" s="32">
+        <f>IF(OR($AU36="",$AV36=""),"",$AU36-$AV36)</f>
+        <v/>
+      </c>
+      <c r="AX36" s="33">
+        <f>IF($AW36="","",IF($AP36="","units?",IF(ISNUMBER(SEARCH("yellow",$AP36)),IF($AW36&gt;=0.05,"OVER",IF($AW36&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY36" s="34">
+        <f>IF(OR($AX36="",$AX36="skip",$AX36="units?",$AX36="UNITS?"),"",IF($AX36="OVER",$AT36*($AU36*$AR36-1),$AT36*((1-$AU36)*$AS36-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ36" s="27" t="n"/>
+      <c r="BA36" s="33">
+        <f>IF(OR($AX36="",$AX36="skip",$AX36="units?",$AX36="UNITS?",$AZ36="",$AQ36=""),"",IF($AX36="OVER",IF($AZ36&gt;$AQ36,"WON","LOST"),IF($AZ36&lt;$AQ36,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB36" s="34">
+        <f>IF($BA36="","",IF($BA36="WON",IF($AX36="OVER",$AT36*($AR36-1),$AT36*($AS36-1)),-$AT36))</f>
+        <v/>
+      </c>
+      <c r="BC36" s="34">
+        <f>IF(COUNT($BB$2:$BB36)=0,"",SUM($BB$2:$BB36))</f>
+        <v/>
+      </c>
+      <c r="BD36" s="27" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>Port Vale</t>
+        </is>
+      </c>
+      <c r="E37" s="26" t="inlineStr">
+        <is>
+          <t>Grimsby</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="28" t="n"/>
+      <c r="I37" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J37" s="29" t="n">
+        <v>3.648743580310875</v>
+      </c>
+      <c r="K37" s="30" t="n">
+        <v>-0.05514629049801034</v>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N37" s="31" t="n">
+        <v>0.02969144750067591</v>
+      </c>
+      <c r="O37" s="31" t="n">
+        <v>0.1006933635665977</v>
+      </c>
+      <c r="P37" s="31" t="n">
+        <v>0.1742939340661351</v>
+      </c>
+      <c r="Q37" s="31" t="n">
+        <v>0.2052267547117308</v>
+      </c>
+      <c r="R37" s="31" t="n">
+        <v>0.1848567095807532</v>
+      </c>
+      <c r="S37" s="31" t="n">
+        <v>0.1358151356505844</v>
+      </c>
+      <c r="T37" s="31" t="n">
+        <v>0.08475032933243061</v>
+      </c>
+      <c r="U37" s="31" t="n">
+        <v>0.04618437969068305</v>
+      </c>
+      <c r="V37" s="31" t="n">
+        <v>0.02242929383240135</v>
+      </c>
+      <c r="W37" s="28" t="n">
+        <v>0.8696151889327264</v>
+      </c>
+      <c r="X37" s="28" t="n">
+        <v>0.6953212548665914</v>
+      </c>
+      <c r="Y37" s="28" t="n">
+        <v>0.4900945001548606</v>
+      </c>
+      <c r="Z37" s="28" t="n">
+        <v>0.3052377905741073</v>
+      </c>
+      <c r="AA37" s="28" t="n">
+        <v>0.1694226549235229</v>
+      </c>
+      <c r="AB37" s="28" t="n">
+        <v>0.08467232559109228</v>
+      </c>
+      <c r="AC37" s="29" t="n">
+        <v>1.149933916434112</v>
+      </c>
+      <c r="AD37" s="29" t="n">
+        <v>1.43818413862793</v>
+      </c>
+      <c r="AE37" s="29" t="n">
+        <v>2.040422815771283</v>
+      </c>
+      <c r="AF37" s="29" t="n">
+        <v>3.276134315214206</v>
+      </c>
+      <c r="AG37" s="29" t="n">
+        <v>5.902398356650698</v>
+      </c>
+      <c r="AH37" s="29" t="n">
+        <v>11.81023425327061</v>
+      </c>
+      <c r="AI37" s="29" t="n">
+        <v>7.669605008546877</v>
+      </c>
+      <c r="AJ37" s="29" t="n">
+        <v>3.282145590963798</v>
+      </c>
+      <c r="AK37" s="29" t="n">
+        <v>1.961147703454276</v>
+      </c>
+      <c r="AL37" s="29" t="n">
+        <v>1.439341383905058</v>
+      </c>
+      <c r="AM37" s="29" t="n">
+        <v>1.203981791614992</v>
+      </c>
+      <c r="AN37" s="29" t="n">
+        <v>1.092504933433561</v>
+      </c>
+      <c r="AO37" s="27" t="n"/>
+      <c r="AP37" s="27" t="n"/>
+      <c r="AQ37" s="27" t="n"/>
+      <c r="AR37" s="27" t="n"/>
+      <c r="AS37" s="27" t="n"/>
+      <c r="AT37" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU37" s="32">
+        <f>IFERROR(IF($AQ37="","",INDEX($W37:$AB37,$AQ37-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV37" s="32">
+        <f>IF($AR37="","",IF($AS37="",1/$AR37,(1/$AR37)/((1/$AR37)+(1/$AS37))))</f>
+        <v/>
+      </c>
+      <c r="AW37" s="32">
+        <f>IF(OR($AU37="",$AV37=""),"",$AU37-$AV37)</f>
+        <v/>
+      </c>
+      <c r="AX37" s="33">
+        <f>IF($AW37="","",IF($AP37="","units?",IF(ISNUMBER(SEARCH("yellow",$AP37)),IF($AW37&gt;=0.05,"OVER",IF($AW37&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY37" s="34">
+        <f>IF(OR($AX37="",$AX37="skip",$AX37="units?",$AX37="UNITS?"),"",IF($AX37="OVER",$AT37*($AU37*$AR37-1),$AT37*((1-$AU37)*$AS37-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ37" s="27" t="n"/>
+      <c r="BA37" s="33">
+        <f>IF(OR($AX37="",$AX37="skip",$AX37="units?",$AX37="UNITS?",$AZ37="",$AQ37=""),"",IF($AX37="OVER",IF($AZ37&gt;$AQ37,"WON","LOST"),IF($AZ37&lt;$AQ37,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB37" s="34">
+        <f>IF($BA37="","",IF($BA37="WON",IF($AX37="OVER",$AT37*($AR37-1),$AT37*($AS37-1)),-$AT37))</f>
+        <v/>
+      </c>
+      <c r="BC37" s="34">
+        <f>IF(COUNT($BB$2:$BB37)=0,"",SUM($BB$2:$BB37))</f>
+        <v/>
+      </c>
+      <c r="BD37" s="27" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>Rotherham</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J38" s="29" t="n">
+        <v>3.913350095431361</v>
+      </c>
+      <c r="K38" s="30" t="n">
+        <v>0.01337440487754238</v>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N38" s="31" t="n">
+        <v>0.02323239088198201</v>
+      </c>
+      <c r="O38" s="31" t="n">
+        <v>0.08407220581743316</v>
+      </c>
+      <c r="P38" s="31" t="n">
+        <v>0.1552826468286881</v>
+      </c>
+      <c r="Q38" s="31" t="n">
+        <v>0.195102883722373</v>
+      </c>
+      <c r="R38" s="31" t="n">
+        <v>0.187522760599819</v>
+      </c>
+      <c r="S38" s="31" t="n">
+        <v>0.1470130878769104</v>
+      </c>
+      <c r="T38" s="31" t="n">
+        <v>0.09788998927185841</v>
+      </c>
+      <c r="U38" s="31" t="n">
+        <v>0.05692211912182336</v>
+      </c>
+      <c r="V38" s="31" t="n">
+        <v>0.0294978663646414</v>
+      </c>
+      <c r="W38" s="28" t="n">
+        <v>0.8926954033005848</v>
+      </c>
+      <c r="X38" s="28" t="n">
+        <v>0.7374127564718967</v>
+      </c>
+      <c r="Y38" s="28" t="n">
+        <v>0.5423098727495237</v>
+      </c>
+      <c r="Z38" s="28" t="n">
+        <v>0.3547871121497048</v>
+      </c>
+      <c r="AA38" s="28" t="n">
+        <v>0.2077740242727943</v>
+      </c>
+      <c r="AB38" s="28" t="n">
+        <v>0.1098840350009359</v>
+      </c>
+      <c r="AC38" s="29" t="n">
+        <v>1.120202922858878</v>
+      </c>
+      <c r="AD38" s="29" t="n">
+        <v>1.356092624142325</v>
+      </c>
+      <c r="AE38" s="29" t="n">
+        <v>1.843964217228753</v>
+      </c>
+      <c r="AF38" s="29" t="n">
+        <v>2.818591673020082</v>
+      </c>
+      <c r="AG38" s="29" t="n">
+        <v>4.812921170006614</v>
+      </c>
+      <c r="AH38" s="29" t="n">
+        <v>9.100503089384029</v>
+      </c>
+      <c r="AI38" s="29" t="n">
+        <v>9.319265257584721</v>
+      </c>
+      <c r="AJ38" s="29" t="n">
+        <v>3.808258110957989</v>
+      </c>
+      <c r="AK38" s="29" t="n">
+        <v>2.184884358348281</v>
+      </c>
+      <c r="AL38" s="29" t="n">
+        <v>1.549876046852964</v>
+      </c>
+      <c r="AM38" s="29" t="n">
+        <v>1.262266109214701</v>
+      </c>
+      <c r="AN38" s="29" t="n">
+        <v>1.123449122723073</v>
+      </c>
+      <c r="AO38" s="27" t="n"/>
+      <c r="AP38" s="27" t="n"/>
+      <c r="AQ38" s="27" t="n"/>
+      <c r="AR38" s="27" t="n"/>
+      <c r="AS38" s="27" t="n"/>
+      <c r="AT38" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU38" s="32">
+        <f>IFERROR(IF($AQ38="","",INDEX($W38:$AB38,$AQ38-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV38" s="32">
+        <f>IF($AR38="","",IF($AS38="",1/$AR38,(1/$AR38)/((1/$AR38)+(1/$AS38))))</f>
+        <v/>
+      </c>
+      <c r="AW38" s="32">
+        <f>IF(OR($AU38="",$AV38=""),"",$AU38-$AV38)</f>
+        <v/>
+      </c>
+      <c r="AX38" s="33">
+        <f>IF($AW38="","",IF($AP38="","units?",IF(ISNUMBER(SEARCH("yellow",$AP38)),IF($AW38&gt;=0.05,"OVER",IF($AW38&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY38" s="34">
+        <f>IF(OR($AX38="",$AX38="skip",$AX38="units?",$AX38="UNITS?"),"",IF($AX38="OVER",$AT38*($AU38*$AR38-1),$AT38*((1-$AU38)*$AS38-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ38" s="27" t="n"/>
+      <c r="BA38" s="33">
+        <f>IF(OR($AX38="",$AX38="skip",$AX38="units?",$AX38="UNITS?",$AZ38="",$AQ38=""),"",IF($AX38="OVER",IF($AZ38&gt;$AQ38,"WON","LOST"),IF($AZ38&lt;$AQ38,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB38" s="34">
+        <f>IF($BA38="","",IF($BA38="WON",IF($AX38="OVER",$AT38*($AR38-1),$AT38*($AS38-1)),-$AT38))</f>
+        <v/>
+      </c>
+      <c r="BC38" s="34">
+        <f>IF(COUNT($BB$2:$BB38)=0,"",SUM($BB$2:$BB38))</f>
+        <v/>
+      </c>
+      <c r="BD38" s="27" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>Shrewsbury</t>
+        </is>
+      </c>
+      <c r="E39" s="26" t="inlineStr">
+        <is>
+          <t>Exeter</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="28" t="n"/>
+      <c r="I39" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J39" s="29" t="n">
+        <v>3.751071668248361</v>
+      </c>
+      <c r="K39" s="30" t="n">
+        <v>-0.02864810794670547</v>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M39" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N39" s="31" t="n">
+        <v>0.02700019647008065</v>
+      </c>
+      <c r="O39" s="31" t="n">
+        <v>0.09394853134281284</v>
+      </c>
+      <c r="P39" s="31" t="n">
+        <v>0.166849539749597</v>
+      </c>
+      <c r="Q39" s="31" t="n">
+        <v>0.2015720493514632</v>
+      </c>
+      <c r="R39" s="31" t="n">
+        <v>0.1862881137470122</v>
+      </c>
+      <c r="S39" s="31" t="n">
+        <v>0.1404273472661864</v>
+      </c>
+      <c r="T39" s="31" t="n">
+        <v>0.08990803541254841</v>
+      </c>
+      <c r="U39" s="31" t="n">
+        <v>0.05026964539056043</v>
+      </c>
+      <c r="V39" s="31" t="n">
+        <v>0.02504839483617266</v>
+      </c>
+      <c r="W39" s="28" t="n">
+        <v>0.8790512721871065</v>
+      </c>
+      <c r="X39" s="28" t="n">
+        <v>0.7122017324375096</v>
+      </c>
+      <c r="Y39" s="28" t="n">
+        <v>0.5106296830860464</v>
+      </c>
+      <c r="Z39" s="28" t="n">
+        <v>0.3243415693390341</v>
+      </c>
+      <c r="AA39" s="28" t="n">
+        <v>0.1839142220728478</v>
+      </c>
+      <c r="AB39" s="28" t="n">
+        <v>0.09400618666029936</v>
+      </c>
+      <c r="AC39" s="29" t="n">
+        <v>1.137590071978361</v>
+      </c>
+      <c r="AD39" s="29" t="n">
+        <v>1.404096556431422</v>
+      </c>
+      <c r="AE39" s="29" t="n">
+        <v>1.958366372194406</v>
+      </c>
+      <c r="AF39" s="29" t="n">
+        <v>3.083169394653512</v>
+      </c>
+      <c r="AG39" s="29" t="n">
+        <v>5.437317401173594</v>
+      </c>
+      <c r="AH39" s="29" t="n">
+        <v>10.63759775315213</v>
+      </c>
+      <c r="AI39" s="29" t="n">
+        <v>8.267966253824435</v>
+      </c>
+      <c r="AJ39" s="29" t="n">
+        <v>3.474656079306897</v>
+      </c>
+      <c r="AK39" s="29" t="n">
+        <v>2.043442287848919</v>
+      </c>
+      <c r="AL39" s="29" t="n">
+        <v>1.480037774444323</v>
+      </c>
+      <c r="AM39" s="29" t="n">
+        <v>1.225361386078787</v>
+      </c>
+      <c r="AN39" s="29" t="n">
+        <v>1.10376029645696</v>
+      </c>
+      <c r="AO39" s="27" t="n"/>
+      <c r="AP39" s="27" t="n"/>
+      <c r="AQ39" s="27" t="n"/>
+      <c r="AR39" s="27" t="n"/>
+      <c r="AS39" s="27" t="n"/>
+      <c r="AT39" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU39" s="32">
+        <f>IFERROR(IF($AQ39="","",INDEX($W39:$AB39,$AQ39-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV39" s="32">
+        <f>IF($AR39="","",IF($AS39="",1/$AR39,(1/$AR39)/((1/$AR39)+(1/$AS39))))</f>
+        <v/>
+      </c>
+      <c r="AW39" s="32">
+        <f>IF(OR($AU39="",$AV39=""),"",$AU39-$AV39)</f>
+        <v/>
+      </c>
+      <c r="AX39" s="33">
+        <f>IF($AW39="","",IF($AP39="","units?",IF(ISNUMBER(SEARCH("yellow",$AP39)),IF($AW39&gt;=0.05,"OVER",IF($AW39&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY39" s="34">
+        <f>IF(OR($AX39="",$AX39="skip",$AX39="units?",$AX39="UNITS?"),"",IF($AX39="OVER",$AT39*($AU39*$AR39-1),$AT39*((1-$AU39)*$AS39-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ39" s="27" t="n"/>
+      <c r="BA39" s="33">
+        <f>IF(OR($AX39="",$AX39="skip",$AX39="units?",$AX39="UNITS?",$AZ39="",$AQ39=""),"",IF($AX39="OVER",IF($AZ39&gt;$AQ39,"WON","LOST"),IF($AZ39&lt;$AQ39,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB39" s="34">
+        <f>IF($BA39="","",IF($BA39="WON",IF($AX39="OVER",$AT39*($AR39-1),$AT39*($AS39-1)),-$AT39))</f>
+        <v/>
+      </c>
+      <c r="BC39" s="34">
+        <f>IF(COUNT($BB$2:$BB39)=0,"",SUM($BB$2:$BB39))</f>
+        <v/>
+      </c>
+      <c r="BD39" s="27" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>Swindon</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>Crewe</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="28" t="n"/>
+      <c r="I40" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J40" s="29" t="n">
+        <v>3.383327832811613</v>
+      </c>
+      <c r="K40" s="30" t="n">
+        <v>-0.1238765391617311</v>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N40" s="31" t="n">
+        <v>0.03802276035707616</v>
+      </c>
+      <c r="O40" s="31" t="n">
+        <v>0.1201844710200877</v>
+      </c>
+      <c r="P40" s="31" t="n">
+        <v>0.193894288747511</v>
+      </c>
+      <c r="Q40" s="31" t="n">
+        <v>0.2127903643039682</v>
+      </c>
+      <c r="R40" s="31" t="n">
+        <v>0.1786440002839714</v>
+      </c>
+      <c r="S40" s="31" t="n">
+        <v>0.1223310278214615</v>
+      </c>
+      <c r="T40" s="31" t="n">
+        <v>0.0711483910977003</v>
+      </c>
+      <c r="U40" s="31" t="n">
+        <v>0.03613716180880345</v>
+      </c>
+      <c r="V40" s="31" t="n">
+        <v>0.01635723006322951</v>
+      </c>
+      <c r="W40" s="28" t="n">
+        <v>0.8417927686228361</v>
+      </c>
+      <c r="X40" s="28" t="n">
+        <v>0.6478984798753251</v>
+      </c>
+      <c r="Y40" s="28" t="n">
+        <v>0.435108115571357</v>
+      </c>
+      <c r="Z40" s="28" t="n">
+        <v>0.2564641152873856</v>
+      </c>
+      <c r="AA40" s="28" t="n">
+        <v>0.134133087465924</v>
+      </c>
+      <c r="AB40" s="28" t="n">
+        <v>0.06298469636822368</v>
+      </c>
+      <c r="AC40" s="29" t="n">
+        <v>1.187940829707992</v>
+      </c>
+      <c r="AD40" s="29" t="n">
+        <v>1.543451684270705</v>
+      </c>
+      <c r="AE40" s="29" t="n">
+        <v>2.298279356814253</v>
+      </c>
+      <c r="AF40" s="29" t="n">
+        <v>3.899180978514018</v>
+      </c>
+      <c r="AG40" s="29" t="n">
+        <v>7.455282055250135</v>
+      </c>
+      <c r="AH40" s="29" t="n">
+        <v>15.876872600191</v>
+      </c>
+      <c r="AI40" s="29" t="n">
+        <v>6.320823588752488</v>
+      </c>
+      <c r="AJ40" s="29" t="n">
+        <v>2.840089982133312</v>
+      </c>
+      <c r="AK40" s="29" t="n">
+        <v>1.770250250650078</v>
+      </c>
+      <c r="AL40" s="29" t="n">
+        <v>1.344925000340114</v>
+      </c>
+      <c r="AM40" s="29" t="n">
+        <v>1.154911898727445</v>
+      </c>
+      <c r="AN40" s="29" t="n">
+        <v>1.067218428689586</v>
+      </c>
+      <c r="AO40" s="27" t="n"/>
+      <c r="AP40" s="27" t="n"/>
+      <c r="AQ40" s="27" t="n"/>
+      <c r="AR40" s="27" t="n"/>
+      <c r="AS40" s="27" t="n"/>
+      <c r="AT40" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU40" s="32">
+        <f>IFERROR(IF($AQ40="","",INDEX($W40:$AB40,$AQ40-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV40" s="32">
+        <f>IF($AR40="","",IF($AS40="",1/$AR40,(1/$AR40)/((1/$AR40)+(1/$AS40))))</f>
+        <v/>
+      </c>
+      <c r="AW40" s="32">
+        <f>IF(OR($AU40="",$AV40=""),"",$AU40-$AV40)</f>
+        <v/>
+      </c>
+      <c r="AX40" s="33">
+        <f>IF($AW40="","",IF($AP40="","units?",IF(ISNUMBER(SEARCH("yellow",$AP40)),IF($AW40&gt;=0.05,"OVER",IF($AW40&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY40" s="34">
+        <f>IF(OR($AX40="",$AX40="skip",$AX40="units?",$AX40="UNITS?"),"",IF($AX40="OVER",$AT40*($AU40*$AR40-1),$AT40*((1-$AU40)*$AS40-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ40" s="27" t="n"/>
+      <c r="BA40" s="33">
+        <f>IF(OR($AX40="",$AX40="skip",$AX40="units?",$AX40="UNITS?",$AZ40="",$AQ40=""),"",IF($AX40="OVER",IF($AZ40&gt;$AQ40,"WON","LOST"),IF($AZ40&lt;$AQ40,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB40" s="34">
+        <f>IF($BA40="","",IF($BA40="WON",IF($AX40="OVER",$AT40*($AR40-1),$AT40*($AS40-1)),-$AT40))</f>
+        <v/>
+      </c>
+      <c r="BC40" s="34">
+        <f>IF(COUNT($BB$2:$BB40)=0,"",SUM($BB$2:$BB40))</f>
+        <v/>
+      </c>
+      <c r="BD40" s="27" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="inlineStr">
+        <is>
+          <t>Tranmere</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="inlineStr">
+        <is>
+          <t>Rochdale</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J41" s="29" t="n">
+        <v>3.640484193204629</v>
+      </c>
+      <c r="K41" s="30" t="n">
+        <v>-0.05728508495527529</v>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M41" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N41" s="31" t="n">
+        <v>0.02992027498057563</v>
+      </c>
+      <c r="O41" s="31" t="n">
+        <v>0.1012558737736421</v>
+      </c>
+      <c r="P41" s="31" t="n">
+        <v>0.1748987950663275</v>
+      </c>
+      <c r="Q41" s="31" t="n">
+        <v>0.2055056137391038</v>
+      </c>
+      <c r="R41" s="31" t="n">
+        <v>0.1847183744543017</v>
+      </c>
+      <c r="S41" s="31" t="n">
+        <v>0.1354279232846224</v>
+      </c>
+      <c r="T41" s="31" t="n">
+        <v>0.08433087549278315</v>
+      </c>
+      <c r="U41" s="31" t="n">
+        <v>0.04585909678727113</v>
+      </c>
+      <c r="V41" s="31" t="n">
+        <v>0.02222445653568638</v>
+      </c>
+      <c r="W41" s="28" t="n">
+        <v>0.8688238512457823</v>
+      </c>
+      <c r="X41" s="28" t="n">
+        <v>0.6939250561794548</v>
+      </c>
+      <c r="Y41" s="28" t="n">
+        <v>0.488419442440351</v>
+      </c>
+      <c r="Z41" s="28" t="n">
+        <v>0.3037010679860492</v>
+      </c>
+      <c r="AA41" s="28" t="n">
+        <v>0.1682731447014267</v>
+      </c>
+      <c r="AB41" s="28" t="n">
+        <v>0.08394226920864356</v>
+      </c>
+      <c r="AC41" s="29" t="n">
+        <v>1.150981293349771</v>
+      </c>
+      <c r="AD41" s="29" t="n">
+        <v>1.441077809620686</v>
+      </c>
+      <c r="AE41" s="29" t="n">
+        <v>2.047420542891527</v>
+      </c>
+      <c r="AF41" s="29" t="n">
+        <v>3.292711502897764</v>
+      </c>
+      <c r="AG41" s="29" t="n">
+        <v>5.942718915572279</v>
+      </c>
+      <c r="AH41" s="29" t="n">
+        <v>11.91294933324282</v>
+      </c>
+      <c r="AI41" s="29" t="n">
+        <v>7.623337089074641</v>
+      </c>
+      <c r="AJ41" s="29" t="n">
+        <v>3.267173678177035</v>
+      </c>
+      <c r="AK41" s="29" t="n">
+        <v>1.954726357800262</v>
+      </c>
+      <c r="AL41" s="29" t="n">
+        <v>1.436164776395154</v>
+      </c>
+      <c r="AM41" s="29" t="n">
+        <v>1.202317796557164</v>
+      </c>
+      <c r="AN41" s="29" t="n">
+        <v>1.091634256649008</v>
+      </c>
+      <c r="AO41" s="27" t="n"/>
+      <c r="AP41" s="27" t="n"/>
+      <c r="AQ41" s="27" t="n"/>
+      <c r="AR41" s="27" t="n"/>
+      <c r="AS41" s="27" t="n"/>
+      <c r="AT41" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU41" s="32">
+        <f>IFERROR(IF($AQ41="","",INDEX($W41:$AB41,$AQ41-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV41" s="32">
+        <f>IF($AR41="","",IF($AS41="",1/$AR41,(1/$AR41)/((1/$AR41)+(1/$AS41))))</f>
+        <v/>
+      </c>
+      <c r="AW41" s="32">
+        <f>IF(OR($AU41="",$AV41=""),"",$AU41-$AV41)</f>
+        <v/>
+      </c>
+      <c r="AX41" s="33">
+        <f>IF($AW41="","",IF($AP41="","units?",IF(ISNUMBER(SEARCH("yellow",$AP41)),IF($AW41&gt;=0.05,"OVER",IF($AW41&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY41" s="34">
+        <f>IF(OR($AX41="",$AX41="skip",$AX41="units?",$AX41="UNITS?"),"",IF($AX41="OVER",$AT41*($AU41*$AR41-1),$AT41*((1-$AU41)*$AS41-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ41" s="27" t="n"/>
+      <c r="BA41" s="33">
+        <f>IF(OR($AX41="",$AX41="skip",$AX41="units?",$AX41="UNITS?",$AZ41="",$AQ41=""),"",IF($AX41="OVER",IF($AZ41&gt;$AQ41,"WON","LOST"),IF($AZ41&lt;$AQ41,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB41" s="34">
+        <f>IF($BA41="","",IF($BA41="WON",IF($AX41="OVER",$AT41*($AR41-1),$AT41*($AS41-1)),-$AT41))</f>
+        <v/>
+      </c>
+      <c r="BC41" s="34">
+        <f>IF(COUNT($BB$2:$BB41)=0,"",SUM($BB$2:$BB41))</f>
+        <v/>
+      </c>
+      <c r="BD41" s="27" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
+        <is>
+          <t>Northampton</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="28" t="n"/>
+      <c r="I42" s="29" t="n">
+        <v>3.861702127659575</v>
+      </c>
+      <c r="J42" s="29" t="n">
+        <v>3.42893103161802</v>
+      </c>
+      <c r="K42" s="30" t="n">
+        <v>-0.1120674463578681</v>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M42" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N42" s="31" t="n">
+        <v>0.03643752901941007</v>
+      </c>
+      <c r="O42" s="31" t="n">
+        <v>0.1166228242354891</v>
+      </c>
+      <c r="P42" s="31" t="n">
+        <v>0.1905154222281872</v>
+      </c>
+      <c r="Q42" s="31" t="n">
+        <v>0.2117127441158494</v>
+      </c>
+      <c r="R42" s="31" t="n">
+        <v>0.1799755050004021</v>
+      </c>
+      <c r="S42" s="31" t="n">
+        <v>0.1247933700295986</v>
+      </c>
+      <c r="T42" s="31" t="n">
+        <v>0.07349366314800895</v>
+      </c>
+      <c r="U42" s="31" t="n">
+        <v>0.03779799590696169</v>
+      </c>
+      <c r="V42" s="31" t="n">
+        <v>0.01732424902846542</v>
+      </c>
+      <c r="W42" s="28" t="n">
+        <v>0.8469396467451009</v>
+      </c>
+      <c r="X42" s="28" t="n">
+        <v>0.6564242245169136</v>
+      </c>
+      <c r="Y42" s="28" t="n">
+        <v>0.4447114804010643</v>
+      </c>
+      <c r="Z42" s="28" t="n">
+        <v>0.2647359754006622</v>
+      </c>
+      <c r="AA42" s="28" t="n">
+        <v>0.1399426053710636</v>
+      </c>
+      <c r="AB42" s="28" t="n">
+        <v>0.06644894222305464</v>
+      </c>
+      <c r="AC42" s="29" t="n">
+        <v>1.180721676973241</v>
+      </c>
+      <c r="AD42" s="29" t="n">
+        <v>1.523405082644438</v>
+      </c>
+      <c r="AE42" s="29" t="n">
+        <v>2.248648942226873</v>
+      </c>
+      <c r="AF42" s="29" t="n">
+        <v>3.777348350508688</v>
+      </c>
+      <c r="AG42" s="29" t="n">
+        <v>7.145786641233801</v>
+      </c>
+      <c r="AH42" s="29" t="n">
+        <v>15.04914851230013</v>
+      </c>
+      <c r="AI42" s="29" t="n">
+        <v>6.533370521722564</v>
+      </c>
+      <c r="AJ42" s="29" t="n">
+        <v>2.910566085731583</v>
+      </c>
+      <c r="AK42" s="29" t="n">
+        <v>1.800865612568873</v>
+      </c>
+      <c r="AL42" s="29" t="n">
+        <v>1.360055662379134</v>
+      </c>
+      <c r="AM42" s="29" t="n">
+        <v>1.162713100596549</v>
+      </c>
+      <c r="AN42" s="29" t="n">
+        <v>1.071178690945184</v>
+      </c>
+      <c r="AO42" s="27" t="n"/>
+      <c r="AP42" s="27" t="n"/>
+      <c r="AQ42" s="27" t="n"/>
+      <c r="AR42" s="27" t="n"/>
+      <c r="AS42" s="27" t="n"/>
+      <c r="AT42" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU42" s="32">
+        <f>IFERROR(IF($AQ42="","",INDEX($W42:$AB42,$AQ42-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV42" s="32">
+        <f>IF($AR42="","",IF($AS42="",1/$AR42,(1/$AR42)/((1/$AR42)+(1/$AS42))))</f>
+        <v/>
+      </c>
+      <c r="AW42" s="32">
+        <f>IF(OR($AU42="",$AV42=""),"",$AU42-$AV42)</f>
+        <v/>
+      </c>
+      <c r="AX42" s="33">
+        <f>IF($AW42="","",IF($AP42="","units?",IF(ISNUMBER(SEARCH("yellow",$AP42)),IF($AW42&gt;=0.05,"OVER",IF($AW42&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY42" s="34">
+        <f>IF(OR($AX42="",$AX42="skip",$AX42="units?",$AX42="UNITS?"),"",IF($AX42="OVER",$AT42*($AU42*$AR42-1),$AT42*((1-$AU42)*$AS42-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ42" s="27" t="n"/>
+      <c r="BA42" s="33">
+        <f>IF(OR($AX42="",$AX42="skip",$AX42="units?",$AX42="UNITS?",$AZ42="",$AQ42=""),"",IF($AX42="OVER",IF($AZ42&gt;$AQ42,"WON","LOST"),IF($AZ42&lt;$AQ42,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB42" s="34">
+        <f>IF($BA42="","",IF($BA42="WON",IF($AX42="OVER",$AT42*($AR42-1),$AT42*($AS42-1)),-$AT42))</f>
+        <v/>
+      </c>
+      <c r="BC42" s="34">
+        <f>IF(COUNT($BB$2:$BB42)=0,"",SUM($BB$2:$BB42))</f>
+        <v/>
+      </c>
+      <c r="BD42" s="27" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
+        <is>
+          <t>Nott'm Forest</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="29" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J43" s="29" t="n">
+        <v>3.656077773412012</v>
+      </c>
+      <c r="K43" s="30" t="n">
+        <v>-0.02763889004999676</v>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M43" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N43" s="31" t="n">
+        <v>0.02948975035307553</v>
+      </c>
+      <c r="O43" s="31" t="n">
+        <v>0.1001961589056015</v>
+      </c>
+      <c r="P43" s="31" t="n">
+        <v>0.1737572747304789</v>
+      </c>
+      <c r="Q43" s="31" t="n">
+        <v>0.2049770320036517</v>
+      </c>
+      <c r="R43" s="31" t="n">
+        <v>0.1849766629335755</v>
+      </c>
+      <c r="S43" s="31" t="n">
+        <v>0.1361571313277305</v>
+      </c>
+      <c r="T43" s="31" t="n">
+        <v>0.08512244992653137</v>
+      </c>
+      <c r="U43" s="31" t="n">
+        <v>0.04647381599905168</v>
+      </c>
+      <c r="V43" s="31" t="n">
+        <v>0.02261201780582751</v>
+      </c>
+      <c r="W43" s="28" t="n">
+        <v>0.8703140907413229</v>
+      </c>
+      <c r="X43" s="28" t="n">
+        <v>0.6965568160108441</v>
+      </c>
+      <c r="Y43" s="28" t="n">
+        <v>0.4915797840071924</v>
+      </c>
+      <c r="Z43" s="28" t="n">
+        <v>0.3066031210736169</v>
+      </c>
+      <c r="AA43" s="28" t="n">
+        <v>0.1704459897458863</v>
+      </c>
+      <c r="AB43" s="28" t="n">
+        <v>0.08532353981935492</v>
+      </c>
+      <c r="AC43" s="29" t="n">
+        <v>1.149010467184568</v>
+      </c>
+      <c r="AD43" s="29" t="n">
+        <v>1.435633069714204</v>
+      </c>
+      <c r="AE43" s="29" t="n">
+        <v>2.034257779781621</v>
+      </c>
+      <c r="AF43" s="29" t="n">
+        <v>3.261545402728941</v>
+      </c>
+      <c r="AG43" s="29" t="n">
+        <v>5.866961149927171</v>
+      </c>
+      <c r="AH43" s="29" t="n">
+        <v>11.72009508884861</v>
+      </c>
+      <c r="AI43" s="29" t="n">
+        <v>7.710937955528824</v>
+      </c>
+      <c r="AJ43" s="29" t="n">
+        <v>3.2955098442275</v>
+      </c>
+      <c r="AK43" s="29" t="n">
+        <v>1.966876942623671</v>
+      </c>
+      <c r="AL43" s="29" t="n">
+        <v>1.44217551360823</v>
+      </c>
+      <c r="AM43" s="29" t="n">
+        <v>1.205467019192246</v>
+      </c>
+      <c r="AN43" s="29" t="n">
+        <v>1.093282754650211</v>
+      </c>
+      <c r="AO43" s="27" t="n"/>
+      <c r="AP43" s="27" t="n"/>
+      <c r="AQ43" s="27" t="n"/>
+      <c r="AR43" s="27" t="n"/>
+      <c r="AS43" s="27" t="n"/>
+      <c r="AT43" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU43" s="32">
+        <f>IFERROR(IF($AQ43="","",INDEX($W43:$AB43,$AQ43-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV43" s="32">
+        <f>IF($AR43="","",IF($AS43="",1/$AR43,(1/$AR43)/((1/$AR43)+(1/$AS43))))</f>
+        <v/>
+      </c>
+      <c r="AW43" s="32">
+        <f>IF(OR($AU43="",$AV43=""),"",$AU43-$AV43)</f>
+        <v/>
+      </c>
+      <c r="AX43" s="33">
+        <f>IF($AW43="","",IF($AP43="","units?",IF(ISNUMBER(SEARCH("yellow",$AP43)),IF($AW43&gt;=0.05,"OVER",IF($AW43&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY43" s="34">
+        <f>IF(OR($AX43="",$AX43="skip",$AX43="units?",$AX43="UNITS?"),"",IF($AX43="OVER",$AT43*($AU43*$AR43-1),$AT43*((1-$AU43)*$AS43-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ43" s="27" t="n"/>
+      <c r="BA43" s="33">
+        <f>IF(OR($AX43="",$AX43="skip",$AX43="units?",$AX43="UNITS?",$AZ43="",$AQ43=""),"",IF($AX43="OVER",IF($AZ43&gt;$AQ43,"WON","LOST"),IF($AZ43&lt;$AQ43,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB43" s="34">
+        <f>IF($BA43="","",IF($BA43="WON",IF($AX43="OVER",$AT43*($AR43-1),$AT43*($AS43-1)),-$AT43))</f>
+        <v/>
+      </c>
+      <c r="BC43" s="34">
+        <f>IF(COUNT($BB$2:$BB43)=0,"",SUM($BB$2:$BB43))</f>
+        <v/>
+      </c>
+      <c r="BD43" s="27" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>Hull</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="28" t="n"/>
+      <c r="I44" s="29" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J44" s="29" t="n">
+        <v>3.901640318062532</v>
+      </c>
+      <c r="K44" s="30" t="n">
+        <v>0.0376702973570564</v>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M44" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N44" s="31" t="n">
+        <v>0.02348535272104956</v>
+      </c>
+      <c r="O44" s="31" t="n">
+        <v>0.08475239734239323</v>
+      </c>
+      <c r="P44" s="31" t="n">
+        <v>0.1561057294194045</v>
+      </c>
+      <c r="Q44" s="31" t="n">
+        <v>0.1955942010352802</v>
+      </c>
+      <c r="R44" s="31" t="n">
+        <v>0.1874746892186152</v>
+      </c>
+      <c r="S44" s="31" t="n">
+        <v>0.1465686279969983</v>
+      </c>
+      <c r="T44" s="31" t="n">
+        <v>0.09732393771937314</v>
+      </c>
+      <c r="U44" s="31" t="n">
+        <v>0.05643633716658476</v>
+      </c>
+      <c r="V44" s="31" t="n">
+        <v>0.02916518474069787</v>
+      </c>
+      <c r="W44" s="28" t="n">
+        <v>0.8917622499365572</v>
+      </c>
+      <c r="X44" s="28" t="n">
+        <v>0.7356565205171527</v>
+      </c>
+      <c r="Y44" s="28" t="n">
+        <v>0.5400623194818726</v>
+      </c>
+      <c r="Z44" s="28" t="n">
+        <v>0.3525876302632573</v>
+      </c>
+      <c r="AA44" s="28" t="n">
+        <v>0.206019002266259</v>
+      </c>
+      <c r="AB44" s="28" t="n">
+        <v>0.1086950645468858</v>
+      </c>
+      <c r="AC44" s="29" t="n">
+        <v>1.121375119961787</v>
+      </c>
+      <c r="AD44" s="29" t="n">
+        <v>1.359330029858253</v>
+      </c>
+      <c r="AE44" s="29" t="n">
+        <v>1.851638160868887</v>
+      </c>
+      <c r="AF44" s="29" t="n">
+        <v>2.836174369626513</v>
+      </c>
+      <c r="AG44" s="29" t="n">
+        <v>4.853921186879644</v>
+      </c>
+      <c r="AH44" s="29" t="n">
+        <v>9.200049737020471</v>
+      </c>
+      <c r="AI44" s="29" t="n">
+        <v>9.238920796245827</v>
+      </c>
+      <c r="AJ44" s="29" t="n">
+        <v>3.782956939041456</v>
+      </c>
+      <c r="AK44" s="29" t="n">
+        <v>2.174207598893579</v>
+      </c>
+      <c r="AL44" s="29" t="n">
+        <v>1.544610586304723</v>
+      </c>
+      <c r="AM44" s="29" t="n">
+        <v>1.259475986017674</v>
+      </c>
+      <c r="AN44" s="29" t="n">
+        <v>1.121950479822742</v>
+      </c>
+      <c r="AO44" s="27" t="n"/>
+      <c r="AP44" s="27" t="n"/>
+      <c r="AQ44" s="27" t="n"/>
+      <c r="AR44" s="27" t="n"/>
+      <c r="AS44" s="27" t="n"/>
+      <c r="AT44" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU44" s="32">
+        <f>IFERROR(IF($AQ44="","",INDEX($W44:$AB44,$AQ44-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV44" s="32">
+        <f>IF($AR44="","",IF($AS44="",1/$AR44,(1/$AR44)/((1/$AR44)+(1/$AS44))))</f>
+        <v/>
+      </c>
+      <c r="AW44" s="32">
+        <f>IF(OR($AU44="",$AV44=""),"",$AU44-$AV44)</f>
+        <v/>
+      </c>
+      <c r="AX44" s="33">
+        <f>IF($AW44="","",IF($AP44="","units?",IF(ISNUMBER(SEARCH("yellow",$AP44)),IF($AW44&gt;=0.05,"OVER",IF($AW44&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY44" s="34">
+        <f>IF(OR($AX44="",$AX44="skip",$AX44="units?",$AX44="UNITS?"),"",IF($AX44="OVER",$AT44*($AU44*$AR44-1),$AT44*((1-$AU44)*$AS44-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ44" s="27" t="n"/>
+      <c r="BA44" s="33">
+        <f>IF(OR($AX44="",$AX44="skip",$AX44="units?",$AX44="UNITS?",$AZ44="",$AQ44=""),"",IF($AX44="OVER",IF($AZ44&gt;$AQ44,"WON","LOST"),IF($AZ44&lt;$AQ44,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB44" s="34">
+        <f>IF($BA44="","",IF($BA44="WON",IF($AX44="OVER",$AT44*($AR44-1),$AT44*($AS44-1)),-$AT44))</f>
+        <v/>
+      </c>
+      <c r="BC44" s="34">
+        <f>IF(COUNT($BB$2:$BB44)=0,"",SUM($BB$2:$BB44))</f>
+        <v/>
+      </c>
+      <c r="BD44" s="27" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="E45" s="26" t="inlineStr">
+        <is>
+          <t>Man City</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="29" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J45" s="29" t="n">
+        <v>3.8838094992955</v>
+      </c>
+      <c r="K45" s="30" t="n">
+        <v>0.03292805832327139</v>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M45" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N45" s="31" t="n">
+        <v>0.0238759573044888</v>
+      </c>
+      <c r="O45" s="31" t="n">
+        <v>0.08579765421532556</v>
+      </c>
+      <c r="P45" s="31" t="n">
+        <v>0.1573627661506122</v>
+      </c>
+      <c r="Q45" s="31" t="n">
+        <v>0.1963354981800754</v>
+      </c>
+      <c r="R45" s="31" t="n">
+        <v>0.1873894826619654</v>
+      </c>
+      <c r="S45" s="31" t="n">
+        <v>0.1458825372898855</v>
+      </c>
+      <c r="T45" s="31" t="n">
+        <v>0.0964587597929633</v>
+      </c>
+      <c r="U45" s="31" t="n">
+        <v>0.05569812004301452</v>
+      </c>
+      <c r="V45" s="31" t="n">
+        <v>0.02866197844270757</v>
+      </c>
+      <c r="W45" s="28" t="n">
+        <v>0.8903263884801856</v>
+      </c>
+      <c r="X45" s="28" t="n">
+        <v>0.7329636223295735</v>
+      </c>
+      <c r="Y45" s="28" t="n">
+        <v>0.5366281241494981</v>
+      </c>
+      <c r="Z45" s="28" t="n">
+        <v>0.3492386414875327</v>
+      </c>
+      <c r="AA45" s="28" t="n">
+        <v>0.2033561041976473</v>
+      </c>
+      <c r="AB45" s="28" t="n">
+        <v>0.106897344404684</v>
+      </c>
+      <c r="AC45" s="29" t="n">
+        <v>1.123183602035014</v>
+      </c>
+      <c r="AD45" s="29" t="n">
+        <v>1.364324189543959</v>
+      </c>
+      <c r="AE45" s="29" t="n">
+        <v>1.863487869900408</v>
+      </c>
+      <c r="AF45" s="29" t="n">
+        <v>2.863371578072349</v>
+      </c>
+      <c r="AG45" s="29" t="n">
+        <v>4.917482088602922</v>
+      </c>
+      <c r="AH45" s="29" t="n">
+        <v>9.354769340333418</v>
+      </c>
+      <c r="AI45" s="29" t="n">
+        <v>9.117963620805297</v>
+      </c>
+      <c r="AJ45" s="29" t="n">
+        <v>3.744808137092802</v>
+      </c>
+      <c r="AK45" s="29" t="n">
+        <v>2.158093859633878</v>
+      </c>
+      <c r="AL45" s="29" t="n">
+        <v>1.536661614767408</v>
+      </c>
+      <c r="AM45" s="29" t="n">
+        <v>1.255266004383093</v>
+      </c>
+      <c r="AN45" s="29" t="n">
+        <v>1.119692113482105</v>
+      </c>
+      <c r="AO45" s="27" t="n"/>
+      <c r="AP45" s="27" t="n"/>
+      <c r="AQ45" s="27" t="n"/>
+      <c r="AR45" s="27" t="n"/>
+      <c r="AS45" s="27" t="n"/>
+      <c r="AT45" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU45" s="32">
+        <f>IFERROR(IF($AQ45="","",INDEX($W45:$AB45,$AQ45-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV45" s="32">
+        <f>IF($AR45="","",IF($AS45="",1/$AR45,(1/$AR45)/((1/$AR45)+(1/$AS45))))</f>
+        <v/>
+      </c>
+      <c r="AW45" s="32">
+        <f>IF(OR($AU45="",$AV45=""),"",$AU45-$AV45)</f>
+        <v/>
+      </c>
+      <c r="AX45" s="33">
+        <f>IF($AW45="","",IF($AP45="","units?",IF(ISNUMBER(SEARCH("yellow",$AP45)),IF($AW45&gt;=0.05,"OVER",IF($AW45&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY45" s="34">
+        <f>IF(OR($AX45="",$AX45="skip",$AX45="units?",$AX45="UNITS?"),"",IF($AX45="OVER",$AT45*($AU45*$AR45-1),$AT45*((1-$AU45)*$AS45-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ45" s="27" t="n"/>
+      <c r="BA45" s="33">
+        <f>IF(OR($AX45="",$AX45="skip",$AX45="units?",$AX45="UNITS?",$AZ45="",$AQ45=""),"",IF($AX45="OVER",IF($AZ45&gt;$AQ45,"WON","LOST"),IF($AZ45&lt;$AQ45,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB45" s="34">
+        <f>IF($BA45="","",IF($BA45="WON",IF($AX45="OVER",$AT45*($AR45-1),$AT45*($AS45-1)),-$AT45))</f>
+        <v/>
+      </c>
+      <c r="BC45" s="34">
+        <f>IF(COUNT($BB$2:$BB45)=0,"",SUM($BB$2:$BB45))</f>
+        <v/>
+      </c>
+      <c r="BD45" s="27" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="28" t="n"/>
+      <c r="I46" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J46" s="29" t="n">
+        <v>3.854486520365823</v>
+      </c>
+      <c r="K46" s="30" t="n">
+        <v>0.01433855799100603</v>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" s="26" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="N46" s="31" t="n">
+        <v>0.02453278970725653</v>
+      </c>
+      <c r="O46" s="31" t="n">
+        <v>0.08754177645900069</v>
+      </c>
+      <c r="P46" s="31" t="n">
+        <v>0.1594394256721349</v>
+      </c>
+      <c r="Q46" s="31" t="n">
+        <v>0.1975360511729997</v>
+      </c>
+      <c r="R46" s="31" t="n">
+        <v>0.1872175467747135</v>
+      </c>
+      <c r="S46" s="31" t="n">
+        <v>0.144729960974943</v>
+      </c>
+      <c r="T46" s="31" t="n">
+        <v>0.09502778563465739</v>
+      </c>
+      <c r="U46" s="31" t="n">
+        <v>0.05448830161611989</v>
+      </c>
+      <c r="V46" s="31" t="n">
+        <v>0.02784342768171281</v>
+      </c>
+      <c r="W46" s="28" t="n">
+        <v>0.8879254338337428</v>
+      </c>
+      <c r="X46" s="28" t="n">
+        <v>0.7284860081616078</v>
+      </c>
+      <c r="Y46" s="28" t="n">
+        <v>0.5309499569886081</v>
+      </c>
+      <c r="Z46" s="28" t="n">
+        <v>0.3437324102138947</v>
+      </c>
+      <c r="AA46" s="28" t="n">
+        <v>0.1990024492389517</v>
+      </c>
+      <c r="AB46" s="28" t="n">
+        <v>0.1039746636042943</v>
+      </c>
+      <c r="AC46" s="29" t="n">
+        <v>1.12622069590051</v>
+      </c>
+      <c r="AD46" s="29" t="n">
+        <v>1.372709961202384</v>
+      </c>
+      <c r="AE46" s="29" t="n">
+        <v>1.883416670135366</v>
+      </c>
+      <c r="AF46" s="29" t="n">
+        <v>2.909239775724754</v>
+      </c>
+      <c r="AG46" s="29" t="n">
+        <v>5.025063780995239</v>
+      </c>
+      <c r="AH46" s="29" t="n">
+        <v>9.617727678406247</v>
+      </c>
+      <c r="AI46" s="29" t="n">
+        <v>8.922631014395792</v>
+      </c>
+      <c r="AJ46" s="29" t="n">
+        <v>3.683051445080627</v>
+      </c>
+      <c r="AK46" s="29" t="n">
+        <v>2.131968677755164</v>
+      </c>
+      <c r="AL46" s="29" t="n">
+        <v>1.523768681500676</v>
+      </c>
+      <c r="AM46" s="29" t="n">
+        <v>1.248443268084745</v>
+      </c>
+      <c r="AN46" s="29" t="n">
+        <v>1.116039870058291</v>
+      </c>
+      <c r="AO46" s="27" t="n"/>
+      <c r="AP46" s="27" t="n"/>
+      <c r="AQ46" s="27" t="n"/>
+      <c r="AR46" s="27" t="n"/>
+      <c r="AS46" s="27" t="n"/>
+      <c r="AT46" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU46" s="32">
+        <f>IFERROR(IF($AQ46="","",INDEX($W46:$AB46,$AQ46-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV46" s="32">
+        <f>IF($AR46="","",IF($AS46="",1/$AR46,(1/$AR46)/((1/$AR46)+(1/$AS46))))</f>
+        <v/>
+      </c>
+      <c r="AW46" s="32">
+        <f>IF(OR($AU46="",$AV46=""),"",$AU46-$AV46)</f>
+        <v/>
+      </c>
+      <c r="AX46" s="33">
+        <f>IF($AW46="","",IF($AP46="","units?",IF(ISNUMBER(SEARCH("yellow",$AP46)),IF($AW46&gt;=0.05,"OVER",IF($AW46&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY46" s="34">
+        <f>IF(OR($AX46="",$AX46="skip",$AX46="units?",$AX46="UNITS?"),"",IF($AX46="OVER",$AT46*($AU46*$AR46-1),$AT46*((1-$AU46)*$AS46-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ46" s="27" t="n"/>
+      <c r="BA46" s="33">
+        <f>IF(OR($AX46="",$AX46="skip",$AX46="units?",$AX46="UNITS?",$AZ46="",$AQ46=""),"",IF($AX46="OVER",IF($AZ46&gt;$AQ46,"WON","LOST"),IF($AZ46&lt;$AQ46,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB46" s="34">
+        <f>IF($BA46="","",IF($BA46="WON",IF($AX46="OVER",$AT46*($AR46-1),$AT46*($AS46-1)),-$AT46))</f>
+        <v/>
+      </c>
+      <c r="BC46" s="34">
+        <f>IF(COUNT($BB$2:$BB46)=0,"",SUM($BB$2:$BB46))</f>
+        <v/>
+      </c>
+      <c r="BD46" s="27" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="G47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="29" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J47" s="29" t="n">
+        <v>3.89911562598766</v>
+      </c>
+      <c r="K47" s="30" t="n">
+        <v>0.03699883669884563</v>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M47" s="26" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="N47" s="31" t="n">
+        <v>0.02354026012503138</v>
+      </c>
+      <c r="O47" s="31" t="n">
+        <v>0.08489969765189745</v>
+      </c>
+      <c r="P47" s="31" t="n">
+        <v>0.1562834451405931</v>
+      </c>
+      <c r="Q47" s="31" t="n">
+        <v>0.1956996683258302</v>
+      </c>
+      <c r="R47" s="31" t="n">
+        <v>0.187463507574434</v>
+      </c>
+      <c r="S47" s="31" t="n">
+        <v>0.1464721648293098</v>
+      </c>
+      <c r="T47" s="31" t="n">
+        <v>0.09720167111748283</v>
+      </c>
+      <c r="U47" s="31" t="n">
+        <v>0.05633170032497743</v>
+      </c>
+      <c r="V47" s="31" t="n">
+        <v>0.02909368645211623</v>
+      </c>
+      <c r="W47" s="28" t="n">
+        <v>0.8915600422230712</v>
+      </c>
+      <c r="X47" s="28" t="n">
+        <v>0.7352765970824782</v>
+      </c>
+      <c r="Y47" s="28" t="n">
+        <v>0.5395769287566479</v>
+      </c>
+      <c r="Z47" s="28" t="n">
+        <v>0.3521134211822139</v>
+      </c>
+      <c r="AA47" s="28" t="n">
+        <v>0.2056412563529041</v>
+      </c>
+      <c r="AB47" s="28" t="n">
+        <v>0.1084395852354213</v>
+      </c>
+      <c r="AC47" s="29" t="n">
+        <v>1.121629450223608</v>
+      </c>
+      <c r="AD47" s="29" t="n">
+        <v>1.360032406808437</v>
+      </c>
+      <c r="AE47" s="29" t="n">
+        <v>1.853303851045502</v>
+      </c>
+      <c r="AF47" s="29" t="n">
+        <v>2.839993990125453</v>
+      </c>
+      <c r="AG47" s="29" t="n">
+        <v>4.862837437074809</v>
+      </c>
+      <c r="AH47" s="29" t="n">
+        <v>9.221724685030928</v>
+      </c>
+      <c r="AI47" s="29" t="n">
+        <v>9.221693004133162</v>
+      </c>
+      <c r="AJ47" s="29" t="n">
+        <v>3.777527747750975</v>
+      </c>
+      <c r="AK47" s="29" t="n">
+        <v>2.171915489159881</v>
+      </c>
+      <c r="AL47" s="29" t="n">
+        <v>1.543480036003715</v>
+      </c>
+      <c r="AM47" s="29" t="n">
+        <v>1.258877060267197</v>
+      </c>
+      <c r="AN47" s="29" t="n">
+        <v>1.121628981546983</v>
+      </c>
+      <c r="AO47" s="27" t="n"/>
+      <c r="AP47" s="27" t="n"/>
+      <c r="AQ47" s="27" t="n"/>
+      <c r="AR47" s="27" t="n"/>
+      <c r="AS47" s="27" t="n"/>
+      <c r="AT47" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU47" s="32">
+        <f>IFERROR(IF($AQ47="","",INDEX($W47:$AB47,$AQ47-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV47" s="32">
+        <f>IF($AR47="","",IF($AS47="",1/$AR47,(1/$AR47)/((1/$AR47)+(1/$AS47))))</f>
+        <v/>
+      </c>
+      <c r="AW47" s="32">
+        <f>IF(OR($AU47="",$AV47=""),"",$AU47-$AV47)</f>
+        <v/>
+      </c>
+      <c r="AX47" s="33">
+        <f>IF($AW47="","",IF($AP47="","units?",IF(ISNUMBER(SEARCH("yellow",$AP47)),IF($AW47&gt;=0.05,"OVER",IF($AW47&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY47" s="34">
+        <f>IF(OR($AX47="",$AX47="skip",$AX47="units?",$AX47="UNITS?"),"",IF($AX47="OVER",$AT47*($AU47*$AR47-1),$AT47*((1-$AU47)*$AS47-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ47" s="27" t="n"/>
+      <c r="BA47" s="33">
+        <f>IF(OR($AX47="",$AX47="skip",$AX47="units?",$AX47="UNITS?",$AZ47="",$AQ47=""),"",IF($AX47="OVER",IF($AZ47&gt;$AQ47,"WON","LOST"),IF($AZ47&lt;$AQ47,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB47" s="34">
+        <f>IF($BA47="","",IF($BA47="WON",IF($AX47="OVER",$AT47*($AR47-1),$AT47*($AS47-1)),-$AT47))</f>
+        <v/>
+      </c>
+      <c r="BC47" s="34">
+        <f>IF(COUNT($BB$2:$BB47)=0,"",SUM($BB$2:$BB47))</f>
+        <v/>
+      </c>
+      <c r="BD47" s="27" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="35" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="36" t="inlineStr">
+        <is>
+          <t>bets placed</t>
+        </is>
+      </c>
+      <c r="E50" s="37">
+        <f>COUNTIF($AX$2:$AX47,"OVER")+COUNTIF($AX$2:$AX47,"UNDER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="36" t="inlineStr">
+        <is>
+          <t>bets won</t>
+        </is>
+      </c>
+      <c r="E51" s="37">
+        <f>COUNTIF($BA$2:$BA47,"WON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="36" t="inlineStr">
+        <is>
+          <t>total staked</t>
+        </is>
+      </c>
+      <c r="E52" s="38">
+        <f>SUMPRODUCT(($BA$2:$BA47&lt;&gt;"")*$AT$2:$AT47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="36" t="inlineStr">
+        <is>
+          <t>profit / loss EUR</t>
+        </is>
+      </c>
+      <c r="E53" s="38">
+        <f>IF(COUNT($BB$2:$BB47)=0,"",SUM($BB$2:$BB47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="36" t="inlineStr">
+        <is>
+          <t>return on stake</t>
+        </is>
+      </c>
+      <c r="E54" s="39">
+        <f>IF($E52=0,"",$E53/$E52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="46" t="inlineStr">
+        <is>
+          <t>HOW TO USE THIS SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="47" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="47" t="inlineStr">
+        <is>
+          <t>1. Fill the yellow columns only. Everything green is computed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="47" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="47" t="inlineStr">
+        <is>
+          <t>2. 'Settles on' must say what the market actually pays out on. Write 'yellow cards' only if the bookmaker settles on yellows alone. If it says total cards or booking points, BET? shows UNITS? and gives no verdict -- on purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="47" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The model predicts yellows. Counting a red as two cards adds about 5-6 percentage points at every line, always upward, which is larger than the 5% edge threshold. Priced against the wrong market the model shows an OVER edge on nearly every game, and that looks identical to finding an edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="47" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The market to look for is 'Yellow Cards', as in the Chelsea screenshot -- not 'Cards' and not 'Booking Points'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="47" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="47" t="inlineStr">
+        <is>
+          <t>3. Record BOTH sides of the price. With one side only, the de-vig cannot run and the implied probability is overstated by the whole margin, which invents edge that is not there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="47" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="47" t="inlineStr">
+        <is>
+          <t>4. Record the price when you see it, before kick-off. A price looked up afterwards is not one you could have taken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="47" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="47" t="inlineStr">
+        <is>
+          <t>5. Stake is EUR 100 a bet. Change the column if you want; the P/L follows it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="47" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="46" t="inlineStr">
+        <is>
+          <t>WHAT THIS SHEET IS AND IS NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="47" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="47" t="inlineStr">
+        <is>
+          <t>46 fixtures. A sample this size tells you nothing about whether the model beats a bookmaker -- a verdict on profitability needs thousands of bets. Treat a single week as practice for the workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="47" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="47" t="inlineStr">
+        <is>
+          <t>The referee is 48% of the model's value. If the Referee column says 'not known', the EFL has not published appointments yet (they come one to three days ahead) and these are the weaker version of the model. Re-run run_week_sheet.py for the same dates once they are out and every unplayed row updates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="47" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="47" t="inlineStr">
+        <is>
+          <t>Model fingerprint d30beac40c73a847, frozen for the season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="47" t="inlineStr">
+        <is>
+          <t>Scoring these results against the model is a holdout look.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/forward_test_2026-09-18.xlsx
+++ b/forward_test_2026-09-18.xlsx
@@ -10089,7 +10089,9 @@
         <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?"),"",IF($AX2="OVER",$AT2*($AU2*$AR2-1),$AT2*((1-$AU2)*$AS2-1)))</f>
         <v/>
       </c>
-      <c r="AZ2" s="27" t="n"/>
+      <c r="AZ2" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA2" s="33">
         <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?",$AZ2="",$AQ2=""),"",IF($AX2="OVER",IF($AZ2&gt;$AQ2,"WON","LOST"),IF($AZ2&lt;$AQ2,"WON","LOST")))</f>
         <v/>
@@ -10102,7 +10104,11 @@
         <f>IF(COUNT($BB$2:$BB2)=0,"",SUM($BB$2:$BB2))</f>
         <v/>
       </c>
-      <c r="BD2" s="27" t="n"/>
+      <c r="BD2" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="26" t="inlineStr">
@@ -10265,7 +10271,9 @@
         <f>IF(OR($AX3="",$AX3="skip",$AX3="units?",$AX3="UNITS?"),"",IF($AX3="OVER",$AT3*($AU3*$AR3-1),$AT3*((1-$AU3)*$AS3-1)))</f>
         <v/>
       </c>
-      <c r="AZ3" s="27" t="n"/>
+      <c r="AZ3" s="27" t="n">
+        <v>6</v>
+      </c>
       <c r="BA3" s="33">
         <f>IF(OR($AX3="",$AX3="skip",$AX3="units?",$AX3="UNITS?",$AZ3="",$AQ3=""),"",IF($AX3="OVER",IF($AZ3&gt;$AQ3,"WON","LOST"),IF($AZ3&lt;$AQ3,"WON","LOST")))</f>
         <v/>
@@ -10278,7 +10286,11 @@
         <f>IF(COUNT($BB$2:$BB3)=0,"",SUM($BB$2:$BB3))</f>
         <v/>
       </c>
-      <c r="BD3" s="27" t="n"/>
+      <c r="BD3" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
@@ -10441,7 +10453,9 @@
         <f>IF(OR($AX4="",$AX4="skip",$AX4="units?",$AX4="UNITS?"),"",IF($AX4="OVER",$AT4*($AU4*$AR4-1),$AT4*((1-$AU4)*$AS4-1)))</f>
         <v/>
       </c>
-      <c r="AZ4" s="27" t="n"/>
+      <c r="AZ4" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA4" s="33">
         <f>IF(OR($AX4="",$AX4="skip",$AX4="units?",$AX4="UNITS?",$AZ4="",$AQ4=""),"",IF($AX4="OVER",IF($AZ4&gt;$AQ4,"WON","LOST"),IF($AZ4&lt;$AQ4,"WON","LOST")))</f>
         <v/>
@@ -10454,7 +10468,11 @@
         <f>IF(COUNT($BB$2:$BB4)=0,"",SUM($BB$2:$BB4))</f>
         <v/>
       </c>
-      <c r="BD4" s="27" t="n"/>
+      <c r="BD4" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
@@ -10617,7 +10635,9 @@
         <f>IF(OR($AX5="",$AX5="skip",$AX5="units?",$AX5="UNITS?"),"",IF($AX5="OVER",$AT5*($AU5*$AR5-1),$AT5*((1-$AU5)*$AS5-1)))</f>
         <v/>
       </c>
-      <c r="AZ5" s="27" t="n"/>
+      <c r="AZ5" s="27" t="n">
+        <v>5</v>
+      </c>
       <c r="BA5" s="33">
         <f>IF(OR($AX5="",$AX5="skip",$AX5="units?",$AX5="UNITS?",$AZ5="",$AQ5=""),"",IF($AX5="OVER",IF($AZ5&gt;$AQ5,"WON","LOST"),IF($AZ5&lt;$AQ5,"WON","LOST")))</f>
         <v/>
@@ -10630,7 +10650,11 @@
         <f>IF(COUNT($BB$2:$BB5)=0,"",SUM($BB$2:$BB5))</f>
         <v/>
       </c>
-      <c r="BD5" s="27" t="n"/>
+      <c r="BD5" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
@@ -10793,7 +10817,9 @@
         <f>IF(OR($AX6="",$AX6="skip",$AX6="units?",$AX6="UNITS?"),"",IF($AX6="OVER",$AT6*($AU6*$AR6-1),$AT6*((1-$AU6)*$AS6-1)))</f>
         <v/>
       </c>
-      <c r="AZ6" s="27" t="n"/>
+      <c r="AZ6" s="27" t="n">
+        <v>2</v>
+      </c>
       <c r="BA6" s="33">
         <f>IF(OR($AX6="",$AX6="skip",$AX6="units?",$AX6="UNITS?",$AZ6="",$AQ6=""),"",IF($AX6="OVER",IF($AZ6&gt;$AQ6,"WON","LOST"),IF($AZ6&lt;$AQ6,"WON","LOST")))</f>
         <v/>
@@ -10806,7 +10832,11 @@
         <f>IF(COUNT($BB$2:$BB6)=0,"",SUM($BB$2:$BB6))</f>
         <v/>
       </c>
-      <c r="BD6" s="27" t="n"/>
+      <c r="BD6" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
@@ -10969,7 +10999,9 @@
         <f>IF(OR($AX7="",$AX7="skip",$AX7="units?",$AX7="UNITS?"),"",IF($AX7="OVER",$AT7*($AU7*$AR7-1),$AT7*((1-$AU7)*$AS7-1)))</f>
         <v/>
       </c>
-      <c r="AZ7" s="27" t="n"/>
+      <c r="AZ7" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA7" s="33">
         <f>IF(OR($AX7="",$AX7="skip",$AX7="units?",$AX7="UNITS?",$AZ7="",$AQ7=""),"",IF($AX7="OVER",IF($AZ7&gt;$AQ7,"WON","LOST"),IF($AZ7&lt;$AQ7,"WON","LOST")))</f>
         <v/>
@@ -10982,7 +11014,11 @@
         <f>IF(COUNT($BB$2:$BB7)=0,"",SUM($BB$2:$BB7))</f>
         <v/>
       </c>
-      <c r="BD7" s="27" t="n"/>
+      <c r="BD7" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
@@ -11321,7 +11357,9 @@
         <f>IF(OR($AX9="",$AX9="skip",$AX9="units?",$AX9="UNITS?"),"",IF($AX9="OVER",$AT9*($AU9*$AR9-1),$AT9*((1-$AU9)*$AS9-1)))</f>
         <v/>
       </c>
-      <c r="AZ9" s="27" t="n"/>
+      <c r="AZ9" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA9" s="33">
         <f>IF(OR($AX9="",$AX9="skip",$AX9="units?",$AX9="UNITS?",$AZ9="",$AQ9=""),"",IF($AX9="OVER",IF($AZ9&gt;$AQ9,"WON","LOST"),IF($AZ9&lt;$AQ9,"WON","LOST")))</f>
         <v/>
@@ -11334,7 +11372,11 @@
         <f>IF(COUNT($BB$2:$BB9)=0,"",SUM($BB$2:$BB9))</f>
         <v/>
       </c>
-      <c r="BD9" s="27" t="n"/>
+      <c r="BD9" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
@@ -11497,7 +11539,9 @@
         <f>IF(OR($AX10="",$AX10="skip",$AX10="units?",$AX10="UNITS?"),"",IF($AX10="OVER",$AT10*($AU10*$AR10-1),$AT10*((1-$AU10)*$AS10-1)))</f>
         <v/>
       </c>
-      <c r="AZ10" s="27" t="n"/>
+      <c r="AZ10" s="27" t="n">
+        <v>2</v>
+      </c>
       <c r="BA10" s="33">
         <f>IF(OR($AX10="",$AX10="skip",$AX10="units?",$AX10="UNITS?",$AZ10="",$AQ10=""),"",IF($AX10="OVER",IF($AZ10&gt;$AQ10,"WON","LOST"),IF($AZ10&lt;$AQ10,"WON","LOST")))</f>
         <v/>
@@ -11510,7 +11554,11 @@
         <f>IF(COUNT($BB$2:$BB10)=0,"",SUM($BB$2:$BB10))</f>
         <v/>
       </c>
-      <c r="BD10" s="27" t="n"/>
+      <c r="BD10" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
@@ -11673,7 +11721,9 @@
         <f>IF(OR($AX11="",$AX11="skip",$AX11="units?",$AX11="UNITS?"),"",IF($AX11="OVER",$AT11*($AU11*$AR11-1),$AT11*((1-$AU11)*$AS11-1)))</f>
         <v/>
       </c>
-      <c r="AZ11" s="27" t="n"/>
+      <c r="AZ11" s="27" t="n">
+        <v>3</v>
+      </c>
       <c r="BA11" s="33">
         <f>IF(OR($AX11="",$AX11="skip",$AX11="units?",$AX11="UNITS?",$AZ11="",$AQ11=""),"",IF($AX11="OVER",IF($AZ11&gt;$AQ11,"WON","LOST"),IF($AZ11&lt;$AQ11,"WON","LOST")))</f>
         <v/>
@@ -11686,7 +11736,11 @@
         <f>IF(COUNT($BB$2:$BB11)=0,"",SUM($BB$2:$BB11))</f>
         <v/>
       </c>
-      <c r="BD11" s="27" t="n"/>
+      <c r="BD11" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
@@ -11849,7 +11903,9 @@
         <f>IF(OR($AX12="",$AX12="skip",$AX12="units?",$AX12="UNITS?"),"",IF($AX12="OVER",$AT12*($AU12*$AR12-1),$AT12*((1-$AU12)*$AS12-1)))</f>
         <v/>
       </c>
-      <c r="AZ12" s="27" t="n"/>
+      <c r="AZ12" s="27" t="n">
+        <v>3</v>
+      </c>
       <c r="BA12" s="33">
         <f>IF(OR($AX12="",$AX12="skip",$AX12="units?",$AX12="UNITS?",$AZ12="",$AQ12=""),"",IF($AX12="OVER",IF($AZ12&gt;$AQ12,"WON","LOST"),IF($AZ12&lt;$AQ12,"WON","LOST")))</f>
         <v/>
@@ -11862,7 +11918,11 @@
         <f>IF(COUNT($BB$2:$BB12)=0,"",SUM($BB$2:$BB12))</f>
         <v/>
       </c>
-      <c r="BD12" s="27" t="n"/>
+      <c r="BD12" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
@@ -12025,7 +12085,9 @@
         <f>IF(OR($AX13="",$AX13="skip",$AX13="units?",$AX13="UNITS?"),"",IF($AX13="OVER",$AT13*($AU13*$AR13-1),$AT13*((1-$AU13)*$AS13-1)))</f>
         <v/>
       </c>
-      <c r="AZ13" s="27" t="n"/>
+      <c r="AZ13" s="27" t="n">
+        <v>2</v>
+      </c>
       <c r="BA13" s="33">
         <f>IF(OR($AX13="",$AX13="skip",$AX13="units?",$AX13="UNITS?",$AZ13="",$AQ13=""),"",IF($AX13="OVER",IF($AZ13&gt;$AQ13,"WON","LOST"),IF($AZ13&lt;$AQ13,"WON","LOST")))</f>
         <v/>
@@ -12038,7 +12100,11 @@
         <f>IF(COUNT($BB$2:$BB13)=0,"",SUM($BB$2:$BB13))</f>
         <v/>
       </c>
-      <c r="BD13" s="27" t="n"/>
+      <c r="BD13" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="26" t="inlineStr">
@@ -12201,7 +12267,9 @@
         <f>IF(OR($AX14="",$AX14="skip",$AX14="units?",$AX14="UNITS?"),"",IF($AX14="OVER",$AT14*($AU14*$AR14-1),$AT14*((1-$AU14)*$AS14-1)))</f>
         <v/>
       </c>
-      <c r="AZ14" s="27" t="n"/>
+      <c r="AZ14" s="27" t="n">
+        <v>3</v>
+      </c>
       <c r="BA14" s="33">
         <f>IF(OR($AX14="",$AX14="skip",$AX14="units?",$AX14="UNITS?",$AZ14="",$AQ14=""),"",IF($AX14="OVER",IF($AZ14&gt;$AQ14,"WON","LOST"),IF($AZ14&lt;$AQ14,"WON","LOST")))</f>
         <v/>
@@ -12214,7 +12282,11 @@
         <f>IF(COUNT($BB$2:$BB14)=0,"",SUM($BB$2:$BB14))</f>
         <v/>
       </c>
-      <c r="BD14" s="27" t="n"/>
+      <c r="BD14" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="26" t="inlineStr">
@@ -12377,7 +12449,9 @@
         <f>IF(OR($AX15="",$AX15="skip",$AX15="units?",$AX15="UNITS?"),"",IF($AX15="OVER",$AT15*($AU15*$AR15-1),$AT15*((1-$AU15)*$AS15-1)))</f>
         <v/>
       </c>
-      <c r="AZ15" s="27" t="n"/>
+      <c r="AZ15" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA15" s="33">
         <f>IF(OR($AX15="",$AX15="skip",$AX15="units?",$AX15="UNITS?",$AZ15="",$AQ15=""),"",IF($AX15="OVER",IF($AZ15&gt;$AQ15,"WON","LOST"),IF($AZ15&lt;$AQ15,"WON","LOST")))</f>
         <v/>
@@ -12390,8 +12464,13 @@
         <f>IF(COUNT($BB$2:$BB15)=0,"",SUM($BB$2:$BB15))</f>
         <v/>
       </c>
-      <c r="BD15" s="27" t="n"/>
-    </row>
+      <c r="BD15" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data); 1 second-caution dismissal(s) -- not adjusted</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
@@ -12454,135 +12533,137 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25">
-      <c r="A25" s="46" t="inlineStr">
+      <c r="A25" s="48" t="inlineStr">
         <is>
           <t>HOW TO USE THIS SHEET</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="47" t="inlineStr"/>
+      <c r="A26" s="49" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="47" t="inlineStr">
+      <c r="A27" s="49" t="inlineStr">
         <is>
           <t>1. Fill the yellow columns only. Everything green is computed.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="47" t="inlineStr"/>
+      <c r="A28" s="49" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="47" t="inlineStr">
+      <c r="A29" s="49" t="inlineStr">
         <is>
           <t>2. 'Settles on' must say what the market actually pays out on. Write 'yellow cards' only if the bookmaker settles on yellows alone. If it says total cards or booking points, BET? shows UNITS? and gives no verdict -- on purpose.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="47" t="inlineStr"/>
+      <c r="A30" s="49" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="47" t="inlineStr">
+      <c r="A31" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">   The model predicts yellows. Counting a red as two cards adds about 5-6 percentage points at every line, always upward, which is larger than the 5% edge threshold. Priced against the wrong market the model shows an OVER edge on nearly every game, and that looks identical to finding an edge.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="47" t="inlineStr"/>
+      <c r="A32" s="49" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="47" t="inlineStr">
+      <c r="A33" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">   The market to look for is 'Yellow Cards', as in the Chelsea screenshot -- not 'Cards' and not 'Booking Points'.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="47" t="inlineStr"/>
+      <c r="A34" s="49" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="47" t="inlineStr">
+      <c r="A35" s="49" t="inlineStr">
         <is>
           <t>3. Record BOTH sides of the price. With one side only, the de-vig cannot run and the implied probability is overstated by the whole margin, which invents edge that is not there.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="47" t="inlineStr"/>
+      <c r="A36" s="49" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="47" t="inlineStr">
+      <c r="A37" s="49" t="inlineStr">
         <is>
           <t>4. Record the price when you see it, before kick-off. A price looked up afterwards is not one you could have taken.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="47" t="inlineStr"/>
+      <c r="A38" s="49" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="47" t="inlineStr">
+      <c r="A39" s="49" t="inlineStr">
         <is>
           <t>5. Stake is EUR 100 a bet. Change the column if you want; the P/L follows it.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="47" t="inlineStr"/>
+      <c r="A40" s="49" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="46" t="inlineStr">
+      <c r="A41" s="48" t="inlineStr">
         <is>
           <t>WHAT THIS WEEK IS AND IS NOT</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="47" t="inlineStr"/>
+      <c r="A42" s="49" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="47" t="inlineStr">
+      <c r="A43" s="49" t="inlineStr">
         <is>
           <t>Fourteen fixtures, League One and League Two only -- 26 September starts a two-weekend international break, and seven more EFL matches are postponed. No Premier League or Championship football until 10 October.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="47" t="inlineStr"/>
+      <c r="A44" s="49" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="47" t="inlineStr">
+      <c r="A45" s="49" t="inlineStr">
         <is>
           <t>Fourteen matches is far too few to tell you anything about whether the model beats a bookmaker. Treat this as practice for the workflow. A verdict on profitability needs thousands of bets.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="47" t="inlineStr"/>
+      <c r="A46" s="49" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="47" t="inlineStr">
+      <c r="A47" s="49" t="inlineStr">
         <is>
           <t>Referees are not in yet. The EFL publishes appointments one to three days ahead, and the referee is 48% of the model's value -- so these numbers are the weaker version of the model. Re-run cards/run_week_sheet.py once the appointments are out.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="47" t="inlineStr"/>
+      <c r="A48" s="49" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="47" t="inlineStr">
+      <c r="A49" s="49" t="inlineStr">
         <is>
           <t>Model fingerprint d30beac40c73a847, frozen for the season.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="47" t="inlineStr">
+      <c r="A50" s="49" t="inlineStr">
         <is>
           <t>Scoring these results against the model is a holdout look.</t>
         </is>
@@ -21101,124 +21182,124 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="46" t="inlineStr">
+      <c r="A57" s="48" t="inlineStr">
         <is>
           <t>HOW TO USE THIS SHEET</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="47" t="inlineStr"/>
+      <c r="A58" s="49" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="47" t="inlineStr">
+      <c r="A59" s="49" t="inlineStr">
         <is>
           <t>1. Fill the yellow columns only. Everything green is computed.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="47" t="inlineStr"/>
+      <c r="A60" s="49" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="47" t="inlineStr">
+      <c r="A61" s="49" t="inlineStr">
         <is>
           <t>2. 'Settles on' must say what the market actually pays out on. Write 'yellow cards' only if the bookmaker settles on yellows alone. If it says total cards or booking points, BET? shows UNITS? and gives no verdict -- on purpose.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="47" t="inlineStr"/>
+      <c r="A62" s="49" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="47" t="inlineStr">
+      <c r="A63" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">   The model predicts yellows. Counting a red as two cards adds about 5-6 percentage points at every line, always upward, which is larger than the 5% edge threshold. Priced against the wrong market the model shows an OVER edge on nearly every game, and that looks identical to finding an edge.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="47" t="inlineStr"/>
+      <c r="A64" s="49" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="47" t="inlineStr">
+      <c r="A65" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">   The market to look for is 'Yellow Cards', as in the Chelsea screenshot -- not 'Cards' and not 'Booking Points'.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="47" t="inlineStr"/>
+      <c r="A66" s="49" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="47" t="inlineStr">
+      <c r="A67" s="49" t="inlineStr">
         <is>
           <t>3. Record BOTH sides of the price. With one side only, the de-vig cannot run and the implied probability is overstated by the whole margin, which invents edge that is not there.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="47" t="inlineStr"/>
+      <c r="A68" s="49" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="47" t="inlineStr">
+      <c r="A69" s="49" t="inlineStr">
         <is>
           <t>4. Record the price when you see it, before kick-off. A price looked up afterwards is not one you could have taken.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="47" t="inlineStr"/>
+      <c r="A70" s="49" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="47" t="inlineStr">
+      <c r="A71" s="49" t="inlineStr">
         <is>
           <t>5. Stake is EUR 100 a bet. Change the column if you want; the P/L follows it.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="47" t="inlineStr"/>
+      <c r="A72" s="49" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="46" t="inlineStr">
+      <c r="A73" s="48" t="inlineStr">
         <is>
           <t>WHAT THIS SHEET IS AND IS NOT</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="47" t="inlineStr"/>
+      <c r="A74" s="49" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="47" t="inlineStr">
+      <c r="A75" s="49" t="inlineStr">
         <is>
           <t>46 fixtures. A sample this size tells you nothing about whether the model beats a bookmaker -- a verdict on profitability needs thousands of bets. Treat a single week as practice for the workflow.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="47" t="inlineStr"/>
+      <c r="A76" s="49" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="47" t="inlineStr">
+      <c r="A77" s="49" t="inlineStr">
         <is>
           <t>The referee is 48% of the model's value. If the Referee column says 'not known', the EFL has not published appointments yet (they come one to three days ahead) and these are the weaker version of the model. Re-run run_week_sheet.py for the same dates once they are out and every unplayed row updates.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="47" t="inlineStr"/>
+      <c r="A78" s="49" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="47" t="inlineStr">
+      <c r="A79" s="49" t="inlineStr">
         <is>
           <t>Model fingerprint d30beac40c73a847, frozen for the season.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="47" t="inlineStr">
+      <c r="A80" s="49" t="inlineStr">
         <is>
           <t>Scoring these results against the model is a holdout look.</t>
         </is>
@@ -21741,7 +21822,9 @@
         <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?"),"",IF($AX2="OVER",$AT2*($AU2*$AR2-1),$AT2*((1-$AU2)*$AS2-1)))</f>
         <v/>
       </c>
-      <c r="AZ2" s="27" t="n"/>
+      <c r="AZ2" s="27" t="n">
+        <v>2</v>
+      </c>
       <c r="BA2" s="33">
         <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?",$AZ2="",$AQ2=""),"",IF($AX2="OVER",IF($AZ2&gt;$AQ2,"WON","LOST"),IF($AZ2&lt;$AQ2,"WON","LOST")))</f>
         <v/>
@@ -21754,7 +21837,11 @@
         <f>IF(COUNT($BB$2:$BB2)=0,"",SUM($BB$2:$BB2))</f>
         <v/>
       </c>
-      <c r="BD2" s="27" t="n"/>
+      <c r="BD2" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-03 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="26" t="inlineStr">
@@ -21919,7 +22006,9 @@
         <f>IF(OR($AX3="",$AX3="skip",$AX3="units?",$AX3="UNITS?"),"",IF($AX3="OVER",$AT3*($AU3*$AR3-1),$AT3*((1-$AU3)*$AS3-1)))</f>
         <v/>
       </c>
-      <c r="AZ3" s="27" t="n"/>
+      <c r="AZ3" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA3" s="33">
         <f>IF(OR($AX3="",$AX3="skip",$AX3="units?",$AX3="UNITS?",$AZ3="",$AQ3=""),"",IF($AX3="OVER",IF($AZ3&gt;$AQ3,"WON","LOST"),IF($AZ3&lt;$AQ3,"WON","LOST")))</f>
         <v/>
@@ -21932,7 +22021,11 @@
         <f>IF(COUNT($BB$2:$BB3)=0,"",SUM($BB$2:$BB3))</f>
         <v/>
       </c>
-      <c r="BD3" s="27" t="n"/>
+      <c r="BD3" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-03 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
@@ -22097,7 +22190,9 @@
         <f>IF(OR($AX4="",$AX4="skip",$AX4="units?",$AX4="UNITS?"),"",IF($AX4="OVER",$AT4*($AU4*$AR4-1),$AT4*((1-$AU4)*$AS4-1)))</f>
         <v/>
       </c>
-      <c r="AZ4" s="27" t="n"/>
+      <c r="AZ4" s="27" t="n">
+        <v>5</v>
+      </c>
       <c r="BA4" s="33">
         <f>IF(OR($AX4="",$AX4="skip",$AX4="units?",$AX4="UNITS?",$AZ4="",$AQ4=""),"",IF($AX4="OVER",IF($AZ4&gt;$AQ4,"WON","LOST"),IF($AZ4&lt;$AQ4,"WON","LOST")))</f>
         <v/>
@@ -22110,7 +22205,11 @@
         <f>IF(COUNT($BB$2:$BB4)=0,"",SUM($BB$2:$BB4))</f>
         <v/>
       </c>
-      <c r="BD4" s="27" t="n"/>
+      <c r="BD4" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-03 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
@@ -22275,7 +22374,9 @@
         <f>IF(OR($AX5="",$AX5="skip",$AX5="units?",$AX5="UNITS?"),"",IF($AX5="OVER",$AT5*($AU5*$AR5-1),$AT5*((1-$AU5)*$AS5-1)))</f>
         <v/>
       </c>
-      <c r="AZ5" s="27" t="n"/>
+      <c r="AZ5" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA5" s="33">
         <f>IF(OR($AX5="",$AX5="skip",$AX5="units?",$AX5="UNITS?",$AZ5="",$AQ5=""),"",IF($AX5="OVER",IF($AZ5&gt;$AQ5,"WON","LOST"),IF($AZ5&lt;$AQ5,"WON","LOST")))</f>
         <v/>
@@ -22288,7 +22389,11 @@
         <f>IF(COUNT($BB$2:$BB5)=0,"",SUM($BB$2:$BB5))</f>
         <v/>
       </c>
-      <c r="BD5" s="27" t="n"/>
+      <c r="BD5" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-03 (provisional, ~97% exact vs football-data); 1 second-caution dismissal(s) -- not adjusted</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
@@ -22453,7 +22558,9 @@
         <f>IF(OR($AX6="",$AX6="skip",$AX6="units?",$AX6="UNITS?"),"",IF($AX6="OVER",$AT6*($AU6*$AR6-1),$AT6*((1-$AU6)*$AS6-1)))</f>
         <v/>
       </c>
-      <c r="AZ6" s="27" t="n"/>
+      <c r="AZ6" s="27" t="n">
+        <v>6</v>
+      </c>
       <c r="BA6" s="33">
         <f>IF(OR($AX6="",$AX6="skip",$AX6="units?",$AX6="UNITS?",$AZ6="",$AQ6=""),"",IF($AX6="OVER",IF($AZ6&gt;$AQ6,"WON","LOST"),IF($AZ6&lt;$AQ6,"WON","LOST")))</f>
         <v/>
@@ -22466,7 +22573,11 @@
         <f>IF(COUNT($BB$2:$BB6)=0,"",SUM($BB$2:$BB6))</f>
         <v/>
       </c>
-      <c r="BD6" s="27" t="n"/>
+      <c r="BD6" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-03 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
@@ -22631,7 +22742,9 @@
         <f>IF(OR($AX7="",$AX7="skip",$AX7="units?",$AX7="UNITS?"),"",IF($AX7="OVER",$AT7*($AU7*$AR7-1),$AT7*((1-$AU7)*$AS7-1)))</f>
         <v/>
       </c>
-      <c r="AZ7" s="27" t="n"/>
+      <c r="AZ7" s="27" t="n">
+        <v>8</v>
+      </c>
       <c r="BA7" s="33">
         <f>IF(OR($AX7="",$AX7="skip",$AX7="units?",$AX7="UNITS?",$AZ7="",$AQ7=""),"",IF($AX7="OVER",IF($AZ7&gt;$AQ7,"WON","LOST"),IF($AZ7&lt;$AQ7,"WON","LOST")))</f>
         <v/>
@@ -22644,7 +22757,11 @@
         <f>IF(COUNT($BB$2:$BB7)=0,"",SUM($BB$2:$BB7))</f>
         <v/>
       </c>
-      <c r="BD7" s="27" t="n"/>
+      <c r="BD7" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-03 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
@@ -22809,7 +22926,9 @@
         <f>IF(OR($AX8="",$AX8="skip",$AX8="units?",$AX8="UNITS?"),"",IF($AX8="OVER",$AT8*($AU8*$AR8-1),$AT8*((1-$AU8)*$AS8-1)))</f>
         <v/>
       </c>
-      <c r="AZ8" s="27" t="n"/>
+      <c r="AZ8" s="27" t="n">
+        <v>3</v>
+      </c>
       <c r="BA8" s="33">
         <f>IF(OR($AX8="",$AX8="skip",$AX8="units?",$AX8="UNITS?",$AZ8="",$AQ8=""),"",IF($AX8="OVER",IF($AZ8&gt;$AQ8,"WON","LOST"),IF($AZ8&lt;$AQ8,"WON","LOST")))</f>
         <v/>
@@ -22822,7 +22941,11 @@
         <f>IF(COUNT($BB$2:$BB8)=0,"",SUM($BB$2:$BB8))</f>
         <v/>
       </c>
-      <c r="BD8" s="27" t="n"/>
+      <c r="BD8" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-03 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
@@ -22987,7 +23110,9 @@
         <f>IF(OR($AX9="",$AX9="skip",$AX9="units?",$AX9="UNITS?"),"",IF($AX9="OVER",$AT9*($AU9*$AR9-1),$AT9*((1-$AU9)*$AS9-1)))</f>
         <v/>
       </c>
-      <c r="AZ9" s="27" t="n"/>
+      <c r="AZ9" s="27" t="n">
+        <v>6</v>
+      </c>
       <c r="BA9" s="33">
         <f>IF(OR($AX9="",$AX9="skip",$AX9="units?",$AX9="UNITS?",$AZ9="",$AQ9=""),"",IF($AX9="OVER",IF($AZ9&gt;$AQ9,"WON","LOST"),IF($AZ9&lt;$AQ9,"WON","LOST")))</f>
         <v/>
@@ -23000,7 +23125,11 @@
         <f>IF(COUNT($BB$2:$BB9)=0,"",SUM($BB$2:$BB9))</f>
         <v/>
       </c>
-      <c r="BD9" s="27" t="n"/>
+      <c r="BD9" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-03 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
@@ -23165,7 +23294,9 @@
         <f>IF(OR($AX10="",$AX10="skip",$AX10="units?",$AX10="UNITS?"),"",IF($AX10="OVER",$AT10*($AU10*$AR10-1),$AT10*((1-$AU10)*$AS10-1)))</f>
         <v/>
       </c>
-      <c r="AZ10" s="27" t="n"/>
+      <c r="AZ10" s="27" t="n">
+        <v>7</v>
+      </c>
       <c r="BA10" s="33">
         <f>IF(OR($AX10="",$AX10="skip",$AX10="units?",$AX10="UNITS?",$AZ10="",$AQ10=""),"",IF($AX10="OVER",IF($AZ10&gt;$AQ10,"WON","LOST"),IF($AZ10&lt;$AQ10,"WON","LOST")))</f>
         <v/>
@@ -23178,7 +23309,11 @@
         <f>IF(COUNT($BB$2:$BB10)=0,"",SUM($BB$2:$BB10))</f>
         <v/>
       </c>
-      <c r="BD10" s="27" t="n"/>
+      <c r="BD10" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-03 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
@@ -23521,7 +23656,9 @@
         <f>IF(OR($AX12="",$AX12="skip",$AX12="units?",$AX12="UNITS?"),"",IF($AX12="OVER",$AT12*($AU12*$AR12-1),$AT12*((1-$AU12)*$AS12-1)))</f>
         <v/>
       </c>
-      <c r="AZ12" s="27" t="n"/>
+      <c r="AZ12" s="27" t="n">
+        <v>2</v>
+      </c>
       <c r="BA12" s="33">
         <f>IF(OR($AX12="",$AX12="skip",$AX12="units?",$AX12="UNITS?",$AZ12="",$AQ12=""),"",IF($AX12="OVER",IF($AZ12&gt;$AQ12,"WON","LOST"),IF($AZ12&lt;$AQ12,"WON","LOST")))</f>
         <v/>
@@ -23534,7 +23671,11 @@
         <f>IF(COUNT($BB$2:$BB12)=0,"",SUM($BB$2:$BB12))</f>
         <v/>
       </c>
-      <c r="BD12" s="27" t="n"/>
+      <c r="BD12" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-03 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">

--- a/forward_test_2026-09-18.xlsx
+++ b/forward_test_2026-09-18.xlsx
@@ -12470,7 +12470,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
@@ -12533,8 +12532,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="48" t="inlineStr">
         <is>
@@ -13184,7 +13181,9 @@
         <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?"),"",IF($AX2="OVER",$AT2*($AU2*$AR2-1),$AT2*((1-$AU2)*$AS2-1)))</f>
         <v/>
       </c>
-      <c r="AZ2" s="27" t="n"/>
+      <c r="AZ2" s="27" t="n">
+        <v>6</v>
+      </c>
       <c r="BA2" s="33">
         <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?",$AZ2="",$AQ2=""),"",IF($AX2="OVER",IF($AZ2&gt;$AQ2,"WON","LOST"),IF($AZ2&lt;$AQ2,"WON","LOST")))</f>
         <v/>
@@ -13197,7 +13196,11 @@
         <f>IF(COUNT($BB$2:$BB2)=0,"",SUM($BB$2:$BB2))</f>
         <v/>
       </c>
-      <c r="BD2" s="27" t="n"/>
+      <c r="BD2" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-09 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="26" t="inlineStr">
@@ -13360,7 +13363,9 @@
         <f>IF(OR($AX3="",$AX3="skip",$AX3="units?",$AX3="UNITS?"),"",IF($AX3="OVER",$AT3*($AU3*$AR3-1),$AT3*((1-$AU3)*$AS3-1)))</f>
         <v/>
       </c>
-      <c r="AZ3" s="27" t="n"/>
+      <c r="AZ3" s="27" t="n">
+        <v>5</v>
+      </c>
       <c r="BA3" s="33">
         <f>IF(OR($AX3="",$AX3="skip",$AX3="units?",$AX3="UNITS?",$AZ3="",$AQ3=""),"",IF($AX3="OVER",IF($AZ3&gt;$AQ3,"WON","LOST"),IF($AZ3&lt;$AQ3,"WON","LOST")))</f>
         <v/>
@@ -13373,7 +13378,11 @@
         <f>IF(COUNT($BB$2:$BB3)=0,"",SUM($BB$2:$BB3))</f>
         <v/>
       </c>
-      <c r="BD3" s="27" t="n"/>
+      <c r="BD3" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
@@ -13536,7 +13545,9 @@
         <f>IF(OR($AX4="",$AX4="skip",$AX4="units?",$AX4="UNITS?"),"",IF($AX4="OVER",$AT4*($AU4*$AR4-1),$AT4*((1-$AU4)*$AS4-1)))</f>
         <v/>
       </c>
-      <c r="AZ4" s="27" t="n"/>
+      <c r="AZ4" s="27" t="n">
+        <v>7</v>
+      </c>
       <c r="BA4" s="33">
         <f>IF(OR($AX4="",$AX4="skip",$AX4="units?",$AX4="UNITS?",$AZ4="",$AQ4=""),"",IF($AX4="OVER",IF($AZ4&gt;$AQ4,"WON","LOST"),IF($AZ4&lt;$AQ4,"WON","LOST")))</f>
         <v/>
@@ -13549,7 +13560,11 @@
         <f>IF(COUNT($BB$2:$BB4)=0,"",SUM($BB$2:$BB4))</f>
         <v/>
       </c>
-      <c r="BD4" s="27" t="n"/>
+      <c r="BD4" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
@@ -13712,7 +13727,9 @@
         <f>IF(OR($AX5="",$AX5="skip",$AX5="units?",$AX5="UNITS?"),"",IF($AX5="OVER",$AT5*($AU5*$AR5-1),$AT5*((1-$AU5)*$AS5-1)))</f>
         <v/>
       </c>
-      <c r="AZ5" s="27" t="n"/>
+      <c r="AZ5" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA5" s="33">
         <f>IF(OR($AX5="",$AX5="skip",$AX5="units?",$AX5="UNITS?",$AZ5="",$AQ5=""),"",IF($AX5="OVER",IF($AZ5&gt;$AQ5,"WON","LOST"),IF($AZ5&lt;$AQ5,"WON","LOST")))</f>
         <v/>
@@ -13725,7 +13742,11 @@
         <f>IF(COUNT($BB$2:$BB5)=0,"",SUM($BB$2:$BB5))</f>
         <v/>
       </c>
-      <c r="BD5" s="27" t="n"/>
+      <c r="BD5" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
@@ -13888,7 +13909,9 @@
         <f>IF(OR($AX6="",$AX6="skip",$AX6="units?",$AX6="UNITS?"),"",IF($AX6="OVER",$AT6*($AU6*$AR6-1),$AT6*((1-$AU6)*$AS6-1)))</f>
         <v/>
       </c>
-      <c r="AZ6" s="27" t="n"/>
+      <c r="AZ6" s="27" t="n">
+        <v>6</v>
+      </c>
       <c r="BA6" s="33">
         <f>IF(OR($AX6="",$AX6="skip",$AX6="units?",$AX6="UNITS?",$AZ6="",$AQ6=""),"",IF($AX6="OVER",IF($AZ6&gt;$AQ6,"WON","LOST"),IF($AZ6&lt;$AQ6,"WON","LOST")))</f>
         <v/>
@@ -13901,7 +13924,11 @@
         <f>IF(COUNT($BB$2:$BB6)=0,"",SUM($BB$2:$BB6))</f>
         <v/>
       </c>
-      <c r="BD6" s="27" t="n"/>
+      <c r="BD6" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
@@ -14064,7 +14091,9 @@
         <f>IF(OR($AX7="",$AX7="skip",$AX7="units?",$AX7="UNITS?"),"",IF($AX7="OVER",$AT7*($AU7*$AR7-1),$AT7*((1-$AU7)*$AS7-1)))</f>
         <v/>
       </c>
-      <c r="AZ7" s="27" t="n"/>
+      <c r="AZ7" s="27" t="n">
+        <v>7</v>
+      </c>
       <c r="BA7" s="33">
         <f>IF(OR($AX7="",$AX7="skip",$AX7="units?",$AX7="UNITS?",$AZ7="",$AQ7=""),"",IF($AX7="OVER",IF($AZ7&gt;$AQ7,"WON","LOST"),IF($AZ7&lt;$AQ7,"WON","LOST")))</f>
         <v/>
@@ -14077,7 +14106,11 @@
         <f>IF(COUNT($BB$2:$BB7)=0,"",SUM($BB$2:$BB7))</f>
         <v/>
       </c>
-      <c r="BD7" s="27" t="n"/>
+      <c r="BD7" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data); 1 straight red (no yellows added)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
@@ -14240,7 +14273,9 @@
         <f>IF(OR($AX8="",$AX8="skip",$AX8="units?",$AX8="UNITS?"),"",IF($AX8="OVER",$AT8*($AU8*$AR8-1),$AT8*((1-$AU8)*$AS8-1)))</f>
         <v/>
       </c>
-      <c r="AZ8" s="27" t="n"/>
+      <c r="AZ8" s="27" t="n">
+        <v>1</v>
+      </c>
       <c r="BA8" s="33">
         <f>IF(OR($AX8="",$AX8="skip",$AX8="units?",$AX8="UNITS?",$AZ8="",$AQ8=""),"",IF($AX8="OVER",IF($AZ8&gt;$AQ8,"WON","LOST"),IF($AZ8&lt;$AQ8,"WON","LOST")))</f>
         <v/>
@@ -14253,7 +14288,11 @@
         <f>IF(COUNT($BB$2:$BB8)=0,"",SUM($BB$2:$BB8))</f>
         <v/>
       </c>
-      <c r="BD8" s="27" t="n"/>
+      <c r="BD8" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data); 1 straight red (no yellows added)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
@@ -14416,7 +14455,9 @@
         <f>IF(OR($AX9="",$AX9="skip",$AX9="units?",$AX9="UNITS?"),"",IF($AX9="OVER",$AT9*($AU9*$AR9-1),$AT9*((1-$AU9)*$AS9-1)))</f>
         <v/>
       </c>
-      <c r="AZ9" s="27" t="n"/>
+      <c r="AZ9" s="27" t="n">
+        <v>1</v>
+      </c>
       <c r="BA9" s="33">
         <f>IF(OR($AX9="",$AX9="skip",$AX9="units?",$AX9="UNITS?",$AZ9="",$AQ9=""),"",IF($AX9="OVER",IF($AZ9&gt;$AQ9,"WON","LOST"),IF($AZ9&lt;$AQ9,"WON","LOST")))</f>
         <v/>
@@ -14429,7 +14470,11 @@
         <f>IF(COUNT($BB$2:$BB9)=0,"",SUM($BB$2:$BB9))</f>
         <v/>
       </c>
-      <c r="BD9" s="27" t="n"/>
+      <c r="BD9" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
@@ -14592,7 +14637,9 @@
         <f>IF(OR($AX10="",$AX10="skip",$AX10="units?",$AX10="UNITS?"),"",IF($AX10="OVER",$AT10*($AU10*$AR10-1),$AT10*((1-$AU10)*$AS10-1)))</f>
         <v/>
       </c>
-      <c r="AZ10" s="27" t="n"/>
+      <c r="AZ10" s="27" t="n">
+        <v>2</v>
+      </c>
       <c r="BA10" s="33">
         <f>IF(OR($AX10="",$AX10="skip",$AX10="units?",$AX10="UNITS?",$AZ10="",$AQ10=""),"",IF($AX10="OVER",IF($AZ10&gt;$AQ10,"WON","LOST"),IF($AZ10&lt;$AQ10,"WON","LOST")))</f>
         <v/>
@@ -14605,7 +14652,11 @@
         <f>IF(COUNT($BB$2:$BB10)=0,"",SUM($BB$2:$BB10))</f>
         <v/>
       </c>
-      <c r="BD10" s="27" t="n"/>
+      <c r="BD10" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data); 1 straight red (no yellows added)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
@@ -14768,7 +14819,9 @@
         <f>IF(OR($AX11="",$AX11="skip",$AX11="units?",$AX11="UNITS?"),"",IF($AX11="OVER",$AT11*($AU11*$AR11-1),$AT11*((1-$AU11)*$AS11-1)))</f>
         <v/>
       </c>
-      <c r="AZ11" s="27" t="n"/>
+      <c r="AZ11" s="27" t="n">
+        <v>3</v>
+      </c>
       <c r="BA11" s="33">
         <f>IF(OR($AX11="",$AX11="skip",$AX11="units?",$AX11="UNITS?",$AZ11="",$AQ11=""),"",IF($AX11="OVER",IF($AZ11&gt;$AQ11,"WON","LOST"),IF($AZ11&lt;$AQ11,"WON","LOST")))</f>
         <v/>
@@ -14781,7 +14834,11 @@
         <f>IF(COUNT($BB$2:$BB11)=0,"",SUM($BB$2:$BB11))</f>
         <v/>
       </c>
-      <c r="BD11" s="27" t="n"/>
+      <c r="BD11" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
@@ -14944,7 +15001,9 @@
         <f>IF(OR($AX12="",$AX12="skip",$AX12="units?",$AX12="UNITS?"),"",IF($AX12="OVER",$AT12*($AU12*$AR12-1),$AT12*((1-$AU12)*$AS12-1)))</f>
         <v/>
       </c>
-      <c r="AZ12" s="27" t="n"/>
+      <c r="AZ12" s="27" t="n">
+        <v>5</v>
+      </c>
       <c r="BA12" s="33">
         <f>IF(OR($AX12="",$AX12="skip",$AX12="units?",$AX12="UNITS?",$AZ12="",$AQ12=""),"",IF($AX12="OVER",IF($AZ12&gt;$AQ12,"WON","LOST"),IF($AZ12&lt;$AQ12,"WON","LOST")))</f>
         <v/>
@@ -14957,7 +15016,11 @@
         <f>IF(COUNT($BB$2:$BB12)=0,"",SUM($BB$2:$BB12))</f>
         <v/>
       </c>
-      <c r="BD12" s="27" t="n"/>
+      <c r="BD12" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
@@ -15120,7 +15183,9 @@
         <f>IF(OR($AX13="",$AX13="skip",$AX13="units?",$AX13="UNITS?"),"",IF($AX13="OVER",$AT13*($AU13*$AR13-1),$AT13*((1-$AU13)*$AS13-1)))</f>
         <v/>
       </c>
-      <c r="AZ13" s="27" t="n"/>
+      <c r="AZ13" s="27" t="n">
+        <v>6</v>
+      </c>
       <c r="BA13" s="33">
         <f>IF(OR($AX13="",$AX13="skip",$AX13="units?",$AX13="UNITS?",$AZ13="",$AQ13=""),"",IF($AX13="OVER",IF($AZ13&gt;$AQ13,"WON","LOST"),IF($AZ13&lt;$AQ13,"WON","LOST")))</f>
         <v/>
@@ -15133,7 +15198,11 @@
         <f>IF(COUNT($BB$2:$BB13)=0,"",SUM($BB$2:$BB13))</f>
         <v/>
       </c>
-      <c r="BD13" s="27" t="n"/>
+      <c r="BD13" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="26" t="inlineStr">
@@ -15296,7 +15365,9 @@
         <f>IF(OR($AX14="",$AX14="skip",$AX14="units?",$AX14="UNITS?"),"",IF($AX14="OVER",$AT14*($AU14*$AR14-1),$AT14*((1-$AU14)*$AS14-1)))</f>
         <v/>
       </c>
-      <c r="AZ14" s="27" t="n"/>
+      <c r="AZ14" s="27" t="n">
+        <v>3</v>
+      </c>
       <c r="BA14" s="33">
         <f>IF(OR($AX14="",$AX14="skip",$AX14="units?",$AX14="UNITS?",$AZ14="",$AQ14=""),"",IF($AX14="OVER",IF($AZ14&gt;$AQ14,"WON","LOST"),IF($AZ14&lt;$AQ14,"WON","LOST")))</f>
         <v/>
@@ -15309,7 +15380,11 @@
         <f>IF(COUNT($BB$2:$BB14)=0,"",SUM($BB$2:$BB14))</f>
         <v/>
       </c>
-      <c r="BD14" s="27" t="n"/>
+      <c r="BD14" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="26" t="inlineStr">
@@ -15472,7 +15547,9 @@
         <f>IF(OR($AX15="",$AX15="skip",$AX15="units?",$AX15="UNITS?"),"",IF($AX15="OVER",$AT15*($AU15*$AR15-1),$AT15*((1-$AU15)*$AS15-1)))</f>
         <v/>
       </c>
-      <c r="AZ15" s="27" t="n"/>
+      <c r="AZ15" s="27" t="n">
+        <v>7</v>
+      </c>
       <c r="BA15" s="33">
         <f>IF(OR($AX15="",$AX15="skip",$AX15="units?",$AX15="UNITS?",$AZ15="",$AQ15=""),"",IF($AX15="OVER",IF($AZ15&gt;$AQ15,"WON","LOST"),IF($AZ15&lt;$AQ15,"WON","LOST")))</f>
         <v/>
@@ -15485,7 +15562,11 @@
         <f>IF(COUNT($BB$2:$BB15)=0,"",SUM($BB$2:$BB15))</f>
         <v/>
       </c>
-      <c r="BD15" s="27" t="n"/>
+      <c r="BD15" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="26" t="inlineStr">
@@ -15648,7 +15729,9 @@
         <f>IF(OR($AX16="",$AX16="skip",$AX16="units?",$AX16="UNITS?"),"",IF($AX16="OVER",$AT16*($AU16*$AR16-1),$AT16*((1-$AU16)*$AS16-1)))</f>
         <v/>
       </c>
-      <c r="AZ16" s="27" t="n"/>
+      <c r="AZ16" s="27" t="n">
+        <v>2</v>
+      </c>
       <c r="BA16" s="33">
         <f>IF(OR($AX16="",$AX16="skip",$AX16="units?",$AX16="UNITS?",$AZ16="",$AQ16=""),"",IF($AX16="OVER",IF($AZ16&gt;$AQ16,"WON","LOST"),IF($AZ16&lt;$AQ16,"WON","LOST")))</f>
         <v/>
@@ -15661,7 +15744,11 @@
         <f>IF(COUNT($BB$2:$BB16)=0,"",SUM($BB$2:$BB16))</f>
         <v/>
       </c>
-      <c r="BD16" s="27" t="n"/>
+      <c r="BD16" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
@@ -15824,7 +15911,9 @@
         <f>IF(OR($AX17="",$AX17="skip",$AX17="units?",$AX17="UNITS?"),"",IF($AX17="OVER",$AT17*($AU17*$AR17-1),$AT17*((1-$AU17)*$AS17-1)))</f>
         <v/>
       </c>
-      <c r="AZ17" s="27" t="n"/>
+      <c r="AZ17" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="BA17" s="33">
         <f>IF(OR($AX17="",$AX17="skip",$AX17="units?",$AX17="UNITS?",$AZ17="",$AQ17=""),"",IF($AX17="OVER",IF($AZ17&gt;$AQ17,"WON","LOST"),IF($AZ17&lt;$AQ17,"WON","LOST")))</f>
         <v/>
@@ -15837,7 +15926,11 @@
         <f>IF(COUNT($BB$2:$BB17)=0,"",SUM($BB$2:$BB17))</f>
         <v/>
       </c>
-      <c r="BD17" s="27" t="n"/>
+      <c r="BD17" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="26" t="inlineStr">
@@ -16000,7 +16093,9 @@
         <f>IF(OR($AX18="",$AX18="skip",$AX18="units?",$AX18="UNITS?"),"",IF($AX18="OVER",$AT18*($AU18*$AR18-1),$AT18*((1-$AU18)*$AS18-1)))</f>
         <v/>
       </c>
-      <c r="AZ18" s="27" t="n"/>
+      <c r="AZ18" s="27" t="n">
+        <v>6</v>
+      </c>
       <c r="BA18" s="33">
         <f>IF(OR($AX18="",$AX18="skip",$AX18="units?",$AX18="UNITS?",$AZ18="",$AQ18=""),"",IF($AX18="OVER",IF($AZ18&gt;$AQ18,"WON","LOST"),IF($AZ18&lt;$AQ18,"WON","LOST")))</f>
         <v/>
@@ -16013,7 +16108,11 @@
         <f>IF(COUNT($BB$2:$BB18)=0,"",SUM($BB$2:$BB18))</f>
         <v/>
       </c>
-      <c r="BD18" s="27" t="n"/>
+      <c r="BD18" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="26" t="inlineStr">
@@ -16176,7 +16275,9 @@
         <f>IF(OR($AX19="",$AX19="skip",$AX19="units?",$AX19="UNITS?"),"",IF($AX19="OVER",$AT19*($AU19*$AR19-1),$AT19*((1-$AU19)*$AS19-1)))</f>
         <v/>
       </c>
-      <c r="AZ19" s="27" t="n"/>
+      <c r="AZ19" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA19" s="33">
         <f>IF(OR($AX19="",$AX19="skip",$AX19="units?",$AX19="UNITS?",$AZ19="",$AQ19=""),"",IF($AX19="OVER",IF($AZ19&gt;$AQ19,"WON","LOST"),IF($AZ19&lt;$AQ19,"WON","LOST")))</f>
         <v/>
@@ -16189,7 +16290,11 @@
         <f>IF(COUNT($BB$2:$BB19)=0,"",SUM($BB$2:$BB19))</f>
         <v/>
       </c>
-      <c r="BD19" s="27" t="n"/>
+      <c r="BD19" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="26" t="inlineStr">
@@ -16352,7 +16457,9 @@
         <f>IF(OR($AX20="",$AX20="skip",$AX20="units?",$AX20="UNITS?"),"",IF($AX20="OVER",$AT20*($AU20*$AR20-1),$AT20*((1-$AU20)*$AS20-1)))</f>
         <v/>
       </c>
-      <c r="AZ20" s="27" t="n"/>
+      <c r="AZ20" s="27" t="n">
+        <v>3</v>
+      </c>
       <c r="BA20" s="33">
         <f>IF(OR($AX20="",$AX20="skip",$AX20="units?",$AX20="UNITS?",$AZ20="",$AQ20=""),"",IF($AX20="OVER",IF($AZ20&gt;$AQ20,"WON","LOST"),IF($AZ20&lt;$AQ20,"WON","LOST")))</f>
         <v/>
@@ -16365,7 +16472,11 @@
         <f>IF(COUNT($BB$2:$BB20)=0,"",SUM($BB$2:$BB20))</f>
         <v/>
       </c>
-      <c r="BD20" s="27" t="n"/>
+      <c r="BD20" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data); 1 straight red (no yellows added)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="26" t="inlineStr">
@@ -16528,7 +16639,9 @@
         <f>IF(OR($AX21="",$AX21="skip",$AX21="units?",$AX21="UNITS?"),"",IF($AX21="OVER",$AT21*($AU21*$AR21-1),$AT21*((1-$AU21)*$AS21-1)))</f>
         <v/>
       </c>
-      <c r="AZ21" s="27" t="n"/>
+      <c r="AZ21" s="27" t="n">
+        <v>5</v>
+      </c>
       <c r="BA21" s="33">
         <f>IF(OR($AX21="",$AX21="skip",$AX21="units?",$AX21="UNITS?",$AZ21="",$AQ21=""),"",IF($AX21="OVER",IF($AZ21&gt;$AQ21,"WON","LOST"),IF($AZ21&lt;$AQ21,"WON","LOST")))</f>
         <v/>
@@ -16541,7 +16654,11 @@
         <f>IF(COUNT($BB$2:$BB21)=0,"",SUM($BB$2:$BB21))</f>
         <v/>
       </c>
-      <c r="BD21" s="27" t="n"/>
+      <c r="BD21" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="26" t="inlineStr">
@@ -16704,7 +16821,9 @@
         <f>IF(OR($AX22="",$AX22="skip",$AX22="units?",$AX22="UNITS?"),"",IF($AX22="OVER",$AT22*($AU22*$AR22-1),$AT22*((1-$AU22)*$AS22-1)))</f>
         <v/>
       </c>
-      <c r="AZ22" s="27" t="n"/>
+      <c r="AZ22" s="27" t="n">
+        <v>5</v>
+      </c>
       <c r="BA22" s="33">
         <f>IF(OR($AX22="",$AX22="skip",$AX22="units?",$AX22="UNITS?",$AZ22="",$AQ22=""),"",IF($AX22="OVER",IF($AZ22&gt;$AQ22,"WON","LOST"),IF($AZ22&lt;$AQ22,"WON","LOST")))</f>
         <v/>
@@ -16717,7 +16836,11 @@
         <f>IF(COUNT($BB$2:$BB22)=0,"",SUM($BB$2:$BB22))</f>
         <v/>
       </c>
-      <c r="BD22" s="27" t="n"/>
+      <c r="BD22" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="26" t="inlineStr">
@@ -16880,7 +17003,9 @@
         <f>IF(OR($AX23="",$AX23="skip",$AX23="units?",$AX23="UNITS?"),"",IF($AX23="OVER",$AT23*($AU23*$AR23-1),$AT23*((1-$AU23)*$AS23-1)))</f>
         <v/>
       </c>
-      <c r="AZ23" s="27" t="n"/>
+      <c r="AZ23" s="27" t="n">
+        <v>1</v>
+      </c>
       <c r="BA23" s="33">
         <f>IF(OR($AX23="",$AX23="skip",$AX23="units?",$AX23="UNITS?",$AZ23="",$AQ23=""),"",IF($AX23="OVER",IF($AZ23&gt;$AQ23,"WON","LOST"),IF($AZ23&lt;$AQ23,"WON","LOST")))</f>
         <v/>
@@ -16893,7 +17018,11 @@
         <f>IF(COUNT($BB$2:$BB23)=0,"",SUM($BB$2:$BB23))</f>
         <v/>
       </c>
-      <c r="BD23" s="27" t="n"/>
+      <c r="BD23" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="26" t="inlineStr">
@@ -17056,7 +17185,9 @@
         <f>IF(OR($AX24="",$AX24="skip",$AX24="units?",$AX24="UNITS?"),"",IF($AX24="OVER",$AT24*($AU24*$AR24-1),$AT24*((1-$AU24)*$AS24-1)))</f>
         <v/>
       </c>
-      <c r="AZ24" s="27" t="n"/>
+      <c r="AZ24" s="27" t="n">
+        <v>2</v>
+      </c>
       <c r="BA24" s="33">
         <f>IF(OR($AX24="",$AX24="skip",$AX24="units?",$AX24="UNITS?",$AZ24="",$AQ24=""),"",IF($AX24="OVER",IF($AZ24&gt;$AQ24,"WON","LOST"),IF($AZ24&lt;$AQ24,"WON","LOST")))</f>
         <v/>
@@ -17069,7 +17200,11 @@
         <f>IF(COUNT($BB$2:$BB24)=0,"",SUM($BB$2:$BB24))</f>
         <v/>
       </c>
-      <c r="BD24" s="27" t="n"/>
+      <c r="BD24" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="26" t="inlineStr">
@@ -17232,7 +17367,9 @@
         <f>IF(OR($AX25="",$AX25="skip",$AX25="units?",$AX25="UNITS?"),"",IF($AX25="OVER",$AT25*($AU25*$AR25-1),$AT25*((1-$AU25)*$AS25-1)))</f>
         <v/>
       </c>
-      <c r="AZ25" s="27" t="n"/>
+      <c r="AZ25" s="27" t="n">
+        <v>7</v>
+      </c>
       <c r="BA25" s="33">
         <f>IF(OR($AX25="",$AX25="skip",$AX25="units?",$AX25="UNITS?",$AZ25="",$AQ25=""),"",IF($AX25="OVER",IF($AZ25&gt;$AQ25,"WON","LOST"),IF($AZ25&lt;$AQ25,"WON","LOST")))</f>
         <v/>
@@ -17245,7 +17382,11 @@
         <f>IF(COUNT($BB$2:$BB25)=0,"",SUM($BB$2:$BB25))</f>
         <v/>
       </c>
-      <c r="BD25" s="27" t="n"/>
+      <c r="BD25" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="26" t="inlineStr">
@@ -17408,7 +17549,9 @@
         <f>IF(OR($AX26="",$AX26="skip",$AX26="units?",$AX26="UNITS?"),"",IF($AX26="OVER",$AT26*($AU26*$AR26-1),$AT26*((1-$AU26)*$AS26-1)))</f>
         <v/>
       </c>
-      <c r="AZ26" s="27" t="n"/>
+      <c r="AZ26" s="27" t="n">
+        <v>9</v>
+      </c>
       <c r="BA26" s="33">
         <f>IF(OR($AX26="",$AX26="skip",$AX26="units?",$AX26="UNITS?",$AZ26="",$AQ26=""),"",IF($AX26="OVER",IF($AZ26&gt;$AQ26,"WON","LOST"),IF($AZ26&lt;$AQ26,"WON","LOST")))</f>
         <v/>
@@ -17421,7 +17564,11 @@
         <f>IF(COUNT($BB$2:$BB26)=0,"",SUM($BB$2:$BB26))</f>
         <v/>
       </c>
-      <c r="BD26" s="27" t="n"/>
+      <c r="BD26" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="26" t="inlineStr">
@@ -17584,7 +17731,9 @@
         <f>IF(OR($AX27="",$AX27="skip",$AX27="units?",$AX27="UNITS?"),"",IF($AX27="OVER",$AT27*($AU27*$AR27-1),$AT27*((1-$AU27)*$AS27-1)))</f>
         <v/>
       </c>
-      <c r="AZ27" s="27" t="n"/>
+      <c r="AZ27" s="27" t="n">
+        <v>1</v>
+      </c>
       <c r="BA27" s="33">
         <f>IF(OR($AX27="",$AX27="skip",$AX27="units?",$AX27="UNITS?",$AZ27="",$AQ27=""),"",IF($AX27="OVER",IF($AZ27&gt;$AQ27,"WON","LOST"),IF($AZ27&lt;$AQ27,"WON","LOST")))</f>
         <v/>
@@ -17597,7 +17746,11 @@
         <f>IF(COUNT($BB$2:$BB27)=0,"",SUM($BB$2:$BB27))</f>
         <v/>
       </c>
-      <c r="BD27" s="27" t="n"/>
+      <c r="BD27" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="26" t="inlineStr">
@@ -17760,7 +17913,9 @@
         <f>IF(OR($AX28="",$AX28="skip",$AX28="units?",$AX28="UNITS?"),"",IF($AX28="OVER",$AT28*($AU28*$AR28-1),$AT28*((1-$AU28)*$AS28-1)))</f>
         <v/>
       </c>
-      <c r="AZ28" s="27" t="n"/>
+      <c r="AZ28" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA28" s="33">
         <f>IF(OR($AX28="",$AX28="skip",$AX28="units?",$AX28="UNITS?",$AZ28="",$AQ28=""),"",IF($AX28="OVER",IF($AZ28&gt;$AQ28,"WON","LOST"),IF($AZ28&lt;$AQ28,"WON","LOST")))</f>
         <v/>
@@ -17773,7 +17928,11 @@
         <f>IF(COUNT($BB$2:$BB28)=0,"",SUM($BB$2:$BB28))</f>
         <v/>
       </c>
-      <c r="BD28" s="27" t="n"/>
+      <c r="BD28" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="26" t="inlineStr">
@@ -17936,7 +18095,9 @@
         <f>IF(OR($AX29="",$AX29="skip",$AX29="units?",$AX29="UNITS?"),"",IF($AX29="OVER",$AT29*($AU29*$AR29-1),$AT29*((1-$AU29)*$AS29-1)))</f>
         <v/>
       </c>
-      <c r="AZ29" s="27" t="n"/>
+      <c r="AZ29" s="27" t="n">
+        <v>3</v>
+      </c>
       <c r="BA29" s="33">
         <f>IF(OR($AX29="",$AX29="skip",$AX29="units?",$AX29="UNITS?",$AZ29="",$AQ29=""),"",IF($AX29="OVER",IF($AZ29&gt;$AQ29,"WON","LOST"),IF($AZ29&lt;$AQ29,"WON","LOST")))</f>
         <v/>
@@ -17949,7 +18110,11 @@
         <f>IF(COUNT($BB$2:$BB29)=0,"",SUM($BB$2:$BB29))</f>
         <v/>
       </c>
-      <c r="BD29" s="27" t="n"/>
+      <c r="BD29" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="26" t="inlineStr">
@@ -18112,7 +18277,9 @@
         <f>IF(OR($AX30="",$AX30="skip",$AX30="units?",$AX30="UNITS?"),"",IF($AX30="OVER",$AT30*($AU30*$AR30-1),$AT30*((1-$AU30)*$AS30-1)))</f>
         <v/>
       </c>
-      <c r="AZ30" s="27" t="n"/>
+      <c r="AZ30" s="27" t="n">
+        <v>2</v>
+      </c>
       <c r="BA30" s="33">
         <f>IF(OR($AX30="",$AX30="skip",$AX30="units?",$AX30="UNITS?",$AZ30="",$AQ30=""),"",IF($AX30="OVER",IF($AZ30&gt;$AQ30,"WON","LOST"),IF($AZ30&lt;$AQ30,"WON","LOST")))</f>
         <v/>
@@ -18125,7 +18292,11 @@
         <f>IF(COUNT($BB$2:$BB30)=0,"",SUM($BB$2:$BB30))</f>
         <v/>
       </c>
-      <c r="BD30" s="27" t="n"/>
+      <c r="BD30" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="26" t="inlineStr">
@@ -18288,7 +18459,9 @@
         <f>IF(OR($AX31="",$AX31="skip",$AX31="units?",$AX31="UNITS?"),"",IF($AX31="OVER",$AT31*($AU31*$AR31-1),$AT31*((1-$AU31)*$AS31-1)))</f>
         <v/>
       </c>
-      <c r="AZ31" s="27" t="n"/>
+      <c r="AZ31" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA31" s="33">
         <f>IF(OR($AX31="",$AX31="skip",$AX31="units?",$AX31="UNITS?",$AZ31="",$AQ31=""),"",IF($AX31="OVER",IF($AZ31&gt;$AQ31,"WON","LOST"),IF($AZ31&lt;$AQ31,"WON","LOST")))</f>
         <v/>
@@ -18301,7 +18474,11 @@
         <f>IF(COUNT($BB$2:$BB31)=0,"",SUM($BB$2:$BB31))</f>
         <v/>
       </c>
-      <c r="BD31" s="27" t="n"/>
+      <c r="BD31" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data); 1 straight red (no yellows added)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="26" t="inlineStr">
@@ -18464,7 +18641,9 @@
         <f>IF(OR($AX32="",$AX32="skip",$AX32="units?",$AX32="UNITS?"),"",IF($AX32="OVER",$AT32*($AU32*$AR32-1),$AT32*((1-$AU32)*$AS32-1)))</f>
         <v/>
       </c>
-      <c r="AZ32" s="27" t="n"/>
+      <c r="AZ32" s="27" t="n">
+        <v>9</v>
+      </c>
       <c r="BA32" s="33">
         <f>IF(OR($AX32="",$AX32="skip",$AX32="units?",$AX32="UNITS?",$AZ32="",$AQ32=""),"",IF($AX32="OVER",IF($AZ32&gt;$AQ32,"WON","LOST"),IF($AZ32&lt;$AQ32,"WON","LOST")))</f>
         <v/>
@@ -18477,7 +18656,11 @@
         <f>IF(COUNT($BB$2:$BB32)=0,"",SUM($BB$2:$BB32))</f>
         <v/>
       </c>
-      <c r="BD32" s="27" t="n"/>
+      <c r="BD32" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data); 1 straight red (no yellows added)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="26" t="inlineStr">
@@ -18640,7 +18823,9 @@
         <f>IF(OR($AX33="",$AX33="skip",$AX33="units?",$AX33="UNITS?"),"",IF($AX33="OVER",$AT33*($AU33*$AR33-1),$AT33*((1-$AU33)*$AS33-1)))</f>
         <v/>
       </c>
-      <c r="AZ33" s="27" t="n"/>
+      <c r="AZ33" s="27" t="n">
+        <v>7</v>
+      </c>
       <c r="BA33" s="33">
         <f>IF(OR($AX33="",$AX33="skip",$AX33="units?",$AX33="UNITS?",$AZ33="",$AQ33=""),"",IF($AX33="OVER",IF($AZ33&gt;$AQ33,"WON","LOST"),IF($AZ33&lt;$AQ33,"WON","LOST")))</f>
         <v/>
@@ -18653,7 +18838,11 @@
         <f>IF(COUNT($BB$2:$BB33)=0,"",SUM($BB$2:$BB33))</f>
         <v/>
       </c>
-      <c r="BD33" s="27" t="n"/>
+      <c r="BD33" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="26" t="inlineStr">
@@ -18816,7 +19005,9 @@
         <f>IF(OR($AX34="",$AX34="skip",$AX34="units?",$AX34="UNITS?"),"",IF($AX34="OVER",$AT34*($AU34*$AR34-1),$AT34*((1-$AU34)*$AS34-1)))</f>
         <v/>
       </c>
-      <c r="AZ34" s="27" t="n"/>
+      <c r="AZ34" s="27" t="n">
+        <v>7</v>
+      </c>
       <c r="BA34" s="33">
         <f>IF(OR($AX34="",$AX34="skip",$AX34="units?",$AX34="UNITS?",$AZ34="",$AQ34=""),"",IF($AX34="OVER",IF($AZ34&gt;$AQ34,"WON","LOST"),IF($AZ34&lt;$AQ34,"WON","LOST")))</f>
         <v/>
@@ -18829,7 +19020,11 @@
         <f>IF(COUNT($BB$2:$BB34)=0,"",SUM($BB$2:$BB34))</f>
         <v/>
       </c>
-      <c r="BD34" s="27" t="n"/>
+      <c r="BD34" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="26" t="inlineStr">
@@ -18992,7 +19187,9 @@
         <f>IF(OR($AX35="",$AX35="skip",$AX35="units?",$AX35="UNITS?"),"",IF($AX35="OVER",$AT35*($AU35*$AR35-1),$AT35*((1-$AU35)*$AS35-1)))</f>
         <v/>
       </c>
-      <c r="AZ35" s="27" t="n"/>
+      <c r="AZ35" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA35" s="33">
         <f>IF(OR($AX35="",$AX35="skip",$AX35="units?",$AX35="UNITS?",$AZ35="",$AQ35=""),"",IF($AX35="OVER",IF($AZ35&gt;$AQ35,"WON","LOST"),IF($AZ35&lt;$AQ35,"WON","LOST")))</f>
         <v/>
@@ -19005,7 +19202,11 @@
         <f>IF(COUNT($BB$2:$BB35)=0,"",SUM($BB$2:$BB35))</f>
         <v/>
       </c>
-      <c r="BD35" s="27" t="n"/>
+      <c r="BD35" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="26" t="inlineStr">
@@ -19168,7 +19369,9 @@
         <f>IF(OR($AX36="",$AX36="skip",$AX36="units?",$AX36="UNITS?"),"",IF($AX36="OVER",$AT36*($AU36*$AR36-1),$AT36*((1-$AU36)*$AS36-1)))</f>
         <v/>
       </c>
-      <c r="AZ36" s="27" t="n"/>
+      <c r="AZ36" s="27" t="n">
+        <v>6</v>
+      </c>
       <c r="BA36" s="33">
         <f>IF(OR($AX36="",$AX36="skip",$AX36="units?",$AX36="UNITS?",$AZ36="",$AQ36=""),"",IF($AX36="OVER",IF($AZ36&gt;$AQ36,"WON","LOST"),IF($AZ36&lt;$AQ36,"WON","LOST")))</f>
         <v/>
@@ -19181,7 +19384,11 @@
         <f>IF(COUNT($BB$2:$BB36)=0,"",SUM($BB$2:$BB36))</f>
         <v/>
       </c>
-      <c r="BD36" s="27" t="n"/>
+      <c r="BD36" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="26" t="inlineStr">
@@ -19344,7 +19551,9 @@
         <f>IF(OR($AX37="",$AX37="skip",$AX37="units?",$AX37="UNITS?"),"",IF($AX37="OVER",$AT37*($AU37*$AR37-1),$AT37*((1-$AU37)*$AS37-1)))</f>
         <v/>
       </c>
-      <c r="AZ37" s="27" t="n"/>
+      <c r="AZ37" s="27" t="n">
+        <v>2</v>
+      </c>
       <c r="BA37" s="33">
         <f>IF(OR($AX37="",$AX37="skip",$AX37="units?",$AX37="UNITS?",$AZ37="",$AQ37=""),"",IF($AX37="OVER",IF($AZ37&gt;$AQ37,"WON","LOST"),IF($AZ37&lt;$AQ37,"WON","LOST")))</f>
         <v/>
@@ -19357,7 +19566,11 @@
         <f>IF(COUNT($BB$2:$BB37)=0,"",SUM($BB$2:$BB37))</f>
         <v/>
       </c>
-      <c r="BD37" s="27" t="n"/>
+      <c r="BD37" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="26" t="inlineStr">
@@ -19520,7 +19733,9 @@
         <f>IF(OR($AX38="",$AX38="skip",$AX38="units?",$AX38="UNITS?"),"",IF($AX38="OVER",$AT38*($AU38*$AR38-1),$AT38*((1-$AU38)*$AS38-1)))</f>
         <v/>
       </c>
-      <c r="AZ38" s="27" t="n"/>
+      <c r="AZ38" s="27" t="n">
+        <v>5</v>
+      </c>
       <c r="BA38" s="33">
         <f>IF(OR($AX38="",$AX38="skip",$AX38="units?",$AX38="UNITS?",$AZ38="",$AQ38=""),"",IF($AX38="OVER",IF($AZ38&gt;$AQ38,"WON","LOST"),IF($AZ38&lt;$AQ38,"WON","LOST")))</f>
         <v/>
@@ -19533,7 +19748,11 @@
         <f>IF(COUNT($BB$2:$BB38)=0,"",SUM($BB$2:$BB38))</f>
         <v/>
       </c>
-      <c r="BD38" s="27" t="n"/>
+      <c r="BD38" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="26" t="inlineStr">
@@ -19696,7 +19915,9 @@
         <f>IF(OR($AX39="",$AX39="skip",$AX39="units?",$AX39="UNITS?"),"",IF($AX39="OVER",$AT39*($AU39*$AR39-1),$AT39*((1-$AU39)*$AS39-1)))</f>
         <v/>
       </c>
-      <c r="AZ39" s="27" t="n"/>
+      <c r="AZ39" s="27" t="n">
+        <v>6</v>
+      </c>
       <c r="BA39" s="33">
         <f>IF(OR($AX39="",$AX39="skip",$AX39="units?",$AX39="UNITS?",$AZ39="",$AQ39=""),"",IF($AX39="OVER",IF($AZ39&gt;$AQ39,"WON","LOST"),IF($AZ39&lt;$AQ39,"WON","LOST")))</f>
         <v/>
@@ -19709,7 +19930,11 @@
         <f>IF(COUNT($BB$2:$BB39)=0,"",SUM($BB$2:$BB39))</f>
         <v/>
       </c>
-      <c r="BD39" s="27" t="n"/>
+      <c r="BD39" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="26" t="inlineStr">
@@ -19872,7 +20097,9 @@
         <f>IF(OR($AX40="",$AX40="skip",$AX40="units?",$AX40="UNITS?"),"",IF($AX40="OVER",$AT40*($AU40*$AR40-1),$AT40*((1-$AU40)*$AS40-1)))</f>
         <v/>
       </c>
-      <c r="AZ40" s="27" t="n"/>
+      <c r="AZ40" s="27" t="n">
+        <v>3</v>
+      </c>
       <c r="BA40" s="33">
         <f>IF(OR($AX40="",$AX40="skip",$AX40="units?",$AX40="UNITS?",$AZ40="",$AQ40=""),"",IF($AX40="OVER",IF($AZ40&gt;$AQ40,"WON","LOST"),IF($AZ40&lt;$AQ40,"WON","LOST")))</f>
         <v/>
@@ -19885,7 +20112,11 @@
         <f>IF(COUNT($BB$2:$BB40)=0,"",SUM($BB$2:$BB40))</f>
         <v/>
       </c>
-      <c r="BD40" s="27" t="n"/>
+      <c r="BD40" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="26" t="inlineStr">
@@ -20048,7 +20279,9 @@
         <f>IF(OR($AX41="",$AX41="skip",$AX41="units?",$AX41="UNITS?"),"",IF($AX41="OVER",$AT41*($AU41*$AR41-1),$AT41*((1-$AU41)*$AS41-1)))</f>
         <v/>
       </c>
-      <c r="AZ41" s="27" t="n"/>
+      <c r="AZ41" s="27" t="n">
+        <v>1</v>
+      </c>
       <c r="BA41" s="33">
         <f>IF(OR($AX41="",$AX41="skip",$AX41="units?",$AX41="UNITS?",$AZ41="",$AQ41=""),"",IF($AX41="OVER",IF($AZ41&gt;$AQ41,"WON","LOST"),IF($AZ41&lt;$AQ41,"WON","LOST")))</f>
         <v/>
@@ -20061,7 +20294,11 @@
         <f>IF(COUNT($BB$2:$BB41)=0,"",SUM($BB$2:$BB41))</f>
         <v/>
       </c>
-      <c r="BD41" s="27" t="n"/>
+      <c r="BD41" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="26" t="inlineStr">
@@ -20224,7 +20461,9 @@
         <f>IF(OR($AX42="",$AX42="skip",$AX42="units?",$AX42="UNITS?"),"",IF($AX42="OVER",$AT42*($AU42*$AR42-1),$AT42*((1-$AU42)*$AS42-1)))</f>
         <v/>
       </c>
-      <c r="AZ42" s="27" t="n"/>
+      <c r="AZ42" s="27" t="n">
+        <v>3</v>
+      </c>
       <c r="BA42" s="33">
         <f>IF(OR($AX42="",$AX42="skip",$AX42="units?",$AX42="UNITS?",$AZ42="",$AQ42=""),"",IF($AX42="OVER",IF($AZ42&gt;$AQ42,"WON","LOST"),IF($AZ42&lt;$AQ42,"WON","LOST")))</f>
         <v/>
@@ -20237,7 +20476,11 @@
         <f>IF(COUNT($BB$2:$BB42)=0,"",SUM($BB$2:$BB42))</f>
         <v/>
       </c>
-      <c r="BD42" s="27" t="n"/>
+      <c r="BD42" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="26" t="inlineStr">
@@ -20400,7 +20643,9 @@
         <f>IF(OR($AX43="",$AX43="skip",$AX43="units?",$AX43="UNITS?"),"",IF($AX43="OVER",$AT43*($AU43*$AR43-1),$AT43*((1-$AU43)*$AS43-1)))</f>
         <v/>
       </c>
-      <c r="AZ43" s="27" t="n"/>
+      <c r="AZ43" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA43" s="33">
         <f>IF(OR($AX43="",$AX43="skip",$AX43="units?",$AX43="UNITS?",$AZ43="",$AQ43=""),"",IF($AX43="OVER",IF($AZ43&gt;$AQ43,"WON","LOST"),IF($AZ43&lt;$AQ43,"WON","LOST")))</f>
         <v/>
@@ -20413,7 +20658,11 @@
         <f>IF(COUNT($BB$2:$BB43)=0,"",SUM($BB$2:$BB43))</f>
         <v/>
       </c>
-      <c r="BD43" s="27" t="n"/>
+      <c r="BD43" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-11 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="26" t="inlineStr">
@@ -20576,7 +20825,9 @@
         <f>IF(OR($AX44="",$AX44="skip",$AX44="units?",$AX44="UNITS?"),"",IF($AX44="OVER",$AT44*($AU44*$AR44-1),$AT44*((1-$AU44)*$AS44-1)))</f>
         <v/>
       </c>
-      <c r="AZ44" s="27" t="n"/>
+      <c r="AZ44" s="27" t="n">
+        <v>2</v>
+      </c>
       <c r="BA44" s="33">
         <f>IF(OR($AX44="",$AX44="skip",$AX44="units?",$AX44="UNITS?",$AZ44="",$AQ44=""),"",IF($AX44="OVER",IF($AZ44&gt;$AQ44,"WON","LOST"),IF($AZ44&lt;$AQ44,"WON","LOST")))</f>
         <v/>
@@ -20589,7 +20840,11 @@
         <f>IF(COUNT($BB$2:$BB44)=0,"",SUM($BB$2:$BB44))</f>
         <v/>
       </c>
-      <c r="BD44" s="27" t="n"/>
+      <c r="BD44" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-11 (provisional, ~97% exact vs football-data)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="26" t="inlineStr">
@@ -20752,7 +21007,9 @@
         <f>IF(OR($AX45="",$AX45="skip",$AX45="units?",$AX45="UNITS?"),"",IF($AX45="OVER",$AT45*($AU45*$AR45-1),$AT45*((1-$AU45)*$AS45-1)))</f>
         <v/>
       </c>
-      <c r="AZ45" s="27" t="n"/>
+      <c r="AZ45" s="27" t="n">
+        <v>4</v>
+      </c>
       <c r="BA45" s="33">
         <f>IF(OR($AX45="",$AX45="skip",$AX45="units?",$AX45="UNITS?",$AZ45="",$AQ45=""),"",IF($AX45="OVER",IF($AZ45&gt;$AQ45,"WON","LOST"),IF($AZ45&lt;$AQ45,"WON","LOST")))</f>
         <v/>
@@ -20765,7 +21022,11 @@
         <f>IF(COUNT($BB$2:$BB45)=0,"",SUM($BB$2:$BB45))</f>
         <v/>
       </c>
-      <c r="BD45" s="27" t="n"/>
+      <c r="BD45" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-11 (provisional, ~97% exact vs football-data); 1 second-caution dismissal(s) -- not adjusted</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="26" t="inlineStr">
@@ -20928,7 +21189,9 @@
         <f>IF(OR($AX46="",$AX46="skip",$AX46="units?",$AX46="UNITS?"),"",IF($AX46="OVER",$AT46*($AU46*$AR46-1),$AT46*((1-$AU46)*$AS46-1)))</f>
         <v/>
       </c>
-      <c r="AZ46" s="27" t="n"/>
+      <c r="AZ46" s="27" t="n">
+        <v>6</v>
+      </c>
       <c r="BA46" s="33">
         <f>IF(OR($AX46="",$AX46="skip",$AX46="units?",$AX46="UNITS?",$AZ46="",$AQ46=""),"",IF($AX46="OVER",IF($AZ46&gt;$AQ46,"WON","LOST"),IF($AZ46&lt;$AQ46,"WON","LOST")))</f>
         <v/>
@@ -20941,7 +21204,11 @@
         <f>IF(COUNT($BB$2:$BB46)=0,"",SUM($BB$2:$BB46))</f>
         <v/>
       </c>
-      <c r="BD46" s="27" t="n"/>
+      <c r="BD46" s="27" t="inlineStr">
+        <is>
+          <t>actual from BBC 2026-10-11 (provisional, ~97% exact vs football-data); 1 second-caution dismissal(s) -- not adjusted</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="26" t="inlineStr">
@@ -21119,6 +21386,7 @@
       </c>
       <c r="BD47" s="27" t="n"/>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="35" t="inlineStr">
         <is>
@@ -21181,6 +21449,8 @@
         <v/>
       </c>
     </row>
+    <row r="55"/>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="48" t="inlineStr">
         <is>

--- a/forward_test_2026-09-18.xlsx
+++ b/forward_test_2026-09-18.xlsx
@@ -115,7 +115,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -157,6 +157,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -184,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -283,6 +288,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9585,7 +9592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD50"/>
+  <dimension ref="A1:BE50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9644,6 +9651,7 @@
     <col width="9" customWidth="1" min="54" max="54"/>
     <col width="12" customWidth="1" min="55" max="55"/>
     <col width="34" customWidth="1" min="56" max="56"/>
+    <col width="17" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -9925,6 +9933,11 @@
       <c r="BD1" s="25" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="BE1" s="50" t="inlineStr">
+        <is>
+          <t>Referee (actual)</t>
         </is>
       </c>
     </row>
@@ -10109,6 +10122,11 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE2" s="51" t="inlineStr">
+        <is>
+          <t>b toner</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="26" t="inlineStr">
@@ -10291,6 +10309,11 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE3" s="51" t="inlineStr">
+        <is>
+          <t>s mather</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
@@ -10473,6 +10496,11 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE4" s="51" t="inlineStr">
+        <is>
+          <t>r martin</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
@@ -10655,6 +10683,11 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE5" s="51" t="inlineStr">
+        <is>
+          <t>t reeves</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
@@ -10837,6 +10870,11 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE6" s="51" t="inlineStr">
+        <is>
+          <t>m coy</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
@@ -11019,6 +11057,11 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE7" s="51" t="inlineStr">
+        <is>
+          <t>d whitestone</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
@@ -11195,6 +11238,11 @@
         <v/>
       </c>
       <c r="BD8" s="27" t="n"/>
+      <c r="BE8" s="51" t="inlineStr">
+        <is>
+          <t>a chilowicz</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
@@ -11377,6 +11425,11 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE9" s="51" t="inlineStr">
+        <is>
+          <t>d drysdale</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
@@ -11559,6 +11612,11 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE10" s="51" t="inlineStr">
+        <is>
+          <t>i searle</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
@@ -11741,6 +11799,11 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE11" s="51" t="inlineStr">
+        <is>
+          <t>d rock</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
@@ -11923,6 +11986,11 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE12" s="51" t="inlineStr">
+        <is>
+          <t>j robinson</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
@@ -12105,6 +12173,11 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE13" s="51" t="inlineStr">
+        <is>
+          <t>h blair</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="26" t="inlineStr">
@@ -12287,6 +12360,11 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE14" s="51" t="inlineStr">
+        <is>
+          <t>s parkinson</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="26" t="inlineStr">
@@ -12469,7 +12547,13 @@
           <t>actual from BBC 2026-09-26 (provisional, ~97% exact vs football-data); 1 second-caution dismissal(s) -- not adjusted</t>
         </is>
       </c>
-    </row>
+      <c r="BE15" s="51" t="inlineStr">
+        <is>
+          <t>s oldham</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
@@ -12532,6 +12616,8 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="48" t="inlineStr">
         <is>
@@ -12677,7 +12763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD80"/>
+  <dimension ref="A1:BE80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12736,6 +12822,7 @@
     <col width="9" customWidth="1" min="54" max="54"/>
     <col width="12" customWidth="1" min="55" max="55"/>
     <col width="34" customWidth="1" min="56" max="56"/>
+    <col width="17" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -13017,6 +13104,11 @@
       <c r="BD1" s="25" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="BE1" s="50" t="inlineStr">
+        <is>
+          <t>Referee (actual)</t>
         </is>
       </c>
     </row>
@@ -13201,6 +13293,11 @@
           <t>actual from BBC 2026-10-09 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE2" s="51" t="inlineStr">
+        <is>
+          <t>r ricardo</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="26" t="inlineStr">
@@ -14475,6 +14572,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE9" s="51" t="inlineStr">
+        <is>
+          <t>a backhouse</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
@@ -14657,6 +14759,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data); 1 straight red (no yellows added)</t>
         </is>
       </c>
+      <c r="BE10" s="51" t="inlineStr">
+        <is>
+          <t>t kird</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
@@ -14839,6 +14946,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE11" s="51" t="inlineStr">
+        <is>
+          <t>t reeves</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
@@ -15021,6 +15133,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE12" s="51" t="inlineStr">
+        <is>
+          <t>m donohue</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
@@ -15203,6 +15320,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE13" s="51" t="inlineStr">
+        <is>
+          <t>f hallam</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="26" t="inlineStr">
@@ -15385,6 +15507,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE14" s="51" t="inlineStr">
+        <is>
+          <t>b speedie</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="26" t="inlineStr">
@@ -15567,6 +15694,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE15" s="51" t="inlineStr">
+        <is>
+          <t>j smith</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="26" t="inlineStr">
@@ -15749,6 +15881,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE16" s="51" t="inlineStr">
+        <is>
+          <t>a kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
@@ -15931,6 +16068,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE17" s="51" t="inlineStr">
+        <is>
+          <t>a madley</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="26" t="inlineStr">
@@ -16113,6 +16255,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE18" s="51" t="inlineStr">
+        <is>
+          <t>g ward</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="26" t="inlineStr">
@@ -16295,6 +16442,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE19" s="51" t="inlineStr">
+        <is>
+          <t>d whitestone</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="26" t="inlineStr">
@@ -16477,6 +16629,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data); 1 straight red (no yellows added)</t>
         </is>
       </c>
+      <c r="BE20" s="51" t="inlineStr">
+        <is>
+          <t>l sandoe</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="26" t="inlineStr">
@@ -16659,6 +16816,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE21" s="51" t="inlineStr">
+        <is>
+          <t>h blair</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="26" t="inlineStr">
@@ -16841,6 +17003,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE22" s="51" t="inlineStr">
+        <is>
+          <t>e duckworth</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="26" t="inlineStr">
@@ -17023,6 +17190,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE23" s="51" t="inlineStr">
+        <is>
+          <t>s hooper</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="26" t="inlineStr">
@@ -17205,6 +17377,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE24" s="51" t="inlineStr">
+        <is>
+          <t>m corlett</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="26" t="inlineStr">
@@ -17387,6 +17564,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE25" s="51" t="inlineStr">
+        <is>
+          <t>s mather</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="26" t="inlineStr">
@@ -17569,6 +17751,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE26" s="51" t="inlineStr">
+        <is>
+          <t>c brook</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="26" t="inlineStr">
@@ -17751,6 +17938,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE27" s="51" t="inlineStr">
+        <is>
+          <t>s parkinson</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="26" t="inlineStr">
@@ -17933,6 +18125,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE28" s="51" t="inlineStr">
+        <is>
+          <t>a byrne</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="26" t="inlineStr">
@@ -18115,6 +18312,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE29" s="51" t="inlineStr">
+        <is>
+          <t>m coy</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="26" t="inlineStr">
@@ -18297,6 +18499,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE30" s="51" t="inlineStr">
+        <is>
+          <t>s oldham</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="26" t="inlineStr">
@@ -18479,6 +18686,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data); 1 straight red (no yellows added)</t>
         </is>
       </c>
+      <c r="BE31" s="51" t="inlineStr">
+        <is>
+          <t>t robinson</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="26" t="inlineStr">
@@ -18661,6 +18873,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data); 1 straight red (no yellows added)</t>
         </is>
       </c>
+      <c r="BE32" s="51" t="inlineStr">
+        <is>
+          <t>d rock</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="26" t="inlineStr">
@@ -18843,6 +19060,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE33" s="51" t="inlineStr">
+        <is>
+          <t>b atkinson</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="26" t="inlineStr">
@@ -19025,6 +19247,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE34" s="51" t="inlineStr">
+        <is>
+          <t>j robinson</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="26" t="inlineStr">
@@ -19207,6 +19434,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE35" s="51" t="inlineStr">
+        <is>
+          <t>o mackey</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="26" t="inlineStr">
@@ -19389,6 +19621,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE36" s="51" t="inlineStr">
+        <is>
+          <t>b toner</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="26" t="inlineStr">
@@ -19571,6 +19808,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE37" s="51" t="inlineStr">
+        <is>
+          <t>r martin</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="26" t="inlineStr">
@@ -19753,6 +19995,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE38" s="51" t="inlineStr">
+        <is>
+          <t>w davis</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="26" t="inlineStr">
@@ -19935,6 +20182,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE39" s="51" t="inlineStr">
+        <is>
+          <t>d brown</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="26" t="inlineStr">
@@ -20117,6 +20369,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE40" s="51" t="inlineStr">
+        <is>
+          <t>j o'connor</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="26" t="inlineStr">
@@ -20299,6 +20556,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE41" s="51" t="inlineStr">
+        <is>
+          <t>s gill</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="26" t="inlineStr">
@@ -20481,6 +20743,11 @@
           <t>actual from BBC 2026-10-10 (provisional, ~97% exact vs football-data)</t>
         </is>
       </c>
+      <c r="BE42" s="51" t="inlineStr">
+        <is>
+          <t>m barlow</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="26" t="inlineStr">
@@ -21209,6 +21476,11 @@
           <t>actual from BBC 2026-10-11 (provisional, ~97% exact vs football-data); 1 second-caution dismissal(s) -- not adjusted</t>
         </is>
       </c>
+      <c r="BE46" s="51" t="inlineStr">
+        <is>
+          <t>a herczeg</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="26" t="inlineStr">
@@ -21386,7 +21658,6 @@
       </c>
       <c r="BD47" s="27" t="n"/>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="35" t="inlineStr">
         <is>
@@ -21449,8 +21720,6 @@
         <v/>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="48" t="inlineStr">
         <is>

--- a/forward_test_2026-09-18.xlsx
+++ b/forward_test_2026-09-18.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Week 26 Sep" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Week 9-12 Oct" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Week 3 Oct" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Week 22-28 Oct" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -189,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -290,6 +291,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12553,7 +12560,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
@@ -12616,8 +12622,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="48" t="inlineStr">
         <is>
@@ -24405,4 +24409,722 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BD35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="7" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
+    <col width="9" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="11" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="8" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="9" customWidth="1" min="51" max="51"/>
+    <col width="14" customWidth="1" min="52" max="52"/>
+    <col width="8" customWidth="1" min="53" max="53"/>
+    <col width="9" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="34" customWidth="1" min="56" max="56"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>Div</t>
+        </is>
+      </c>
+      <c r="C1" s="24" t="inlineStr">
+        <is>
+          <t>League</t>
+        </is>
+      </c>
+      <c r="D1" s="24" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="E1" s="24" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F1" s="25" t="inlineStr">
+        <is>
+          <t>Referee</t>
+        </is>
+      </c>
+      <c r="G1" s="24" t="inlineStr">
+        <is>
+          <t>Ref matches</t>
+        </is>
+      </c>
+      <c r="H1" s="24" t="inlineStr">
+        <is>
+          <t>Ref vs avg</t>
+        </is>
+      </c>
+      <c r="I1" s="24" t="inlineStr">
+        <is>
+          <t>League avg</t>
+        </is>
+      </c>
+      <c r="J1" s="24" t="inlineStr">
+        <is>
+          <t>Model expects</t>
+        </is>
+      </c>
+      <c r="K1" s="24" t="inlineStr">
+        <is>
+          <t>vs league avg</t>
+        </is>
+      </c>
+      <c r="L1" s="24" t="inlineStr">
+        <is>
+          <t>Most likely</t>
+        </is>
+      </c>
+      <c r="M1" s="24" t="inlineStr">
+        <is>
+          <t>80% range</t>
+        </is>
+      </c>
+      <c r="N1" s="24" t="inlineStr">
+        <is>
+          <t>P(0)</t>
+        </is>
+      </c>
+      <c r="O1" s="24" t="inlineStr">
+        <is>
+          <t>P(1)</t>
+        </is>
+      </c>
+      <c r="P1" s="24" t="inlineStr">
+        <is>
+          <t>P(2)</t>
+        </is>
+      </c>
+      <c r="Q1" s="24" t="inlineStr">
+        <is>
+          <t>P(3)</t>
+        </is>
+      </c>
+      <c r="R1" s="24" t="inlineStr">
+        <is>
+          <t>P(4)</t>
+        </is>
+      </c>
+      <c r="S1" s="24" t="inlineStr">
+        <is>
+          <t>P(5)</t>
+        </is>
+      </c>
+      <c r="T1" s="24" t="inlineStr">
+        <is>
+          <t>P(6)</t>
+        </is>
+      </c>
+      <c r="U1" s="24" t="inlineStr">
+        <is>
+          <t>P(7)</t>
+        </is>
+      </c>
+      <c r="V1" s="24" t="inlineStr">
+        <is>
+          <t>P(8)</t>
+        </is>
+      </c>
+      <c r="W1" s="24" t="inlineStr">
+        <is>
+          <t>P(o1.5)</t>
+        </is>
+      </c>
+      <c r="X1" s="24" t="inlineStr">
+        <is>
+          <t>P(o2.5)</t>
+        </is>
+      </c>
+      <c r="Y1" s="24" t="inlineStr">
+        <is>
+          <t>P(o3.5)</t>
+        </is>
+      </c>
+      <c r="Z1" s="24" t="inlineStr">
+        <is>
+          <t>P(o4.5)</t>
+        </is>
+      </c>
+      <c r="AA1" s="24" t="inlineStr">
+        <is>
+          <t>P(o5.5)</t>
+        </is>
+      </c>
+      <c r="AB1" s="24" t="inlineStr">
+        <is>
+          <t>P(o6.5)</t>
+        </is>
+      </c>
+      <c r="AC1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 1.5</t>
+        </is>
+      </c>
+      <c r="AD1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 2.5</t>
+        </is>
+      </c>
+      <c r="AE1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 3.5</t>
+        </is>
+      </c>
+      <c r="AF1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 4.5</t>
+        </is>
+      </c>
+      <c r="AG1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 5.5</t>
+        </is>
+      </c>
+      <c r="AH1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR over 6.5</t>
+        </is>
+      </c>
+      <c r="AI1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 1.5</t>
+        </is>
+      </c>
+      <c r="AJ1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 2.5</t>
+        </is>
+      </c>
+      <c r="AK1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 3.5</t>
+        </is>
+      </c>
+      <c r="AL1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 4.5</t>
+        </is>
+      </c>
+      <c r="AM1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 5.5</t>
+        </is>
+      </c>
+      <c r="AN1" s="24" t="inlineStr">
+        <is>
+          <t>FAIR under 6.5</t>
+        </is>
+      </c>
+      <c r="AO1" s="25" t="inlineStr">
+        <is>
+          <t>Bookmaker</t>
+        </is>
+      </c>
+      <c r="AP1" s="25" t="inlineStr">
+        <is>
+          <t>Settles on</t>
+        </is>
+      </c>
+      <c r="AQ1" s="25" t="inlineStr">
+        <is>
+          <t>Card line</t>
+        </is>
+      </c>
+      <c r="AR1" s="25" t="inlineStr">
+        <is>
+          <t>Over price</t>
+        </is>
+      </c>
+      <c r="AS1" s="25" t="inlineStr">
+        <is>
+          <t>Under price</t>
+        </is>
+      </c>
+      <c r="AT1" s="25" t="inlineStr">
+        <is>
+          <t>Stake EUR</t>
+        </is>
+      </c>
+      <c r="AU1" s="24" t="inlineStr">
+        <is>
+          <t>Model P(over)</t>
+        </is>
+      </c>
+      <c r="AV1" s="24" t="inlineStr">
+        <is>
+          <t>Implied P(over)</t>
+        </is>
+      </c>
+      <c r="AW1" s="24" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="AX1" s="24" t="inlineStr">
+        <is>
+          <t>BET?</t>
+        </is>
+      </c>
+      <c r="AY1" s="24" t="inlineStr">
+        <is>
+          <t>EV EUR</t>
+        </is>
+      </c>
+      <c r="AZ1" s="25" t="inlineStr">
+        <is>
+          <t>ACTUAL yellows</t>
+        </is>
+      </c>
+      <c r="BA1" s="24" t="inlineStr">
+        <is>
+          <t>Won?</t>
+        </is>
+      </c>
+      <c r="BB1" s="24" t="inlineStr">
+        <is>
+          <t>P/L EUR</t>
+        </is>
+      </c>
+      <c r="BC1" s="24" t="inlineStr">
+        <is>
+          <t>Running P/L</t>
+        </is>
+      </c>
+      <c r="BD1" s="25" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D2" s="26" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="inlineStr">
+        <is>
+          <t>Salford</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="inlineStr">
+        <is>
+          <t>m coy</t>
+        </is>
+      </c>
+      <c r="G2" s="26" t="n">
+        <v>213</v>
+      </c>
+      <c r="H2" s="28" t="n">
+        <v>-0.4490018148820326</v>
+      </c>
+      <c r="I2" s="29" t="n">
+        <v>3.992753623188406</v>
+      </c>
+      <c r="J2" s="29" t="n">
+        <v>3.295274393631539</v>
+      </c>
+      <c r="K2" s="30" t="n">
+        <v>-0.174686268019687</v>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" s="26" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="N2" s="31" t="n">
+        <v>0.04127989534019522</v>
+      </c>
+      <c r="O2" s="31" t="n">
+        <v>0.1273131546529031</v>
+      </c>
+      <c r="P2" s="31" t="n">
+        <v>0.2004045838105295</v>
+      </c>
+      <c r="Q2" s="31" t="n">
+        <v>0.2145855754175058</v>
+      </c>
+      <c r="R2" s="31" t="n">
+        <v>0.1757646842689452</v>
+      </c>
+      <c r="S2" s="31" t="n">
+        <v>0.1174258038543715</v>
+      </c>
+      <c r="T2" s="31" t="n">
+        <v>0.0666293017985575</v>
+      </c>
+      <c r="U2" s="31" t="n">
+        <v>0.03301546323174859</v>
+      </c>
+      <c r="V2" s="31" t="n">
+        <v>0.01457896098207048</v>
+      </c>
+      <c r="W2" s="28" t="n">
+        <v>0.8314069500069017</v>
+      </c>
+      <c r="X2" s="28" t="n">
+        <v>0.6310023661963722</v>
+      </c>
+      <c r="Y2" s="28" t="n">
+        <v>0.4164167907788664</v>
+      </c>
+      <c r="Z2" s="28" t="n">
+        <v>0.2406521065099212</v>
+      </c>
+      <c r="AA2" s="28" t="n">
+        <v>0.1232263026555497</v>
+      </c>
+      <c r="AB2" s="28" t="n">
+        <v>0.05659700085699215</v>
+      </c>
+      <c r="AC2" s="29" t="n">
+        <v>1.202780419374289</v>
+      </c>
+      <c r="AD2" s="29" t="n">
+        <v>1.584780111091997</v>
+      </c>
+      <c r="AE2" s="29" t="n">
+        <v>2.401440148774018</v>
+      </c>
+      <c r="AF2" s="29" t="n">
+        <v>4.15537605094171</v>
+      </c>
+      <c r="AG2" s="29" t="n">
+        <v>8.115150568099622</v>
+      </c>
+      <c r="AH2" s="29" t="n">
+        <v>17.66878076325589</v>
+      </c>
+      <c r="AI2" s="29" t="n">
+        <v>5.931442607159292</v>
+      </c>
+      <c r="AJ2" s="29" t="n">
+        <v>2.710044478312772</v>
+      </c>
+      <c r="AK2" s="29" t="n">
+        <v>1.713551699567621</v>
+      </c>
+      <c r="AL2" s="29" t="n">
+        <v>1.316919436496818</v>
+      </c>
+      <c r="AM2" s="29" t="n">
+        <v>1.140545163511148</v>
+      </c>
+      <c r="AN2" s="29" t="n">
+        <v>1.059992390217548</v>
+      </c>
+      <c r="AO2" s="27" t="n"/>
+      <c r="AP2" s="27" t="n"/>
+      <c r="AQ2" s="27" t="n"/>
+      <c r="AR2" s="27" t="n"/>
+      <c r="AS2" s="27" t="n"/>
+      <c r="AT2" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU2" s="32">
+        <f>IFERROR(IF($AQ2="","",INDEX($W2:$AB2,$AQ2-0.5)),"")</f>
+        <v/>
+      </c>
+      <c r="AV2" s="32">
+        <f>IF($AR2="","",IF($AS2="",1/$AR2,(1/$AR2)/((1/$AR2)+(1/$AS2))))</f>
+        <v/>
+      </c>
+      <c r="AW2" s="32">
+        <f>IF(OR($AU2="",$AV2=""),"",$AU2-$AV2)</f>
+        <v/>
+      </c>
+      <c r="AX2" s="33">
+        <f>IF($AW2="","",IF($AP2="","units?",IF(ISNUMBER(SEARCH("yellow",$AP2)),IF($AW2&gt;=0.05,"OVER",IF($AW2&lt;=-0.05,"UNDER","skip")),"UNITS?")))</f>
+        <v/>
+      </c>
+      <c r="AY2" s="34">
+        <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?"),"",IF($AX2="OVER",$AT2*($AU2*$AR2-1),$AT2*((1-$AU2)*$AS2-1)))</f>
+        <v/>
+      </c>
+      <c r="AZ2" s="27" t="n"/>
+      <c r="BA2" s="33">
+        <f>IF(OR($AX2="",$AX2="skip",$AX2="units?",$AX2="UNITS?",$AZ2="",$AQ2=""),"",IF($AX2="OVER",IF($AZ2&gt;$AQ2,"WON","LOST"),IF($AZ2&lt;$AQ2,"WON","LOST")))</f>
+        <v/>
+      </c>
+      <c r="BB2" s="34">
+        <f>IF($BA2="","",IF($BA2="WON",IF($AX2="OVER",$AT2*($AR2-1),$AT2*($AS2-1)),-$AT2))</f>
+        <v/>
+      </c>
+      <c r="BC2" s="34">
+        <f>IF(COUNT($BB$2:$BB2)=0,"",SUM($BB$2:$BB2))</f>
+        <v/>
+      </c>
+      <c r="BD2" s="27" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>bets placed</t>
+        </is>
+      </c>
+      <c r="E5" s="37">
+        <f>COUNTIF($AX$2:$AX2,"OVER")+COUNTIF($AX$2:$AX2,"UNDER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>bets won</t>
+        </is>
+      </c>
+      <c r="E6" s="37">
+        <f>COUNTIF($BA$2:$BA2,"WON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>total staked</t>
+        </is>
+      </c>
+      <c r="E7" s="38">
+        <f>SUMPRODUCT(($BA$2:$BA2&lt;&gt;"")*$AT$2:$AT2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>profit / loss EUR</t>
+        </is>
+      </c>
+      <c r="E8" s="38">
+        <f>IF(COUNT($BB$2:$BB2)=0,"",SUM($BB$2:$BB2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>return on stake</t>
+        </is>
+      </c>
+      <c r="E9" s="39">
+        <f>IF($E7=0,"",$E8/$E7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="52" t="inlineStr">
+        <is>
+          <t>HOW TO USE THIS SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="53" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="53" t="inlineStr">
+        <is>
+          <t>1. Fill the yellow columns only. Everything green is computed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="53" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="53" t="inlineStr">
+        <is>
+          <t>2. 'Settles on' must say what the market actually pays out on. Write 'yellow cards' only if the bookmaker settles on yellows alone. If it says total cards or booking points, BET? shows UNITS? and gives no verdict -- on purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="53" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The model predicts yellows. Counting a red as two cards adds about 5-6 percentage points at every line, always upward, which is larger than the 5% edge threshold. Priced against the wrong market the model shows an OVER edge on nearly every game, and that looks identical to finding an edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="53" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The market to look for is 'Yellow Cards', as in the Chelsea screenshot -- not 'Cards' and not 'Booking Points'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="53" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="53" t="inlineStr">
+        <is>
+          <t>3. Record BOTH sides of the price. With one side only, the de-vig cannot run and the implied probability is overstated by the whole margin, which invents edge that is not there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="53" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="53" t="inlineStr">
+        <is>
+          <t>4. Record the price when you see it, before kick-off. A price looked up afterwards is not one you could have taken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="53" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="53" t="inlineStr">
+        <is>
+          <t>5. Stake is EUR 100 a bet. Change the column if you want; the P/L follows it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="53" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="52" t="inlineStr">
+        <is>
+          <t>WHAT THIS SHEET IS AND IS NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="53" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="53" t="inlineStr">
+        <is>
+          <t>1 fixtures. A sample this size tells you nothing about whether the model beats a bookmaker -- a verdict on profitability needs thousands of bets. Treat a single week as practice for the workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="53" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="53" t="inlineStr">
+        <is>
+          <t>The referee is 48% of the model's value. If the Referee column says 'not known', the EFL has not published appointments yet (they come one to three days ahead) and these are the weaker version of the model. Re-run run_week_sheet.py for the same dates once they are out and every unplayed row updates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="53" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="53" t="inlineStr">
+        <is>
+          <t>Model fingerprint d30beac40c73a847, frozen for the season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="53" t="inlineStr">
+        <is>
+          <t>Scoring these results against the model is a holdout look.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/forward_test_2026-09-18.xlsx
+++ b/forward_test_2026-09-18.xlsx
@@ -190,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,6 +291,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -12623,134 +12629,134 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="48" t="inlineStr">
+      <c r="A25" s="52" t="inlineStr">
         <is>
           <t>HOW TO USE THIS SHEET</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="49" t="inlineStr"/>
+      <c r="A26" s="53" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="49" t="inlineStr">
+      <c r="A27" s="53" t="inlineStr">
         <is>
           <t>1. Fill the yellow columns only. Everything green is computed.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="49" t="inlineStr"/>
+      <c r="A28" s="53" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="49" t="inlineStr">
+      <c r="A29" s="53" t="inlineStr">
         <is>
           <t>2. 'Settles on' must say what the market actually pays out on. Write 'yellow cards' only if the bookmaker settles on yellows alone. If it says total cards or booking points, BET? shows UNITS? and gives no verdict -- on purpose.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="49" t="inlineStr"/>
+      <c r="A30" s="53" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="49" t="inlineStr">
+      <c r="A31" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">   The model predicts yellows. Counting a red as two cards adds about 5-6 percentage points at every line, always upward, which is larger than the 5% edge threshold. Priced against the wrong market the model shows an OVER edge on nearly every game, and that looks identical to finding an edge.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="49" t="inlineStr"/>
+      <c r="A32" s="53" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="49" t="inlineStr">
+      <c r="A33" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">   The market to look for is 'Yellow Cards', as in the Chelsea screenshot -- not 'Cards' and not 'Booking Points'.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="49" t="inlineStr"/>
+      <c r="A34" s="53" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="49" t="inlineStr">
+      <c r="A35" s="53" t="inlineStr">
         <is>
           <t>3. Record BOTH sides of the price. With one side only, the de-vig cannot run and the implied probability is overstated by the whole margin, which invents edge that is not there.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="49" t="inlineStr"/>
+      <c r="A36" s="53" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="49" t="inlineStr">
+      <c r="A37" s="53" t="inlineStr">
         <is>
           <t>4. Record the price when you see it, before kick-off. A price looked up afterwards is not one you could have taken.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="49" t="inlineStr"/>
+      <c r="A38" s="53" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="49" t="inlineStr">
+      <c r="A39" s="53" t="inlineStr">
         <is>
           <t>5. Stake is EUR 100 a bet. Change the column if you want; the P/L follows it.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="49" t="inlineStr"/>
+      <c r="A40" s="53" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="48" t="inlineStr">
+      <c r="A41" s="52" t="inlineStr">
         <is>
           <t>WHAT THIS WEEK IS AND IS NOT</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="49" t="inlineStr"/>
+      <c r="A42" s="53" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="49" t="inlineStr">
+      <c r="A43" s="53" t="inlineStr">
         <is>
           <t>Fourteen fixtures, League One and League Two only -- 26 September starts a two-weekend international break, and seven more EFL matches are postponed. No Premier League or Championship football until 10 October.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="49" t="inlineStr"/>
+      <c r="A44" s="53" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="49" t="inlineStr">
+      <c r="A45" s="53" t="inlineStr">
         <is>
           <t>Fourteen matches is far too few to tell you anything about whether the model beats a bookmaker. Treat this as practice for the workflow. A verdict on profitability needs thousands of bets.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="49" t="inlineStr"/>
+      <c r="A46" s="53" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="49" t="inlineStr">
+      <c r="A47" s="53" t="inlineStr">
         <is>
           <t>Referees are not in yet. The EFL publishes appointments one to three days ahead, and the referee is 48% of the model's value -- so these numbers are the weaker version of the model. Re-run cards/run_week_sheet.py once the appointments are out.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="49" t="inlineStr"/>
+      <c r="A48" s="53" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="49" t="inlineStr">
+      <c r="A49" s="53" t="inlineStr">
         <is>
           <t>Model fingerprint d30beac40c73a847, frozen for the season.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="49" t="inlineStr">
+      <c r="A50" s="53" t="inlineStr">
         <is>
           <t>Scoring these results against the model is a holdout look.</t>
         </is>
@@ -21725,124 +21731,124 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="48" t="inlineStr">
+      <c r="A57" s="52" t="inlineStr">
         <is>
           <t>HOW TO USE THIS SHEET</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="49" t="inlineStr"/>
+      <c r="A58" s="53" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="49" t="inlineStr">
+      <c r="A59" s="53" t="inlineStr">
         <is>
           <t>1. Fill the yellow columns only. Everything green is computed.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="49" t="inlineStr"/>
+      <c r="A60" s="53" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="49" t="inlineStr">
+      <c r="A61" s="53" t="inlineStr">
         <is>
           <t>2. 'Settles on' must say what the market actually pays out on. Write 'yellow cards' only if the bookmaker settles on yellows alone. If it says total cards or booking points, BET? shows UNITS? and gives no verdict -- on purpose.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="49" t="inlineStr"/>
+      <c r="A62" s="53" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="49" t="inlineStr">
+      <c r="A63" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">   The model predicts yellows. Counting a red as two cards adds about 5-6 percentage points at every line, always upward, which is larger than the 5% edge threshold. Priced against the wrong market the model shows an OVER edge on nearly every game, and that looks identical to finding an edge.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="49" t="inlineStr"/>
+      <c r="A64" s="53" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="49" t="inlineStr">
+      <c r="A65" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">   The market to look for is 'Yellow Cards', as in the Chelsea screenshot -- not 'Cards' and not 'Booking Points'.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="49" t="inlineStr"/>
+      <c r="A66" s="53" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="49" t="inlineStr">
+      <c r="A67" s="53" t="inlineStr">
         <is>
           <t>3. Record BOTH sides of the price. With one side only, the de-vig cannot run and the implied probability is overstated by the whole margin, which invents edge that is not there.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="49" t="inlineStr"/>
+      <c r="A68" s="53" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="49" t="inlineStr">
+      <c r="A69" s="53" t="inlineStr">
         <is>
           <t>4. Record the price when you see it, before kick-off. A price looked up afterwards is not one you could have taken.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="49" t="inlineStr"/>
+      <c r="A70" s="53" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="49" t="inlineStr">
+      <c r="A71" s="53" t="inlineStr">
         <is>
           <t>5. Stake is EUR 100 a bet. Change the column if you want; the P/L follows it.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="49" t="inlineStr"/>
+      <c r="A72" s="53" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="48" t="inlineStr">
+      <c r="A73" s="52" t="inlineStr">
         <is>
           <t>WHAT THIS SHEET IS AND IS NOT</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="49" t="inlineStr"/>
+      <c r="A74" s="53" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="49" t="inlineStr">
+      <c r="A75" s="53" t="inlineStr">
         <is>
           <t>46 fixtures. A sample this size tells you nothing about whether the model beats a bookmaker -- a verdict on profitability needs thousands of bets. Treat a single week as practice for the workflow.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="49" t="inlineStr"/>
+      <c r="A76" s="53" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="49" t="inlineStr">
+      <c r="A77" s="53" t="inlineStr">
         <is>
           <t>The referee is 48% of the model's value. If the Referee column says 'not known', the EFL has not published appointments yet (they come one to three days ahead) and these are the weaker version of the model. Re-run run_week_sheet.py for the same dates once they are out and every unplayed row updates.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="49" t="inlineStr"/>
+      <c r="A78" s="53" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="49" t="inlineStr">
+      <c r="A79" s="53" t="inlineStr">
         <is>
           <t>Model fingerprint d30beac40c73a847, frozen for the season.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="49" t="inlineStr">
+      <c r="A80" s="53" t="inlineStr">
         <is>
           <t>Scoring these results against the model is a holdout look.</t>
         </is>
@@ -24283,124 +24289,124 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="52" t="inlineStr">
         <is>
           <t>HOW TO USE THIS SHEET</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="49" t="inlineStr"/>
+      <c r="A23" s="53" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="49" t="inlineStr">
+      <c r="A24" s="53" t="inlineStr">
         <is>
           <t>1. Fill the yellow columns only. Everything green is computed.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="49" t="inlineStr"/>
+      <c r="A25" s="53" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="49" t="inlineStr">
+      <c r="A26" s="53" t="inlineStr">
         <is>
           <t>2. 'Settles on' must say what the market actually pays out on. Write 'yellow cards' only if the bookmaker settles on yellows alone. If it says total cards or booking points, BET? shows UNITS? and gives no verdict -- on purpose.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="49" t="inlineStr"/>
+      <c r="A27" s="53" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="49" t="inlineStr">
+      <c r="A28" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">   The model predicts yellows. Counting a red as two cards adds about 5-6 percentage points at every line, always upward, which is larger than the 5% edge threshold. Priced against the wrong market the model shows an OVER edge on nearly every game, and that looks identical to finding an edge.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="49" t="inlineStr"/>
+      <c r="A29" s="53" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="49" t="inlineStr">
+      <c r="A30" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">   The market to look for is 'Yellow Cards', as in the Chelsea screenshot -- not 'Cards' and not 'Booking Points'.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="49" t="inlineStr"/>
+      <c r="A31" s="53" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="49" t="inlineStr">
+      <c r="A32" s="53" t="inlineStr">
         <is>
           <t>3. Record BOTH sides of the price. With one side only, the de-vig cannot run and the implied probability is overstated by the whole margin, which invents edge that is not there.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="49" t="inlineStr"/>
+      <c r="A33" s="53" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="49" t="inlineStr">
+      <c r="A34" s="53" t="inlineStr">
         <is>
           <t>4. Record the price when you see it, before kick-off. A price looked up afterwards is not one you could have taken.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="49" t="inlineStr"/>
+      <c r="A35" s="53" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="49" t="inlineStr">
+      <c r="A36" s="53" t="inlineStr">
         <is>
           <t>5. Stake is EUR 100 a bet. Change the column if you want; the P/L follows it.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="49" t="inlineStr"/>
+      <c r="A37" s="53" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="48" t="inlineStr">
+      <c r="A38" s="52" t="inlineStr">
         <is>
           <t>WHAT THIS SHEET IS AND IS NOT</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="49" t="inlineStr"/>
+      <c r="A39" s="53" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="49" t="inlineStr">
+      <c r="A40" s="53" t="inlineStr">
         <is>
           <t>11 fixtures. A sample this size tells you nothing about whether the model beats a bookmaker -- a verdict on profitability needs thousands of bets. Treat a single week as practice for the workflow.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="49" t="inlineStr"/>
+      <c r="A41" s="53" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="49" t="inlineStr">
+      <c r="A42" s="53" t="inlineStr">
         <is>
           <t>The referee is 48% of the model's value. If the Referee column says 'not known', the EFL has not published appointments yet (they come one to three days ahead) and these are the weaker version of the model. Re-run run_week_sheet.py for the same dates once they are out and every unplayed row updates.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="49" t="inlineStr"/>
+      <c r="A43" s="53" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="49" t="inlineStr">
+      <c r="A44" s="53" t="inlineStr">
         <is>
           <t>Model fingerprint d30beac40c73a847, frozen for the season.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="49" t="inlineStr">
+      <c r="A45" s="53" t="inlineStr">
         <is>
           <t>Scoring these results against the model is a holdout look.</t>
         </is>
@@ -25001,124 +25007,124 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="52" t="inlineStr">
+      <c r="A12" s="54" t="inlineStr">
         <is>
           <t>HOW TO USE THIS SHEET</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="53" t="inlineStr"/>
+      <c r="A13" s="55" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="53" t="inlineStr">
+      <c r="A14" s="55" t="inlineStr">
         <is>
           <t>1. Fill the yellow columns only. Everything green is computed.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="53" t="inlineStr"/>
+      <c r="A15" s="55" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="inlineStr">
+      <c r="A16" s="55" t="inlineStr">
         <is>
           <t>2. 'Settles on' must say what the market actually pays out on. Write 'yellow cards' only if the bookmaker settles on yellows alone. If it says total cards or booking points, BET? shows UNITS? and gives no verdict -- on purpose.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="53" t="inlineStr"/>
+      <c r="A17" s="55" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="A18" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">   The model predicts yellows. Counting a red as two cards adds about 5-6 percentage points at every line, always upward, which is larger than the 5% edge threshold. Priced against the wrong market the model shows an OVER edge on nearly every game, and that looks identical to finding an edge.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="53" t="inlineStr"/>
+      <c r="A19" s="55" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="inlineStr">
+      <c r="A20" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">   The market to look for is 'Yellow Cards', as in the Chelsea screenshot -- not 'Cards' and not 'Booking Points'.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr"/>
+      <c r="A21" s="55" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="53" t="inlineStr">
+      <c r="A22" s="55" t="inlineStr">
         <is>
           <t>3. Record BOTH sides of the price. With one side only, the de-vig cannot run and the implied probability is overstated by the whole margin, which invents edge that is not there.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="53" t="inlineStr"/>
+      <c r="A23" s="55" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="53" t="inlineStr">
+      <c r="A24" s="55" t="inlineStr">
         <is>
           <t>4. Record the price when you see it, before kick-off. A price looked up afterwards is not one you could have taken.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="53" t="inlineStr"/>
+      <c r="A25" s="55" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="inlineStr">
+      <c r="A26" s="55" t="inlineStr">
         <is>
           <t>5. Stake is EUR 100 a bet. Change the column if you want; the P/L follows it.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="53" t="inlineStr"/>
+      <c r="A27" s="55" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="52" t="inlineStr">
+      <c r="A28" s="54" t="inlineStr">
         <is>
           <t>WHAT THIS SHEET IS AND IS NOT</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="53" t="inlineStr"/>
+      <c r="A29" s="55" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="53" t="inlineStr">
+      <c r="A30" s="55" t="inlineStr">
         <is>
           <t>1 fixtures. A sample this size tells you nothing about whether the model beats a bookmaker -- a verdict on profitability needs thousands of bets. Treat a single week as practice for the workflow.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="53" t="inlineStr"/>
+      <c r="A31" s="55" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="53" t="inlineStr">
+      <c r="A32" s="55" t="inlineStr">
         <is>
           <t>The referee is 48% of the model's value. If the Referee column says 'not known', the EFL has not published appointments yet (they come one to three days ahead) and these are the weaker version of the model. Re-run run_week_sheet.py for the same dates once they are out and every unplayed row updates.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="53" t="inlineStr"/>
+      <c r="A33" s="55" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="53" t="inlineStr">
+      <c r="A34" s="55" t="inlineStr">
         <is>
           <t>Model fingerprint d30beac40c73a847, frozen for the season.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="53" t="inlineStr">
+      <c r="A35" s="55" t="inlineStr">
         <is>
           <t>Scoring these results against the model is a holdout look.</t>
         </is>
